--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quebec" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Quebec" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X136"/>
+  <dimension ref="A1:X141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Titanium, Iron, Vanadium, Chromium</t>
+          <t>Iron, Titanium, Vanadium, Chromium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mine Sweet</t>
+          <t>Mine Fletcher-1</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,12 +654,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>32</v>
       </c>
       <c r="V3" t="n">
-        <v>45.14002</v>
+        <v>45.41052</v>
       </c>
       <c r="W3" t="n">
-        <v>-72.63646</v>
+        <v>-72.10888</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1260</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=52377</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mine Girardin</t>
+          <t>Mine Forsyth</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -767,14 +767,14 @@
         <v>32</v>
       </c>
       <c r="V4" t="n">
-        <v>46.50377</v>
+        <v>45.47323</v>
       </c>
       <c r="W4" t="n">
-        <v>-72.73112999999999</v>
+        <v>-75.78742</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=63379</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4740</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mine Lac Breeches (Garthby)</t>
+          <t>Mine Baldwin</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -794,12 +794,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chromium, Nickel</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -828,23 +828,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>32</v>
       </c>
       <c r="V5" t="n">
-        <v>45.89069</v>
+        <v>45.47432</v>
       </c>
       <c r="W5" t="n">
-        <v>-71.49263999999999</v>
+        <v>-75.80007000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=430</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4739</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mine Washer</t>
+          <t>Mine Chib-Kayrand</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Lead, Molybdenum, Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -898,23 +898,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
         <v>32</v>
       </c>
       <c r="V6" t="n">
-        <v>45.16933</v>
+        <v>49.86737</v>
       </c>
       <c r="W6" t="n">
-        <v>-72.61743</v>
+        <v>-74.34103</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1264</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1976</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mine Shepherd</t>
+          <t>Nadeau Hill</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -934,12 +934,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Titanium</t>
+          <t>Chromium, Nickel, Silver, Iron</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -977,14 +977,14 @@
         <v>32</v>
       </c>
       <c r="V7" t="n">
-        <v>45.18327</v>
+        <v>45.96227</v>
       </c>
       <c r="W7" t="n">
-        <v>-72.59520999999999</v>
+        <v>-71.32575</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1267</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=426</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mine de la Rivière Moisie</t>
+          <t>Mine Bennett-Martin</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1004,12 +1004,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iron, Titanium</t>
+          <t>Chromium, Nickel</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1047,14 +1047,14 @@
         <v>32</v>
       </c>
       <c r="V8" t="n">
-        <v>50.2275</v>
+        <v>45.98834</v>
       </c>
       <c r="W8" t="n">
-        <v>-66.03745000000001</v>
+        <v>-71.4055</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5032</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=424</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mine Bennett-Martin</t>
+          <t>Mine Belmina</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chromium, Nickel</t>
+          <t>Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1117,14 +1117,14 @@
         <v>32</v>
       </c>
       <c r="V9" t="n">
-        <v>45.98834</v>
+        <v>45.96875</v>
       </c>
       <c r="W9" t="n">
-        <v>-71.4055</v>
+        <v>-71.46084999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=424</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=423</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mine Belmina</t>
+          <t>Mine Moss</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1144,12 +1144,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chromium, Nickel, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1187,14 +1187,14 @@
         <v>32</v>
       </c>
       <c r="V10" t="n">
-        <v>45.96875</v>
+        <v>45.57336</v>
       </c>
       <c r="W10" t="n">
-        <v>-71.46084999999999</v>
+        <v>-76.24823000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=423</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=983</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mine Moss</t>
+          <t>Mine Shepherd</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1214,12 +1214,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper, Gold, Silver, Titanium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1257,14 +1257,14 @@
         <v>32</v>
       </c>
       <c r="V11" t="n">
-        <v>45.57336</v>
+        <v>45.18327</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.24823000000001</v>
+        <v>-72.59520999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=983</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1267</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mine Pinnacle Mountain</t>
+          <t>Mine Girardin</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1284,12 +1284,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1327,14 +1327,14 @@
         <v>32</v>
       </c>
       <c r="V12" t="n">
-        <v>45.04329</v>
+        <v>46.50377</v>
       </c>
       <c r="W12" t="n">
-        <v>-72.73821</v>
+        <v>-72.73112999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1270</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=63379</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nadeau Hill</t>
+          <t>Mine Yale (Durham)</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1354,12 +1354,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chromium, Nickel, Iron, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1397,14 +1397,14 @@
         <v>32</v>
       </c>
       <c r="V13" t="n">
-        <v>45.96227</v>
+        <v>45.71013</v>
       </c>
       <c r="W13" t="n">
-        <v>-71.32575</v>
+        <v>-72.34399999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=426</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4617</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mine Yale (Durham)</t>
+          <t>Mine Washer</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1467,14 +1467,14 @@
         <v>32</v>
       </c>
       <c r="V14" t="n">
-        <v>45.71013</v>
+        <v>45.16933</v>
       </c>
       <c r="W14" t="n">
-        <v>-72.34399999999999</v>
+        <v>-72.61743</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1264</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Mine Lac Breeches (Garthby)</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1494,12 +1494,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Chromium, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1528,23 +1528,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
         <v>32</v>
       </c>
       <c r="V15" t="n">
-        <v>49.01028</v>
+        <v>45.89069</v>
       </c>
       <c r="W15" t="n">
-        <v>-66.00369999999999</v>
+        <v>-71.49263999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=430</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mine Baldwin</t>
+          <t>Mine Copperstream Frontenac-Zone Nord</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1564,12 +1564,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1598,23 +1598,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U16" t="n">
         <v>32</v>
       </c>
       <c r="V16" t="n">
-        <v>45.47432</v>
+        <v>45.77983</v>
       </c>
       <c r="W16" t="n">
-        <v>-75.80007000000001</v>
+        <v>-70.90228</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4739</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4855</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mine St-Élie-d'Orford</t>
+          <t>Mine de la Rivière Moisie</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iron, Chromium</t>
+          <t>Iron, Titanium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1677,14 +1677,14 @@
         <v>32</v>
       </c>
       <c r="V17" t="n">
-        <v>45.40241</v>
+        <v>50.2275</v>
       </c>
       <c r="W17" t="n">
-        <v>-72.10866</v>
+        <v>-66.03745000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58049</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5032</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mine Forsyth</t>
+          <t>Mine St-Élie-d'Orford</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Iron, Chromium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1747,14 +1747,14 @@
         <v>32</v>
       </c>
       <c r="V18" t="n">
-        <v>45.47323</v>
+        <v>45.40241</v>
       </c>
       <c r="W18" t="n">
-        <v>-75.78742</v>
+        <v>-72.10866</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4740</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58049</t>
         </is>
       </c>
     </row>
@@ -1764,22 +1764,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mine Silver Star</t>
+          <t>Haycock</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Copper, Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1817,14 +1817,14 @@
         <v>32</v>
       </c>
       <c r="V19" t="n">
-        <v>45.32783</v>
+        <v>45.55426</v>
       </c>
       <c r="W19" t="n">
-        <v>-71.95946000000001</v>
+        <v>-75.71674</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4383</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=881</t>
         </is>
       </c>
     </row>
@@ -1834,22 +1834,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mine King</t>
+          <t>Mine Molybdenite Corporation</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Molybdenum, Beryllium, Cs, Bismuth</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1878,23 +1878,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U20" t="n">
         <v>32</v>
       </c>
       <c r="V20" t="n">
-        <v>45.32764</v>
+        <v>48.28826</v>
       </c>
       <c r="W20" t="n">
-        <v>-71.95626</v>
+        <v>-77.99378</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4382</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5458</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mine Fish</t>
+          <t>Mine Grondin</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1914,12 +1914,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver</t>
+          <t>Iron, Titanium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>32</v>
       </c>
       <c r="V21" t="n">
-        <v>45.29706</v>
+        <v>46.50696</v>
       </c>
       <c r="W21" t="n">
-        <v>-71.98643</v>
+        <v>-72.87829000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4370</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3660</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mine Sherbrooke</t>
+          <t>Mine Mc Dougall</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2018,23 +2018,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U22" t="n">
         <v>32</v>
       </c>
       <c r="V22" t="n">
-        <v>45.3707</v>
+        <v>45.69139</v>
       </c>
       <c r="W22" t="n">
-        <v>-71.89006000000001</v>
+        <v>-72.66091</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4368</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4327</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mine Ascot</t>
+          <t>Mine Bissonnette</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2054,12 +2054,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2088,23 +2088,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U23" t="n">
         <v>32</v>
       </c>
       <c r="V23" t="n">
-        <v>45.34757</v>
+        <v>45.69028</v>
       </c>
       <c r="W23" t="n">
-        <v>-71.90573000000001</v>
+        <v>-72.6718</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4366</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4328</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mine Capelton (Albert)</t>
+          <t>Mine Acton</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver, Lead</t>
+          <t>Zinc, Copper, Barium, Silver, Lead</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2167,14 +2167,14 @@
         <v>32</v>
       </c>
       <c r="V24" t="n">
-        <v>45.32298</v>
+        <v>45.64407</v>
       </c>
       <c r="W24" t="n">
-        <v>-71.90649999999999</v>
+        <v>-72.55431</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4330</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Mine Ely Copper</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2194,12 +2194,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2237,14 +2237,14 @@
         <v>32</v>
       </c>
       <c r="V25" t="n">
-        <v>45.3192</v>
+        <v>45.4998</v>
       </c>
       <c r="W25" t="n">
-        <v>-71.92023</v>
+        <v>-72.26111</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6686</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mine Hepburn</t>
+          <t>Mine Radnor</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2264,12 +2264,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Iron, Lead, Sulphur</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2307,14 +2307,14 @@
         <v>32</v>
       </c>
       <c r="V26" t="n">
-        <v>45.34276</v>
+        <v>46.50958</v>
       </c>
       <c r="W26" t="n">
-        <v>-71.91799</v>
+        <v>-72.55862999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4361</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6571</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mine Marrington</t>
+          <t>Mine de Grand-Mère</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2334,12 +2334,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2377,14 +2377,14 @@
         <v>32</v>
       </c>
       <c r="V27" t="n">
-        <v>45.33871</v>
+        <v>46.67036</v>
       </c>
       <c r="W27" t="n">
-        <v>-71.91777999999999</v>
+        <v>-72.64637999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4360</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6568</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mine Belvédère</t>
+          <t>Mine du Lac à la Tortue</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2404,12 +2404,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2447,14 +2447,14 @@
         <v>32</v>
       </c>
       <c r="V28" t="n">
-        <v>45.35983</v>
+        <v>46.62764</v>
       </c>
       <c r="W28" t="n">
-        <v>-71.92270000000001</v>
+        <v>-72.61087000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4359</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6567</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mine Howard</t>
+          <t>Mine Rahel (Ryan)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2474,12 +2474,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2517,14 +2517,14 @@
         <v>32</v>
       </c>
       <c r="V29" t="n">
-        <v>45.32927</v>
+        <v>45.60806</v>
       </c>
       <c r="W29" t="n">
-        <v>-71.95571</v>
+        <v>-72.26194</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4358</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6424</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mine Suffield</t>
+          <t>Mine Belvédère</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2544,12 +2544,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2587,14 +2587,14 @@
         <v>32</v>
       </c>
       <c r="V30" t="n">
-        <v>45.31892</v>
+        <v>45.35983</v>
       </c>
       <c r="W30" t="n">
-        <v>-71.95913</v>
+        <v>-71.92270000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4359</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mine Victoria</t>
+          <t>Mine Howard</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2614,12 +2614,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Zinc, Lead, Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2657,14 +2657,14 @@
         <v>32</v>
       </c>
       <c r="V31" t="n">
-        <v>45.32653</v>
+        <v>45.32927</v>
       </c>
       <c r="W31" t="n">
-        <v>-71.90121000000001</v>
+        <v>-71.95571</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4367</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4358</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mine Molybdenite Corporation</t>
+          <t>Mine Suffield</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2684,12 +2684,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Molybdenum, Beryllium, Cs, Bismuth</t>
+          <t>Silver, Lead, Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2718,23 +2718,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T32" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U32" t="n">
         <v>32</v>
       </c>
       <c r="V32" t="n">
-        <v>48.28826</v>
+        <v>45.31892</v>
       </c>
       <c r="W32" t="n">
-        <v>-77.99378</v>
+        <v>-71.95913</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4356</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mine Bissonnette</t>
+          <t>Mine Aldermac Moulton Hill</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2754,12 +2754,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Lead, Copper, Gold, Silver, Barium, Cadmium, Molybdenum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2797,14 +2797,14 @@
         <v>32</v>
       </c>
       <c r="V33" t="n">
-        <v>45.69028</v>
+        <v>45.40941</v>
       </c>
       <c r="W33" t="n">
-        <v>-72.6718</v>
+        <v>-71.81791</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4328</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mine Mc Dougall</t>
+          <t>Mine Iron Smith</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2824,12 +2824,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron, Phosphate</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2858,23 +2858,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>32</v>
       </c>
       <c r="V34" t="n">
-        <v>45.69139</v>
+        <v>45.4157</v>
       </c>
       <c r="W34" t="n">
-        <v>-72.66091</v>
+        <v>-71.86328</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4327</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4351</t>
         </is>
       </c>
     </row>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mine Fletcher-1</t>
+          <t>Mine Silver Star</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Lead, Zinc, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2937,14 +2937,14 @@
         <v>32</v>
       </c>
       <c r="V35" t="n">
-        <v>45.41052</v>
+        <v>45.32783</v>
       </c>
       <c r="W35" t="n">
-        <v>-72.10888</v>
+        <v>-71.95946000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=52377</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4383</t>
         </is>
       </c>
     </row>
@@ -2954,22 +2954,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mine Aldermac Moulton Hill</t>
+          <t>Mine King</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Molybdenum, Cadmium, Barium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2998,23 +2998,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>32</v>
       </c>
       <c r="V36" t="n">
-        <v>45.40941</v>
+        <v>45.32764</v>
       </c>
       <c r="W36" t="n">
-        <v>-71.81791</v>
+        <v>-71.95626</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4382</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mine Iron Smith</t>
+          <t>Mine Marrington</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3034,12 +3034,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Iron, Phosphate</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3077,14 +3077,14 @@
         <v>32</v>
       </c>
       <c r="V37" t="n">
-        <v>45.4157</v>
+        <v>45.33871</v>
       </c>
       <c r="W37" t="n">
-        <v>-71.86328</v>
+        <v>-71.91777999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4351</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4360</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Haycock</t>
+          <t>Mine Fish</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3104,12 +3104,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3147,14 +3147,14 @@
         <v>32</v>
       </c>
       <c r="V38" t="n">
-        <v>45.55426</v>
+        <v>45.29706</v>
       </c>
       <c r="W38" t="n">
-        <v>-75.71674</v>
+        <v>-71.98643</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=881</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4370</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mine Acton</t>
+          <t>Mine Sherbrooke</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3174,12 +3174,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Barium, Lead, Silver</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3208,23 +3208,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U39" t="n">
         <v>32</v>
       </c>
       <c r="V39" t="n">
-        <v>45.64407</v>
+        <v>45.3707</v>
       </c>
       <c r="W39" t="n">
-        <v>-72.55431</v>
+        <v>-71.89006000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4330</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4368</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nicolet Branch</t>
+          <t>Mine Victoria</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Silver, Chromium, Zinc, Gold</t>
+          <t>Copper, Zinc, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3287,14 +3287,14 @@
         <v>32</v>
       </c>
       <c r="V40" t="n">
-        <v>45.91495</v>
+        <v>45.32653</v>
       </c>
       <c r="W40" t="n">
-        <v>-71.65255999999999</v>
+        <v>-71.90121000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2252</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4367</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mine Lac Nicolet-Rive Est</t>
+          <t>Mine Ascot</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3314,12 +3314,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Copper, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3348,23 +3348,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U41" t="n">
         <v>32</v>
       </c>
       <c r="V41" t="n">
-        <v>45.82175</v>
+        <v>45.34757</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.56406</v>
+        <v>-71.90573000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2254</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4366</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mine Lac Nicolet nord (Leckie)</t>
+          <t>Mine Capelton (Albert)</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3384,12 +3384,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Iron, Titanium, Chromium, Vanadium</t>
+          <t>Zinc, Copper, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3418,23 +3418,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
         <v>32</v>
       </c>
       <c r="V42" t="n">
-        <v>45.82853</v>
+        <v>45.32298</v>
       </c>
       <c r="W42" t="n">
-        <v>-71.57442</v>
+        <v>-71.90649999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2255</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mine Grondin</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3454,12 +3454,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Iron, Titanium</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3497,14 +3497,14 @@
         <v>32</v>
       </c>
       <c r="V43" t="n">
-        <v>46.50696</v>
+        <v>45.3192</v>
       </c>
       <c r="W43" t="n">
-        <v>-72.87829000000001</v>
+        <v>-71.92023</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3660</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mine Lord Aylmer</t>
+          <t>Mine Hepburn</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Silver, Barium</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3567,14 +3567,14 @@
         <v>32</v>
       </c>
       <c r="V44" t="n">
-        <v>45.49096</v>
+        <v>45.34276</v>
       </c>
       <c r="W44" t="n">
-        <v>-72.49369</v>
+        <v>-71.91799</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2270</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4361</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mine Shefford</t>
+          <t>Mine Bouchard</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3594,12 +3594,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Iron, Titanium, Phosphate</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3637,14 +3637,14 @@
         <v>32</v>
       </c>
       <c r="V45" t="n">
-        <v>45.46441</v>
+        <v>47.53342</v>
       </c>
       <c r="W45" t="n">
-        <v>-72.35231</v>
+        <v>-70.55920999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2271</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2671</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mine McCaw</t>
+          <t>Mine Bignell</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chromium, Nickel</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3698,23 +3698,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T46" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U46" t="n">
         <v>32</v>
       </c>
       <c r="V46" t="n">
-        <v>45.46875</v>
+        <v>47.54008</v>
       </c>
       <c r="W46" t="n">
-        <v>-72.1155</v>
+        <v>-70.56605999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2272</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2670</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mine Fletcher-4</t>
+          <t>Mine Lac Nicolet-Rive Est</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3734,12 +3734,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chromium, Nickel</t>
+          <t>Iron, Titanium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3768,23 +3768,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U47" t="n">
         <v>32</v>
       </c>
       <c r="V47" t="n">
-        <v>45.41088</v>
+        <v>45.82175</v>
       </c>
       <c r="W47" t="n">
-        <v>-72.10975999999999</v>
+        <v>-71.56406</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2279</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2254</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mine Rahel (Ryan)</t>
+          <t>Mine Lac Nicolet nord (Leckie)</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3804,12 +3804,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Iron, Titanium, Chromium, Vanadium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3838,23 +3838,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T48" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U48" t="n">
         <v>32</v>
       </c>
       <c r="V48" t="n">
-        <v>45.60806</v>
+        <v>45.82853</v>
       </c>
       <c r="W48" t="n">
-        <v>-72.26194</v>
+        <v>-71.57442</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6424</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2255</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mine Glen</t>
+          <t>Mine Lord Aylmer</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3874,12 +3874,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Silver, Copper, Barium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3917,14 +3917,14 @@
         <v>32</v>
       </c>
       <c r="V49" t="n">
-        <v>47.53358</v>
+        <v>45.49096</v>
       </c>
       <c r="W49" t="n">
-        <v>-70.54725999999999</v>
+        <v>-72.49369</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2676</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2270</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mine General Electric</t>
+          <t>Mine Shefford</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3944,12 +3944,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Iron, Vanadium, Titanium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3987,14 +3987,14 @@
         <v>32</v>
       </c>
       <c r="V50" t="n">
-        <v>47.53753</v>
+        <v>45.46441</v>
       </c>
       <c r="W50" t="n">
-        <v>-70.55468999999999</v>
+        <v>-72.35231</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2674</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2271</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mine Coulombe (Est et Ouest)</t>
+          <t>Mine McCaw</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Chromium, Nickel</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4048,23 +4048,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U51" t="n">
         <v>32</v>
       </c>
       <c r="V51" t="n">
-        <v>47.53526</v>
+        <v>45.46875</v>
       </c>
       <c r="W51" t="n">
-        <v>-70.55661000000001</v>
+        <v>-72.1155</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2673</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2272</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mine Bouchard</t>
+          <t>Nicolet Branch</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4084,12 +4084,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Iron, Titanium, Phosphate</t>
+          <t>Copper, Silver, Gold, Zinc, Chromium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4127,14 +4127,14 @@
         <v>32</v>
       </c>
       <c r="V52" t="n">
-        <v>47.53342</v>
+        <v>45.91495</v>
       </c>
       <c r="W52" t="n">
-        <v>-70.55920999999999</v>
+        <v>-71.65255999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2671</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2252</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mine Bignell</t>
+          <t>Mine Sweet</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4154,12 +4154,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4197,14 +4197,14 @@
         <v>32</v>
       </c>
       <c r="V53" t="n">
-        <v>47.54008</v>
+        <v>45.14002</v>
       </c>
       <c r="W53" t="n">
-        <v>-70.56605999999999</v>
+        <v>-72.63646</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2670</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1260</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mine Fourneau</t>
+          <t>Mine Pinnacle Mountain</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4224,12 +4224,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Copper, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4267,14 +4267,14 @@
         <v>32</v>
       </c>
       <c r="V54" t="n">
-        <v>47.54523</v>
+        <v>45.04329</v>
       </c>
       <c r="W54" t="n">
-        <v>-70.55092999999999</v>
+        <v>-72.73821</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2675</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1270</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mine Logan</t>
+          <t>Mine Glen</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4294,12 +4294,12 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Cadmium, Silver</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4337,14 +4337,14 @@
         <v>32</v>
       </c>
       <c r="V55" t="n">
-        <v>45.37752</v>
+        <v>47.53358</v>
       </c>
       <c r="W55" t="n">
-        <v>-72.39219</v>
+        <v>-70.54725999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2676</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mine Radnor</t>
+          <t>Mine Fourneau</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4364,12 +4364,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Iron, Lead, Sulphur</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4407,14 +4407,14 @@
         <v>32</v>
       </c>
       <c r="V56" t="n">
-        <v>46.50958</v>
+        <v>47.54523</v>
       </c>
       <c r="W56" t="n">
-        <v>-72.55862999999999</v>
+        <v>-70.55092999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6571</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2675</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mine de Grand-Mère</t>
+          <t>Mine General Electric</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4434,12 +4434,12 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Titanium, Iron, Vanadium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4477,14 +4477,14 @@
         <v>32</v>
       </c>
       <c r="V57" t="n">
-        <v>46.67036</v>
+        <v>47.53753</v>
       </c>
       <c r="W57" t="n">
-        <v>-72.64637999999999</v>
+        <v>-70.55468999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2674</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mine du Lac à la Tortue</t>
+          <t>Mine Coulombe (Est et Ouest)</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4504,12 +4504,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4547,14 +4547,14 @@
         <v>32</v>
       </c>
       <c r="V58" t="n">
-        <v>46.62764</v>
+        <v>47.53526</v>
       </c>
       <c r="W58" t="n">
-        <v>-72.61087000000001</v>
+        <v>-70.55661000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6567</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2673</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mine Ely Copper</t>
+          <t>Mine Fletcher No 5</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -4574,12 +4574,12 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4617,14 +4617,14 @@
         <v>32</v>
       </c>
       <c r="V59" t="n">
-        <v>45.4998</v>
+        <v>45.46221</v>
       </c>
       <c r="W59" t="n">
-        <v>-72.26111</v>
+        <v>-72.10592</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6686</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2292</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mine Quebec Copper (Huntingdon)</t>
+          <t>Mine Woolsey Chrome</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -4644,12 +4644,12 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>32</v>
       </c>
       <c r="V60" t="n">
-        <v>45.26379</v>
+        <v>45.99578</v>
       </c>
       <c r="W60" t="n">
-        <v>-72.33176</v>
+        <v>-71.39064</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7496</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mine Fletcher No 3</t>
+          <t>Mine de St-Jérôme</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -4784,12 +4784,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chromium, Copper</t>
+          <t>Iron, Titanium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4818,23 +4818,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
         <v>32</v>
       </c>
       <c r="V62" t="n">
-        <v>45.44615</v>
+        <v>45.74773</v>
       </c>
       <c r="W62" t="n">
-        <v>-72.11154000000001</v>
+        <v>-74.03348</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2291</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4073</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mine Fletcher No 5</t>
+          <t>Mine Bedford Mining</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4854,12 +4854,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4897,14 +4897,14 @@
         <v>32</v>
       </c>
       <c r="V63" t="n">
-        <v>45.46221</v>
+        <v>45.1877</v>
       </c>
       <c r="W63" t="n">
-        <v>-72.10592</v>
+        <v>-72.59184</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2292</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7219</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mine Woolsey Chrome</t>
+          <t>Mine Fletcher No 3</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Chromium, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4958,23 +4958,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T64" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U64" t="n">
         <v>32</v>
       </c>
       <c r="V64" t="n">
-        <v>45.99578</v>
+        <v>45.44615</v>
       </c>
       <c r="W64" t="n">
-        <v>-71.39064</v>
+        <v>-72.11154000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7496</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2291</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mine de St-Jérôme</t>
+          <t>Mine Quebec Copper (Huntingdon)</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4994,12 +4994,12 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Iron, Titanium</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5037,14 +5037,14 @@
         <v>32</v>
       </c>
       <c r="V65" t="n">
-        <v>45.74773</v>
+        <v>45.26379</v>
       </c>
       <c r="W65" t="n">
-        <v>-74.03348</v>
+        <v>-72.33176</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4073</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2285</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mine Bedford Mining</t>
+          <t>Mine Logan</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Zinc, Cadmium, Silver</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5107,14 +5107,14 @@
         <v>32</v>
       </c>
       <c r="V66" t="n">
-        <v>45.1877</v>
+        <v>45.37752</v>
       </c>
       <c r="W66" t="n">
-        <v>-72.59184</v>
+        <v>-72.39219</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7219</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2282</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lac Tuttle</t>
+          <t>Mine Fletcher-4</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5134,17 +5134,17 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Chromium, Nickel</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I67" t="b">
@@ -5168,23 +5168,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T67" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U67" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V67" t="n">
-        <v>52.56929</v>
+        <v>45.41088</v>
       </c>
       <c r="W67" t="n">
-        <v>-67.63967</v>
+        <v>-72.10975999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5055</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2279</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Southwest Island</t>
+          <t>Lac Tuttle</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5204,17 +5204,17 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5238,23 +5238,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U68" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="V68" t="n">
-        <v>51.18966</v>
+        <v>52.56929</v>
       </c>
       <c r="W68" t="n">
-        <v>-68.94568</v>
+        <v>-67.63967</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4662</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5055</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B-88-01</t>
+          <t>Lac Romanet No 1</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5274,12 +5274,12 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5317,14 +5317,14 @@
         <v>23</v>
       </c>
       <c r="V69" t="n">
-        <v>45.52488</v>
+        <v>56.24523</v>
       </c>
       <c r="W69" t="n">
-        <v>-72.07191</v>
+        <v>-67.74785</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4630</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Xavier (Claims Duval)</t>
+          <t>B-88-01</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5387,14 +5387,14 @@
         <v>23</v>
       </c>
       <c r="V70" t="n">
-        <v>45.53875</v>
+        <v>45.52488</v>
       </c>
       <c r="W70" t="n">
-        <v>-72.07156999999999</v>
+        <v>-72.07191</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4623</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lac Tarsac : Veine I et III</t>
+          <t>Xavier (Claims Duval)</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5414,12 +5414,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5448,23 +5448,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
         <v>23</v>
       </c>
       <c r="V71" t="n">
-        <v>48.3561</v>
+        <v>45.53875</v>
       </c>
       <c r="W71" t="n">
-        <v>-79.43788000000001</v>
+        <v>-72.07156999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4623</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Balrath</t>
+          <t>Southwest Island</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -5484,12 +5484,12 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Palladium, Platinum, Copper, Nickel, Egp</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5527,14 +5527,14 @@
         <v>23</v>
       </c>
       <c r="V72" t="n">
-        <v>45.62407</v>
+        <v>51.18966</v>
       </c>
       <c r="W72" t="n">
-        <v>-72.24473999999999</v>
+        <v>-68.94568</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4621</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4662</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mine Wickham</t>
+          <t>Lac Beauchastel-Sud</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -5554,12 +5554,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Zinc, Lead, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5597,14 +5597,14 @@
         <v>23</v>
       </c>
       <c r="V73" t="n">
-        <v>45.74755</v>
+        <v>48.1305</v>
       </c>
       <c r="W73" t="n">
-        <v>-72.48441</v>
+        <v>-79.11775</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4616</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5161</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mine Beaupas</t>
+          <t>Baie Paul T</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -5624,21 +5624,21 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Nickel, Zinc</t>
+          <t>Thorium, Etr, Uranium, Lead, Zinc</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
@@ -5658,23 +5658,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T74" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U74" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="V74" t="n">
-        <v>46.55122</v>
+        <v>53.95655</v>
       </c>
       <c r="W74" t="n">
-        <v>-71.54106</v>
+        <v>-78.94996</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4658</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4576</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mine de la Plage Moisie-Ouest</t>
+          <t>Baie Paul P (Bouro)</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -5694,21 +5694,21 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Uranium, Thorium, Etr, Lead</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -5728,23 +5728,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U75" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="V75" t="n">
-        <v>50.19967</v>
+        <v>53.95713</v>
       </c>
       <c r="W75" t="n">
-        <v>-66.18422</v>
+        <v>-78.93695</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5031</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4571</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mine Wright (Villa, Decouverte Coignac)</t>
+          <t>Viau (ou Bordulac)</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -5764,21 +5764,21 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -5798,23 +5798,23 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T76" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U76" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="V76" t="n">
-        <v>47.4226</v>
+        <v>48.26547</v>
       </c>
       <c r="W76" t="n">
-        <v>-79.49269</v>
+        <v>-79.41453</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4694</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
         </is>
       </c>
     </row>
@@ -5824,31 +5824,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mine Principale (Campbell)</t>
+          <t>Radur-Sud</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Uranium, Thorium</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -5868,23 +5868,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T77" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="V77" t="n">
-        <v>49.87147</v>
+        <v>53.93351</v>
       </c>
       <c r="W77" t="n">
-        <v>-74.33438</v>
+        <v>-78.71953000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2049</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4570</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mine Canada Iron Furnace</t>
+          <t>Mine Wright (Villa, Decouverte Coignac)</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -5904,12 +5904,12 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Iron, Titanium</t>
+          <t>Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5938,23 +5938,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T78" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U78" t="n">
         <v>18</v>
       </c>
       <c r="V78" t="n">
-        <v>48.43663</v>
+        <v>47.4226</v>
       </c>
       <c r="W78" t="n">
-        <v>-71.44662</v>
+        <v>-79.49269</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1369</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4694</t>
         </is>
       </c>
     </row>
@@ -5964,22 +5964,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ward-Chromore</t>
+          <t>Mine Principale (Campbell)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chromium, Nickel, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6008,23 +6008,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="U79" t="n">
         <v>18</v>
       </c>
       <c r="V79" t="n">
-        <v>45.97485</v>
+        <v>49.87147</v>
       </c>
       <c r="W79" t="n">
-        <v>-71.30437000000001</v>
+        <v>-74.33438</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=427</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2049</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mine St-François</t>
+          <t>Mine Canada Iron Furnace</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -6044,12 +6044,12 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Iron, Titanium</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6078,23 +6078,23 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T80" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U80" t="n">
         <v>18</v>
       </c>
       <c r="V80" t="n">
-        <v>45.70642</v>
+        <v>48.43663</v>
       </c>
       <c r="W80" t="n">
-        <v>-72.16173999999999</v>
+        <v>-71.44662</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4618</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1369</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mine Sterrett (Lili)</t>
+          <t>Mine Lafontaine</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6114,12 +6114,12 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chromium, Nickel</t>
+          <t>Zinc, Mercury, Cadmium</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6148,23 +6148,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T81" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="U81" t="n">
         <v>18</v>
       </c>
       <c r="V81" t="n">
-        <v>45.68285</v>
+        <v>46.11749</v>
       </c>
       <c r="W81" t="n">
-        <v>-72.03998</v>
+        <v>-75.96186</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4619</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4726</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mine Brousseau</t>
+          <t>Mine Merrill Island</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -6184,12 +6184,12 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper, Silver, Gold, Molybdenum, Zinc</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6218,23 +6218,23 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U82" t="n">
         <v>18</v>
       </c>
       <c r="V82" t="n">
-        <v>45.92581</v>
+        <v>49.87032</v>
       </c>
       <c r="W82" t="n">
-        <v>-71.36319</v>
+        <v>-74.32952</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1977</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Mine Beaupas</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Cadmium, Gold, Zinc, Cs</t>
+          <t>Copper, Silver, Zinc, Nickel, Gold, Lead</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6288,23 +6288,23 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T83" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="U83" t="n">
         <v>18</v>
       </c>
       <c r="V83" t="n">
-        <v>45.80476</v>
+        <v>46.55122</v>
       </c>
       <c r="W83" t="n">
-        <v>-71.28747</v>
+        <v>-71.54106</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4658</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mine Greenshields</t>
+          <t>Mine Sterrett (Lili)</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -6358,23 +6358,23 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T84" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U84" t="n">
         <v>18</v>
       </c>
       <c r="V84" t="n">
-        <v>46.01729</v>
+        <v>45.68285</v>
       </c>
       <c r="W84" t="n">
-        <v>-71.35663</v>
+        <v>-72.03998</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5545</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4619</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mine Copperstream Frontenac-Zone Nord</t>
+          <t>Mine St-François</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -6394,12 +6394,12 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6428,23 +6428,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="U85" t="n">
         <v>18</v>
       </c>
       <c r="V85" t="n">
-        <v>45.77983</v>
+        <v>45.70642</v>
       </c>
       <c r="W85" t="n">
-        <v>-70.90228</v>
+        <v>-72.16173999999999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4855</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4618</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mine Copperstream Frontenac-Zone Sud</t>
+          <t>Ward-Chromore</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -6464,12 +6464,12 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum</t>
+          <t>Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6498,23 +6498,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T86" t="n">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="U86" t="n">
         <v>18</v>
       </c>
       <c r="V86" t="n">
-        <v>45.77065</v>
+        <v>45.97485</v>
       </c>
       <c r="W86" t="n">
-        <v>-70.91289999999999</v>
+        <v>-71.30437000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4853</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=427</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mine St-Herménégilde</t>
+          <t>Solbec Copper</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -6534,12 +6534,12 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bismuth, Copper, Lead, Zinc, Molybdenum, Gold</t>
+          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6568,23 +6568,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T87" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U87" t="n">
         <v>18</v>
       </c>
       <c r="V87" t="n">
-        <v>45.07957</v>
+        <v>45.80476</v>
       </c>
       <c r="W87" t="n">
-        <v>-71.69364</v>
+        <v>-71.28747</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4849</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mine Lafontaine</t>
+          <t>Stratford Pyrite</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -6604,12 +6604,12 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Zinc, Mercury, Cadmium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6638,23 +6638,23 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T88" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="U88" t="n">
         <v>18</v>
       </c>
       <c r="V88" t="n">
-        <v>46.11749</v>
+        <v>45.75917</v>
       </c>
       <c r="W88" t="n">
-        <v>-75.96186</v>
+        <v>-71.3031</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4726</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=442</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mine Chib-Kayrand</t>
+          <t>Mine Greenshields</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -6674,12 +6674,12 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Molybdenum, Lead, Silver, Gold</t>
+          <t>Chromium, Nickel</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6708,23 +6708,23 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T89" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U89" t="n">
         <v>18</v>
       </c>
       <c r="V89" t="n">
-        <v>49.86737</v>
+        <v>46.01729</v>
       </c>
       <c r="W89" t="n">
-        <v>-74.34103</v>
+        <v>-71.35663</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1976</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5545</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mine Clark</t>
+          <t>Mine Copperstream Frontenac-Zone Sud</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -6744,12 +6744,12 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6778,23 +6778,23 @@
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T90" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="U90" t="n">
         <v>18</v>
       </c>
       <c r="V90" t="n">
-        <v>45.36519</v>
+        <v>45.77065</v>
       </c>
       <c r="W90" t="n">
-        <v>-71.88531</v>
+        <v>-70.91289999999999</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4369</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4853</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mine Molson</t>
+          <t>Mine St-Herménégilde</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -6814,12 +6814,12 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Copper, Bismuth, Lead, Gold, Molybdenum, Zinc</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6848,23 +6848,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T91" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="U91" t="n">
         <v>18</v>
       </c>
       <c r="V91" t="n">
-        <v>50.27595</v>
+        <v>45.07957</v>
       </c>
       <c r="W91" t="n">
-        <v>-66.45515</v>
+        <v>-71.69364</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4926</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4849</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mine du Lac Memphrémagog</t>
+          <t>Mine Preissac Molybdenite</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -6884,12 +6884,12 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tin</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tin, Antimony, Zinc, Copper, Silver, Iron, Lead</t>
+          <t>Molybdenum, Bismuth, Copper</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6918,23 +6918,23 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T92" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="U92" t="n">
         <v>18</v>
       </c>
       <c r="V92" t="n">
-        <v>45.14504</v>
+        <v>48.34652</v>
       </c>
       <c r="W92" t="n">
-        <v>-72.31379</v>
+        <v>-78.39901</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4390</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1521</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mine Moulton Hill</t>
+          <t>Mine de la Plage Moisie-Ouest</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -6954,12 +6954,12 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Copper, Gold</t>
+          <t>Iron, Titanium</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6988,23 +6988,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T93" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U93" t="n">
         <v>18</v>
       </c>
       <c r="V93" t="n">
-        <v>45.42621</v>
+        <v>50.19967</v>
       </c>
       <c r="W93" t="n">
-        <v>-71.81171999999999</v>
+        <v>-66.18422</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4355</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5031</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mine Prince of Wales</t>
+          <t>Lambly-Nadeau/Victoria</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -7024,12 +7024,12 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium, Egp, Nickel, Ir, Os, Ru</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7058,23 +7058,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U94" t="n">
         <v>18</v>
       </c>
       <c r="V94" t="n">
-        <v>45.68037</v>
+        <v>46.01608</v>
       </c>
       <c r="W94" t="n">
-        <v>-72.67106</v>
+        <v>-71.35127</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5544</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Viger</t>
+          <t>Mine Cadillac Moly</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -7094,12 +7094,12 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Zinc, Manganese</t>
+          <t>Molybdenum, Copper, Silver, Bismuth</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7137,14 +7137,14 @@
         <v>18</v>
       </c>
       <c r="V95" t="n">
-        <v>45.98953</v>
+        <v>48.31956</v>
       </c>
       <c r="W95" t="n">
-        <v>-71.73424</v>
+        <v>-78.37992</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2249</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1523</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Québec Antimoine</t>
+          <t>Mine American Chrome</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Antimony, Silver, Gold, Arsenic, Mercury</t>
+          <t>Chromium, Nickel</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7207,14 +7207,14 @@
         <v>18</v>
       </c>
       <c r="V96" t="n">
-        <v>45.85081</v>
+        <v>46.01051</v>
       </c>
       <c r="W96" t="n">
-        <v>-71.53242</v>
+        <v>-71.27082</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2257</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5559</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mine Halliwell</t>
+          <t>Mine Molson</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -7234,12 +7234,12 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bismuth, Copper, Gold, Silver, Zinc</t>
+          <t>Iron, Titanium</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7277,14 +7277,14 @@
         <v>18</v>
       </c>
       <c r="V97" t="n">
-        <v>48.25375</v>
+        <v>50.27595</v>
       </c>
       <c r="W97" t="n">
-        <v>-79.18368</v>
+        <v>-66.45515</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5819</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4926</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mine Preissac Molybdenite</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -7304,12 +7304,12 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Bismuth</t>
+          <t>Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7338,23 +7338,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T98" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U98" t="n">
         <v>18</v>
       </c>
       <c r="V98" t="n">
-        <v>48.34652</v>
+        <v>49.01028</v>
       </c>
       <c r="W98" t="n">
-        <v>-78.39901</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1521</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mine Fletcher Old No 2</t>
+          <t>Mine Prince of Wales</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -7374,12 +7374,12 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7408,23 +7408,23 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="U99" t="n">
         <v>18</v>
       </c>
       <c r="V99" t="n">
-        <v>45.43685</v>
+        <v>45.68037</v>
       </c>
       <c r="W99" t="n">
-        <v>-72.10948</v>
+        <v>-72.67106</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2278</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4329</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mine Fletcher Old No 1</t>
+          <t>Mine Chesbar</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -7444,12 +7444,12 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chromium, Nickel</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7478,23 +7478,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T100" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U100" t="n">
         <v>18</v>
       </c>
       <c r="V100" t="n">
-        <v>45.42593</v>
+        <v>49.45235</v>
       </c>
       <c r="W100" t="n">
-        <v>-72.11288999999999</v>
+        <v>-76.50215</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2280</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4419</t>
         </is>
       </c>
     </row>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mine Duvan</t>
+          <t>Mine Moulton Hill</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7514,12 +7514,12 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Zinc, Lead, Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7548,23 +7548,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T101" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U101" t="n">
         <v>18</v>
       </c>
       <c r="V101" t="n">
-        <v>48.8894</v>
+        <v>45.42621</v>
       </c>
       <c r="W101" t="n">
-        <v>-79.42655000000001</v>
+        <v>-71.81171999999999</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2705</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4355</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lambly-Nadeau/Victoria</t>
+          <t>Mine du Lac Memphrémagog</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -7584,12 +7584,12 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Egp, Chromium, Nickel, Ir, Os, Ru</t>
+          <t>Zinc, Copper, Antimony, Tin, Lead, Iron, Silver</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7618,23 +7618,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T102" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U102" t="n">
         <v>18</v>
       </c>
       <c r="V102" t="n">
-        <v>46.01608</v>
+        <v>45.14504</v>
       </c>
       <c r="W102" t="n">
-        <v>-71.35127</v>
+        <v>-72.31379</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5544</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4390</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mine Cadillac Moly</t>
+          <t>Mine Clark</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -7654,12 +7654,12 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Molybdenum, Bismuth, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7688,23 +7688,23 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T103" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U103" t="n">
         <v>18</v>
       </c>
       <c r="V103" t="n">
-        <v>48.31956</v>
+        <v>45.36519</v>
       </c>
       <c r="W103" t="n">
-        <v>-78.37992</v>
+        <v>-71.88531</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1523</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4369</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mine Chesbar</t>
+          <t>Mine French</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Iron, Manganese</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7767,14 +7767,14 @@
         <v>18</v>
       </c>
       <c r="V104" t="n">
-        <v>49.45235</v>
+        <v>54.81434</v>
       </c>
       <c r="W104" t="n">
-        <v>-76.50215</v>
+        <v>-66.88673</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4419</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=296</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mine Ivry</t>
+          <t>Viger</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -7794,12 +7794,12 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Iron, Titanium, Vanadium, Copper, Chromium, Phosphate</t>
+          <t>Copper, Silver, Lead, Manganese, Zinc</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7828,23 +7828,23 @@
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T105" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U105" t="n">
         <v>18</v>
       </c>
       <c r="V105" t="n">
-        <v>46.07903</v>
+        <v>45.98953</v>
       </c>
       <c r="W105" t="n">
-        <v>-74.3672</v>
+        <v>-71.73424</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=246</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2249</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LPM-LPMN</t>
+          <t>Québec Antimoine</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -7864,17 +7864,17 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Antimony, Silver, Mercury, Arsenic, Gold</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I106" t="b">
@@ -7888,11 +7888,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Ni 1.20%</t>
-        </is>
-      </c>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
@@ -7902,23 +7898,23 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U106" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V106" t="n">
-        <v>49.91875</v>
+        <v>45.85081</v>
       </c>
       <c r="W106" t="n">
-        <v>-69.76845</v>
+        <v>-71.53242</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=32738</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2257</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Mine Duvan</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -7938,17 +7934,17 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -7978,17 +7974,17 @@
         <v>25</v>
       </c>
       <c r="U107" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V107" t="n">
-        <v>49.75792</v>
+        <v>48.8894</v>
       </c>
       <c r="W107" t="n">
-        <v>-74.3342</v>
+        <v>-79.42655000000001</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2705</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7994,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Mine Ivry</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -8008,17 +8004,17 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nickel, Rh, Platinum, Egp, Chromium, Palladium</t>
+          <t>Iron, Titanium, Vanadium, Phosphate, Chromium, Copper</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I108" t="b">
@@ -8042,23 +8038,23 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T108" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="U108" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V108" t="n">
-        <v>46.04018</v>
+        <v>46.07903</v>
       </c>
       <c r="W108" t="n">
-        <v>-71.28144</v>
+        <v>-74.3672</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=246</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8064,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Mine St-Lawrence Columbium (Main Oka)</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -8083,12 +8079,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Vanadium, Lead, Gold, Uranium, Molybdenum, Silver, Thorium</t>
+          <t>Niobium, Etr, Ce, La, Nd</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8118,17 +8114,17 @@
         <v>25</v>
       </c>
       <c r="U109" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V109" t="n">
-        <v>52.18408</v>
+        <v>45.50102</v>
       </c>
       <c r="W109" t="n">
-        <v>-70.99409</v>
+        <v>-74.03024000000001</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4071</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8134,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Zone Bond</t>
+          <t>Mine Fletcher Old No 1</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -8153,12 +8149,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Niobium, Thorium, Uranium</t>
+          <t>Chromium, Nickel</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I110" t="b">
@@ -8182,23 +8178,23 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T110" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U110" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V110" t="n">
-        <v>45.50259</v>
+        <v>45.42593</v>
       </c>
       <c r="W110" t="n">
-        <v>-74.04985000000001</v>
+        <v>-72.11288999999999</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4068</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2280</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8204,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lac Rocher</t>
+          <t>Mine Fletcher Old No 2</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -8223,12 +8219,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt, Gold</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I111" t="b">
@@ -8258,17 +8254,17 @@
         <v>25</v>
       </c>
       <c r="U111" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V111" t="n">
-        <v>50.58471</v>
+        <v>45.43685</v>
       </c>
       <c r="W111" t="n">
-        <v>-76.34242</v>
+        <v>-72.10948</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4260</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2278</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8274,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Zone S5-T1</t>
+          <t>Mine Halliwell</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -8288,17 +8284,17 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead</t>
+          <t>Gold, Bismuth, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I112" t="b">
@@ -8312,11 +8308,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>Zn 1.21%</t>
-        </is>
-      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
@@ -8332,17 +8324,17 @@
         <v>25</v>
       </c>
       <c r="U112" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V112" t="n">
-        <v>45.54882</v>
+        <v>48.25375</v>
       </c>
       <c r="W112" t="n">
-        <v>-71.68844</v>
+        <v>-79.18368</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=37593</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5819</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8344,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>César</t>
+          <t>LPM-LPMN</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -8362,12 +8354,12 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chromium, Egp, Nickel, Platinum</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8388,7 +8380,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Ni 0.18%</t>
+          <t>Ni 1.20%</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -8400,23 +8392,23 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T113" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U113" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V113" t="n">
-        <v>46.02001</v>
+        <v>49.91875</v>
       </c>
       <c r="W113" t="n">
-        <v>-71.28955000000001</v>
+        <v>-69.76845</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5569</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=32738</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8418,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Anomalie 79-1 (Bacon)</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -8441,12 +8433,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Copper, Lead, Uranium, Gold, Silver, Selenium</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I114" t="b">
@@ -8470,23 +8462,23 @@
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T114" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U114" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V114" t="n">
-        <v>56.27035</v>
+        <v>49.75792</v>
       </c>
       <c r="W114" t="n">
-        <v>-67.79839</v>
+        <v>-74.3342</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4652</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8488,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lac Lavoie-Ouest</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -8506,17 +8498,17 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Copper</t>
+          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I115" t="b">
@@ -8540,23 +8532,23 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T115" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U115" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V115" t="n">
-        <v>48.55765</v>
+        <v>46.04018</v>
       </c>
       <c r="W115" t="n">
-        <v>-79.03133</v>
+        <v>-71.28144</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5638</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8558,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michaud-Simard (Zone Gaudry)</t>
+          <t>Lavoie (Zone L)</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -8576,17 +8568,17 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thorium, Uranium</t>
+          <t>Lead, Vanadium, Molybdenum, Uranium, Gold, Silver, Thorium</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I116" t="b">
@@ -8610,23 +8602,23 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U116" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V116" t="n">
-        <v>46.73781</v>
+        <v>52.18408</v>
       </c>
       <c r="W116" t="n">
-        <v>-71.90752999999999</v>
+        <v>-70.99409</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4656</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8628,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lac du Cèdre</t>
+          <t>Sirmac</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -8646,17 +8638,17 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Silver, Egp, Cobalt</t>
+          <t>Lithium, Tantalum, Beryllium, Tin, Tungsten, Niobium</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I117" t="b">
@@ -8680,23 +8672,23 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T117" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U117" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V117" t="n">
-        <v>47.86971</v>
+        <v>50.62206</v>
       </c>
       <c r="W117" t="n">
-        <v>-72.97538</v>
+        <v>-75.47598000000001</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4680</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8698,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lac Cutaway</t>
+          <t>Zone Bond</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -8716,17 +8708,17 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Silver, Gold, Cobalt</t>
+          <t>Niobium, Uranium, Thorium</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I118" t="b">
@@ -8750,23 +8742,23 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T118" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U118" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V118" t="n">
-        <v>47.85684</v>
+        <v>45.50259</v>
       </c>
       <c r="W118" t="n">
-        <v>-72.97214</v>
+        <v>-74.04985000000001</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4682</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4068</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8768,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lac Bacon</t>
+          <t>Zone S5-T1</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -8786,12 +8778,12 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Copper, Lead</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8810,7 +8802,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Zn 1.21%</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
@@ -8820,23 +8816,23 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U119" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V119" t="n">
-        <v>56.26861</v>
+        <v>45.54882</v>
       </c>
       <c r="W119" t="n">
-        <v>-67.79407999999999</v>
+        <v>-71.68844</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4653</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=37593</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8842,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Zulapa</t>
+          <t>César</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -8856,12 +8852,12 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Chromium, Egp, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8880,7 +8876,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Ni 0.18%</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="n">
@@ -8890,23 +8890,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T120" t="n">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="U120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V120" t="n">
-        <v>48.46467</v>
+        <v>46.02001</v>
       </c>
       <c r="W120" t="n">
-        <v>-78.87600999999999</v>
+        <v>-71.28955000000001</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5737</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5569</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lac Kennedy</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -8926,12 +8926,12 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Uranium, Copper, Gold, Thorium, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8969,14 +8969,14 @@
         <v>9</v>
       </c>
       <c r="V121" t="n">
-        <v>47.70732</v>
+        <v>56.38722</v>
       </c>
       <c r="W121" t="n">
-        <v>-72.81572</v>
+        <v>-67.84119</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4683</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4642</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Lac Hope</t>
+          <t>Lac de Fer à Cheval</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -8996,12 +8996,12 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9039,14 +9039,14 @@
         <v>9</v>
       </c>
       <c r="V122" t="n">
-        <v>52.29585</v>
+        <v>48.4783</v>
       </c>
       <c r="W122" t="n">
-        <v>-67.22499999999999</v>
+        <v>-79.38352999999999</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4769</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5764</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Anaconda Brass</t>
+          <t>Lac Bertin (Jonsmith)</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -9066,12 +9066,12 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9100,23 +9100,23 @@
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T123" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U123" t="n">
         <v>9</v>
       </c>
       <c r="V123" t="n">
-        <v>48.34022</v>
+        <v>56.30946</v>
       </c>
       <c r="W123" t="n">
-        <v>-78.74214000000001</v>
+        <v>-67.93810999999999</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5739</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4643</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Portneuf (Moly)</t>
+          <t>Duparquet-SE</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -9136,12 +9136,12 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium, Barium</t>
+          <t>Copper, Silver, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9170,23 +9170,23 @@
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T124" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U124" t="n">
         <v>9</v>
       </c>
       <c r="V124" t="n">
-        <v>46.69019</v>
+        <v>48.46364</v>
       </c>
       <c r="W124" t="n">
-        <v>-71.93496</v>
+        <v>-79.17858</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4657</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5768</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lac Aubrey</t>
+          <t>Lac Dunphy</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -9206,12 +9206,12 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9240,23 +9240,23 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T125" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U125" t="n">
         <v>9</v>
       </c>
       <c r="V125" t="n">
-        <v>52.13973</v>
+        <v>56.05097</v>
       </c>
       <c r="W125" t="n">
-        <v>-68.14232</v>
+        <v>-67.71257</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4772</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lac Dufresnoy</t>
+          <t>Lac Maugue</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9310,23 +9310,23 @@
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T126" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U126" t="n">
         <v>9</v>
       </c>
       <c r="V126" t="n">
-        <v>48.42006</v>
+        <v>56.16635</v>
       </c>
       <c r="W126" t="n">
-        <v>-79.01940999999999</v>
+        <v>-67.59905000000001</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5776</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4631</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Orco-Tranchée 35-2</t>
+          <t>Anomalie C11r4</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -9346,12 +9346,12 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Copper, Lead</t>
+          <t>Uranium, Thorium</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9389,14 +9389,14 @@
         <v>9</v>
       </c>
       <c r="V127" t="n">
-        <v>48.42459</v>
+        <v>48.66393</v>
       </c>
       <c r="W127" t="n">
-        <v>-78.74975999999999</v>
+        <v>-69.23025</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5730</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4628</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mine Goldspring (Coldspring, Coldstream)</t>
+          <t>Lac Maugue-Sud</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -9450,23 +9450,23 @@
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T128" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U128" t="n">
         <v>9</v>
       </c>
       <c r="V128" t="n">
-        <v>45.59094</v>
+        <v>56.13465</v>
       </c>
       <c r="W128" t="n">
-        <v>-72.25027</v>
+        <v>-67.6163</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4622</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4637</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bowers</t>
+          <t>Zulapa</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -9520,23 +9520,23 @@
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U129" t="n">
         <v>9</v>
       </c>
       <c r="V129" t="n">
-        <v>45.5805</v>
+        <v>48.46467</v>
       </c>
       <c r="W129" t="n">
-        <v>-72.24822</v>
+        <v>-78.87600999999999</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4620</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5737</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lac Romanet-Ouest</t>
+          <t>Portneuf (Moly)</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -9556,12 +9556,12 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Molybdenum, Uranium, Thorium, Barium</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9599,14 +9599,14 @@
         <v>9</v>
       </c>
       <c r="V130" t="n">
-        <v>56.28057</v>
+        <v>46.69019</v>
       </c>
       <c r="W130" t="n">
-        <v>-67.82632</v>
+        <v>-71.93496</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4648</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4657</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Lac Ronsin</t>
+          <t>Anaconda Brass</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -9626,12 +9626,12 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Uranium, Copper</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9660,23 +9660,23 @@
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U131" t="n">
         <v>9</v>
       </c>
       <c r="V131" t="n">
-        <v>56.28932</v>
+        <v>48.34022</v>
       </c>
       <c r="W131" t="n">
-        <v>-67.84577</v>
+        <v>-78.74214000000001</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4647</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5739</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lac de Fer à Cheval</t>
+          <t>Michaud-Simard (Zone Gaudry)</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -9696,12 +9696,12 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Copper</t>
+          <t>Uranium, Thorium</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9730,23 +9730,23 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T132" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U132" t="n">
         <v>9</v>
       </c>
       <c r="V132" t="n">
-        <v>48.4783</v>
+        <v>46.73781</v>
       </c>
       <c r="W132" t="n">
-        <v>-79.38352999999999</v>
+        <v>-71.90752999999999</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5764</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4656</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Anacon</t>
+          <t>Anomalie 79-1 (Bacon)</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -9766,12 +9766,12 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Uranium, Lead, Copper, Silver, Selenium</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9800,23 +9800,23 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T133" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U133" t="n">
         <v>9</v>
       </c>
       <c r="V133" t="n">
-        <v>56.29678</v>
+        <v>56.27035</v>
       </c>
       <c r="W133" t="n">
-        <v>-67.87625</v>
+        <v>-67.79839</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4646</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4652</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lac Bertin (Jonsmith)</t>
+          <t>Lac Romanet-Ouest</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -9836,12 +9836,12 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9870,23 +9870,23 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T134" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U134" t="n">
         <v>9</v>
       </c>
       <c r="V134" t="n">
-        <v>56.30946</v>
+        <v>56.28057</v>
       </c>
       <c r="W134" t="n">
-        <v>-67.93810999999999</v>
+        <v>-67.82632</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4643</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4648</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Lac Ronsin</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -9906,12 +9906,12 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Gold, Copper, Uranium, Silver</t>
+          <t>Copper, Uranium</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9940,23 +9940,23 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U135" t="n">
         <v>9</v>
       </c>
       <c r="V135" t="n">
-        <v>56.38722</v>
+        <v>56.28932</v>
       </c>
       <c r="W135" t="n">
-        <v>-67.84119</v>
+        <v>-67.84577</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4642</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4647</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Anomalie C11r4</t>
+          <t>Anacon</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -9976,12 +9976,12 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Uranium, Thorium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10019,14 +10019,364 @@
         <v>9</v>
       </c>
       <c r="V136" t="n">
-        <v>48.66393</v>
+        <v>56.29678</v>
       </c>
       <c r="W136" t="n">
-        <v>-69.23025</v>
+        <v>-67.87625</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4628</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4646</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Mine Goldspring (Coldspring, Coldstream)</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I137" t="b">
+        <v>0</v>
+      </c>
+      <c r="J137" t="b">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="n">
+        <v>6</v>
+      </c>
+      <c r="T137" t="n">
+        <v>150</v>
+      </c>
+      <c r="U137" t="n">
+        <v>9</v>
+      </c>
+      <c r="V137" t="n">
+        <v>45.59094</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-72.25027</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4622</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Lac Bacon</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I138" t="b">
+        <v>0</v>
+      </c>
+      <c r="J138" t="b">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="n">
+        <v>4</v>
+      </c>
+      <c r="T138" t="n">
+        <v>100</v>
+      </c>
+      <c r="U138" t="n">
+        <v>9</v>
+      </c>
+      <c r="V138" t="n">
+        <v>56.26861</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-67.79407999999999</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4653</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Montserrat</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Gold, Iron, Silver</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I139" t="b">
+        <v>0</v>
+      </c>
+      <c r="J139" t="b">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="n">
+        <v>2</v>
+      </c>
+      <c r="T139" t="n">
+        <v>50</v>
+      </c>
+      <c r="U139" t="n">
+        <v>9</v>
+      </c>
+      <c r="V139" t="n">
+        <v>48.29238</v>
+      </c>
+      <c r="W139" t="n">
+        <v>-79.38334999999999</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5798</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Riv. Cheno-Ouest</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I140" t="b">
+        <v>0</v>
+      </c>
+      <c r="J140" t="b">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="n">
+        <v>2</v>
+      </c>
+      <c r="T140" t="n">
+        <v>50</v>
+      </c>
+      <c r="U140" t="n">
+        <v>9</v>
+      </c>
+      <c r="V140" t="n">
+        <v>51.53813</v>
+      </c>
+      <c r="W140" t="n">
+        <v>-72.67167999999999</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4564</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Lac Dufresnoy</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I141" t="b">
+        <v>0</v>
+      </c>
+      <c r="J141" t="b">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="n">
+        <v>2</v>
+      </c>
+      <c r="T141" t="n">
+        <v>50</v>
+      </c>
+      <c r="U141" t="n">
+        <v>9</v>
+      </c>
+      <c r="V141" t="n">
+        <v>48.42006</v>
+      </c>
+      <c r="W141" t="n">
+        <v>-79.01940999999999</v>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5776</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quebec" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Quebec" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mine Renzy</t>
+          <t>Lac Harris</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Copper, Nickel, Egp, Silver, Gold, Chromium, Cobalt</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>766 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ni 2.3%, Cu 1.75%, Co 0.11%, Pt 0.66 g/t, Pd 0.53 g/t</t>
+          <t>Cu 5.07%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>46.81194</v>
+        <v>47.68996</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.70332999999999</v>
+        <v>-76.66074999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4560</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lac Rivon-Ouest</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Molybdenum, Silver, Copper</t>
+          <t>Zinc, Barium, Mercury, Cadmium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
+          <t>Zn 31.5%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,23 +778,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U4" t="n">
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>51.72313</v>
+        <v>46.11447</v>
       </c>
       <c r="W4" t="n">
-        <v>-72.79697</v>
+        <v>-75.95323</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lac Harris</t>
+          <t>Sainte-Cécile (Maheu) - ancien</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Bismuth, Lead, Zinc, Silver, Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 5.07%</t>
+          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>47.68996</v>
+        <v>45.67446</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.66074999999999</v>
+        <v>-70.96669</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>B-88-01</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zinc, Barium, Mercury, Cadmium</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Zn 31.5%</t>
+          <t>Ag 203.00 g/t, Cu 1.56%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -934,23 +934,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>46.11447</v>
+        <v>45.52488</v>
       </c>
       <c r="W6" t="n">
-        <v>-75.95323</v>
+        <v>-72.07191</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sainte-Cécile (Maheu) - ancien</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bismuth, Lead, Zinc, Silver, Molybdenum, Copper, Gold</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>45.67446</v>
+        <v>48.70382</v>
       </c>
       <c r="W7" t="n">
-        <v>-70.96669</v>
+        <v>-78.25041</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B-88-01</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 203.00 g/t, Cu 1.56%</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>45.52488</v>
+        <v>48.71945</v>
       </c>
       <c r="W8" t="n">
-        <v>-72.07191</v>
+        <v>-78.33144</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -1116,11 +1116,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chibtown</t>
+          <t>Monarch - Veine 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
+          <t>Au 83.00 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>56.39152</v>
+        <v>48.23207</v>
       </c>
       <c r="W9" t="n">
-        <v>-67.87103</v>
+        <v>-79.41287</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delhi Pacific</t>
+          <t>St-Armand (Phillipsburg-Est)</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Uranium, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
+          <t>U 0.578%, Zn 0.0798%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>56.40258</v>
+        <v>45.02084</v>
       </c>
       <c r="W10" t="n">
-        <v>-67.9023</v>
+        <v>-73.0196</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Riv. Cheno-Ouest</t>
+          <t>Chalifour-1</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Lead, Silver, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>U 1.2%</t>
+          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1324,23 +1324,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>51.53813</v>
+        <v>50.3781</v>
       </c>
       <c r="W11" t="n">
-        <v>-72.67167999999999</v>
+        <v>-73.70041000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4564</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>48.70382</v>
+        <v>52.20175</v>
       </c>
       <c r="W12" t="n">
-        <v>-78.25041</v>
+        <v>-70.89798</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Lac du Castor</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>U 0.328%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>48.71945</v>
+        <v>52.2149</v>
       </c>
       <c r="W13" t="n">
-        <v>-78.33144</v>
+        <v>-70.93367000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Monarch - Veine 1</t>
+          <t>Petit Lac Brompton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1558,23 +1558,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>48.23207</v>
+        <v>45.44828</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.41287</v>
+        <v>-72.1057</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
         </is>
       </c>
     </row>
@@ -1584,22 +1584,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>St-Armand (Phillipsburg-Est)</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Uranium, Zinc</t>
+          <t>Copper, Molybdenum, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>U 0.578%, Zn 0.0798%</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1636,23 +1636,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U15" t="n">
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>45.02084</v>
+        <v>45.99171</v>
       </c>
       <c r="W15" t="n">
-        <v>-73.0196</v>
+        <v>-71.70617</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chalifour-1</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>50.3781</v>
+        <v>48.57696</v>
       </c>
       <c r="W16" t="n">
-        <v>-73.70041000000001</v>
+        <v>-78.14164</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Glencoe</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>Cu 4.28%, Ag 3.00 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>52.20175</v>
+        <v>45.32873</v>
       </c>
       <c r="W17" t="n">
-        <v>-70.89798</v>
+        <v>-72.47421</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lac du Castor</t>
+          <t>Zone Nicholson (Puits Racicot)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold, Zinc, Cadmium, Lead, Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>U 0.328%</t>
+          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>52.2149</v>
+        <v>45.29835</v>
       </c>
       <c r="W18" t="n">
-        <v>-70.93367000000001</v>
+        <v>-72.31643</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Petit Lac Brompton</t>
+          <t>Sond. Umex 132</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Silver, Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
+          <t>Cu 4%, Zn 6%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1948,23 +1948,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>45.44828</v>
+        <v>49.79699</v>
       </c>
       <c r="W19" t="n">
-        <v>-72.1057</v>
+        <v>-75.81529</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
         </is>
       </c>
     </row>
@@ -1974,11 +1974,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Lead, Zinc, Silver</t>
+          <t>Copper, Silver, Zinc, Manganese</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.99171</v>
+        <v>46.00535</v>
       </c>
       <c r="W20" t="n">
-        <v>-71.70617</v>
+        <v>-71.70357</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Marguerite</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>48.57696</v>
+        <v>48.29078</v>
       </c>
       <c r="W21" t="n">
-        <v>-78.14164</v>
+        <v>-69.96804</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Glencoe</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2145,28 +2145,28 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>16 kt</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2182,23 +2182,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U22" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="V22" t="n">
-        <v>45.32873</v>
+        <v>49.75792</v>
       </c>
       <c r="W22" t="n">
-        <v>-72.47421</v>
+        <v>-74.3342</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
+          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,28 +2223,28 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Cadmium, Lead, Copper, Silver</t>
+          <t>Gold, Copper, Tungsten, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>29 kt</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2260,23 +2260,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U23" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="V23" t="n">
-        <v>45.29835</v>
+        <v>48.24607</v>
       </c>
       <c r="W23" t="n">
-        <v>-72.31643</v>
+        <v>-79.50617</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Drouet</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,33 +2296,33 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2338,23 +2338,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U24" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="V24" t="n">
-        <v>49.49319</v>
+        <v>49.01028</v>
       </c>
       <c r="W24" t="n">
-        <v>-75.12523</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lac Odon</t>
+          <t>Sirmac</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,21 +2374,21 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Copper, Silver</t>
+          <t>Tungsten, Tin, Beryllium, Tantalum, Lithium, Niobium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 19.20 g/t, Cu 3.51%, Mo 0.96%, Ag 8.40 g/t</t>
+          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U25" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>50.68338</v>
+        <v>50.62206</v>
       </c>
       <c r="W25" t="n">
-        <v>-74.36037</v>
+        <v>-75.47598000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4293</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,33 +2452,33 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Nickel, Rh, Platinum, Egp, Chromium, Palladium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2494,23 +2494,23 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U26" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>49.79699</v>
+        <v>46.04018</v>
       </c>
       <c r="W26" t="n">
-        <v>-75.81529</v>
+        <v>-71.28144</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Umex-2</t>
+          <t>Lavoie (Zone L)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,21 +2530,21 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Copper</t>
+          <t>Vanadium, Lead, Gold, Uranium, Molybdenum, Silver, Thorium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U27" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V27" t="n">
-        <v>49.81674</v>
+        <v>52.18408</v>
       </c>
       <c r="W27" t="n">
-        <v>-75.52503</v>
+        <v>-70.99409</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Solbec Copper</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2613,28 +2613,28 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Manganese</t>
+          <t>Copper, Silver, Lead, Cadmium, Gold, Zinc, Cs</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>2.1 Mt</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2650,23 +2650,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="U28" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V28" t="n">
-        <v>46.00535</v>
+        <v>45.80476</v>
       </c>
       <c r="W28" t="n">
-        <v>-71.70357</v>
+        <v>-71.28747</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lac Phooey</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Bismuth, Gold, Silver, Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="U29" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V29" t="n">
-        <v>49.32384</v>
+        <v>47.43121</v>
       </c>
       <c r="W29" t="n">
-        <v>-75.02628</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lac Rond</t>
+          <t>Struan Uranium</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Gold, Copper</t>
+          <t>Uranium, Nickel, Zinc, Copper</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2806,23 +2806,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U30" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V30" t="n">
-        <v>55.28891</v>
+        <v>45.72522</v>
       </c>
       <c r="W30" t="n">
-        <v>-65.74114</v>
+        <v>-76.71849</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marguerite</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="I31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U31" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V31" t="n">
-        <v>48.29078</v>
+        <v>53.56991</v>
       </c>
       <c r="W31" t="n">
-        <v>-69.96804</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GD-32</t>
+          <t>Fabre Nord</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="I32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 4.40 g/t</t>
+          <t>Au 6.48 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2962,23 +2962,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U32" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V32" t="n">
-        <v>49.49854</v>
+        <v>47.26406</v>
       </c>
       <c r="W32" t="n">
-        <v>-75.14399</v>
+        <v>-79.40157000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3646</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>Riv. Cheno-Ouest</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="I33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 11.00 g/t, Cu 3.3%</t>
+          <t>U 1.2%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3040,23 +3040,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V33" t="n">
-        <v>49.49222</v>
+        <v>51.53813</v>
       </c>
       <c r="W33" t="n">
-        <v>-75.32478999999999</v>
+        <v>-72.67167999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3643</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4564</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rosembaum</t>
+          <t>Dalquier (rg 8 lot 14)</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Zinc, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Zn 4.16%, Cu 0.63%</t>
+          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3118,23 +3118,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U34" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V34" t="n">
-        <v>49.50469</v>
+        <v>48.68159</v>
       </c>
       <c r="W34" t="n">
-        <v>-75.32402999999999</v>
+        <v>-78.15861</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3604</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fenton 98-18</t>
+          <t>Raymor (Zone A)</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="I35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 5.47 g/t</t>
+          <t>Au 5.50 g/t, Zn 2.97%, Ag 7.11 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U35" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V35" t="n">
-        <v>49.51092</v>
+        <v>48.63575</v>
       </c>
       <c r="W35" t="n">
-        <v>-75.36535000000001</v>
+        <v>-78.14138</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3601</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2217</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA-93-04</t>
+          <t>Lac Pascalis</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="I36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 36.07 g/t</t>
+          <t>Au 6.86 g/t, Cu 1.63%, Ag 29.00 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3274,23 +3274,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U36" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V36" t="n">
-        <v>49.55796</v>
+        <v>48.27224</v>
       </c>
       <c r="W36" t="n">
-        <v>-75.37448000000001</v>
+        <v>-77.37222</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3600</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2389</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LF-93-03</t>
+          <t>Lullwitz-Kaeppeli</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold</t>
+          <t>Ir, Gold, Gallium, Zr</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="I37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
+          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U37" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V37" t="n">
-        <v>49.5436</v>
+        <v>47.76432</v>
       </c>
       <c r="W37" t="n">
-        <v>-75.41676</v>
+        <v>-70.46635000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Kogaluc 1</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,17 +3388,17 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U38" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="V38" t="n">
-        <v>49.75792</v>
+        <v>58.81627</v>
       </c>
       <c r="W38" t="n">
-        <v>-74.3342</v>
+        <v>-74.70458000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
+          <t>Bravo (Train No 3)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,17 +3466,17 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Copper, Tungsten, Silver</t>
+          <t>Copper, Uranium, Silver, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I39" t="b">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>29 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
+          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U39" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="V39" t="n">
-        <v>48.24607</v>
+        <v>56.38071</v>
       </c>
       <c r="W39" t="n">
-        <v>-79.50617</v>
+        <v>-68.37362</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Kogaluc 4</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,17 +3544,17 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Au 5.60 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3592,17 +3592,17 @@
         <v>125</v>
       </c>
       <c r="U40" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="V40" t="n">
-        <v>49.01028</v>
+        <v>58.81552</v>
       </c>
       <c r="W40" t="n">
-        <v>-66.00369999999999</v>
+        <v>-74.68685000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sirmac</t>
+          <t>Norseman-2</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,17 +3622,17 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tungsten, Tin, Beryllium, Tantalum, Lithium, Niobium</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
+          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,23 +3664,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T41" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U41" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V41" t="n">
-        <v>50.62206</v>
+        <v>48.05412</v>
       </c>
       <c r="W41" t="n">
-        <v>-75.47598000000001</v>
+        <v>-79.17482</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Black Bay</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,17 +3700,17 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nickel, Rh, Platinum, Egp, Chromium, Palladium</t>
+          <t>Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I42" t="b">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Cu 15.9%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3742,23 +3742,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U42" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V42" t="n">
-        <v>46.04018</v>
+        <v>48.0662</v>
       </c>
       <c r="W42" t="n">
-        <v>-71.28144</v>
+        <v>-79.18935</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Brompton Copper</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,17 +3778,17 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Vanadium, Lead, Gold, Uranium, Molybdenum, Silver, Thorium</t>
+          <t>Copper, Silver, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I43" t="b">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U43" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V43" t="n">
-        <v>52.18408</v>
+        <v>45.48343</v>
       </c>
       <c r="W43" t="n">
-        <v>-70.99409</v>
+        <v>-72.10835</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Weedon-Nord</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Cadmium, Gold, Zinc, Cs</t>
+          <t>Copper, Zinc, Silver, Manganese, Gold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I44" t="b">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Cu 4%, Ag 63.60 g/t, Au 0.34 g/t, Zn 0.928%, Mn 0.365%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T44" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V44" t="n">
-        <v>45.80476</v>
+        <v>45.81174</v>
       </c>
       <c r="W44" t="n">
-        <v>-71.28747</v>
+        <v>-71.52803</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2263</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
+          <t>Western Buff II : Veine 2</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bismuth, Gold, Silver, Molybdenum, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+          <t>Cu 6.03%, Ag 6.68 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3976,23 +3976,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="U45" t="n">
         <v>39</v>
       </c>
       <c r="V45" t="n">
-        <v>47.43121</v>
+        <v>48.15294</v>
       </c>
       <c r="W45" t="n">
-        <v>-79.32868999999999</v>
+        <v>-79.28442</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Struan Uranium</t>
+          <t>East Dalquier</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Uranium, Nickel, Zinc, Copper</t>
+          <t>Gold, Tungsten</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
+          <t>W 1.86%, Au 5.49 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4054,23 +4054,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U46" t="n">
         <v>39</v>
       </c>
       <c r="V46" t="n">
-        <v>45.72522</v>
+        <v>48.65564</v>
       </c>
       <c r="W46" t="n">
-        <v>-76.71849</v>
+        <v>-78.02257</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Fayolle (Renault)</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Gold, Copper, Molybdenum, Lead</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Au 6.68 g/t, Cu 3.9%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4132,23 +4132,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T47" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="U47" t="n">
         <v>39</v>
       </c>
       <c r="V47" t="n">
-        <v>53.56991</v>
+        <v>48.20461</v>
       </c>
       <c r="W47" t="n">
-        <v>-77.31073000000001</v>
+        <v>-79.4071</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fabre Nord</t>
+          <t>Bernierville-WNW</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 6.48 g/t</t>
+          <t>Cu 4.96%, Mo 0.2%, Ag 14.50 g/t, Pb 0.31%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4210,23 +4210,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U48" t="n">
         <v>39</v>
       </c>
       <c r="V48" t="n">
-        <v>47.26406</v>
+        <v>46.11365</v>
       </c>
       <c r="W48" t="n">
-        <v>-79.40157000000001</v>
+        <v>-71.60383</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3611</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dalquier (rg 8 lot 14)</t>
+          <t>Kl Zone</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
+          <t>Au 5.17 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4288,23 +4288,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="U49" t="n">
         <v>39</v>
       </c>
       <c r="V49" t="n">
-        <v>48.68159</v>
+        <v>49.66889</v>
       </c>
       <c r="W49" t="n">
-        <v>-78.15861</v>
+        <v>-78.37572</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Raymor (Zone A)</t>
+          <t>PUI-87-43</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Au 5.50 g/t, Zn 2.97%, Ag 7.11 g/t</t>
+          <t>Au 3.73 g/t</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,23 +4366,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T50" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U50" t="n">
         <v>39</v>
       </c>
       <c r="V50" t="n">
-        <v>48.63575</v>
+        <v>49.68374</v>
       </c>
       <c r="W50" t="n">
-        <v>-78.14138</v>
+        <v>-78.9585</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lac Pascalis</t>
+          <t>Chioak</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Uranium, Copper, Thorium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 6.86 g/t, Cu 1.63%, Ag 29.00 g/t</t>
+          <t>U 0.425%, Cu 0.15%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4444,1191 +4444,21 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T51" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U51" t="n">
         <v>39</v>
       </c>
       <c r="V51" t="n">
-        <v>48.27224</v>
+        <v>58.12937</v>
       </c>
       <c r="W51" t="n">
-        <v>-77.37222</v>
+        <v>-70.18866</v>
       </c>
       <c r="X51" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2389</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Lullwitz-Kaeppeli</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Ir, Gold, Gallium, Zr</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="n">
-        <v>1</v>
-      </c>
-      <c r="T52" t="n">
-        <v>25</v>
-      </c>
-      <c r="U52" t="n">
-        <v>39</v>
-      </c>
-      <c r="V52" t="n">
-        <v>47.76432</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-70.46635000000001</v>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Kogaluc 1</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="n">
-        <v>5</v>
-      </c>
-      <c r="T53" t="n">
-        <v>125</v>
-      </c>
-      <c r="U53" t="n">
-        <v>39</v>
-      </c>
-      <c r="V53" t="n">
-        <v>58.81627</v>
-      </c>
-      <c r="W53" t="n">
-        <v>-74.70458000000001</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Bravo (Train No 3)</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Copper, Uranium, Silver, Gold, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>4</v>
-      </c>
-      <c r="T54" t="n">
-        <v>100</v>
-      </c>
-      <c r="U54" t="n">
-        <v>39</v>
-      </c>
-      <c r="V54" t="n">
-        <v>56.38071</v>
-      </c>
-      <c r="W54" t="n">
-        <v>-68.37362</v>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Kogaluc 4</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Au 5.60 g/t</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="n">
-        <v>5</v>
-      </c>
-      <c r="T55" t="n">
-        <v>125</v>
-      </c>
-      <c r="U55" t="n">
-        <v>39</v>
-      </c>
-      <c r="V55" t="n">
-        <v>58.81552</v>
-      </c>
-      <c r="W55" t="n">
-        <v>-74.68685000000001</v>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Norseman-2</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="n">
-        <v>5</v>
-      </c>
-      <c r="T56" t="n">
-        <v>125</v>
-      </c>
-      <c r="U56" t="n">
-        <v>39</v>
-      </c>
-      <c r="V56" t="n">
-        <v>48.05412</v>
-      </c>
-      <c r="W56" t="n">
-        <v>-79.17482</v>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Black Bay</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Copper, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Cu 15.9%</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
-      <c r="T57" t="n">
-        <v>25</v>
-      </c>
-      <c r="U57" t="n">
-        <v>39</v>
-      </c>
-      <c r="V57" t="n">
-        <v>48.0662</v>
-      </c>
-      <c r="W57" t="n">
-        <v>-79.18935</v>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Brompton Copper</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Nickel, Zinc</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="n">
-        <v>3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>75</v>
-      </c>
-      <c r="U58" t="n">
-        <v>39</v>
-      </c>
-      <c r="V58" t="n">
-        <v>45.48343</v>
-      </c>
-      <c r="W58" t="n">
-        <v>-72.10835</v>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Weedon-Nord</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Silver, Manganese, Gold</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Cu 4%, Ag 63.60 g/t, Au 0.34 g/t, Zn 0.928%, Mn 0.365%</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>2</v>
-      </c>
-      <c r="T59" t="n">
-        <v>50</v>
-      </c>
-      <c r="U59" t="n">
-        <v>39</v>
-      </c>
-      <c r="V59" t="n">
-        <v>45.81174</v>
-      </c>
-      <c r="W59" t="n">
-        <v>-71.52803</v>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2263</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Western Buff II : Veine 2</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>0</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Cu 6.03%, Ag 6.68 g/t</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>2</v>
-      </c>
-      <c r="T60" t="n">
-        <v>50</v>
-      </c>
-      <c r="U60" t="n">
-        <v>39</v>
-      </c>
-      <c r="V60" t="n">
-        <v>48.15294</v>
-      </c>
-      <c r="W60" t="n">
-        <v>-79.28442</v>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>East Dalquier</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>W 1.86%, Au 5.49 g/t</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
-        <v>1</v>
-      </c>
-      <c r="T61" t="n">
-        <v>25</v>
-      </c>
-      <c r="U61" t="n">
-        <v>39</v>
-      </c>
-      <c r="V61" t="n">
-        <v>48.65564</v>
-      </c>
-      <c r="W61" t="n">
-        <v>-78.02257</v>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Fayolle (Renault)</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Molybdenum, Lead</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>0</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Au 6.68 g/t, Cu 3.9%</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
-        <v>2</v>
-      </c>
-      <c r="T62" t="n">
-        <v>50</v>
-      </c>
-      <c r="U62" t="n">
-        <v>39</v>
-      </c>
-      <c r="V62" t="n">
-        <v>48.20461</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-79.4071</v>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Bernierville-WNW</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Molybdenum</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Molybdenum, Copper, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>0</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Cu 4.96%, Mo 0.2%, Ag 14.50 g/t, Pb 0.31%</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" t="n">
-        <v>25</v>
-      </c>
-      <c r="U63" t="n">
-        <v>39</v>
-      </c>
-      <c r="V63" t="n">
-        <v>46.11365</v>
-      </c>
-      <c r="W63" t="n">
-        <v>-71.60383</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3611</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Kl Zone</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Au 5.17 g/t</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="T64" t="n">
-        <v>25</v>
-      </c>
-      <c r="U64" t="n">
-        <v>39</v>
-      </c>
-      <c r="V64" t="n">
-        <v>49.66889</v>
-      </c>
-      <c r="W64" t="n">
-        <v>-78.37572</v>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>PUI-87-43</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>0</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Au 3.73 g/t</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>2</v>
-      </c>
-      <c r="T65" t="n">
-        <v>50</v>
-      </c>
-      <c r="U65" t="n">
-        <v>39</v>
-      </c>
-      <c r="V65" t="n">
-        <v>49.68374</v>
-      </c>
-      <c r="W65" t="n">
-        <v>-78.9585</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Chioak</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Uranium, Copper, Thorium</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>0</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>U 0.425%, Cu 0.15%</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>5</v>
-      </c>
-      <c r="T66" t="n">
-        <v>125</v>
-      </c>
-      <c r="U66" t="n">
-        <v>39</v>
-      </c>
-      <c r="V66" t="n">
-        <v>58.12937</v>
-      </c>
-      <c r="W66" t="n">
-        <v>-70.18866</v>
-      </c>
-      <c r="X66" t="inlineStr">
         <is>
           <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
         </is>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Lac du Castor</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zinc, Barium, Mercury, Cadmium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Zn 31.5%</t>
+          <t>U 0.328%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,23 +778,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>46.11447</v>
+        <v>52.2149</v>
       </c>
       <c r="W4" t="n">
-        <v>-75.95323</v>
+        <v>-70.93367000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sainte-Cécile (Maheu) - ancien</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bismuth, Lead, Zinc, Silver, Molybdenum, Copper, Gold</t>
+          <t>Zinc, Cadmium, Mercury, Barium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
+          <t>Zn 31.5%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -856,23 +856,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>45.67446</v>
+        <v>46.11447</v>
       </c>
       <c r="W5" t="n">
-        <v>-70.96669</v>
+        <v>-75.95323</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B-88-01</t>
+          <t>Sainte-Cécile (Maheu) - ancien</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Molybdenum, Silver, Zinc, Lead, Bismuth, Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ag 203.00 g/t, Cu 1.56%</t>
+          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>45.52488</v>
+        <v>45.67446</v>
       </c>
       <c r="W6" t="n">
-        <v>-72.07191</v>
+        <v>-70.96669</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>48.70382</v>
+        <v>52.20175</v>
       </c>
       <c r="W7" t="n">
-        <v>-78.25041</v>
+        <v>-70.89798</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Chalifour-1</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1090,23 +1090,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U8" t="n">
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>48.71945</v>
+        <v>50.3781</v>
       </c>
       <c r="W8" t="n">
-        <v>-78.33144</v>
+        <v>-73.70041000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
         </is>
       </c>
     </row>
@@ -1116,22 +1116,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Monarch - Veine 1</t>
+          <t>St-Armand (Phillipsburg-Est)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>U 0.578%, Zn 0.0798%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>48.23207</v>
+        <v>45.02084</v>
       </c>
       <c r="W9" t="n">
-        <v>-79.41287</v>
+        <v>-73.0196</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>St-Armand (Phillipsburg-Est)</t>
+          <t>Monarch - Veine 1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Uranium, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>U 0.578%, Zn 0.0798%</t>
+          <t>Au 83.00 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>45.02084</v>
+        <v>48.23207</v>
       </c>
       <c r="W10" t="n">
-        <v>-73.0196</v>
+        <v>-79.41287</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chalifour-1</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Copper</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1324,23 +1324,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>50.3781</v>
+        <v>48.70382</v>
       </c>
       <c r="W11" t="n">
-        <v>-73.70041000000001</v>
+        <v>-78.25041</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>52.20175</v>
+        <v>48.71945</v>
       </c>
       <c r="W12" t="n">
-        <v>-70.89798</v>
+        <v>-78.33144</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lac du Castor</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>U 0.328%</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>52.2149</v>
+        <v>48.57696</v>
       </c>
       <c r="W13" t="n">
-        <v>-70.93367000000001</v>
+        <v>-78.14164</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Petit Lac Brompton</t>
+          <t>Zone Nicholson (Puits Racicot)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Silver, Gold</t>
+          <t>Gold, Zinc, Cadmium, Lead, Silver, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
+          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1558,23 +1558,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>45.44828</v>
+        <v>45.29835</v>
       </c>
       <c r="W14" t="n">
-        <v>-72.1057</v>
+        <v>-72.31643</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
         </is>
       </c>
     </row>
@@ -1584,11 +1584,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>Glencoe</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Lead, Zinc, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Cu 4.28%, Ag 3.00 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1636,23 +1636,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>45.99171</v>
+        <v>45.32873</v>
       </c>
       <c r="W15" t="n">
-        <v>-71.70617</v>
+        <v>-72.47421</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
         </is>
       </c>
     </row>
@@ -1662,11 +1662,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Molybdenum, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>48.57696</v>
+        <v>45.99171</v>
       </c>
       <c r="W16" t="n">
-        <v>-78.14164</v>
+        <v>-71.70617</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Glencoe</t>
+          <t>Petit Lac Brompton</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel, Gold, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
+          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1792,23 +1792,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>45.32873</v>
+        <v>45.44828</v>
       </c>
       <c r="W17" t="n">
-        <v>-72.47421</v>
+        <v>-72.1057</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
+          <t>Marguerite</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Cadmium, Lead, Copper, Silver</t>
+          <t>Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>45.29835</v>
+        <v>48.29078</v>
       </c>
       <c r="W18" t="n">
-        <v>-72.31643</v>
+        <v>-69.96804</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Mine Merrill Island</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,28 +1911,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>2.5 Mt</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Cu 1.82%, Au 0.40 g/t, Ag 20.00 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1948,23 +1948,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="V19" t="n">
-        <v>49.79699</v>
+        <v>49.87032</v>
       </c>
       <c r="W19" t="n">
-        <v>-75.81529</v>
+        <v>-74.32952</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1977</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1989,28 +1989,28 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Manganese</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>16 kt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2026,23 +2026,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U20" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="V20" t="n">
-        <v>46.00535</v>
+        <v>49.75792</v>
       </c>
       <c r="W20" t="n">
-        <v>-71.70357</v>
+        <v>-74.3342</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Marguerite</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,33 +2062,33 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="V21" t="n">
-        <v>48.29078</v>
+        <v>49.01028</v>
       </c>
       <c r="W21" t="n">
-        <v>-69.96804</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Lavoie (Zone L)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Lead, Vanadium, Molybdenum, Uranium, Gold, Silver, Thorium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2188,17 +2188,17 @@
         <v>25</v>
       </c>
       <c r="U22" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V22" t="n">
-        <v>49.75792</v>
+        <v>52.18408</v>
       </c>
       <c r="W22" t="n">
-        <v>-74.3342</v>
+        <v>-70.99409</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Copper, Tungsten, Silver</t>
+          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>29 kt</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2260,23 +2260,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U23" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V23" t="n">
-        <v>48.24607</v>
+        <v>46.04018</v>
       </c>
       <c r="W23" t="n">
-        <v>-79.50617</v>
+        <v>-71.28144</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Solbec Copper</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>2.1 Mt</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2344,17 +2344,17 @@
         <v>125</v>
       </c>
       <c r="U24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V24" t="n">
-        <v>49.01028</v>
+        <v>45.80476</v>
       </c>
       <c r="W24" t="n">
-        <v>-66.00369999999999</v>
+        <v>-71.28747</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sirmac</t>
+          <t>Lac Rocher</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tungsten, Tin, Beryllium, Tantalum, Lithium, Niobium</t>
+          <t>Copper, Nickel, Egp, Platinum, Palladium, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
+          <t>Ni 13.2%, Cu 11.4%, Pt 2.49 g/t, Co 0.23%, Au 0.50 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>50.62206</v>
+        <v>50.58471</v>
       </c>
       <c r="W25" t="n">
-        <v>-75.47598000000001</v>
+        <v>-76.34242</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4260</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,17 +2452,17 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nickel, Rh, Platinum, Egp, Chromium, Palladium</t>
+          <t>Copper, Molybdenum, Silver, Gold, Bismuth</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I26" t="b">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2494,23 +2494,23 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="U26" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V26" t="n">
-        <v>46.04018</v>
+        <v>47.43121</v>
       </c>
       <c r="W26" t="n">
-        <v>-71.28144</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Struan Uranium</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,17 +2530,17 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Vanadium, Lead, Gold, Uranium, Molybdenum, Silver, Thorium</t>
+          <t>Nickel, Uranium, Copper, Zinc</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I27" t="b">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U27" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V27" t="n">
-        <v>52.18408</v>
+        <v>45.72522</v>
       </c>
       <c r="W27" t="n">
-        <v>-70.99409</v>
+        <v>-76.71849</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,17 +2608,17 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Cadmium, Gold, Zinc, Cs</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I28" t="b">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2656,17 +2656,17 @@
         <v>125</v>
       </c>
       <c r="U28" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V28" t="n">
-        <v>45.80476</v>
+        <v>53.56991</v>
       </c>
       <c r="W28" t="n">
-        <v>-71.28747</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
+          <t>Fabre Nord</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bismuth, Gold, Silver, Molybdenum, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+          <t>Au 6.48 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="U29" t="n">
         <v>39</v>
       </c>
       <c r="V29" t="n">
-        <v>47.43121</v>
+        <v>47.26406</v>
       </c>
       <c r="W29" t="n">
-        <v>-79.32868999999999</v>
+        <v>-79.40157000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Struan Uranium</t>
+          <t>Bravo (Train No 3)</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Uranium, Nickel, Zinc, Copper</t>
+          <t>Uranium, Copper, Silver, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
+          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2806,23 +2806,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="U30" t="n">
         <v>39</v>
       </c>
       <c r="V30" t="n">
-        <v>45.72522</v>
+        <v>56.38071</v>
       </c>
       <c r="W30" t="n">
-        <v>-76.71849</v>
+        <v>-68.37362</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Fayolle (Renault)</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper, Gold, Molybdenum, Lead</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Au 6.68 g/t, Cu 3.9%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
         <v>39</v>
       </c>
       <c r="V31" t="n">
-        <v>53.56991</v>
+        <v>48.20461</v>
       </c>
       <c r="W31" t="n">
-        <v>-77.31073000000001</v>
+        <v>-79.4071</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fabre Nord</t>
+          <t>Kogaluc 4</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 6.48 g/t</t>
+          <t>Au 5.60 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2962,23 +2962,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="U32" t="n">
         <v>39</v>
       </c>
       <c r="V32" t="n">
-        <v>47.26406</v>
+        <v>58.81552</v>
       </c>
       <c r="W32" t="n">
-        <v>-79.40157000000001</v>
+        <v>-74.68685000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Riv. Cheno-Ouest</t>
+          <t>Kogaluc 1</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>U 1.2%</t>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3040,23 +3040,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="U33" t="n">
         <v>39</v>
       </c>
       <c r="V33" t="n">
-        <v>51.53813</v>
+        <v>58.81627</v>
       </c>
       <c r="W33" t="n">
-        <v>-72.67167999999999</v>
+        <v>-74.70458000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4564</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dalquier (rg 8 lot 14)</t>
+          <t>Weedon-Nord</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Manganese</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
+          <t>Cu 4%, Ag 63.60 g/t, Au 0.34 g/t, Zn 0.928%, Mn 0.365%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3118,23 +3118,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
         <v>39</v>
       </c>
       <c r="V34" t="n">
-        <v>48.68159</v>
+        <v>45.81174</v>
       </c>
       <c r="W34" t="n">
-        <v>-78.15861</v>
+        <v>-71.52803</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2263</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Raymor (Zone A)</t>
+          <t>Norseman-2</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 5.50 g/t, Zn 2.97%, Ag 7.11 g/t</t>
+          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U35" t="n">
         <v>39</v>
       </c>
       <c r="V35" t="n">
-        <v>48.63575</v>
+        <v>48.05412</v>
       </c>
       <c r="W35" t="n">
-        <v>-78.14138</v>
+        <v>-79.17482</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lac Pascalis</t>
+          <t>Black Bay</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 6.86 g/t, Cu 1.63%, Ag 29.00 g/t</t>
+          <t>Cu 15.9%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>39</v>
       </c>
       <c r="V36" t="n">
-        <v>48.27224</v>
+        <v>48.0662</v>
       </c>
       <c r="W36" t="n">
-        <v>-77.37222</v>
+        <v>-79.18935</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2389</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lullwitz-Kaeppeli</t>
+          <t>Dalquier (rg 8 lot 14)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ir, Gold, Gallium, Zr</t>
+          <t>Zinc, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
+          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="U37" t="n">
         <v>39</v>
       </c>
       <c r="V37" t="n">
-        <v>47.76432</v>
+        <v>48.68159</v>
       </c>
       <c r="W37" t="n">
-        <v>-70.46635000000001</v>
+        <v>-78.15861</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kogaluc 1</t>
+          <t>Raymor (Zone A)</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
+          <t>Au 5.50 g/t, Zn 2.97%, Ag 7.11 g/t</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U38" t="n">
         <v>39</v>
       </c>
       <c r="V38" t="n">
-        <v>58.81627</v>
+        <v>48.63575</v>
       </c>
       <c r="W38" t="n">
-        <v>-74.70458000000001</v>
+        <v>-78.14138</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2217</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bravo (Train No 3)</t>
+          <t>East Dalquier</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver, Gold, Lead, Zinc</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
+          <t>W 1.86%, Au 5.49 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U39" t="n">
         <v>39</v>
       </c>
       <c r="V39" t="n">
-        <v>56.38071</v>
+        <v>48.65564</v>
       </c>
       <c r="W39" t="n">
-        <v>-68.37362</v>
+        <v>-78.02257</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kogaluc 4</t>
+          <t>Western Buff II : Veine 2</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 5.60 g/t</t>
+          <t>Cu 6.03%, Ag 6.68 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3586,23 +3586,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="U40" t="n">
         <v>39</v>
       </c>
       <c r="V40" t="n">
-        <v>58.81552</v>
+        <v>48.15294</v>
       </c>
       <c r="W40" t="n">
-        <v>-74.68685000000001</v>
+        <v>-79.28442</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Norseman-2</t>
+          <t>Brompton Copper</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Nickel, Silver, Zinc</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
+          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,23 +3664,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="U41" t="n">
         <v>39</v>
       </c>
       <c r="V41" t="n">
-        <v>48.05412</v>
+        <v>45.48343</v>
       </c>
       <c r="W41" t="n">
-        <v>-79.17482</v>
+        <v>-72.10835</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Black Bay</t>
+          <t>Kl Zone</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 15.9%</t>
+          <t>Au 5.17 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>39</v>
       </c>
       <c r="V42" t="n">
-        <v>48.0662</v>
+        <v>49.66889</v>
       </c>
       <c r="W42" t="n">
-        <v>-79.18935</v>
+        <v>-78.37572</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brompton Copper</t>
+          <t>Gand II: Rivière Opawica</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Copper, Silver, Nickel, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
+          <t>Au 7.20 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>39</v>
       </c>
       <c r="V43" t="n">
-        <v>45.48343</v>
+        <v>49.64493</v>
       </c>
       <c r="W43" t="n">
-        <v>-72.10835</v>
+        <v>-75.94013</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2988</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Weedon-Nord</t>
+          <t>Chioak</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Manganese, Gold</t>
+          <t>Uranium, Thorium, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Cu 4%, Ag 63.60 g/t, Au 0.34 g/t, Zn 0.928%, Mn 0.365%</t>
+          <t>U 0.425%, Cu 0.15%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,558 +3907,12 @@
         <v>39</v>
       </c>
       <c r="V44" t="n">
-        <v>45.81174</v>
+        <v>58.12937</v>
       </c>
       <c r="W44" t="n">
-        <v>-71.52803</v>
+        <v>-70.18866</v>
       </c>
       <c r="X44" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2263</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Western Buff II : Veine 2</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Cu 6.03%, Ag 6.68 g/t</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="n">
-        <v>2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>50</v>
-      </c>
-      <c r="U45" t="n">
-        <v>39</v>
-      </c>
-      <c r="V45" t="n">
-        <v>48.15294</v>
-      </c>
-      <c r="W45" t="n">
-        <v>-79.28442</v>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>East Dalquier</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>W 1.86%, Au 5.49 g/t</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>25</v>
-      </c>
-      <c r="U46" t="n">
-        <v>39</v>
-      </c>
-      <c r="V46" t="n">
-        <v>48.65564</v>
-      </c>
-      <c r="W46" t="n">
-        <v>-78.02257</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Fayolle (Renault)</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Molybdenum, Lead</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Au 6.68 g/t, Cu 3.9%</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="n">
-        <v>2</v>
-      </c>
-      <c r="T47" t="n">
-        <v>50</v>
-      </c>
-      <c r="U47" t="n">
-        <v>39</v>
-      </c>
-      <c r="V47" t="n">
-        <v>48.20461</v>
-      </c>
-      <c r="W47" t="n">
-        <v>-79.4071</v>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Bernierville-WNW</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Molybdenum</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Molybdenum, Copper, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Cu 4.96%, Mo 0.2%, Ag 14.50 g/t, Pb 0.31%</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
-      <c r="T48" t="n">
-        <v>25</v>
-      </c>
-      <c r="U48" t="n">
-        <v>39</v>
-      </c>
-      <c r="V48" t="n">
-        <v>46.11365</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-71.60383</v>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3611</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Kl Zone</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Au 5.17 g/t</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>25</v>
-      </c>
-      <c r="U49" t="n">
-        <v>39</v>
-      </c>
-      <c r="V49" t="n">
-        <v>49.66889</v>
-      </c>
-      <c r="W49" t="n">
-        <v>-78.37572</v>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>PUI-87-43</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Au 3.73 g/t</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="n">
-        <v>2</v>
-      </c>
-      <c r="T50" t="n">
-        <v>50</v>
-      </c>
-      <c r="U50" t="n">
-        <v>39</v>
-      </c>
-      <c r="V50" t="n">
-        <v>49.68374</v>
-      </c>
-      <c r="W50" t="n">
-        <v>-78.9585</v>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Chioak</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Uranium, Copper, Thorium</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>U 0.425%, Cu 0.15%</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>125</v>
-      </c>
-      <c r="U51" t="n">
-        <v>39</v>
-      </c>
-      <c r="V51" t="n">
-        <v>58.12937</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-70.18866</v>
-      </c>
-      <c r="X51" t="inlineStr">
         <is>
           <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
         </is>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X44"/>
+  <dimension ref="A1:X76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lac Harris</t>
+          <t>Relique</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 5.07%</t>
+          <t>Au 10.40 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>47.68996</v>
+        <v>49.61809</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.66074999999999</v>
+        <v>-75.69525</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2962</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lac du Castor</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>U 0.328%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>52.2149</v>
+        <v>49.82919</v>
       </c>
       <c r="W4" t="n">
-        <v>-70.93367000000001</v>
+        <v>-70.58076</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zinc, Cadmium, Mercury, Barium</t>
+          <t>Nickel, Copper, Cobalt, Platinum, Palladium, Egp</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Zn 31.5%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -856,23 +856,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>46.11447</v>
+        <v>49.83681</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.95323</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sainte-Cécile (Maheu) - ancien</t>
+          <t>Insight (Maschakw)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Molybdenum, Silver, Zinc, Lead, Bismuth, Gold, Copper</t>
+          <t>Tungsten, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
+          <t>Au 100.50 g/t, Ag 435.00 g/t, W 0.143%, Cu 1.41%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>45.67446</v>
+        <v>52.55956</v>
       </c>
       <c r="W6" t="n">
-        <v>-70.96669</v>
+        <v>-77.37969</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58182</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Subtile</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Tungsten, Zinc, Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>Au 141.00 g/t, Ag 915.00 g/t, W 0.476%, Zn 7.87%, Cu 0.57%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>52.20175</v>
+        <v>60.35882</v>
       </c>
       <c r="W7" t="n">
-        <v>-70.89798</v>
+        <v>-75.39583</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58443</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chalifour-1</t>
+          <t>Mousquetaires</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
+          <t>Cu 13.7%, Ag 10.40 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1090,23 +1090,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>50.3781</v>
+        <v>60.29225</v>
       </c>
       <c r="W8" t="n">
-        <v>-73.70041000000001</v>
+        <v>-75.42643</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58434</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St-Armand (Phillipsburg-Est)</t>
+          <t>Southwest (Éléonore)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Uranium, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>U 0.578%, Zn 0.0798%</t>
+          <t>Au 3.69 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>45.02084</v>
+        <v>52.6147</v>
       </c>
       <c r="W9" t="n">
-        <v>-73.0196</v>
+        <v>-76.11929000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=59096</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Monarch - Veine 1</t>
+          <t>Kupfer : Mine Val-St-Gilles</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>Cu 7.96%, Ag 89.15 g/t, Zn 2.66%, Au 0.34 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>48.23207</v>
+        <v>48.97156</v>
       </c>
       <c r="W10" t="n">
-        <v>-79.41287</v>
+        <v>-79.08714999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2704</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Val-St-Gilles-SE</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Cu 7.88%, Ag 87.00 g/t, Au 1.06 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>48.70382</v>
+        <v>48.97212</v>
       </c>
       <c r="W11" t="n">
-        <v>-78.25041</v>
+        <v>-79.1088</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2703</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Val-St-Gilles SO</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Silver, Lead, Gold, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Au 8.34 g/t, Zn 5.2%, Pb 9.9%, Ag 61.90 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>48.71945</v>
+        <v>48.96826</v>
       </c>
       <c r="W12" t="n">
-        <v>-78.33144</v>
+        <v>-79.19454</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2702</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Rambull</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>48.57696</v>
+        <v>48.4824</v>
       </c>
       <c r="W13" t="n">
-        <v>-78.14164</v>
+        <v>-78.10243</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Cadmium, Lead, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>45.29835</v>
+        <v>48.31932</v>
       </c>
       <c r="W14" t="n">
-        <v>-72.31643</v>
+        <v>-64.9713</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Glencoe</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>45.32873</v>
+        <v>49.59836</v>
       </c>
       <c r="W15" t="n">
-        <v>-72.47421</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -1662,11 +1662,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Lead, Silver, Zinc</t>
+          <t>Copper, Nickel, Iron</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>45.99171</v>
+        <v>49.63941</v>
       </c>
       <c r="W16" t="n">
-        <v>-71.70617</v>
+        <v>-76.90893</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Petit Lac Brompton</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Gold, Silver</t>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1792,23 +1792,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>45.44828</v>
+        <v>59.80634</v>
       </c>
       <c r="W17" t="n">
-        <v>-72.1057</v>
+        <v>-75.01831</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Marguerite</t>
+          <t>Golden Butterfly</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Lead</t>
+          <t>Gold, Iron, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
+          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1870,23 +1870,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>48.29078</v>
+        <v>51.99697</v>
       </c>
       <c r="W18" t="n">
-        <v>-69.96804</v>
+        <v>-75.22655</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mine Merrill Island</t>
+          <t>Barre de fer</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,28 +1911,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum, Zinc</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.5 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 1.82%, Au 0.40 g/t, Ag 20.00 g/t</t>
+          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1948,23 +1948,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>49.87032</v>
+        <v>51.6436</v>
       </c>
       <c r="W19" t="n">
-        <v>-74.32952</v>
+        <v>-67.33749</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1977</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Louis</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,33 +1984,33 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Au 8.80 g/t, W 0.238%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2026,23 +2026,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.75792</v>
+        <v>52.64315</v>
       </c>
       <c r="W20" t="n">
-        <v>-74.3342</v>
+        <v>-75.48703999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=53060</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Robidoux-appalaches</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,33 +2062,33 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc</t>
+          <t>Lead, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.01028</v>
+        <v>48.35381</v>
       </c>
       <c r="W21" t="n">
-        <v>-66.00369999999999</v>
+        <v>-65.56434</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,21 +2140,21 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lead, Vanadium, Molybdenum, Uranium, Gold, Silver, Thorium</t>
+          <t>Copper, Gold, Silver, Zinc, Chromium, Nickel</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2182,23 +2182,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="U22" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>52.18408</v>
+        <v>46.26109</v>
       </c>
       <c r="W22" t="n">
-        <v>-70.99409</v>
+        <v>-71.22866</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,33 +2218,33 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2260,23 +2260,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T23" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U23" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>46.04018</v>
+        <v>46.26265</v>
       </c>
       <c r="W23" t="n">
-        <v>-71.28144</v>
+        <v>-71.21769</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,33 +2296,33 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2338,23 +2338,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>45.80476</v>
+        <v>46.26532</v>
       </c>
       <c r="W24" t="n">
-        <v>-71.28747</v>
+        <v>-71.28788</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lac Rocher</t>
+          <t>St-Sylvestre-Noranda</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,21 +2374,21 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Platinum, Palladium, Gold, Cobalt</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ni 13.2%, Cu 11.4%, Pt 2.49 g/t, Co 0.23%, Au 0.50 g/t</t>
+          <t>Zn 15.2%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>50.58471</v>
+        <v>46.32835</v>
       </c>
       <c r="W25" t="n">
-        <v>-76.34242</v>
+        <v>-71.13679999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4260</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1218</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Bismuth</t>
+          <t>Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="I26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2494,23 +2494,23 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U26" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>47.43121</v>
+        <v>46.27176</v>
       </c>
       <c r="W26" t="n">
-        <v>-79.32868999999999</v>
+        <v>-71.28612</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Struan Uranium</t>
+          <t>Mine Harvey Hill</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,33 +2530,33 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nickel, Uranium, Copper, Zinc</t>
+          <t>Copper, Silver, Uranium, Molybdenum, Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>453 kt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
+          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="U27" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>45.72522</v>
+        <v>46.26423</v>
       </c>
       <c r="W27" t="n">
-        <v>-76.71849</v>
+        <v>-71.20608</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
         </is>
       </c>
     </row>
@@ -2598,22 +2598,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="I28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2650,23 +2650,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T28" t="n">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="U28" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>53.56991</v>
+        <v>46.265</v>
       </c>
       <c r="W28" t="n">
-        <v>-77.31073000000001</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fabre Nord</t>
+          <t>Sond. Umex 132</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="I29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 6.48 g/t</t>
+          <t>Cu 4%, Zn 6%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T29" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U29" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>47.26406</v>
+        <v>49.79699</v>
       </c>
       <c r="W29" t="n">
-        <v>-79.40157000000001</v>
+        <v>-75.81529</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bravo (Train No 3)</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Uranium, Copper, Silver, Gold, Lead, Zinc</t>
+          <t>Copper, Silver, Zinc, Manganese</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2806,23 +2806,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T30" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U30" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>56.38071</v>
+        <v>46.00535</v>
       </c>
       <c r="W30" t="n">
-        <v>-68.37362</v>
+        <v>-71.70357</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fayolle (Renault)</t>
+          <t>Marguerite</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Gold, Molybdenum, Lead</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="I31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 6.68 g/t, Cu 3.9%</t>
+          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T31" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U31" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>48.20461</v>
+        <v>48.29078</v>
       </c>
       <c r="W31" t="n">
-        <v>-79.4071</v>
+        <v>-69.96804</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kogaluc 4</t>
+          <t>Filon Baker (Lac Arseneault)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="I32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 5.60 g/t</t>
+          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2962,23 +2962,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T32" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U32" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>58.81552</v>
+        <v>48.37895</v>
       </c>
       <c r="W32" t="n">
-        <v>-74.68685000000001</v>
+        <v>-65.22886</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kogaluc 1</t>
+          <t>Lac Anticline</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Silver, Nickel, Zinc, Egp, Copper</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="I33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
+          <t>Ag 444.50 g/t, Ni 0.31%, Cu 0.271%, EGP 2.28e-05%, Zn 0.217%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3040,23 +3040,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>58.81627</v>
+        <v>55.25152</v>
       </c>
       <c r="W33" t="n">
-        <v>-74.70458000000001</v>
+        <v>-66.30022</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1153</t>
         </is>
       </c>
     </row>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Weedon-Nord</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Manganese</t>
+          <t>Copper, Silver, Zinc, Gold, Lead</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 4%, Ag 63.60 g/t, Au 0.34 g/t, Zn 0.928%, Mn 0.365%</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3118,23 +3118,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>45.81174</v>
+        <v>48.37403</v>
       </c>
       <c r="W34" t="n">
-        <v>-71.52803</v>
+        <v>-65.44089</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2263</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Norseman-2</t>
+          <t>Reboul : Centre-Ouest</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Zinc, Lead, Gold, Antimony, Copper</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="I35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
+          <t>Zn 15.4%, Ag 230.00 g/t, Au 1.42 g/t, Pb 2.94%, Cu 0.372%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>48.05412</v>
+        <v>48.37247</v>
       </c>
       <c r="W35" t="n">
-        <v>-79.17482</v>
+        <v>-65.44429</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1161</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Black Bay</t>
+          <t>Lac Baude</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc</t>
+          <t>La, Etr, Ce, Sm, Pr, Nd, Gd</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="I36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 15.9%</t>
+          <t>Nd 1.6%, Pr 0.482%, Ce 4.64%, La 2.36%, ETR 9.5%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3274,23 +3274,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>48.0662</v>
+        <v>47.08116</v>
       </c>
       <c r="W36" t="n">
-        <v>-79.18935</v>
+        <v>-73.285</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=56553</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dalquier (rg 8 lot 14)</t>
+          <t>OR79</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="I37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
+          <t>Au 3.74 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>48.68159</v>
+        <v>49.7697</v>
       </c>
       <c r="W37" t="n">
-        <v>-78.15861</v>
+        <v>-76.03744</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=53722</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Raymor (Zone A)</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="I38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 5.50 g/t, Zn 2.97%, Ag 7.11 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T38" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>48.63575</v>
+        <v>49.84595</v>
       </c>
       <c r="W38" t="n">
-        <v>-78.14138</v>
+        <v>-70.57626</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>East Dalquier</t>
+          <t>Lepage No 2</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Gold, Arsenic, Antimony</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="I39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>W 1.86%, Au 5.49 g/t</t>
+          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>48.65564</v>
+        <v>48.33322</v>
       </c>
       <c r="W39" t="n">
-        <v>-78.02257</v>
+        <v>-66.99834</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Western Buff II : Veine 2</t>
+          <t>Lac Lanctôt</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 6.03%, Ag 6.68 g/t</t>
+          <t>Zn 11.7%, Au 1.30 g/t, Ag 34.00 g/t, Cu 0.48%, Pb 0.69%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3586,23 +3586,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U40" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>48.15294</v>
+        <v>47.2105</v>
       </c>
       <c r="W40" t="n">
-        <v>-79.28442</v>
+        <v>-72.46509</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3297</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brompton Copper</t>
+          <t>Étoile d'or</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Silver, Zinc</t>
+          <t>Silver, Molybdenum, Zinc, Copper, Lead, Bismuth, Cadmium, Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="I41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
+          <t>Bi 1.7%, Ag 505.00 g/t, Zn 7.84%, Mo 0.882%, Cu 1.6%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,23 +3664,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U41" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>45.48343</v>
+        <v>45.42701</v>
       </c>
       <c r="W41" t="n">
-        <v>-72.10835</v>
+        <v>-71.29181</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3321</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kl Zone</t>
+          <t>Lac Viking</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="I42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 5.17 g/t</t>
+          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3742,23 +3742,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>49.66889</v>
+        <v>47.20549</v>
       </c>
       <c r="W42" t="n">
-        <v>-78.37572</v>
+        <v>-72.45211999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gand II: Rivière Opawica</t>
+          <t>Ruisseau Lapointe</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Lead, Copper, Zinc, Manganese, Gold</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 7.20 g/t</t>
+          <t>Cu 2.9%, Ag 170.00 g/t, Au 0.39 g/t, Pb 1.77%, Zn 0.44%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>49.64493</v>
+        <v>47.91173</v>
       </c>
       <c r="W43" t="n">
-        <v>-75.94013</v>
+        <v>-74.4177</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2988</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=59593</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chioak</t>
+          <t>ELR-18-00086</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Uranium, Thorium, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="I44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>U 0.425%, Cu 0.15%</t>
+          <t>Au 5.21 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,2519 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
+        <v>13</v>
+      </c>
+      <c r="T44" t="n">
+        <v>325</v>
+      </c>
+      <c r="U44" t="n">
+        <v>55</v>
+      </c>
+      <c r="V44" t="n">
+        <v>52.68588</v>
+      </c>
+      <c r="W44" t="n">
+        <v>-76.12502000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=59393</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Harriman-1 (New Richmond-1)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Antimony</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Antimony, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Sb 43.8%, Au 13.70 g/t, Ag 4.50 g/t</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="n">
+        <v>325</v>
+      </c>
+      <c r="U45" t="n">
+        <v>55</v>
+      </c>
+      <c r="V45" t="n">
+        <v>48.24307</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-65.79867</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3578</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>13</v>
+      </c>
+      <c r="T46" t="n">
+        <v>325</v>
+      </c>
+      <c r="U46" t="n">
+        <v>55</v>
+      </c>
+      <c r="V46" t="n">
+        <v>45.03676</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-72.77243</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Gagnon</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>13</v>
+      </c>
+      <c r="T47" t="n">
+        <v>325</v>
+      </c>
+      <c r="U47" t="n">
+        <v>55</v>
+      </c>
+      <c r="V47" t="n">
+        <v>55.5908</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-71.13463</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pistolaté</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Egp, Platinum, Palladium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>13</v>
+      </c>
+      <c r="T48" t="n">
+        <v>325</v>
+      </c>
+      <c r="U48" t="n">
+        <v>55</v>
+      </c>
+      <c r="V48" t="n">
+        <v>55.68696</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-71.02212</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nickel, Egp, Copper, Palladium, Platinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>13</v>
+      </c>
+      <c r="T49" t="n">
+        <v>325</v>
+      </c>
+      <c r="U49" t="n">
+        <v>55</v>
+      </c>
+      <c r="V49" t="n">
+        <v>55.58892</v>
+      </c>
+      <c r="W49" t="n">
+        <v>-71.1636</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Egp, Platinum, Palladium, Cobalt</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>13</v>
+      </c>
+      <c r="T50" t="n">
+        <v>325</v>
+      </c>
+      <c r="U50" t="n">
+        <v>55</v>
+      </c>
+      <c r="V50" t="n">
+        <v>55.61902</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-71.054</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Delta (Zone D-9)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Platinum, Gold, Copper, Palladium, Egp, Nickel, Cobalt</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Pd 28.00 g/t, Ni 7.2%, Cu 5.9%, Au 1.80 g/t, Pt 4.13 g/t</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>8</v>
+      </c>
+      <c r="T51" t="n">
+        <v>200</v>
+      </c>
+      <c r="U51" t="n">
+        <v>55</v>
+      </c>
+      <c r="V51" t="n">
+        <v>61.48634</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-74.44287</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3401</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Principal (Zone Olga)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Gold, Arsenic</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>13</v>
+      </c>
+      <c r="T52" t="n">
+        <v>325</v>
+      </c>
+      <c r="U52" t="n">
+        <v>55</v>
+      </c>
+      <c r="V52" t="n">
+        <v>49.78784</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-77.08529</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Lac Noach-Sud</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Zinc, Copper, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Zn 9.8%, Cu 1.97%, Ag 44.00 g/t</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>13</v>
+      </c>
+      <c r="T53" t="n">
+        <v>325</v>
+      </c>
+      <c r="U53" t="n">
+        <v>55</v>
+      </c>
+      <c r="V53" t="n">
+        <v>53.60084</v>
+      </c>
+      <c r="W53" t="n">
+        <v>-77.60271</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3442</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ruisseau Basket</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>13</v>
+      </c>
+      <c r="T54" t="n">
+        <v>325</v>
+      </c>
+      <c r="U54" t="n">
+        <v>55</v>
+      </c>
+      <c r="V54" t="n">
+        <v>48.09296</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-66.78681</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Devlin (Riocanex)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>16 kt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>25</v>
+      </c>
+      <c r="U55" t="n">
+        <v>46</v>
+      </c>
+      <c r="V55" t="n">
+        <v>49.75792</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-74.3342</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mine Madeleine</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>8.1 Mt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="n">
+        <v>125</v>
+      </c>
+      <c r="U56" t="n">
+        <v>44</v>
+      </c>
+      <c r="V56" t="n">
+        <v>49.01028</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-66.00369999999999</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Solbec Copper</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Lead, Cadmium, Gold, Zinc, Cs</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2.1 Mt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T57" t="n">
+        <v>100</v>
+      </c>
+      <c r="U57" t="n">
+        <v>43</v>
+      </c>
+      <c r="V57" t="n">
+        <v>45.80476</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-71.28747</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Lavoie (Zone L)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vanadium</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Vanadium, Lead, Gold, Uranium, Molybdenum, Silver, Thorium</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>25</v>
+      </c>
+      <c r="U58" t="n">
+        <v>43</v>
+      </c>
+      <c r="V58" t="n">
+        <v>52.18408</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-70.99409</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hall (et Extension)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nickel, Rh, Platinum, Egp, Chromium, Palladium</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>4 kt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="n">
+        <v>100</v>
+      </c>
+      <c r="U59" t="n">
+        <v>43</v>
+      </c>
+      <c r="V59" t="n">
+        <v>46.04018</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-71.28144</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lac Wachigabau</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Cu 4.46%, Au 3.14 g/t, Ag 16.60 g/t</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>25</v>
+      </c>
+      <c r="U60" t="n">
+        <v>39</v>
+      </c>
+      <c r="V60" t="n">
+        <v>49.53002</v>
+      </c>
+      <c r="W60" t="n">
+        <v>-75.92335</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gand II: Rivière Opawica</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Au 7.20 g/t</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" t="n">
+        <v>75</v>
+      </c>
+      <c r="U61" t="n">
+        <v>39</v>
+      </c>
+      <c r="V61" t="n">
+        <v>49.64493</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-75.94013</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2988</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PUI-87-43</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Au 3.73 g/t</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
         <v>2</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T62" t="n">
         <v>50</v>
       </c>
-      <c r="U44" t="n">
+      <c r="U62" t="n">
         <v>39</v>
       </c>
-      <c r="V44" t="n">
-        <v>58.12937</v>
-      </c>
-      <c r="W44" t="n">
-        <v>-70.18866</v>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
+      <c r="V62" t="n">
+        <v>49.68374</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-78.9585</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kl Zone</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Au 5.17 g/t</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>25</v>
+      </c>
+      <c r="U63" t="n">
+        <v>39</v>
+      </c>
+      <c r="V63" t="n">
+        <v>49.66889</v>
+      </c>
+      <c r="W63" t="n">
+        <v>-78.37572</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Duvay : Zone de la Fosse</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Au 43.62 g/t</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>25</v>
+      </c>
+      <c r="U64" t="n">
+        <v>39</v>
+      </c>
+      <c r="V64" t="n">
+        <v>48.69352</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-77.96293</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2766</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Lac Macamic-Ouest</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Au 5.09 g/t, Cu 3.33%, Ag 12.00 g/t</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="n">
+        <v>100</v>
+      </c>
+      <c r="U65" t="n">
+        <v>39</v>
+      </c>
+      <c r="V65" t="n">
+        <v>48.77553</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-79.0604</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2717</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>La Reine</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gold, Molybdenum, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Au 11.00 g/t, Mo 0.52%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>25</v>
+      </c>
+      <c r="U66" t="n">
+        <v>39</v>
+      </c>
+      <c r="V66" t="n">
+        <v>48.77182</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-79.33329000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2716</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kerwin</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>25</v>
+      </c>
+      <c r="U67" t="n">
+        <v>39</v>
+      </c>
+      <c r="V67" t="n">
+        <v>48.39017</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-78.41151000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>East Mac (Indice Nord)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Au 108.96 g/t, Ag 1480.90 g/t</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>25</v>
+      </c>
+      <c r="U68" t="n">
+        <v>39</v>
+      </c>
+      <c r="V68" t="n">
+        <v>48.6126</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-77.97836</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2804</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Raglan (Zones 5-8)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Copper, Egp, Palladium, Platinum, Nickel, Cobalt, Gold</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Pd 6.10 g/t, Cu 1.43%, Ni 1.1%, Pt 2.00 g/t, Au 0.74 g/t</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>2</v>
+      </c>
+      <c r="T69" t="n">
+        <v>50</v>
+      </c>
+      <c r="U69" t="n">
+        <v>39</v>
+      </c>
+      <c r="V69" t="n">
+        <v>61.69562</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-73.57513</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1177</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Bernierville-WNW</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Molybdenum</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Molybdenum, Copper, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Cu 4.96%, Mo 0.2%, Ag 14.50 g/t, Pb 0.31%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>25</v>
+      </c>
+      <c r="U70" t="n">
+        <v>39</v>
+      </c>
+      <c r="V70" t="n">
+        <v>46.11365</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-71.60383</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3611</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Albert (LH-90)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Pb 50.6%, Zn 20.5%, Ag 173.70 g/t, Cu 0.53%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>25</v>
+      </c>
+      <c r="U71" t="n">
+        <v>39</v>
+      </c>
+      <c r="V71" t="n">
+        <v>48.74517</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-66.13224</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3389</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lorenz Gully</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Uranium, Gold, Lead, Vanadium, Silver, Thorium</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>U 6.05%, Au 1.39 g/t, Ag 14.95 g/t, Pb 0.628%, V 0.0147%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>25</v>
+      </c>
+      <c r="U72" t="n">
+        <v>39</v>
+      </c>
+      <c r="V72" t="n">
+        <v>52.20987</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-71.92959999999999</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=196</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Golden Rock</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Au 27.23 g/t</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>25</v>
+      </c>
+      <c r="U73" t="n">
+        <v>39</v>
+      </c>
+      <c r="V73" t="n">
+        <v>48.81681</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-78.47028</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2694</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cedar Rapids-Zone 1</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Au 77.80 g/t, Cu 1.45%, Ag 68.60 g/t</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" t="n">
+        <v>50</v>
+      </c>
+      <c r="U74" t="n">
+        <v>39</v>
+      </c>
+      <c r="V74" t="n">
+        <v>49.0051</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-77.04089</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3521</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Delta (Zone D-8)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Copper, Nickel, Egp, Gold, Platinum, Palladium, Cobalt</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Ni 7.8%, Pd 25.50 g/t, Cu 4%, Au 3.63 g/t, Pt 7.96 g/t</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>2</v>
+      </c>
+      <c r="T75" t="n">
+        <v>50</v>
+      </c>
+      <c r="U75" t="n">
+        <v>39</v>
+      </c>
+      <c r="V75" t="n">
+        <v>61.48642</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-74.46145</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3396</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Echo-1</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Platinum, Cobalt, Palladium, Egp, Nickel, Copper, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Ni 2.35%, Cu 2.6%, Co 0.56%, Pd 4.46 g/t, Pt 1.64 g/t</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>25</v>
+      </c>
+      <c r="U76" t="n">
+        <v>39</v>
+      </c>
+      <c r="V76" t="n">
+        <v>61.44723</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-74.72001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3411</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X76"/>
+  <dimension ref="A1:X97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Relique</t>
+          <t>RA13-03</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 10.40 g/t</t>
+          <t>Au 3.71 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>49.61809</v>
+        <v>53.1949</v>
       </c>
       <c r="W3" t="n">
-        <v>-75.69525</v>
+        <v>-77.66768999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2962</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20539</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>RA13-02</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 4.67 g/t, Ag 9.80 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>49.82919</v>
+        <v>53.17502</v>
       </c>
       <c r="W4" t="n">
-        <v>-70.58076</v>
+        <v>-77.75697</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20536</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum, Palladium, Egp</t>
+          <t>Gold, Copper, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>49.83681</v>
+        <v>52.21818</v>
       </c>
       <c r="W5" t="n">
-        <v>-70.57877999999999</v>
+        <v>-77.45902</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Insight (Maschakw)</t>
+          <t>Cancet</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tungsten, Copper, Silver, Gold</t>
+          <t>Lithium, Tantalum, Beryllium, Cs, Bismuth, Niobium, Zinc, Lead, Gallium, Rb, Silver, Cobalt, Chromium, Nickel</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 100.50 g/t, Ag 435.00 g/t, W 0.143%, Cu 1.41%</t>
+          <t>Li 1.92%, Bi 0.14%, Zn 1.38%, Ga 0.0134%, Ni 0.166%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>52.55956</v>
+        <v>53.49988</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.37969</v>
+        <v>-74.90752999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58182</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=156</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Subtile</t>
+          <t>Sond. PLP24-019</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tungsten, Zinc, Silver, Gold, Copper</t>
+          <t>Gold, Bismuth</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 141.00 g/t, Ag 915.00 g/t, W 0.476%, Zn 7.87%, Cu 0.57%</t>
+          <t>Au 4.76 g/t, Bi 0.1%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>60.35882</v>
+        <v>52.59612</v>
       </c>
       <c r="W7" t="n">
-        <v>-75.39583</v>
+        <v>-77.37366</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58443</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mousquetaires</t>
+          <t>Nasigon (Lac Lajoue)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 13.7%, Ag 10.40 g/t</t>
+          <t>Cu 9.21%, Ag 100.00 g/t, Au 0.88 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>60.29225</v>
+        <v>47.53875</v>
       </c>
       <c r="W8" t="n">
-        <v>-75.42643</v>
+        <v>-75.10978</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58434</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20138</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Southwest (Éléonore)</t>
+          <t>Lac Nasigon</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 3.69 g/t</t>
+          <t>Cu 4.4%, Ag 96.30 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>52.6147</v>
+        <v>47.53085</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.11929000000001</v>
+        <v>-75.11848000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=59096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20134</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kupfer : Mine Val-St-Gilles</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold</t>
+          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 7.96%, Ag 89.15 g/t, Zn 2.66%, Au 0.34 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>48.97156</v>
+        <v>49.83681</v>
       </c>
       <c r="W10" t="n">
-        <v>-79.08714999999999</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Val-St-Gilles-SE</t>
+          <t>Galexis</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 7.88%, Ag 87.00 g/t, Au 1.06 g/t</t>
+          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>48.97212</v>
+        <v>53.48752</v>
       </c>
       <c r="W11" t="n">
-        <v>-79.1088</v>
+        <v>-75.33392000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2703</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Val-St-Gilles SO</t>
+          <t>Perseus</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Lead, Gold, Copper</t>
+          <t>Egp, Platinum, Gold, Nickel, Palladium, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 8.34 g/t, Zn 5.2%, Pb 9.9%, Ag 61.90 g/t</t>
+          <t>Ni 8.42%, Cu 9.35%, Au 1.83 g/t, Pd 5.83 g/t, Pt 1.42 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>48.96826</v>
+        <v>53.65127</v>
       </c>
       <c r="W12" t="n">
-        <v>-79.19454</v>
+        <v>-75.87454</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2702</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67054</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rambull</t>
+          <t>Sond. K2-22-10</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
+          <t>Au 3.64 g/t, Zn 0.55%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>48.4824</v>
+        <v>52.28963</v>
       </c>
       <c r="W13" t="n">
-        <v>-78.10243</v>
+        <v>-77.78149999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>48.31932</v>
+        <v>53.43724</v>
       </c>
       <c r="W14" t="n">
-        <v>-64.9713</v>
+        <v>-75.04334</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Au 144.55 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>49.59836</v>
+        <v>53.52019</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.92194000000001</v>
+        <v>-75.40980999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Iron</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>49.63941</v>
+        <v>49.82919</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.90893</v>
+        <v>-70.58076</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Au 12.91 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>59.80634</v>
+        <v>53.51022</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.01831</v>
+        <v>-75.46174000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Golden Butterfly</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Iron, Silver</t>
+          <t>Gold, Copper, Silver, Cobalt, Tungsten, Tellurium, Arsenic</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1870,23 +1870,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>51.99697</v>
+        <v>59.80634</v>
       </c>
       <c r="W18" t="n">
-        <v>-75.22655</v>
+        <v>-75.01831</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Barre de fer</t>
+          <t>Baleine Rouge Au-Zn-Pb</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold, Zinc, Lead</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
+          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>51.6436</v>
+        <v>55.23561</v>
       </c>
       <c r="W19" t="n">
-        <v>-67.33749</v>
+        <v>-67.9516</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Louis</t>
+          <t>Leadville</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 8.80 g/t, W 0.238%</t>
+          <t>Zn 31.4%, Ag 95.98 g/t, Pb 4.94%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>52.64315</v>
+        <v>45.00863</v>
       </c>
       <c r="W20" t="n">
-        <v>-75.48703999999999</v>
+        <v>-72.26421000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=53060</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4394</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Robidoux-appalaches</t>
+          <t>Falaises</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Zinc</t>
+          <t>Zr, Thorium, Ce, La, Nd, Etr, Y</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
+          <t>Nd 0.354%, Ce 0.954%, La 0.368%, ETR 3.24%, Th 0.0831%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>48.35381</v>
+        <v>46.80195</v>
       </c>
       <c r="W21" t="n">
-        <v>-65.56434</v>
+        <v>-78.43706</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=18960</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Rob Ex</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Zinc, Chromium, Nickel</t>
+          <t>Gold, Tungsten, Silver, Manganese</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Au 15.30 g/t, W 0.15%, Ag 2.65 g/t, Mn 0.258%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>46.26109</v>
+        <v>52.70232</v>
       </c>
       <c r="W22" t="n">
-        <v>-71.22866</v>
+        <v>-76.05212</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=18709</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Fortin (GH)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Gold, Antimony, Arsenic</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Sb 24.2%, Au 8.26 g/t, As 0.361%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2260,23 +2260,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>46.26265</v>
+        <v>52.08795</v>
       </c>
       <c r="W23" t="n">
-        <v>-71.21769</v>
+        <v>-75.39556</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=15915</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Mine Capelton (Albert)</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,17 +2296,17 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Zinc, Copper, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>300 kt</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>46.26532</v>
+        <v>45.32298</v>
       </c>
       <c r="W24" t="n">
-        <v>-71.28788</v>
+        <v>-71.90649999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>St-Sylvestre-Noranda</t>
+          <t>Mine Suffield</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,17 +2374,17 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver, Lead, Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>850 kt</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Zn 15.2%</t>
+          <t>Ag 644.80 g/t, Zn 29.6%, Au 7.20 g/t, Cu 6.2%, Pb 3.68%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>46.32835</v>
+        <v>45.31892</v>
       </c>
       <c r="W25" t="n">
-        <v>-71.13679999999999</v>
+        <v>-71.95913</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1218</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4356</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Raglan (Lac Cross Est, zones C-1 et C-2)</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold</t>
+          <t>Nickel, Copper, Egp, Gold, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Ni 2.33%, Au 2.00 g/t, Cu 1.24%, Pd 2.26 g/t, Pt 0.86 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>46.27176</v>
+        <v>61.5996</v>
       </c>
       <c r="W26" t="n">
-        <v>-71.28612</v>
+        <v>-74.24052</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3851</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill</t>
+          <t>Raglan (Lac Cross Ouest)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,17 +2530,17 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium, Molybdenum, Gold</t>
+          <t>Nickel, Egp, Palladium, Platinum, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I27" t="b">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>453 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
+          <t>Ni 3.1%, Pd 4.81 g/t, Cu 0.979%, Pt 1.26 g/t, EGP 0.00055%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>46.26423</v>
+        <v>61.59527</v>
       </c>
       <c r="W27" t="n">
-        <v>-71.20608</v>
+        <v>-74.28905</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3850</t>
         </is>
       </c>
     </row>
@@ -2598,11 +2598,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Ouf</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Cu 11.8%, Ag 204.00 g/t, Zn 8.7%, Pb 1.6%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2650,23 +2650,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>46.265</v>
+        <v>53.90478</v>
       </c>
       <c r="W28" t="n">
-        <v>-71.21259999999999</v>
+        <v>-74.69878</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3841</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Mine Aldermac Moulton Hill</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,17 +2686,17 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Zinc, Lead, Copper, Gold, Silver, Barium, Cadmium, Molybdenum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>871 kt</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U29" t="n">
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.79699</v>
+        <v>45.40941</v>
       </c>
       <c r="W29" t="n">
-        <v>-75.81529</v>
+        <v>-71.81791</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Rambull</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Manganese</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2806,23 +2806,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T30" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="U30" t="n">
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>46.00535</v>
+        <v>48.4824</v>
       </c>
       <c r="W30" t="n">
-        <v>-71.70357</v>
+        <v>-78.10243</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marguerite</t>
+          <t>Rivière Pontois</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Gold, Copper, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
+          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>48.29078</v>
+        <v>53.51426</v>
       </c>
       <c r="W31" t="n">
-        <v>-69.96804</v>
+        <v>-74.51608</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Filon Baker (Lac Arseneault)</t>
+          <t>Sond. LGS09-217</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
+          <t>Cu 2.76%, Au 2.19 g/t, Ag 14.70 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>48.37895</v>
+        <v>53.528</v>
       </c>
       <c r="W32" t="n">
-        <v>-65.22886</v>
+        <v>-76.54774999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20066</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac Anticline</t>
+          <t>Lac Beaver Zoran</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Zinc, Egp, Copper</t>
+          <t>Vanadium, Lead, Zinc, Uranium, Barium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ag 444.50 g/t, Ni 0.31%, Cu 0.271%, EGP 2.28e-05%, Zn 0.217%</t>
+          <t>U 2.09%, V 0.91%, Zn 1.02%, Pb 1.32%, Ba 41.2%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>55.25152</v>
+        <v>51.98869</v>
       </c>
       <c r="W33" t="n">
-        <v>-66.30022</v>
+        <v>-72.37778</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1153</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4397</t>
         </is>
       </c>
     </row>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold, Lead</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>48.37403</v>
+        <v>49.59836</v>
       </c>
       <c r="W34" t="n">
-        <v>-65.44089</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Reboul : Centre-Ouest</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Gold, Antimony, Copper</t>
+          <t>Copper, Nickel, Iron</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Zn 15.4%, Ag 230.00 g/t, Au 1.42 g/t, Pb 2.94%, Cu 0.372%</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>48.37247</v>
+        <v>49.63941</v>
       </c>
       <c r="W35" t="n">
-        <v>-65.44429</v>
+        <v>-76.90893</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1161</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lac Baude</t>
+          <t>Dessureault (Lac Rougemont)</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>La, Etr, Ce, Sm, Pr, Nd, Gd</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Nd 1.6%, Pr 0.482%, Ce 4.64%, La 2.36%, ETR 9.5%</t>
+          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>47.08116</v>
+        <v>58.02817</v>
       </c>
       <c r="W36" t="n">
-        <v>-73.285</v>
+        <v>-69.57268000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=56553</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OR79</t>
+          <t>Venditelli (Lac St-Pierre-Gold)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Palladium, Egp</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 3.74 g/t</t>
+          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>49.7697</v>
+        <v>58.15377</v>
       </c>
       <c r="W37" t="n">
-        <v>-76.03744</v>
+        <v>-69.53443</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=53722</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Fort Chimo (Lac Plissé)</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Copper, Zinc, Gold, Nickel, Silver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>49.84595</v>
+        <v>58.12861</v>
       </c>
       <c r="W38" t="n">
-        <v>-70.57626</v>
+        <v>-69.55745</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lepage No 2</t>
+          <t>Erickson Sud - Goose Pond</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Antimony</t>
+          <t>Copper, Nickel, Egp, Palladium, Gold, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
+          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>48.33322</v>
+        <v>57.99255</v>
       </c>
       <c r="W39" t="n">
-        <v>-66.99834</v>
+        <v>-69.72347000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lac Lanctôt</t>
+          <t>St-Sylvestre-Noranda</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Copper, Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Zn 11.7%, Au 1.30 g/t, Ag 34.00 g/t, Cu 0.48%, Pb 0.69%</t>
+          <t>Zn 15.2%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>47.2105</v>
+        <v>46.32835</v>
       </c>
       <c r="W40" t="n">
-        <v>-72.46509</v>
+        <v>-71.13679999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3297</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1218</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Étoile d'or</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Silver, Molybdenum, Zinc, Copper, Lead, Bismuth, Cadmium, Gold</t>
+          <t>Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Bi 1.7%, Ag 505.00 g/t, Zn 7.84%, Mo 0.882%, Cu 1.6%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>45.42701</v>
+        <v>46.27176</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.29181</v>
+        <v>-71.28612</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3321</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lac Viking</t>
+          <t>Mine Harvey Hill</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Silver</t>
+          <t>Copper, Silver, Uranium, Molybdenum, Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I42" t="b">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>453 kt</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
+          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3742,23 +3742,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U42" t="n">
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>47.20549</v>
+        <v>46.26423</v>
       </c>
       <c r="W42" t="n">
-        <v>-72.45211999999999</v>
+        <v>-71.20608</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ruisseau Lapointe</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Zinc, Manganese, Gold</t>
+          <t>Copper, Gold, Silver, Nickel, Chromium, Zinc</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 2.9%, Ag 170.00 g/t, Au 0.39 g/t, Pb 1.77%, Zn 0.44%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T43" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U43" t="n">
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>47.91173</v>
+        <v>46.26109</v>
       </c>
       <c r="W43" t="n">
-        <v>-74.4177</v>
+        <v>-71.22866</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=59593</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ELR-18-00086</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver, Gold, Zinc, Molybdenum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 5.21 g/t</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>52.68588</v>
+        <v>46.26265</v>
       </c>
       <c r="W44" t="n">
-        <v>-76.12502000000001</v>
+        <v>-71.21769</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=59393</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Harriman-1 (New Richmond-1)</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Antimony, Gold, Silver</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sb 43.8%, Au 13.70 g/t, Ag 4.50 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>48.24307</v>
+        <v>49.84595</v>
       </c>
       <c r="W45" t="n">
-        <v>-65.79867</v>
+        <v>-70.57626</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3578</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel, Cobalt, Egp, Palladium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>45.03676</v>
+        <v>58.23464</v>
       </c>
       <c r="W46" t="n">
-        <v>-72.77243</v>
+        <v>-69.92364000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>PAP Nord (Camp A-1)</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
+          <t>Zinc, Copper, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>55.5908</v>
+        <v>60.2779</v>
       </c>
       <c r="W47" t="n">
-        <v>-71.13463</v>
+        <v>-75.33311</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Reboul : Centre-Ouest</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Platinum, Palladium</t>
+          <t>Silver, Zinc, Lead, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Zn 15.4%, Ag 230.00 g/t, Au 1.42 g/t, Pb 2.94%, Cu 0.372%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>55.68696</v>
+        <v>48.37247</v>
       </c>
       <c r="W48" t="n">
-        <v>-71.02212</v>
+        <v>-65.44429</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1161</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Filon Baker (Lac Arseneault)</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Copper, Palladium, Platinum</t>
+          <t>Lead, Zinc, Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>55.58892</v>
+        <v>48.37895</v>
       </c>
       <c r="W49" t="n">
-        <v>-71.1636</v>
+        <v>-65.22886</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Lac Anticline</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Platinum, Palladium, Cobalt</t>
+          <t>Silver, Nickel, Copper, Egp, Zinc</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>Ag 444.50 g/t, Ni 0.31%, Cu 0.271%, EGP 2.28e-05%, Zn 0.217%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>55.61902</v>
+        <v>55.25152</v>
       </c>
       <c r="W50" t="n">
-        <v>-71.054</v>
+        <v>-66.30022</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1153</t>
         </is>
       </c>
     </row>
@@ -4392,22 +4392,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Delta (Zone D-9)</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Platinum, Gold, Copper, Palladium, Egp, Nickel, Cobalt</t>
+          <t>Copper, Silver, Uranium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Pd 28.00 g/t, Ni 7.2%, Cu 5.9%, Au 1.80 g/t, Pt 4.13 g/t</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4444,23 +4444,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U51" t="n">
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>61.48634</v>
+        <v>46.265</v>
       </c>
       <c r="W51" t="n">
-        <v>-74.44287</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3401</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>OTS-08</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Arsenic</t>
+          <t>Zinc, Uranium, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4522,23 +4522,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U52" t="n">
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>49.78784</v>
+        <v>51.78509</v>
       </c>
       <c r="W52" t="n">
-        <v>-77.08529</v>
+        <v>-71.96465999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
         </is>
       </c>
     </row>
@@ -4548,22 +4548,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lac Noach-Sud</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Copper, Silver, Zinc, Lead, Gold</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Zn 9.8%, Cu 1.97%, Ag 44.00 g/t</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>53.60084</v>
+        <v>48.37403</v>
       </c>
       <c r="W53" t="n">
-        <v>-77.60271</v>
+        <v>-65.44089</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3442</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Au 21.70 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>48.09296</v>
+        <v>57.94973</v>
       </c>
       <c r="W54" t="n">
-        <v>-66.78681</v>
+        <v>-69.51281</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,33 +4714,33 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4756,23 +4756,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T55" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U55" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>49.75792</v>
+        <v>52.03235</v>
       </c>
       <c r="W55" t="n">
-        <v>-74.3342</v>
+        <v>-69.13816</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Kupfer : Mine Val-St-Gilles</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4797,28 +4797,28 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 7.96%, Ag 89.15 g/t, Zn 2.66%, Au 0.34 g/t</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4834,23 +4834,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T56" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U56" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>49.01028</v>
+        <v>48.97156</v>
       </c>
       <c r="W56" t="n">
-        <v>-66.00369999999999</v>
+        <v>-79.08714999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2704</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Val-St-Gilles-SE</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4870,33 +4870,33 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Cadmium, Gold, Zinc, Cs</t>
+          <t>Silver, Copper, Gold</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Cu 7.88%, Ag 87.00 g/t, Au 1.06 g/t</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4912,23 +4912,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U57" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>45.80476</v>
+        <v>48.97212</v>
       </c>
       <c r="W57" t="n">
-        <v>-71.28747</v>
+        <v>-79.1088</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2703</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Val-St-Gilles SO</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,21 +4948,21 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Vanadium, Lead, Gold, Uranium, Molybdenum, Silver, Thorium</t>
+          <t>Zinc, Silver, Lead, Gold, Copper</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>Au 8.34 g/t, Zn 5.2%, Pb 9.9%, Ag 61.90 g/t</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4990,23 +4990,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U58" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>52.18408</v>
+        <v>48.96826</v>
       </c>
       <c r="W58" t="n">
-        <v>-70.99409</v>
+        <v>-79.19454</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2702</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Century</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,33 +5026,33 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nickel, Rh, Platinum, Egp, Chromium, Palladium</t>
+          <t>Copper, Egp, Palladium, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Ni 15.5%, Cu 3.16%, Pd 1.22 g/t, Pt 0.36 g/t, EGP 0.00013%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5068,23 +5068,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T59" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U59" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>46.04018</v>
+        <v>61.35448</v>
       </c>
       <c r="W59" t="n">
-        <v>-71.28144</v>
+        <v>-76.06304</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23835</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lac Wachigabau</t>
+          <t>Lac Nitakwin</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Cu 4.46%, Au 3.14 g/t, Ag 16.60 g/t</t>
+          <t>Au 6.06 g/t</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5146,23 +5146,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T60" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U60" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>49.53002</v>
+        <v>52.1766</v>
       </c>
       <c r="W60" t="n">
-        <v>-75.92335</v>
+        <v>-76.71138999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gand II: Rivière Opawica</t>
+          <t>Mustang</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="I61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Au 7.20 g/t</t>
+          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T61" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U61" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>49.64493</v>
+        <v>52.17024</v>
       </c>
       <c r="W61" t="n">
-        <v>-75.94013</v>
+        <v>-76.57532999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2988</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PUI-87-43</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="I62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Au 3.73 g/t</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5302,23 +5302,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>49.68374</v>
+        <v>55.68696</v>
       </c>
       <c r="W62" t="n">
-        <v>-78.9585</v>
+        <v>-71.02212</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kl Zone</t>
+          <t>Spirit-1</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="I63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Au 5.17 g/t</t>
+          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T63" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U63" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>49.66889</v>
+        <v>61.39663</v>
       </c>
       <c r="W63" t="n">
-        <v>-78.37572</v>
+        <v>-73.13239</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Duvay : Zone de la Fosse</t>
+          <t>G-H-2-79 (Hudbay Mining)</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,12 +5416,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Au 43.62 g/t</t>
+          <t>Cu 3.26%, Ni 1.12%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5458,23 +5458,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T64" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U64" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>48.69352</v>
+        <v>51.50451</v>
       </c>
       <c r="W64" t="n">
-        <v>-77.96293</v>
+        <v>-67.92737</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2766</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lac Macamic-Ouest</t>
+          <t>Lac Couillard (Secteur A)</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5494,12 +5494,12 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Etr, Y, Zr, La, Dy, Pr, Gd, Sm, Ce, Nd</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Au 5.09 g/t, Cu 3.33%, Ag 12.00 g/t</t>
+          <t>Nd 0.649%, Dy 0.0357%, Pr 0.11%, Ce 1.55%, La 0.2%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5536,23 +5536,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U65" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>48.77553</v>
+        <v>50.30421</v>
       </c>
       <c r="W65" t="n">
-        <v>-79.0604</v>
+        <v>-60.82246</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2717</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4100</t>
         </is>
       </c>
     </row>
@@ -5562,22 +5562,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>La Reine</t>
+          <t>Delta (Northeast)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Copper, Lead</t>
+          <t>Nickel, Egp, Palladium, Platinum, Copper</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="I66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Au 11.00 g/t, Mo 0.52%</t>
+          <t>Ni 3.49%, Pd 1.96 g/t, Pt 0.83 g/t, Cu 0.11%, EGP 0.000279%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>48.77182</v>
+        <v>61.48916</v>
       </c>
       <c r="W66" t="n">
-        <v>-79.33329000000001</v>
+        <v>-74.43673</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2716</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24306</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kerwin</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver</t>
+          <t>Copper, Tungsten</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
+          <t>W 0.188%, Cu 4.08%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5692,23 +5692,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T67" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U67" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>48.39017</v>
+        <v>60.39318</v>
       </c>
       <c r="W67" t="n">
-        <v>-78.41151000000001</v>
+        <v>-75.53694</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>East Mac (Indice Nord)</t>
+          <t>Red Zone</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,12 +5728,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="I68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Au 108.96 g/t, Ag 1480.90 g/t</t>
+          <t>Ni 5.75%, Cu 1.35%, Pd 2.97 g/t, Pt 0.46 g/t, EGP 0.000342%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5770,23 +5770,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T68" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U68" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V68" t="n">
-        <v>48.6126</v>
+        <v>61.35949</v>
       </c>
       <c r="W68" t="n">
-        <v>-77.97836</v>
+        <v>-76.01782</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23971</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Raglan (Zones 5-8)</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Copper, Egp, Palladium, Platinum, Nickel, Cobalt, Gold</t>
+          <t>Copper, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Pd 6.10 g/t, Cu 1.43%, Ni 1.1%, Pt 2.00 g/t, Au 0.74 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5848,23 +5848,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T69" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U69" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V69" t="n">
-        <v>61.69562</v>
+        <v>46.26532</v>
       </c>
       <c r="W69" t="n">
-        <v>-73.57513</v>
+        <v>-71.28788</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1177</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bernierville-WNW</t>
+          <t>Seahawk</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5884,12 +5884,12 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Lead, Silver</t>
+          <t>Egp, Palladium, Platinum, Copper, Nickel</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="I70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Cu 4.96%, Mo 0.2%, Ag 14.50 g/t, Pb 0.31%</t>
+          <t>Ni 4.73%, Cu 1.93%, Pd 3.35 g/t, Pt 0.99 g/t, EGP 0.000434%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5926,23 +5926,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T70" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U70" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V70" t="n">
-        <v>46.11365</v>
+        <v>61.35511</v>
       </c>
       <c r="W70" t="n">
-        <v>-71.60383</v>
+        <v>-76.04816</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3611</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23960</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Albert (LH-90)</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,12 +5962,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Zinc</t>
+          <t>Nickel, Egp, Copper, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Pb 50.6%, Zn 20.5%, Ag 173.70 g/t, Cu 0.53%</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6004,23 +6004,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V71" t="n">
-        <v>48.74517</v>
+        <v>55.58892</v>
       </c>
       <c r="W71" t="n">
-        <v>-66.13224</v>
+        <v>-71.1636</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3389</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lorenz Gully</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,12 +6040,12 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Uranium, Gold, Lead, Vanadium, Silver, Thorium</t>
+          <t>Nickel, Copper, Egp, Cobalt, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="I72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>U 6.05%, Au 1.39 g/t, Ag 14.95 g/t, Pb 0.628%, V 0.0147%</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V72" t="n">
-        <v>52.20987</v>
+        <v>55.61902</v>
       </c>
       <c r="W72" t="n">
-        <v>-71.92959999999999</v>
+        <v>-71.054</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=196</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Golden Rock</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,12 +6118,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum, Nickel, Copper, Egp, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Au 27.23 g/t</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6160,23 +6160,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V73" t="n">
-        <v>48.81681</v>
+        <v>55.5908</v>
       </c>
       <c r="W73" t="n">
-        <v>-78.47028</v>
+        <v>-71.13463</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2694</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cedar Rapids-Zone 1</t>
+          <t>Misery - Sond. ML14024</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,12 +6196,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Zr, Niobium, Tungsten, Etr, Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="I74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 77.80 g/t, Cu 1.45%, Ag 68.60 g/t</t>
+          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6238,23 +6238,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T74" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U74" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V74" t="n">
-        <v>49.0051</v>
+        <v>55.35025</v>
       </c>
       <c r="W74" t="n">
-        <v>-77.04089</v>
+        <v>-63.8991</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3521</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Delta (Zone D-8)</t>
+          <t>Misery - Sond. ML11014</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6274,12 +6274,12 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Gold, Platinum, Palladium, Cobalt</t>
+          <t>Zr, Niobium, Y, Sc, Thorium, Germanium, Beryllium, Tantalum, Gallium, Etr, Silver, Tin, Hf, Lead, Uranium, Fluorite</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Ni 7.8%, Pd 25.50 g/t, Cu 4%, Au 3.63 g/t, Pt 7.96 g/t</t>
+          <t>Ge 0.0097%, U 0.0387%, Ga 0.0216%, Sn 0.0913%, Ag 5.30 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6316,23 +6316,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U75" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V75" t="n">
-        <v>61.48642</v>
+        <v>55.34044</v>
       </c>
       <c r="W75" t="n">
-        <v>-74.46145</v>
+        <v>-63.93963</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3396</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25755</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Echo-1</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6352,12 +6352,12 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Palladium, Egp, Nickel, Copper, Silver, Gold</t>
+          <t>Copper, Egp, Palladium, Platinum, Nickel</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="I76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Ni 2.35%, Cu 2.6%, Co 0.56%, Pd 4.46 g/t, Pt 1.64 g/t</t>
+          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6394,23 +6394,1661 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T76" t="n">
+        <v>325</v>
+      </c>
+      <c r="U76" t="n">
+        <v>55</v>
+      </c>
+      <c r="V76" t="n">
+        <v>61.52449</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-72.77941</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gamache A</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>13</v>
+      </c>
+      <c r="T77" t="n">
+        <v>325</v>
+      </c>
+      <c r="U77" t="n">
+        <v>55</v>
+      </c>
+      <c r="V77" t="n">
+        <v>61.55073</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-72.66555</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>13</v>
+      </c>
+      <c r="T78" t="n">
+        <v>325</v>
+      </c>
+      <c r="U78" t="n">
+        <v>55</v>
+      </c>
+      <c r="V78" t="n">
+        <v>45.03676</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-72.77243</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Devlin (Riocanex)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>16 kt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
         <v>25</v>
       </c>
-      <c r="U76" t="n">
+      <c r="U79" t="n">
+        <v>46</v>
+      </c>
+      <c r="V79" t="n">
+        <v>49.75792</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-74.3342</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Tungsten, Copper</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>29 kt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>25</v>
+      </c>
+      <c r="U80" t="n">
+        <v>46</v>
+      </c>
+      <c r="V80" t="n">
+        <v>48.24607</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-79.50617</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mine Madeleine</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Zinc</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>8.1 Mt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="n">
+        <v>125</v>
+      </c>
+      <c r="U81" t="n">
+        <v>44</v>
+      </c>
+      <c r="V81" t="n">
+        <v>49.01028</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-66.00369999999999</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Hall (et Extension)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>4 kt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>3</v>
+      </c>
+      <c r="T82" t="n">
+        <v>75</v>
+      </c>
+      <c r="U82" t="n">
+        <v>43</v>
+      </c>
+      <c r="V82" t="n">
+        <v>46.04018</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-71.28144</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Galloway (GP)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver, Molybdenum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Au 8.66 g/t, Cu 2%, Ag 4.53 g/t</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>25</v>
+      </c>
+      <c r="U83" t="n">
+        <v>43</v>
+      </c>
+      <c r="V83" t="n">
+        <v>48.19278</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-79.4164</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5189</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sirmac</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lithium, Tantalum, Beryllium, Tin, Tungsten, Niobium</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>25</v>
+      </c>
+      <c r="U84" t="n">
+        <v>43</v>
+      </c>
+      <c r="V84" t="n">
+        <v>50.62206</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-75.47598000000001</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Solbec Copper</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2.1 Mt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>4</v>
+      </c>
+      <c r="T85" t="n">
+        <v>100</v>
+      </c>
+      <c r="U85" t="n">
+        <v>43</v>
+      </c>
+      <c r="V85" t="n">
+        <v>45.80476</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-71.28747</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Lavoie (Zone L)</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lead, Vanadium, Molybdenum, Uranium, Gold, Silver, Thorium</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>25</v>
+      </c>
+      <c r="U86" t="n">
+        <v>43</v>
+      </c>
+      <c r="V86" t="n">
+        <v>52.18408</v>
+      </c>
+      <c r="W86" t="n">
+        <v>-70.99409</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Dieppe PN-157</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Au 26.78 g/t</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>25</v>
+      </c>
+      <c r="U87" t="n">
         <v>39</v>
       </c>
-      <c r="V76" t="n">
-        <v>61.44723</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-74.72001</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3411</t>
+      <c r="V87" t="n">
+        <v>49.54284</v>
+      </c>
+      <c r="W87" t="n">
+        <v>-79.50556</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20755</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Anaconda Brass</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Au 5.10 g/t, Cu 1.29%</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>25</v>
+      </c>
+      <c r="U88" t="n">
+        <v>39</v>
+      </c>
+      <c r="V88" t="n">
+        <v>48.34022</v>
+      </c>
+      <c r="W88" t="n">
+        <v>-78.74214000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5739</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KM 55 (DEC 96-01)</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Au 47.90 g/t</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>25</v>
+      </c>
+      <c r="U89" t="n">
+        <v>39</v>
+      </c>
+      <c r="V89" t="n">
+        <v>49.4978</v>
+      </c>
+      <c r="W89" t="n">
+        <v>-76.98484999999999</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4464</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D'Or Val-Beacon : Connell Plug</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Au 9.48 g/t</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>25</v>
+      </c>
+      <c r="U90" t="n">
+        <v>39</v>
+      </c>
+      <c r="V90" t="n">
+        <v>48.10221</v>
+      </c>
+      <c r="W90" t="n">
+        <v>-77.53959</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2628</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Mine d'Or Val : Beacon No 1</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>3 kt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Au 35.76 g/t</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>25</v>
+      </c>
+      <c r="U91" t="n">
+        <v>39</v>
+      </c>
+      <c r="V91" t="n">
+        <v>48.10636</v>
+      </c>
+      <c r="W91" t="n">
+        <v>-77.54895</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2625</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Lac Macamic-Ouest</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Au 5.09 g/t, Cu 3.33%, Ag 12.00 g/t</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>4</v>
+      </c>
+      <c r="T92" t="n">
+        <v>100</v>
+      </c>
+      <c r="U92" t="n">
+        <v>39</v>
+      </c>
+      <c r="V92" t="n">
+        <v>48.77553</v>
+      </c>
+      <c r="W92" t="n">
+        <v>-79.0604</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2717</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>La Reine</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Gold, Molybdenum, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Au 11.00 g/t, Mo 0.52%</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>25</v>
+      </c>
+      <c r="U93" t="n">
+        <v>39</v>
+      </c>
+      <c r="V93" t="n">
+        <v>48.77182</v>
+      </c>
+      <c r="W93" t="n">
+        <v>-79.33329000000001</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2716</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Golden Rock</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Au 27.23 g/t</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>25</v>
+      </c>
+      <c r="U94" t="n">
+        <v>39</v>
+      </c>
+      <c r="V94" t="n">
+        <v>48.81681</v>
+      </c>
+      <c r="W94" t="n">
+        <v>-78.47028</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2694</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Raglan (Zones 5-8)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Platinum, Nickel, Copper, Egp, Palladium, Gold, Cobalt</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Pd 6.10 g/t, Cu 1.43%, Ni 1.1%, Pt 2.00 g/t, Au 0.74 g/t</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>2</v>
+      </c>
+      <c r="T95" t="n">
+        <v>50</v>
+      </c>
+      <c r="U95" t="n">
+        <v>39</v>
+      </c>
+      <c r="V95" t="n">
+        <v>61.69562</v>
+      </c>
+      <c r="W95" t="n">
+        <v>-73.57513</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1177</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Orco-Tranchée 35-2</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Silver, Zinc, Gold, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Au 15.57 g/t, Ag 82.60 g/t, Zn 1%</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>25</v>
+      </c>
+      <c r="U96" t="n">
+        <v>39</v>
+      </c>
+      <c r="V96" t="n">
+        <v>48.42459</v>
+      </c>
+      <c r="W96" t="n">
+        <v>-78.74975999999999</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5730</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Bolt</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Copper, Nickel, Silver</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I97" t="b">
+        <v>0</v>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Cu 2.9%, Ni 0.261%, Ag 17.40 g/t</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>4</v>
+      </c>
+      <c r="T97" t="n">
+        <v>100</v>
+      </c>
+      <c r="U97" t="n">
+        <v>39</v>
+      </c>
+      <c r="V97" t="n">
+        <v>61.57527</v>
+      </c>
+      <c r="W97" t="n">
+        <v>-74.46583</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26280</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X97"/>
+  <dimension ref="A1:X114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RA13-03</t>
+          <t>Sond. SER-21-040</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 3.71 g/t</t>
+          <t>Au 8.71 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>53.1949</v>
+        <v>53.08409</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.66768999999999</v>
+        <v>-77.20562</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20539</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67301</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RA13-02</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 4.67 g/t, Ag 9.80 g/t</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>53.17502</v>
+        <v>48.31932</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.75697</v>
+        <v>-64.9713</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20536</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -804,22 +804,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lidge</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Arsenic</t>
+          <t>Copper, Molybdenum, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -856,23 +856,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>52.21818</v>
+        <v>45.99171</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.45902</v>
+        <v>-71.70617</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cancet</t>
+          <t>Sond. DDH-20-2023</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lithium, Tantalum, Beryllium, Cs, Bismuth, Niobium, Zinc, Lead, Gallium, Rb, Silver, Cobalt, Chromium, Nickel</t>
+          <t>Copper, Iron, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Li 1.92%, Bi 0.14%, Zn 1.38%, Ga 0.0134%, Ni 0.166%</t>
+          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>53.49988</v>
+        <v>46.36809</v>
       </c>
       <c r="W6" t="n">
-        <v>-74.90752999999999</v>
+        <v>-73.97731</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=156</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sond. PLP24-019</t>
+          <t>Mine Renzy</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,17 +970,17 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Bismuth</t>
+          <t>Platinum, Palladium, Copper, Nickel, Egp, Silver, Gold, Chromium, Cobalt</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -991,12 +991,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>766 kt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 4.76 g/t, Bi 0.1%</t>
+          <t>Ni 2.3%, Cu 1.75%, Co 0.11%, Pt 0.66 g/t, Pd 0.53 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>52.59612</v>
+        <v>46.81194</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.37366</v>
+        <v>-76.70332999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4560</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nasigon (Lac Lajoue)</t>
+          <t>B-88-01</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 9.21%, Ag 100.00 g/t, Au 0.88 g/t</t>
+          <t>Ag 203.00 g/t, Cu 1.56%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>47.53875</v>
+        <v>45.52488</v>
       </c>
       <c r="W8" t="n">
-        <v>-75.10978</v>
+        <v>-72.07191</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20138</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lac Nasigon</t>
+          <t>Delhi Pacific</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 4.4%, Ag 96.30 g/t</t>
+          <t>Cu 7.36%, Ag 24.90 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>47.53085</v>
+        <v>56.40258</v>
       </c>
       <c r="W9" t="n">
-        <v>-75.11848000000001</v>
+        <v>-67.9023</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20134</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Rochelom</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
+          <t>Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>49.83681</v>
+        <v>49.77064</v>
       </c>
       <c r="W10" t="n">
-        <v>-70.57877999999999</v>
+        <v>-76.01858</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Galexis</t>
+          <t>Lac Rivon-Ouest</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Zinc, Molybdenum, Silver, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
+          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>53.48752</v>
+        <v>51.72313</v>
       </c>
       <c r="W11" t="n">
-        <v>-75.33392000000001</v>
+        <v>-72.79697</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Perseus</t>
+          <t>Riv. Cheno-Ouest</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Egp, Platinum, Gold, Nickel, Palladium, Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ni 8.42%, Cu 9.35%, Au 1.83 g/t, Pd 5.83 g/t, Pt 1.42 g/t</t>
+          <t>U 1.2%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>53.65127</v>
+        <v>51.53813</v>
       </c>
       <c r="W12" t="n">
-        <v>-75.87454</v>
+        <v>-72.67167999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67054</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4564</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sond. K2-22-10</t>
+          <t>Goshawk</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Zinc</t>
+          <t>Gold, Lead, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 3.64 g/t, Zn 0.55%</t>
+          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>52.28963</v>
+        <v>61.56992</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78149999999999</v>
+        <v>-75.20258</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>Ganiq</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Lead, Uranium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>U 0.77%, Cu 0.52%, Pb 0.82%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>53.43724</v>
+        <v>53.7831</v>
       </c>
       <c r="W14" t="n">
-        <v>-75.04334</v>
+        <v>-75.64593000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4528</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Barre de fer</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 144.55 g/t</t>
+          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>53.52019</v>
+        <v>51.6436</v>
       </c>
       <c r="W15" t="n">
-        <v>-75.40980999999999</v>
+        <v>-67.33749</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Boulder Shear (Cuvier-Est)</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Gold, Zinc, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>49.82919</v>
+        <v>49.9399</v>
       </c>
       <c r="W16" t="n">
-        <v>-70.58076</v>
+        <v>-74.70344</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Lac Barlow</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 12.91 g/t</t>
+          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>53.51022</v>
+        <v>49.94431</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.46174000000001</v>
+        <v>-74.71456000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Lac Chicobi-2</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Cobalt, Tungsten, Tellurium, Arsenic</t>
+          <t>Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Ag 932.70 g/t, Pb 19.2%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>59.80634</v>
+        <v>48.83881</v>
       </c>
       <c r="W18" t="n">
-        <v>-75.01831</v>
+        <v>-78.52331</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4194</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Baleine Rouge Au-Zn-Pb</t>
+          <t>Propriété Authier</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
+          <t>Au 173.90 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>55.23561</v>
+        <v>48.89617</v>
       </c>
       <c r="W19" t="n">
-        <v>-67.9516</v>
+        <v>-78.78440000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4201</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Leadville</t>
+          <t>Bouchette</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Zn 31.4%, Ag 95.98 g/t, Pb 4.94%</t>
+          <t>Zn 32.8%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2026,23 +2026,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U20" t="n">
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.00863</v>
+        <v>46.26106</v>
       </c>
       <c r="W20" t="n">
-        <v>-72.26421000000001</v>
+        <v>-75.97745999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4394</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4050</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Falaises</t>
+          <t>D-91-01 (Option Dejour)</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zr, Thorium, Ce, La, Nd, Etr, Y</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Nd 0.354%, Ce 0.954%, La 0.368%, ETR 3.24%, Th 0.0831%</t>
+          <t>Au 4.35 g/t, Ag 6.90 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>46.80195</v>
+        <v>49.02527</v>
       </c>
       <c r="W21" t="n">
-        <v>-78.43706</v>
+        <v>-78.38705</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=18960</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4045</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rob Ex</t>
+          <t>Gold Fields</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Tungsten, Silver, Manganese</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 15.30 g/t, W 0.15%, Ag 2.65 g/t, Mn 0.258%</t>
+          <t>Au 19.04 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2182,23 +2182,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>52.70232</v>
+        <v>49.09287</v>
       </c>
       <c r="W22" t="n">
-        <v>-76.05212</v>
+        <v>-78.42254</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=18709</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4044</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fortin (GH)</t>
+          <t>Gauthier-Mcneely</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Antimony, Arsenic</t>
+          <t>Zinc, Copper, Silver, Nickel</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sb 24.2%, Au 8.26 g/t, As 0.361%</t>
+          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>52.08795</v>
+        <v>55.62931</v>
       </c>
       <c r="W23" t="n">
-        <v>-75.39556</v>
+        <v>-66.83314</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=15915</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mine Capelton (Albert)</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,17 +2296,17 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Gold, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>300 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>45.32298</v>
+        <v>55.2524</v>
       </c>
       <c r="W24" t="n">
-        <v>-71.90649999999999</v>
+        <v>-67.95193</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mine Suffield</t>
+          <t>Lac du Canoe</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,17 +2374,17 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Silver, Lead, Gold, Zinc, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>850 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 644.80 g/t, Zn 29.6%, Au 7.20 g/t, Cu 6.2%, Pb 3.68%</t>
+          <t>Au 40.00 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>45.31892</v>
+        <v>55.23434</v>
       </c>
       <c r="W25" t="n">
-        <v>-71.95913</v>
+        <v>-67.62649</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Raglan (Lac Cross Est, zones C-1 et C-2)</t>
+          <t>G-H-2-79 (Hudbay Mining)</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Gold, Palladium, Platinum</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ni 2.33%, Au 2.00 g/t, Cu 1.24%, Pd 2.26 g/t, Pt 0.86 g/t</t>
+          <t>Cu 3.26%, Ni 1.12%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>61.5996</v>
+        <v>51.50451</v>
       </c>
       <c r="W26" t="n">
-        <v>-74.24052</v>
+        <v>-67.92737</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3851</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Raglan (Lac Cross Ouest)</t>
+          <t>Lac Couillard (Secteur A)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Palladium, Platinum, Copper</t>
+          <t>Zr, Y, Etr, Ce, Sm, Nd, La, Dy, Gd, Pr</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Pd 4.81 g/t, Cu 0.979%, Pt 1.26 g/t, EGP 0.00055%</t>
+          <t>Nd 0.649%, Dy 0.0357%, Pr 0.11%, Ce 1.55%, La 0.2%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>61.59527</v>
+        <v>50.30421</v>
       </c>
       <c r="W27" t="n">
-        <v>-74.28905</v>
+        <v>-60.82246</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3850</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4100</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ouf</t>
+          <t>CaribGold 99-07</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver</t>
+          <t>Bismuth, Gold, Palladium, Platinum, Egp, Nickel, Zinc, Chromium, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Ag 204.00 g/t, Zn 8.7%, Pb 1.6%</t>
+          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>53.90478</v>
+        <v>50.75408</v>
       </c>
       <c r="W28" t="n">
-        <v>-74.69878</v>
+        <v>-76.84898</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3841</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mine Aldermac Moulton Hill</t>
+          <t>AT-32-91</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,17 +2686,17 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Gold, Silver, Barium, Cadmium, Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>871 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
+          <t>Au 5.09 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T29" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U29" t="n">
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>45.40941</v>
+        <v>48.89509</v>
       </c>
       <c r="W29" t="n">
-        <v>-71.81791</v>
+        <v>-78.79843</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rambull</t>
+          <t>Site-1429-02</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
+          <t>Zn 22.4%, Pb 19.4%, Au 1.25 g/t, Cu 0.0405%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2806,23 +2806,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>48.4824</v>
+        <v>50.85765</v>
       </c>
       <c r="W30" t="n">
-        <v>-78.10243</v>
+        <v>-76.48296999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4232</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rivière Pontois</t>
+          <t>H-1429-046</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Arsenic</t>
+          <t>Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
+          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>53.51426</v>
+        <v>50.85296</v>
       </c>
       <c r="W31" t="n">
-        <v>-74.51608</v>
+        <v>-76.47398</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sond. LGS09-217</t>
+          <t>H-1451-032</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 2.76%, Au 2.19 g/t, Ag 14.70 g/t</t>
+          <t>Au 2.20 g/t, Cu 0.66%, Zn 1.59%, Ag 21.80 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>53.528</v>
+        <v>50.79734</v>
       </c>
       <c r="W32" t="n">
-        <v>-76.54774999999999</v>
+        <v>-76.70574000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20066</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4242</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac Beaver Zoran</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Vanadium, Lead, Zinc, Uranium, Barium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>U 2.09%, V 0.91%, Zn 1.02%, Pb 1.32%, Ba 41.2%</t>
+          <t>Au 26.78 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>51.98869</v>
+        <v>50.8534</v>
       </c>
       <c r="W33" t="n">
-        <v>-72.37778</v>
+        <v>-76.53675</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4397</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4238</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Au 5.00 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>49.59836</v>
+        <v>50.8451</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.92194000000001</v>
+        <v>-76.45574000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4236</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Bloc Est</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Au 83.00 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>49.63941</v>
+        <v>50.84188</v>
       </c>
       <c r="W35" t="n">
-        <v>-76.90893</v>
+        <v>-76.39422</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4235</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dessureault (Lac Rougemont)</t>
+          <t>Noramco Broadback Zone (H-1451-009)</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
+          <t>Zn 15.3%, Cu 1.8%, Ag 68.21 g/t, Pb 0.445%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>58.02817</v>
+        <v>50.78641</v>
       </c>
       <c r="W36" t="n">
-        <v>-69.57268000000001</v>
+        <v>-76.75020000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4239</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Venditelli (Lac St-Pierre-Gold)</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Egp</t>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>58.15377</v>
+        <v>59.80634</v>
       </c>
       <c r="W37" t="n">
-        <v>-69.53443</v>
+        <v>-75.01831</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fort Chimo (Lac Plissé)</t>
+          <t>Leadville</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Nickel, Silver</t>
+          <t>Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
+          <t>Zn 31.4%, Ag 95.98 g/t, Pb 4.94%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>58.12861</v>
+        <v>45.00863</v>
       </c>
       <c r="W38" t="n">
-        <v>-69.55745</v>
+        <v>-72.26421000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4394</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Erickson Sud - Goose Pond</t>
+          <t>H-1456-009</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Palladium, Gold, Platinum, Cobalt</t>
+          <t>Gold, Arsenic, Copper, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
+          <t>Au 8.47 g/t, Cu 0.303%, Ag 9.60 g/t, As 0.565%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>57.99255</v>
+        <v>50.62126</v>
       </c>
       <c r="W39" t="n">
-        <v>-69.72347000000001</v>
+        <v>-77.35012</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4342</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>St-Sylvestre-Noranda</t>
+          <t>Mine Suffield</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,17 +3544,17 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead, Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>850 kt</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Zn 15.2%</t>
+          <t>Ag 644.80 g/t, Zn 29.6%, Au 7.20 g/t, Cu 6.2%, Pb 3.68%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>46.32835</v>
+        <v>45.31892</v>
       </c>
       <c r="W40" t="n">
-        <v>-71.13679999999999</v>
+        <v>-71.95913</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1218</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4356</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Mine Aldermac Moulton Hill</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Molybdenum, Cadmium, Barium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>871 kt</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,23 +3664,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T41" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U41" t="n">
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>46.27176</v>
+        <v>45.40941</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.28612</v>
+        <v>-71.81791</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill</t>
+          <t>Mine Capelton (Albert)</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium, Molybdenum, Gold</t>
+          <t>Zinc, Copper, Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>453 kt</t>
+          <t>300 kt</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
+          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3742,23 +3742,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>46.26423</v>
+        <v>45.32298</v>
       </c>
       <c r="W42" t="n">
-        <v>-71.20608</v>
+        <v>-71.90649999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Lac Beaver Zoran</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Nickel, Chromium, Zinc</t>
+          <t>Uranium, Zinc, Lead, Vanadium, Barium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>U 2.09%, V 0.91%, Zn 1.02%, Pb 1.32%, Ba 41.2%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>46.26109</v>
+        <v>51.98869</v>
       </c>
       <c r="W43" t="n">
-        <v>-71.22866</v>
+        <v>-72.37778</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4397</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Lac De Maurès-Est</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Zinc, Molybdenum</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 12.6%, Au 5.79 g/t, Ag 50.00 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>46.26265</v>
+        <v>50.65811</v>
       </c>
       <c r="W44" t="n">
-        <v>-71.21769</v>
+        <v>-74.36593999999999</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4292</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Copper, Nickel, Egp, Palladium, Platinum, Cobalt, Silver, Gold</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>49.84595</v>
+        <v>58.96701</v>
       </c>
       <c r="W45" t="n">
-        <v>-70.57626</v>
+        <v>-69.59563</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt, Egp, Palladium</t>
+          <t>Palladium, Nickel, Copper, Egp, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>58.23464</v>
+        <v>60.16686</v>
       </c>
       <c r="W46" t="n">
-        <v>-69.92364000000001</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PAP Nord (Camp A-1)</t>
+          <t>Qarqasiaq - C</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver, Tungsten</t>
+          <t>Nickel, Egp, Palladium, Platinum, Copper, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
+          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>60.2779</v>
+        <v>60.17776</v>
       </c>
       <c r="W47" t="n">
-        <v>-75.33311</v>
+        <v>-70.30297</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Reboul : Centre-Ouest</t>
+          <t>Franelle</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Gold, Copper, Antimony</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Zn 15.4%, Ag 230.00 g/t, Au 1.42 g/t, Pb 2.94%, Cu 0.372%</t>
+          <t>Cu 60%, Ag 43.49 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>48.37247</v>
+        <v>55.55824</v>
       </c>
       <c r="W48" t="n">
-        <v>-65.44429</v>
+        <v>-67.34804</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1161</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Filon Baker (Lac Arseneault)</t>
+          <t>Lac Odon</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Gold, Copper</t>
+          <t>Gold, Molybdenum, Copper, Silver</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
+          <t>Au 19.20 g/t, Cu 3.51%, Mo 0.96%, Ag 8.40 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>48.37895</v>
+        <v>50.68338</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.22886</v>
+        <v>-74.36037</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4293</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lac Anticline</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Egp, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Ag 444.50 g/t, Ni 0.31%, Cu 0.271%, EGP 2.28e-05%, Zn 0.217%</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>55.25152</v>
+        <v>45.03676</v>
       </c>
       <c r="W50" t="n">
-        <v>-66.30022</v>
+        <v>-72.77243</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1153</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -4392,22 +4392,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium</t>
+          <t>Nickel, Egp, Copper, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4444,23 +4444,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>46.265</v>
+        <v>55.58892</v>
       </c>
       <c r="W51" t="n">
-        <v>-71.21259999999999</v>
+        <v>-71.1636</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OTS-08</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Zinc, Uranium, Silver</t>
+          <t>Nickel, Copper, Egp, Platinum, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4522,23 +4522,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U52" t="n">
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>51.78509</v>
+        <v>55.61902</v>
       </c>
       <c r="W52" t="n">
-        <v>-71.96465999999999</v>
+        <v>-71.054</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -4548,22 +4548,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Lead, Gold</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>48.37403</v>
+        <v>55.5908</v>
       </c>
       <c r="W53" t="n">
-        <v>-65.44089</v>
+        <v>-71.13463</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 21.70 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>57.94973</v>
+        <v>49.84595</v>
       </c>
       <c r="W54" t="n">
-        <v>-69.51281</v>
+        <v>-70.57626</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -4704,11 +4704,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Monarch - Veine 1</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Au 83.00 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>52.03235</v>
+        <v>48.23207</v>
       </c>
       <c r="W55" t="n">
-        <v>-69.13816</v>
+        <v>-79.41287</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kupfer : Mine Val-St-Gilles</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold</t>
+          <t>Nickel, Copper, Egp, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cu 7.96%, Ag 89.15 g/t, Zn 2.66%, Au 0.34 g/t</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>48.97156</v>
+        <v>55.68696</v>
       </c>
       <c r="W56" t="n">
-        <v>-79.08714999999999</v>
+        <v>-71.02212</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Val-St-Gilles-SE</t>
+          <t>Lac Harris</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4870,12 +4870,12 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Cu 7.88%, Ag 87.00 g/t, Au 1.06 g/t</t>
+          <t>Cu 5.07%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4921,14 +4921,14 @@
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>48.97212</v>
+        <v>47.68996</v>
       </c>
       <c r="W57" t="n">
-        <v>-79.1088</v>
+        <v>-76.66074999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2703</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Val-St-Gilles SO</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,12 +4948,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Lead, Gold, Copper</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Au 8.34 g/t, Zn 5.2%, Pb 9.9%, Ag 61.90 g/t</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>48.96826</v>
+        <v>53.56991</v>
       </c>
       <c r="W58" t="n">
-        <v>-79.19454</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2702</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Century</t>
+          <t>Lac Lyster</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,12 +5026,12 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Copper, Egp, Palladium, Nickel, Platinum</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Ni 15.5%, Cu 3.16%, Pd 1.22 g/t, Pt 0.36 g/t, EGP 0.00013%</t>
+          <t>W 2.93%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>61.35448</v>
+        <v>45.03295</v>
       </c>
       <c r="W59" t="n">
-        <v>-76.06304</v>
+        <v>-71.89901999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23835</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4847</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lac Nitakwin</t>
+          <t>Sainte-Cécile (Maheu) - ancien</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5104,12 +5104,12 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth, Lead, Zinc, Silver, Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Au 6.06 g/t</t>
+          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>52.1766</v>
+        <v>45.67446</v>
       </c>
       <c r="W60" t="n">
-        <v>-76.71138999999999</v>
+        <v>-70.96669</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mustang</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,12 +5182,12 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Zinc, Barium, Mercury, Cadmium</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
+          <t>Zn 31.5%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T61" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U61" t="n">
         <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>52.17024</v>
+        <v>46.11447</v>
       </c>
       <c r="W61" t="n">
-        <v>-76.57532999999999</v>
+        <v>-75.95323</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Mont Opémiska No 1</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
+          <t>Zinc, Copper, Gold, Lead, Silver</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5311,14 +5311,14 @@
         <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>55.68696</v>
+        <v>49.95224</v>
       </c>
       <c r="W62" t="n">
-        <v>-71.02212</v>
+        <v>-74.8797</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Spirit-1</t>
+          <t>Lac Dunphy</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
+          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5389,14 +5389,14 @@
         <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>61.39663</v>
+        <v>56.05097</v>
       </c>
       <c r="W63" t="n">
-        <v>-73.13239</v>
+        <v>-67.71257</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>G-H-2-79 (Hudbay Mining)</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Cu 3.26%, Ni 1.12%</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5467,14 +5467,14 @@
         <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>51.50451</v>
+        <v>49.59836</v>
       </c>
       <c r="W64" t="n">
-        <v>-67.92737</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lac Couillard (Secteur A)</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5494,12 +5494,12 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Etr, Y, Zr, La, Dy, Pr, Gd, Sm, Ce, Nd</t>
+          <t>Copper, Nickel, Iron</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Nd 0.649%, Dy 0.0357%, Pr 0.11%, Ce 1.55%, La 0.2%</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5545,14 +5545,14 @@
         <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>50.30421</v>
+        <v>49.63941</v>
       </c>
       <c r="W65" t="n">
-        <v>-60.82246</v>
+        <v>-76.90893</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4100</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -5562,22 +5562,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Delta (Northeast)</t>
+          <t>Chibtown</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Palladium, Platinum, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Ni 3.49%, Pd 1.96 g/t, Pt 0.83 g/t, Cu 0.11%, EGP 0.000279%</t>
+          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5623,14 +5623,14 @@
         <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>61.48916</v>
+        <v>56.39152</v>
       </c>
       <c r="W66" t="n">
-        <v>-74.43673</v>
+        <v>-67.87103</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24306</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Tungsten</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>W 0.188%, Cu 4.08%</t>
+          <t>Au 29.25 g/t, W 0.122%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5701,14 +5701,14 @@
         <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>60.39318</v>
+        <v>52.64108</v>
       </c>
       <c r="W67" t="n">
-        <v>-75.53694</v>
+        <v>-75.67010999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Red Zone</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Ni 5.75%, Cu 1.35%, Pd 2.97 g/t, Pt 0.46 g/t, EGP 0.000342%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5779,14 +5779,14 @@
         <v>55</v>
       </c>
       <c r="V68" t="n">
-        <v>61.35949</v>
+        <v>49.82919</v>
       </c>
       <c r="W68" t="n">
-        <v>-76.01782</v>
+        <v>-70.58076</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23971</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5806,12 +5806,12 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Nickel, Copper, Cobalt, Platinum, Palladium, Egp</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5857,14 +5857,14 @@
         <v>55</v>
       </c>
       <c r="V69" t="n">
-        <v>46.26532</v>
+        <v>49.83681</v>
       </c>
       <c r="W69" t="n">
-        <v>-71.28788</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Seahawk</t>
+          <t>Chalifour-1</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5884,12 +5884,12 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Egp, Palladium, Platinum, Copper, Nickel</t>
+          <t>Zinc, Lead, Silver, Copper</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Ni 4.73%, Cu 1.93%, Pd 3.35 g/t, Pt 0.99 g/t, EGP 0.000434%</t>
+          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5926,23 +5926,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T70" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U70" t="n">
         <v>55</v>
       </c>
       <c r="V70" t="n">
-        <v>61.35511</v>
+        <v>50.3781</v>
       </c>
       <c r="W70" t="n">
-        <v>-76.04816</v>
+        <v>-73.70041000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23960</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,12 +5962,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Copper, Palladium, Platinum</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>55</v>
       </c>
       <c r="V71" t="n">
-        <v>55.58892</v>
+        <v>52.20175</v>
       </c>
       <c r="W71" t="n">
-        <v>-71.1636</v>
+        <v>-70.89798</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Lac du Castor</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,12 +6040,12 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Cobalt, Palladium, Platinum</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>U 0.328%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6091,14 +6091,14 @@
         <v>55</v>
       </c>
       <c r="V72" t="n">
-        <v>55.61902</v>
+        <v>52.2149</v>
       </c>
       <c r="W72" t="n">
-        <v>-71.054</v>
+        <v>-70.93367000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>St-Armand (Phillipsburg-Est)</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,12 +6118,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Platinum, Nickel, Copper, Egp, Palladium, Cobalt</t>
+          <t>Uranium, Zinc</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>U 0.578%, Zn 0.0798%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>55</v>
       </c>
       <c r="V73" t="n">
-        <v>55.5908</v>
+        <v>45.02084</v>
       </c>
       <c r="W73" t="n">
-        <v>-71.13463</v>
+        <v>-73.0196</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Misery - Sond. ML14024</t>
+          <t>Robidoux-appalaches</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,12 +6196,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Zr, Niobium, Tungsten, Etr, Silver</t>
+          <t>Lead, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
+          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6247,14 +6247,14 @@
         <v>55</v>
       </c>
       <c r="V74" t="n">
-        <v>55.35025</v>
+        <v>48.35381</v>
       </c>
       <c r="W74" t="n">
-        <v>-63.8991</v>
+        <v>-65.56434</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Misery - Sond. ML11014</t>
+          <t>Gémini - A Nord</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6274,12 +6274,12 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Zr, Niobium, Y, Sc, Thorium, Germanium, Beryllium, Tantalum, Gallium, Etr, Silver, Tin, Hf, Lead, Uranium, Fluorite</t>
+          <t>Zinc, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Ge 0.0097%, U 0.0387%, Ga 0.0216%, Sn 0.0913%, Ag 5.30 g/t</t>
+          <t>Cu 6.37%, Au 2.68 g/t, Zn 8.1%, Ag 5.06 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6325,14 +6325,14 @@
         <v>55</v>
       </c>
       <c r="V75" t="n">
-        <v>55.34044</v>
+        <v>49.43645</v>
       </c>
       <c r="W75" t="n">
-        <v>-63.93963</v>
+        <v>-79.26394999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25755</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4009</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Copper, Egp, Palladium, Platinum, Nickel</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6394,23 +6394,23 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U76" t="n">
         <v>55</v>
       </c>
       <c r="V76" t="n">
-        <v>61.52449</v>
+        <v>48.57696</v>
       </c>
       <c r="W76" t="n">
-        <v>-72.77941</v>
+        <v>-78.14164</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Harriman-1 (New Richmond-1)</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6430,12 +6430,12 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
+          <t>Antimony, Gold, Silver</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Sb 43.8%, Au 13.70 g/t, Ag 4.50 g/t</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6481,14 +6481,14 @@
         <v>55</v>
       </c>
       <c r="V77" t="n">
-        <v>61.55073</v>
+        <v>48.24307</v>
       </c>
       <c r="W77" t="n">
-        <v>-72.66555</v>
+        <v>-65.79867</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3578</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Sond. Umex 132</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 4%, Zn 6%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6559,14 +6559,14 @@
         <v>55</v>
       </c>
       <c r="V78" t="n">
-        <v>45.03676</v>
+        <v>49.79699</v>
       </c>
       <c r="W78" t="n">
-        <v>-72.77243</v>
+        <v>-75.81529</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Umex-2</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6586,33 +6586,33 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6628,23 +6628,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T79" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="U79" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="V79" t="n">
-        <v>49.75792</v>
+        <v>49.81674</v>
       </c>
       <c r="W79" t="n">
-        <v>-74.3342</v>
+        <v>-75.52503</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
+          <t>Amaruk</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -6669,28 +6669,28 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>29 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
+          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,23 +6706,23 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T80" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="V80" t="n">
-        <v>48.24607</v>
+        <v>59.60263</v>
       </c>
       <c r="W80" t="n">
-        <v>-79.50617</v>
+        <v>-74.86282</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Pointe-Aux-Gossans-2</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6742,33 +6742,33 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc</t>
+          <t>Gold, Copper, Silver, Tungsten, Tin, Bismuth</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>W 1.03%, Au 27.43 g/t, Cu 2.56%, Ag 90.00 g/t, Sn 0.34%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6784,23 +6784,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T81" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="V81" t="n">
-        <v>49.01028</v>
+        <v>59.77961</v>
       </c>
       <c r="W81" t="n">
-        <v>-66.00369999999999</v>
+        <v>-74.98016</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1854</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -6820,12 +6820,12 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
+          <t>Gold, Copper, Tungsten, Silver</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>29 kt</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6862,23 +6862,23 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U82" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V82" t="n">
-        <v>46.04018</v>
+        <v>48.24607</v>
       </c>
       <c r="W82" t="n">
-        <v>-71.28144</v>
+        <v>-79.50617</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Galloway (GP)</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -6898,12 +6898,12 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Molybdenum</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>16 kt</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Au 8.66 g/t, Cu 2%, Ag 4.53 g/t</t>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6946,17 +6946,17 @@
         <v>25</v>
       </c>
       <c r="U83" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V83" t="n">
-        <v>48.19278</v>
+        <v>49.75792</v>
       </c>
       <c r="W83" t="n">
-        <v>-79.4164</v>
+        <v>-74.3342</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5189</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sirmac</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -6976,17 +6976,17 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lithium, Tantalum, Beryllium, Tin, Tungsten, Niobium</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7018,23 +7018,23 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T84" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U84" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V84" t="n">
-        <v>50.62206</v>
+        <v>49.01028</v>
       </c>
       <c r="W84" t="n">
-        <v>-75.47598000000001</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -7054,12 +7054,12 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
+          <t>Copper, Silver, Lead, Cadmium, Gold, Zinc, Cs</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7096,10 +7096,10 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T85" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U85" t="n">
         <v>43</v>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Galloway (GP)</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -7132,12 +7132,12 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lead, Vanadium, Molybdenum, Uranium, Gold, Silver, Thorium</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>Au 8.66 g/t, Cu 2%, Ag 4.53 g/t</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7183,14 +7183,14 @@
         <v>43</v>
       </c>
       <c r="V86" t="n">
-        <v>52.18408</v>
+        <v>48.19278</v>
       </c>
       <c r="W86" t="n">
-        <v>-70.99409</v>
+        <v>-79.4164</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5189</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dieppe PN-157</t>
+          <t>Lavoie (Zone L)</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -7210,17 +7210,17 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium, Lead, Gold, Uranium, Molybdenum, Silver, Thorium</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Au 26.78 g/t</t>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7258,17 +7258,17 @@
         <v>25</v>
       </c>
       <c r="U87" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V87" t="n">
-        <v>49.54284</v>
+        <v>52.18408</v>
       </c>
       <c r="W87" t="n">
-        <v>-79.50556</v>
+        <v>-70.99409</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20755</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Anaconda Brass</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -7288,17 +7288,17 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Nickel, Rh, Platinum, Egp, Chromium, Palladium</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Au 5.10 g/t, Cu 1.29%</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7330,23 +7330,23 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T88" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U88" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V88" t="n">
-        <v>48.34022</v>
+        <v>46.04018</v>
       </c>
       <c r="W88" t="n">
-        <v>-78.74214000000001</v>
+        <v>-71.28144</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5739</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KM 55 (DEC 96-01)</t>
+          <t>Sirmac</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -7366,17 +7366,17 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten, Tin, Beryllium, Tantalum, Lithium, Niobium</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Au 47.90 g/t</t>
+          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7414,17 +7414,17 @@
         <v>25</v>
       </c>
       <c r="U89" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V89" t="n">
-        <v>49.4978</v>
+        <v>50.62206</v>
       </c>
       <c r="W89" t="n">
-        <v>-76.98484999999999</v>
+        <v>-75.47598000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4464</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
         </is>
       </c>
     </row>
@@ -7434,11 +7434,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>D'Or Val-Beacon : Connell Plug</t>
+          <t>KM 55 (DEC 96-01)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 9.48 g/t</t>
+          <t>Au 47.90 g/t</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7495,14 +7495,14 @@
         <v>39</v>
       </c>
       <c r="V90" t="n">
-        <v>48.10221</v>
+        <v>49.4978</v>
       </c>
       <c r="W90" t="n">
-        <v>-77.53959</v>
+        <v>-76.98484999999999</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2628</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4464</t>
         </is>
       </c>
     </row>
@@ -7512,11 +7512,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mine d'Or Val : Beacon No 1</t>
+          <t>Lac Authier-Est (Tut)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>3 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Au 35.76 g/t</t>
+          <t>Au 29.00 g/t</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7573,14 +7573,14 @@
         <v>39</v>
       </c>
       <c r="V91" t="n">
-        <v>48.10636</v>
+        <v>48.96913</v>
       </c>
       <c r="W91" t="n">
-        <v>-77.54895</v>
+        <v>-78.54470000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2625</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4191</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lac Macamic-Ouest</t>
+          <t>Copperstream-Ouest</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -7600,12 +7600,12 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Au 5.09 g/t, Cu 3.33%, Ag 12.00 g/t</t>
+          <t>Au 8.96 g/t</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7642,23 +7642,23 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U92" t="n">
         <v>39</v>
       </c>
       <c r="V92" t="n">
-        <v>48.77553</v>
+        <v>48.48146</v>
       </c>
       <c r="W92" t="n">
-        <v>-79.0604</v>
+        <v>-78.14755</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2717</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1541</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>La Reine</t>
+          <t>Kerwin</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -7678,12 +7678,12 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Copper, Lead</t>
+          <t>Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Au 11.00 g/t, Mo 0.52%</t>
+          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7720,23 +7720,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T93" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U93" t="n">
         <v>39</v>
       </c>
       <c r="V93" t="n">
-        <v>48.77182</v>
+        <v>48.39017</v>
       </c>
       <c r="W93" t="n">
-        <v>-79.33329000000001</v>
+        <v>-78.41151000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2716</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Golden Rock</t>
+          <t>Rambull</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Au 27.23 g/t</t>
+          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7798,23 +7798,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T94" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U94" t="n">
         <v>39</v>
       </c>
       <c r="V94" t="n">
-        <v>48.81681</v>
+        <v>48.4824</v>
       </c>
       <c r="W94" t="n">
-        <v>-78.47028</v>
+        <v>-78.10243</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2694</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Raglan (Zones 5-8)</t>
+          <t>Stoke 22-V</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -7834,12 +7834,12 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Platinum, Nickel, Copper, Egp, Palladium, Gold, Cobalt</t>
+          <t>Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Pd 6.10 g/t, Cu 1.43%, Ni 1.1%, Pt 2.00 g/t, Au 0.74 g/t</t>
+          <t>Cu 7.14%, Ag 22.60 g/t, Pb 0.015%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7876,23 +7876,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U95" t="n">
         <v>39</v>
       </c>
       <c r="V95" t="n">
-        <v>61.69562</v>
+        <v>45.47913</v>
       </c>
       <c r="W95" t="n">
-        <v>-73.57513</v>
+        <v>-71.79196</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1177</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4350</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Orco-Tranchée 35-2</t>
+          <t>Pio - Zone Du Synclinal</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -7912,12 +7912,12 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Gold, Copper, Lead</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Gold, Silver</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Au 15.57 g/t, Ag 82.60 g/t, Zn 1%</t>
+          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7954,23 +7954,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U96" t="n">
         <v>39</v>
       </c>
       <c r="V96" t="n">
-        <v>48.42459</v>
+        <v>58.99163</v>
       </c>
       <c r="W96" t="n">
-        <v>-78.74975999999999</v>
+        <v>-69.61172000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5730</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bolt</t>
+          <t>Fayolle (Renault)</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -7990,12 +7990,12 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Silver</t>
+          <t>Gold, Copper, Molybdenum, Lead</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Cu 2.9%, Ni 0.261%, Ag 17.40 g/t</t>
+          <t>Au 6.68 g/t, Cu 3.9%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8032,23 +8032,1349 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U97" t="n">
         <v>39</v>
       </c>
       <c r="V97" t="n">
-        <v>61.57527</v>
+        <v>48.20461</v>
       </c>
       <c r="W97" t="n">
-        <v>-74.46583</v>
+        <v>-79.4071</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26280</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Norseman-2</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I98" t="b">
+        <v>0</v>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>4</v>
+      </c>
+      <c r="T98" t="n">
+        <v>100</v>
+      </c>
+      <c r="U98" t="n">
+        <v>39</v>
+      </c>
+      <c r="V98" t="n">
+        <v>48.05412</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-79.17482</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kidd Creek - Zone Bréchique</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I99" t="b">
+        <v>0</v>
+      </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Au 13.20 g/t, Ag 2.40 g/t</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
+        <v>25</v>
+      </c>
+      <c r="U99" t="n">
+        <v>39</v>
+      </c>
+      <c r="V99" t="n">
+        <v>48.23459</v>
+      </c>
+      <c r="W99" t="n">
+        <v>-79.1983</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5126</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Western Buff II : Veine 2</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I100" t="b">
+        <v>0</v>
+      </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Cu 6.03%, Ag 6.68 g/t</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" t="n">
+        <v>25</v>
+      </c>
+      <c r="U100" t="n">
+        <v>39</v>
+      </c>
+      <c r="V100" t="n">
+        <v>48.15294</v>
+      </c>
+      <c r="W100" t="n">
+        <v>-79.28442</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Bravo (Train No 3)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Copper, Uranium, Silver, Gold, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I101" t="b">
+        <v>0</v>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>4</v>
+      </c>
+      <c r="T101" t="n">
+        <v>100</v>
+      </c>
+      <c r="U101" t="n">
+        <v>39</v>
+      </c>
+      <c r="V101" t="n">
+        <v>56.38071</v>
+      </c>
+      <c r="W101" t="n">
+        <v>-68.37362</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Struan Uranium</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Uranium, Nickel, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I102" t="b">
+        <v>0</v>
+      </c>
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="n">
+        <v>125</v>
+      </c>
+      <c r="U102" t="n">
+        <v>39</v>
+      </c>
+      <c r="V102" t="n">
+        <v>45.72522</v>
+      </c>
+      <c r="W102" t="n">
+        <v>-76.71849</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Guimond</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I103" t="b">
+        <v>0</v>
+      </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>2</v>
+      </c>
+      <c r="T103" t="n">
+        <v>50</v>
+      </c>
+      <c r="U103" t="n">
+        <v>39</v>
+      </c>
+      <c r="V103" t="n">
+        <v>47.37388</v>
+      </c>
+      <c r="W103" t="n">
+        <v>-79.13840999999999</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Patry-Duchesne (Laverlochère)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Bismuth</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Bismuth, Gold, Silver, Molybdenum, Copper</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I104" t="b">
+        <v>0</v>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>8</v>
+      </c>
+      <c r="T104" t="n">
+        <v>200</v>
+      </c>
+      <c r="U104" t="n">
+        <v>39</v>
+      </c>
+      <c r="V104" t="n">
+        <v>47.43121</v>
+      </c>
+      <c r="W104" t="n">
+        <v>-79.32868999999999</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Fabre Nord</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I105" t="b">
+        <v>0</v>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Au 6.48 g/t</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" t="n">
+        <v>50</v>
+      </c>
+      <c r="U105" t="n">
+        <v>39</v>
+      </c>
+      <c r="V105" t="n">
+        <v>47.26406</v>
+      </c>
+      <c r="W105" t="n">
+        <v>-79.40157000000001</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>East Mac (Indice Nord)</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I106" t="b">
+        <v>0</v>
+      </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Au 108.96 g/t, Ag 1480.90 g/t</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" t="n">
+        <v>25</v>
+      </c>
+      <c r="U106" t="n">
+        <v>39</v>
+      </c>
+      <c r="V106" t="n">
+        <v>48.6126</v>
+      </c>
+      <c r="W106" t="n">
+        <v>-77.97836</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2804</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pitchvein (RB Gold Zone)</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Zinc, Copper, Gold, Silver, Molybdenum, Lead, Antimony</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I107" t="b">
+        <v>0</v>
+      </c>
+      <c r="J107" t="b">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Au 8.49 g/t, Cu 0.814%, Ag 21.10 g/t, Zn 0.93%</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" t="n">
+        <v>25</v>
+      </c>
+      <c r="U107" t="n">
+        <v>39</v>
+      </c>
+      <c r="V107" t="n">
+        <v>48.19746</v>
+      </c>
+      <c r="W107" t="n">
+        <v>-79.41042</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5111</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Kogaluc 1</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I108" t="b">
+        <v>0</v>
+      </c>
+      <c r="J108" t="b">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" t="n">
+        <v>50</v>
+      </c>
+      <c r="U108" t="n">
+        <v>39</v>
+      </c>
+      <c r="V108" t="n">
+        <v>58.81627</v>
+      </c>
+      <c r="W108" t="n">
+        <v>-74.70458000000001</v>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Kogaluc 4</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I109" t="b">
+        <v>0</v>
+      </c>
+      <c r="J109" t="b">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Au 5.60 g/t</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="n">
+        <v>2</v>
+      </c>
+      <c r="T109" t="n">
+        <v>50</v>
+      </c>
+      <c r="U109" t="n">
+        <v>39</v>
+      </c>
+      <c r="V109" t="n">
+        <v>58.81552</v>
+      </c>
+      <c r="W109" t="n">
+        <v>-74.68685000000001</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Drouet</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I110" t="b">
+        <v>0</v>
+      </c>
+      <c r="J110" t="b">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Au 6.00 g/t</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="n">
+        <v>25</v>
+      </c>
+      <c r="U110" t="n">
+        <v>39</v>
+      </c>
+      <c r="V110" t="n">
+        <v>49.49319</v>
+      </c>
+      <c r="W110" t="n">
+        <v>-75.12523</v>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Lepage No 2</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic, Antimony</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I111" t="b">
+        <v>0</v>
+      </c>
+      <c r="J111" t="b">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="n">
+        <v>2</v>
+      </c>
+      <c r="T111" t="n">
+        <v>50</v>
+      </c>
+      <c r="U111" t="n">
+        <v>39</v>
+      </c>
+      <c r="V111" t="n">
+        <v>48.33322</v>
+      </c>
+      <c r="W111" t="n">
+        <v>-66.99834</v>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>East Dalquier</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I112" t="b">
+        <v>0</v>
+      </c>
+      <c r="J112" t="b">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>W 1.86%, Au 5.49 g/t</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="n">
+        <v>25</v>
+      </c>
+      <c r="U112" t="n">
+        <v>39</v>
+      </c>
+      <c r="V112" t="n">
+        <v>48.65564</v>
+      </c>
+      <c r="W112" t="n">
+        <v>-78.02257</v>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Dalquier (rg 8 lot 14)</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Zinc, Lead, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I113" t="b">
+        <v>0</v>
+      </c>
+      <c r="J113" t="b">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="n">
+        <v>6</v>
+      </c>
+      <c r="T113" t="n">
+        <v>150</v>
+      </c>
+      <c r="U113" t="n">
+        <v>39</v>
+      </c>
+      <c r="V113" t="n">
+        <v>48.68159</v>
+      </c>
+      <c r="W113" t="n">
+        <v>-78.15861</v>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Perry (Lac Barbie-Nord)</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Molybdenum</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Molybdenum, Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I114" t="b">
+        <v>0</v>
+      </c>
+      <c r="J114" t="b">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Au 10.94 g/t, Mo 0.531%, Cu 0.32%</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" t="n">
+        <v>25</v>
+      </c>
+      <c r="U114" t="n">
+        <v>39</v>
+      </c>
+      <c r="V114" t="n">
+        <v>49.5097</v>
+      </c>
+      <c r="W114" t="n">
+        <v>-76.02871</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3505</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X114"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sond. SER-21-040</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 8.71 g/t</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>53.08409</v>
+        <v>55.2524</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.20562</v>
+        <v>-67.95193</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67301</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Rambull</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,23 +778,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U4" t="n">
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>48.31932</v>
+        <v>48.4824</v>
       </c>
       <c r="W4" t="n">
-        <v>-64.9713</v>
+        <v>-78.10243</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
         </is>
       </c>
     </row>
@@ -804,22 +804,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Lead, Zinc, Silver</t>
+          <t>Gold, Copper, Silver, Cobalt, Tungsten, Tellurium, Arsenic</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -856,23 +856,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>45.99171</v>
+        <v>59.80634</v>
       </c>
       <c r="W5" t="n">
-        <v>-71.70617</v>
+        <v>-75.01831</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sond. DDH-20-2023</t>
+          <t>Gauthier-Mcneely</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Iron, Nickel, Cobalt</t>
+          <t>Zinc, Copper, Silver, Nickel</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
+          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>46.36809</v>
+        <v>55.62931</v>
       </c>
       <c r="W6" t="n">
-        <v>-73.97731</v>
+        <v>-66.83314</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mine Renzy</t>
+          <t>Franelle</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,17 +970,17 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Copper, Nickel, Egp, Silver, Gold, Chromium, Cobalt</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -991,12 +991,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>766 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ni 2.3%, Cu 1.75%, Co 0.11%, Pt 0.66 g/t, Pd 0.53 g/t</t>
+          <t>Cu 60%, Ag 43.49 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>46.81194</v>
+        <v>55.55824</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.70332999999999</v>
+        <v>-67.34804</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4560</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B-88-01</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 203.00 g/t, Cu 1.56%</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>45.52488</v>
+        <v>60.16686</v>
       </c>
       <c r="W8" t="n">
-        <v>-72.07191</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delhi Pacific</t>
+          <t>Qarqasiaq - C</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Nickel, Egp, Palladium, Platinum, Copper, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
+          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>56.40258</v>
+        <v>60.17776</v>
       </c>
       <c r="W9" t="n">
-        <v>-67.9023</v>
+        <v>-70.30297</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rochelom</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead</t>
+          <t>Zinc, Cadmium, Mercury, Barium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
+          <t>Zn 31.5%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1246,23 +1246,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U10" t="n">
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>49.77064</v>
+        <v>46.11447</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.01858</v>
+        <v>-75.95323</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lac Rivon-Ouest</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Molybdenum, Silver, Copper</t>
+          <t>Copper, Nickel, Platinum, Egp, Palladium, Silver, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>51.72313</v>
+        <v>58.96701</v>
       </c>
       <c r="W11" t="n">
-        <v>-72.79697</v>
+        <v>-69.59563</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Riv. Cheno-Ouest</t>
+          <t>Sainte-Cécile (Maheu) - ancien</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Molybdenum, Silver, Zinc, Lead, Bismuth, Gold, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>U 1.2%</t>
+          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>51.53813</v>
+        <v>45.67446</v>
       </c>
       <c r="W12" t="n">
-        <v>-72.67167999999999</v>
+        <v>-70.96669</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4564</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Goshawk</t>
+          <t>Mine Renzy</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,17 +1438,17 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Lead, Copper, Zinc, Silver</t>
+          <t>Nickel, Copper, Palladium, Platinum, Cobalt, Chromium, Gold, Egp, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>766 kt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
+          <t>Ni 2.3%, Cu 1.75%, Co 0.11%, Pt 0.66 g/t, Pd 0.53 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>61.56992</v>
+        <v>46.81194</v>
       </c>
       <c r="W13" t="n">
-        <v>-75.20258</v>
+        <v>-76.70332999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4560</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ganiq</t>
+          <t>Lac du Castor</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead, Uranium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>U 0.77%, Cu 0.52%, Pb 0.82%</t>
+          <t>U 0.328%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>53.7831</v>
+        <v>52.2149</v>
       </c>
       <c r="W14" t="n">
-        <v>-75.64593000000001</v>
+        <v>-70.93367000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4528</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Barre de fer</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>51.6436</v>
+        <v>52.20175</v>
       </c>
       <c r="W15" t="n">
-        <v>-67.33749</v>
+        <v>-70.89798</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boulder Shear (Cuvier-Est)</t>
+          <t>Lac Harris</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Arsenic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
+          <t>Cu 5.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>49.9399</v>
+        <v>47.68996</v>
       </c>
       <c r="W16" t="n">
-        <v>-74.70344</v>
+        <v>-76.66074999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lac Barlow</t>
+          <t>Chalifour-1</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
+          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1792,23 +1792,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U17" t="n">
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>49.94431</v>
+        <v>50.3781</v>
       </c>
       <c r="W17" t="n">
-        <v>-74.71456000000001</v>
+        <v>-73.70041000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lac Chicobi-2</t>
+          <t>St-Armand (Phillipsburg-Est)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Lead, Gold</t>
+          <t>Uranium, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 932.70 g/t, Pb 19.2%</t>
+          <t>U 0.578%, Zn 0.0798%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>48.83881</v>
+        <v>45.02084</v>
       </c>
       <c r="W18" t="n">
-        <v>-78.52331</v>
+        <v>-73.0196</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4194</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Propriété Authier</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 173.90 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>48.89617</v>
+        <v>45.03676</v>
       </c>
       <c r="W19" t="n">
-        <v>-78.78440000000001</v>
+        <v>-72.77243</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4201</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bouchette</t>
+          <t>BJB - Rustcliff (Boudrias)</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper, Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Zn 32.8%</t>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2026,23 +2026,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>46.26106</v>
+        <v>50.31401</v>
       </c>
       <c r="W20" t="n">
-        <v>-75.97745999999999</v>
+        <v>-62.73908</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4050</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D-91-01 (Option Dejour)</t>
+          <t>Northern Canada</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 4.35 g/t, Ag 6.90 g/t</t>
+          <t>U 0.373%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.02527</v>
+        <v>50.39968</v>
       </c>
       <c r="W21" t="n">
-        <v>-78.38705</v>
+        <v>-62.92982</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4045</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5401</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gold Fields</t>
+          <t>Ganiq</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Uranium, Lead, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 19.04 g/t</t>
+          <t>U 0.77%, Cu 0.52%, Pb 0.82%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.09287</v>
+        <v>53.7831</v>
       </c>
       <c r="W22" t="n">
-        <v>-78.42254</v>
+        <v>-75.64593000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4044</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4528</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gauthier-Mcneely</t>
+          <t>Cunning-Gault</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Nickel</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
+          <t>Pb 32.7%, Zn 11.7%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.62931</v>
+        <v>48.72575</v>
       </c>
       <c r="W23" t="n">
-        <v>-66.83314</v>
+        <v>-64.47654</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5374</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Mid-Patapédia</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 31.13 g/t</t>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>55.2524</v>
+        <v>47.86378</v>
       </c>
       <c r="W24" t="n">
-        <v>-67.95193</v>
+        <v>-67.38485</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lac du Canoe</t>
+          <t>St-Benoit</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 40.00 g/t</t>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>55.23434</v>
+        <v>47.99637</v>
       </c>
       <c r="W25" t="n">
-        <v>-67.62649</v>
+        <v>-67.11127</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G-H-2-79 (Hudbay Mining)</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 3.26%, Ni 1.12%</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>51.50451</v>
+        <v>55.68696</v>
       </c>
       <c r="W26" t="n">
-        <v>-67.92737</v>
+        <v>-71.02212</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lac Couillard (Secteur A)</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Zr, Y, Etr, Ce, Sm, Nd, La, Dy, Gd, Pr</t>
+          <t>Nickel, Egp, Copper, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Nd 0.649%, Dy 0.0357%, Pr 0.11%, Ce 1.55%, La 0.2%</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>50.30421</v>
+        <v>55.58892</v>
       </c>
       <c r="W27" t="n">
-        <v>-60.82246</v>
+        <v>-71.1636</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4100</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CaribGold 99-07</t>
+          <t>Augustus Exploration</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bismuth, Gold, Palladium, Platinum, Egp, Nickel, Zinc, Chromium, Silver</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
+          <t>Li 0.96%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>50.75408</v>
+        <v>48.42585</v>
       </c>
       <c r="W28" t="n">
-        <v>-76.84898</v>
+        <v>-77.87544</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5443</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AT-32-91</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 5.09 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>48.89509</v>
+        <v>49.82919</v>
       </c>
       <c r="W29" t="n">
-        <v>-78.79843</v>
+        <v>-70.58076</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Site-1429-02</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Copper, Silver</t>
+          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Zn 22.4%, Pb 19.4%, Au 1.25 g/t, Cu 0.0405%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>50.85765</v>
+        <v>49.83681</v>
       </c>
       <c r="W30" t="n">
-        <v>-76.48296999999999</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4232</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H-1429-046</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>50.85296</v>
+        <v>49.84595</v>
       </c>
       <c r="W31" t="n">
-        <v>-76.47398</v>
+        <v>-70.57626</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H-1451-032</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Nickel, Copper, Egp, Cobalt, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 2.20 g/t, Cu 0.66%, Zn 1.59%, Ag 21.80 g/t</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>50.79734</v>
+        <v>55.61902</v>
       </c>
       <c r="W32" t="n">
-        <v>-76.70574000000001</v>
+        <v>-71.054</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4242</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum, Nickel, Copper, Egp, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 26.78 g/t</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>50.8534</v>
+        <v>55.5908</v>
       </c>
       <c r="W33" t="n">
-        <v>-76.53675</v>
+        <v>-71.13463</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4238</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -3066,22 +3066,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver, Uranium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 5.00 g/t</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3118,23 +3118,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U34" t="n">
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>50.8451</v>
+        <v>46.265</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.45574000000001</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4236</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bloc Est</t>
+          <t>St-Sylvestre-Noranda</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>Zn 15.2%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>50.84188</v>
+        <v>46.32835</v>
       </c>
       <c r="W35" t="n">
-        <v>-76.39422</v>
+        <v>-71.13679999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4235</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1218</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Noramco Broadback Zone (H-1451-009)</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc, Lead</t>
+          <t>Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Zn 15.3%, Cu 1.8%, Ag 68.21 g/t, Pb 0.445%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>50.78641</v>
+        <v>46.27176</v>
       </c>
       <c r="W36" t="n">
-        <v>-76.75020000000001</v>
+        <v>-71.28612</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4239</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Mine Harvey Hill</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,17 +3310,17 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
+          <t>Copper, Silver, Uranium, Molybdenum, Gold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>453 kt</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U37" t="n">
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>59.80634</v>
+        <v>46.26423</v>
       </c>
       <c r="W37" t="n">
-        <v>-75.01831</v>
+        <v>-71.20608</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Leadville</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc</t>
+          <t>Copper, Gold, Silver, Nickel, Chromium, Zinc</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Zn 31.4%, Ag 95.98 g/t, Pb 4.94%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T38" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U38" t="n">
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>45.00863</v>
+        <v>46.26109</v>
       </c>
       <c r="W38" t="n">
-        <v>-72.26421000000001</v>
+        <v>-71.22866</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4394</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H-1456-009</t>
+          <t>Martin-McNeely</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Copper, Silver</t>
+          <t>Lithium, Molybdenum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 8.47 g/t, Cu 0.303%, Ag 9.60 g/t, As 0.565%</t>
+          <t>Li 1%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>50.62126</v>
+        <v>48.43133</v>
       </c>
       <c r="W39" t="n">
-        <v>-77.35012</v>
+        <v>-77.89922</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4342</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5442</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mine Suffield</t>
+          <t>Pari</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,17 +3544,17 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>850 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ag 644.80 g/t, Zn 29.6%, Au 7.20 g/t, Cu 6.2%, Pb 3.68%</t>
+          <t>Au 730.77 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>45.31892</v>
+        <v>53.53306</v>
       </c>
       <c r="W40" t="n">
-        <v>-71.95913</v>
+        <v>-76.55201</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mine Aldermac Moulton Hill</t>
+          <t>Brèche</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,17 +3622,17 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Molybdenum, Cadmium, Barium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>871 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
+          <t>Au 8.56 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,23 +3664,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U41" t="n">
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>45.40941</v>
+        <v>53.53187</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.81791</v>
+        <v>-76.54353</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mine Capelton (Albert)</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,17 +3700,17 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver, Lead</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I42" t="b">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>300 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
+          <t>Au 251.66 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>45.32298</v>
+        <v>53.53343</v>
       </c>
       <c r="W42" t="n">
-        <v>-71.90649999999999</v>
+        <v>-76.53331</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lac Beaver Zoran</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Uranium, Zinc, Lead, Vanadium, Barium</t>
+          <t>Copper, Silver, Gold, Zinc, Molybdenum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>U 2.09%, V 0.91%, Zn 1.02%, Pb 1.32%, Ba 41.2%</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T43" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U43" t="n">
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>51.98869</v>
+        <v>46.26265</v>
       </c>
       <c r="W43" t="n">
-        <v>-72.37778</v>
+        <v>-71.21769</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4397</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lac De Maurès-Est</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Cu 12.6%, Au 5.79 g/t, Ag 50.00 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>50.65811</v>
+        <v>46.26532</v>
       </c>
       <c r="W44" t="n">
-        <v>-74.36593999999999</v>
+        <v>-71.28788</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4292</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pio - Filons Est et Ouest</t>
+          <t>Maro</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Palladium, Platinum, Cobalt, Silver, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+          <t>U 14.7%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>58.96701</v>
+        <v>53.54575</v>
       </c>
       <c r="W45" t="n">
-        <v>-69.59563</v>
+        <v>-76.93913999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5498</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Qarqasiaq - A1</t>
+          <t>Canadian Lithium</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Palladium, Nickel, Copper, Egp, Platinum, Cobalt</t>
+          <t>Lithium, Tantalum, Beryllium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
+          <t>Li 0.814%, Be 0.0342%, Ta 0.019%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>60.16686</v>
+        <v>48.43096</v>
       </c>
       <c r="W46" t="n">
-        <v>-70.29604999999999</v>
+        <v>-77.90853</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5441</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Qarqasiaq - C</t>
+          <t>Valor Lithium</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Palladium, Platinum, Copper, Gold, Cobalt</t>
+          <t>Lithium, Beryllium, Tantalum, Cs, Molybdenum, Niobium, Rb</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
+          <t>Li 1.46%, Be 3.23%, Cs 0.139%, Nb 0.0335%, Rb 0.312%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>60.17776</v>
+        <v>48.38862</v>
       </c>
       <c r="W47" t="n">
-        <v>-70.30297</v>
+        <v>-77.92084</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5440</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Franelle</t>
+          <t>Projet 70-Landome</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Cu 60%, Ag 43.49 g/t</t>
+          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>55.55824</v>
+        <v>48.46123</v>
       </c>
       <c r="W48" t="n">
-        <v>-67.34804</v>
+        <v>-77.95265999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lac Odon</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Copper, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 19.20 g/t, Cu 3.51%, Mo 0.96%, Ag 8.40 g/t</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>50.68338</v>
+        <v>49.59836</v>
       </c>
       <c r="W49" t="n">
-        <v>-74.36037</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4293</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel, Iron</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>45.03676</v>
+        <v>49.63941</v>
       </c>
       <c r="W50" t="n">
-        <v>-72.77243</v>
+        <v>-76.90893</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -4392,22 +4392,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Monarch - Veine 1</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Copper, Palladium, Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>Au 83.00 g/t</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>55.58892</v>
+        <v>48.23207</v>
       </c>
       <c r="W51" t="n">
-        <v>-71.1636</v>
+        <v>-79.41287</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Platinum, Palladium, Cobalt</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>55.61902</v>
+        <v>48.71945</v>
       </c>
       <c r="W52" t="n">
-        <v>-71.054</v>
+        <v>-78.33144</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Sond. Umex 132</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>Cu 4%, Zn 6%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>55.5908</v>
+        <v>49.79699</v>
       </c>
       <c r="W53" t="n">
-        <v>-71.13463</v>
+        <v>-75.81529</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4678,23 +4678,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U54" t="n">
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>49.84595</v>
+        <v>48.57696</v>
       </c>
       <c r="W54" t="n">
-        <v>-70.57626</v>
+        <v>-78.14164</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>
@@ -4704,11 +4704,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Monarch - Veine 1</t>
+          <t>Big Dragon</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>Au 6.57 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>48.23207</v>
+        <v>48.23154</v>
       </c>
       <c r="W55" t="n">
-        <v>-79.41287</v>
+        <v>-66.80576000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Castor</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Platinum, Palladium</t>
+          <t>Antimony, Gold, Silver, Barium, Arsenic</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Sb 47.6%, Au 30.00 g/t, Ag 110.00 g/t, As 1.8%, Ba 0.51%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>55.68696</v>
+        <v>48.08376</v>
       </c>
       <c r="W56" t="n">
-        <v>-71.02212</v>
+        <v>-66.92106</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3456</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lac Harris</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Cu 5.07%</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4921,14 +4921,14 @@
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>47.68996</v>
+        <v>48.09296</v>
       </c>
       <c r="W57" t="n">
-        <v>-76.66074999999999</v>
+        <v>-66.78681</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Josselin-Tonnancourt (Greenland)</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,12 +4948,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Au 121.80 g/t, Cu 20%, Zn 13.1%, Ag 130.40 g/t</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>53.56991</v>
+        <v>48.86335</v>
       </c>
       <c r="W58" t="n">
-        <v>-77.31073000000001</v>
+        <v>-76.99204</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3877</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lac Lyster</t>
+          <t>Raglan (Lac Cross Est, zones C-1 et C-2)</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,12 +5026,12 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Nickel, Copper, Egp, Gold, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>W 2.93%</t>
+          <t>Ni 2.33%, Au 2.00 g/t, Cu 1.24%, Pd 2.26 g/t, Pt 0.86 g/t</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>45.03295</v>
+        <v>61.5996</v>
       </c>
       <c r="W59" t="n">
-        <v>-71.89901999999999</v>
+        <v>-74.24052</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4847</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3851</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sainte-Cécile (Maheu) - ancien</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5104,33 +5104,33 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bismuth, Lead, Zinc, Silver, Molybdenum, Copper, Gold</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>16 kt</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5146,23 +5146,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U60" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="V60" t="n">
-        <v>45.67446</v>
+        <v>49.75792</v>
       </c>
       <c r="W60" t="n">
-        <v>-70.96669</v>
+        <v>-74.3342</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,33 +5182,33 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Zinc, Barium, Mercury, Cadmium</t>
+          <t>Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Zn 31.5%</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T61" t="n">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="U61" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="V61" t="n">
-        <v>46.11447</v>
+        <v>49.01028</v>
       </c>
       <c r="W61" t="n">
-        <v>-75.95323</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mont Opémiska No 1</t>
+          <t>Lavoie (Zone L)</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,21 +5260,21 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Lead, Silver</t>
+          <t>Lead, Vanadium, Molybdenum, Uranium, Gold, Silver, Thorium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5302,23 +5302,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U62" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V62" t="n">
-        <v>49.95224</v>
+        <v>52.18408</v>
       </c>
       <c r="W62" t="n">
-        <v>-74.8797</v>
+        <v>-70.99409</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lac Dunphy</t>
+          <t>Sirmac</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,21 +5338,21 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Lithium, Tantalum, Beryllium, Tin, Tungsten, Niobium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
+          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U63" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V63" t="n">
-        <v>56.05097</v>
+        <v>50.62206</v>
       </c>
       <c r="W63" t="n">
-        <v>-67.71257</v>
+        <v>-75.47598000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>Solbec Copper</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,33 +5416,33 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>2.1 Mt</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5458,23 +5458,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U64" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V64" t="n">
-        <v>49.59836</v>
+        <v>45.80476</v>
       </c>
       <c r="W64" t="n">
-        <v>-76.92194000000001</v>
+        <v>-71.28747</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5494,33 +5494,33 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Iron</t>
+          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5536,23 +5536,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T65" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U65" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V65" t="n">
-        <v>49.63941</v>
+        <v>46.04018</v>
       </c>
       <c r="W65" t="n">
-        <v>-76.90893</v>
+        <v>-71.28144</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chibtown</t>
+          <t>Fayolle (Renault)</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5572,12 +5572,12 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Molybdenum, Lead</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="I66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
+          <t>Au 6.68 g/t, Cu 3.9%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U66" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V66" t="n">
-        <v>56.39152</v>
+        <v>48.20461</v>
       </c>
       <c r="W66" t="n">
-        <v>-67.87103</v>
+        <v>-79.4071</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Fabre Nord</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Au 29.25 g/t, W 0.122%</t>
+          <t>Au 6.48 g/t</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5692,23 +5692,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T67" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U67" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V67" t="n">
-        <v>52.64108</v>
+        <v>47.26406</v>
       </c>
       <c r="W67" t="n">
-        <v>-75.67010999999999</v>
+        <v>-79.40157000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,12 +5728,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Copper, Molybdenum, Silver, Gold, Bismuth</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="I68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5770,23 +5770,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T68" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U68" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V68" t="n">
-        <v>49.82919</v>
+        <v>47.43121</v>
       </c>
       <c r="W68" t="n">
-        <v>-70.58076</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Guimond</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5806,12 +5806,12 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum, Palladium, Egp</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5848,23 +5848,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U69" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V69" t="n">
-        <v>49.83681</v>
+        <v>47.37388</v>
       </c>
       <c r="W69" t="n">
-        <v>-70.57877999999999</v>
+        <v>-79.13840999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chalifour-1</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5884,12 +5884,12 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Copper</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="I70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5926,23 +5926,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="U70" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V70" t="n">
-        <v>50.3781</v>
+        <v>53.56991</v>
       </c>
       <c r="W70" t="n">
-        <v>-73.70041000000001</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Bravo (Train No 3)</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,12 +5962,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Uranium, Copper, Silver, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6004,23 +6004,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T71" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U71" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V71" t="n">
-        <v>52.20175</v>
+        <v>56.38071</v>
       </c>
       <c r="W71" t="n">
-        <v>-70.89798</v>
+        <v>-68.37362</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lac du Castor</t>
+          <t>Pio - Zone Du Synclinal</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,12 +6040,12 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Silver, Gold</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="I72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>U 0.328%</t>
+          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T72" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U72" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V72" t="n">
-        <v>52.2149</v>
+        <v>58.99163</v>
       </c>
       <c r="W72" t="n">
-        <v>-70.93367000000001</v>
+        <v>-69.61172000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>St-Armand (Phillipsburg-Est)</t>
+          <t>Kogaluc 1</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,12 +6118,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Uranium, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="I73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>U 0.578%, Zn 0.0798%</t>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6160,23 +6160,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T73" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U73" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V73" t="n">
-        <v>45.02084</v>
+        <v>58.81627</v>
       </c>
       <c r="W73" t="n">
-        <v>-73.0196</v>
+        <v>-74.70458000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Robidoux-appalaches</t>
+          <t>Kogaluc 4</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,12 +6196,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="I74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
+          <t>Au 5.60 g/t</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6238,23 +6238,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U74" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V74" t="n">
-        <v>48.35381</v>
+        <v>58.81552</v>
       </c>
       <c r="W74" t="n">
-        <v>-65.56434</v>
+        <v>-74.68685000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gémini - A Nord</t>
+          <t>Copperstream-Ouest</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6274,12 +6274,12 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="I75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Cu 6.37%, Au 2.68 g/t, Zn 8.1%, Ag 5.06 g/t</t>
+          <t>Au 8.96 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6316,23 +6316,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U75" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V75" t="n">
-        <v>49.43645</v>
+        <v>48.48146</v>
       </c>
       <c r="W75" t="n">
-        <v>-79.26394999999999</v>
+        <v>-78.14755</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4009</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1541</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Kerwin</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6352,12 +6352,12 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="I76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6394,23 +6394,23 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T76" t="n">
-        <v>275</v>
+        <v>50</v>
       </c>
       <c r="U76" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V76" t="n">
-        <v>48.57696</v>
+        <v>48.39017</v>
       </c>
       <c r="W76" t="n">
-        <v>-78.14164</v>
+        <v>-78.41151000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Harriman-1 (New Richmond-1)</t>
+          <t>Struan Uranium</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6430,12 +6430,12 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Antimony, Gold, Silver</t>
+          <t>Nickel, Uranium, Copper, Zinc</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="I77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sb 43.8%, Au 13.70 g/t, Ag 4.50 g/t</t>
+          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6472,23 +6472,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T77" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U77" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V77" t="n">
-        <v>48.24307</v>
+        <v>45.72522</v>
       </c>
       <c r="W77" t="n">
-        <v>-65.79867</v>
+        <v>-76.71849</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3578</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Lac Sheen</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6508,12 +6508,12 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Egp, Platinum, Palladium, Rh, Copper, Nickel, Gold, Silver</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Cu 3.53%, Pt 4.24 g/t, Pd 3.00 g/t, Ni 0.6%, Ag 19.00 g/t</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6550,23 +6550,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U78" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V78" t="n">
-        <v>49.79699</v>
+        <v>47.30605</v>
       </c>
       <c r="W78" t="n">
-        <v>-75.81529</v>
+        <v>-78.57969</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2356</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Umex-2</t>
+          <t>Vallée Lithium</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6586,12 +6586,12 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Copper</t>
+          <t>Lithium, Tantalum, Beryllium, Gallium</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="I79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
+          <t>Li 1.38%, Ga 0.0077%, Be 0.0143%, Ta 0.0323%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6628,23 +6628,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T79" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="U79" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V79" t="n">
-        <v>49.81674</v>
+        <v>48.40109</v>
       </c>
       <c r="W79" t="n">
-        <v>-75.52503</v>
+        <v>-77.77728999999999</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5445</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amaruk</t>
+          <t>Lac Macleod-NE</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -6664,12 +6664,12 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Molybdenum, Gold, Tungsten, Silver</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="I80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
+          <t>W 0.111%, Mo 1.22%, Cu 2.65%, Au 2.00 g/t, Ag 24.00 g/t</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,23 +6706,23 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T80" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U80" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V80" t="n">
-        <v>59.60263</v>
+        <v>52.23858</v>
       </c>
       <c r="W80" t="n">
-        <v>-74.86282</v>
+        <v>-72.98878000000001</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5385</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pointe-Aux-Gossans-2</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Tungsten, Tin, Bismuth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="I81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>W 1.03%, Au 27.43 g/t, Cu 2.56%, Ag 90.00 g/t, Sn 0.34%</t>
+          <t>Au 7.29 g/t</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6784,23 +6784,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U81" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V81" t="n">
-        <v>59.77961</v>
+        <v>49.3283</v>
       </c>
       <c r="W81" t="n">
-        <v>-74.98016</v>
+        <v>-76.11469</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1854</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5343</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
+          <t>Baillairgé-Ouest</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -6820,17 +6820,17 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gold, Copper, Tungsten, Silver</t>
+          <t>Lithium, Tantalum, Silver</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>29 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
+          <t>Li 0.9%, Ag 9.00 g/t, Ta 0.053%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6862,23 +6862,23 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U82" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="V82" t="n">
-        <v>48.24607</v>
+        <v>48.32819</v>
       </c>
       <c r="W82" t="n">
-        <v>-79.50617</v>
+        <v>-77.98884</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5482</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Tri-Cor</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -6898,17 +6898,17 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Au 79.54 g/t, Cu 3.75%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6946,17 +6946,17 @@
         <v>25</v>
       </c>
       <c r="U83" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="V83" t="n">
-        <v>49.75792</v>
+        <v>48.46064</v>
       </c>
       <c r="W83" t="n">
-        <v>-74.3342</v>
+        <v>-77.62456</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5438</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -6976,17 +6976,17 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Au 54.80 g/t</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7018,23 +7018,23 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U84" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="V84" t="n">
-        <v>49.01028</v>
+        <v>48.46597</v>
       </c>
       <c r="W84" t="n">
-        <v>-66.00369999999999</v>
+        <v>-77.6782</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5437</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -7054,17 +7054,17 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Cadmium, Gold, Zinc, Cs</t>
+          <t>Lithium, Molybdenum, Beryllium, Bismuth, Niobium, Rb, Tantalum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Mo 5.47%, Li 1.32%, Bi 0.0383%, Be 0.0688%, Rb 0.37%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7096,23 +7096,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T85" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="U85" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V85" t="n">
-        <v>45.80476</v>
+        <v>48.30767</v>
       </c>
       <c r="W85" t="n">
-        <v>-71.28747</v>
+        <v>-77.95856000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5459</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Galloway (GP)</t>
+          <t>Western Buff II : Veine 2</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Au 8.66 g/t, Cu 2%, Ag 4.53 g/t</t>
+          <t>Cu 6.03%, Ag 6.68 g/t</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7174,23 +7174,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U86" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V86" t="n">
-        <v>48.19278</v>
+        <v>48.15294</v>
       </c>
       <c r="W86" t="n">
-        <v>-79.4164</v>
+        <v>-79.28442</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5189</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>PUI-87-43</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -7210,17 +7210,17 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Vanadium, Lead, Gold, Uranium, Molybdenum, Silver, Thorium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>Au 3.73 g/t</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7252,23 +7252,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U87" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V87" t="n">
-        <v>52.18408</v>
+        <v>49.68374</v>
       </c>
       <c r="W87" t="n">
-        <v>-70.99409</v>
+        <v>-78.9585</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Norseman-2</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -7288,17 +7288,17 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nickel, Rh, Platinum, Egp, Chromium, Palladium</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7336,17 +7336,17 @@
         <v>75</v>
       </c>
       <c r="U88" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V88" t="n">
-        <v>46.04018</v>
+        <v>48.05412</v>
       </c>
       <c r="W88" t="n">
-        <v>-71.28144</v>
+        <v>-79.17482</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sirmac</t>
+          <t>Black Bay</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -7366,17 +7366,17 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tungsten, Tin, Beryllium, Tantalum, Lithium, Niobium</t>
+          <t>Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
+          <t>Cu 15.9%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7414,17 +7414,17 @@
         <v>25</v>
       </c>
       <c r="U89" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V89" t="n">
-        <v>50.62206</v>
+        <v>48.0662</v>
       </c>
       <c r="W89" t="n">
-        <v>-75.47598000000001</v>
+        <v>-79.18935</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KM 55 (DEC 96-01)</t>
+          <t>East Dalquier</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -7444,12 +7444,12 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 47.90 g/t</t>
+          <t>W 1.86%, Au 5.49 g/t</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7495,14 +7495,14 @@
         <v>39</v>
       </c>
       <c r="V90" t="n">
-        <v>49.4978</v>
+        <v>48.65564</v>
       </c>
       <c r="W90" t="n">
-        <v>-76.98484999999999</v>
+        <v>-78.02257</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4464</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lac Authier-Est (Tut)</t>
+          <t>Chioak</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -7522,12 +7522,12 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium, Thorium, Copper</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Au 29.00 g/t</t>
+          <t>U 0.425%, Cu 0.15%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7564,1817 +7564,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T91" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U91" t="n">
         <v>39</v>
       </c>
       <c r="V91" t="n">
-        <v>48.96913</v>
+        <v>58.12937</v>
       </c>
       <c r="W91" t="n">
-        <v>-78.54470000000001</v>
+        <v>-70.18866</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4191</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Copperstream-Ouest</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I92" t="b">
-        <v>0</v>
-      </c>
-      <c r="J92" t="b">
-        <v>0</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Au 8.96 g/t</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="n">
-        <v>1</v>
-      </c>
-      <c r="T92" t="n">
-        <v>25</v>
-      </c>
-      <c r="U92" t="n">
-        <v>39</v>
-      </c>
-      <c r="V92" t="n">
-        <v>48.48146</v>
-      </c>
-      <c r="W92" t="n">
-        <v>-78.14755</v>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1541</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Kerwin</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" t="b">
-        <v>0</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="n">
-        <v>2</v>
-      </c>
-      <c r="T93" t="n">
-        <v>50</v>
-      </c>
-      <c r="U93" t="n">
-        <v>39</v>
-      </c>
-      <c r="V93" t="n">
-        <v>48.39017</v>
-      </c>
-      <c r="W93" t="n">
-        <v>-78.41151000000001</v>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Rambull</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="b">
-        <v>0</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="n">
-        <v>4</v>
-      </c>
-      <c r="T94" t="n">
-        <v>100</v>
-      </c>
-      <c r="U94" t="n">
-        <v>39</v>
-      </c>
-      <c r="V94" t="n">
-        <v>48.4824</v>
-      </c>
-      <c r="W94" t="n">
-        <v>-78.10243</v>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Stoke 22-V</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I95" t="b">
-        <v>0</v>
-      </c>
-      <c r="J95" t="b">
-        <v>0</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Cu 7.14%, Ag 22.60 g/t, Pb 0.015%, Zn 0.14%</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="n">
-        <v>4</v>
-      </c>
-      <c r="T95" t="n">
-        <v>100</v>
-      </c>
-      <c r="U95" t="n">
-        <v>39</v>
-      </c>
-      <c r="V95" t="n">
-        <v>45.47913</v>
-      </c>
-      <c r="W95" t="n">
-        <v>-71.79196</v>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4350</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Pio - Zone Du Synclinal</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I96" t="b">
-        <v>0</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="n">
-        <v>5</v>
-      </c>
-      <c r="T96" t="n">
-        <v>125</v>
-      </c>
-      <c r="U96" t="n">
-        <v>39</v>
-      </c>
-      <c r="V96" t="n">
-        <v>58.99163</v>
-      </c>
-      <c r="W96" t="n">
-        <v>-69.61172000000001</v>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Fayolle (Renault)</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Molybdenum, Lead</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I97" t="b">
-        <v>0</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Au 6.68 g/t, Cu 3.9%</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="n">
-        <v>1</v>
-      </c>
-      <c r="T97" t="n">
-        <v>25</v>
-      </c>
-      <c r="U97" t="n">
-        <v>39</v>
-      </c>
-      <c r="V97" t="n">
-        <v>48.20461</v>
-      </c>
-      <c r="W97" t="n">
-        <v>-79.4071</v>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Norseman-2</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I98" t="b">
-        <v>0</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="n">
-        <v>4</v>
-      </c>
-      <c r="T98" t="n">
-        <v>100</v>
-      </c>
-      <c r="U98" t="n">
-        <v>39</v>
-      </c>
-      <c r="V98" t="n">
-        <v>48.05412</v>
-      </c>
-      <c r="W98" t="n">
-        <v>-79.17482</v>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Kidd Creek - Zone Bréchique</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I99" t="b">
-        <v>0</v>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Au 13.20 g/t, Ag 2.40 g/t</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="n">
-        <v>1</v>
-      </c>
-      <c r="T99" t="n">
-        <v>25</v>
-      </c>
-      <c r="U99" t="n">
-        <v>39</v>
-      </c>
-      <c r="V99" t="n">
-        <v>48.23459</v>
-      </c>
-      <c r="W99" t="n">
-        <v>-79.1983</v>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5126</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Western Buff II : Veine 2</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I100" t="b">
-        <v>0</v>
-      </c>
-      <c r="J100" t="b">
-        <v>0</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Cu 6.03%, Ag 6.68 g/t</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="n">
-        <v>1</v>
-      </c>
-      <c r="T100" t="n">
-        <v>25</v>
-      </c>
-      <c r="U100" t="n">
-        <v>39</v>
-      </c>
-      <c r="V100" t="n">
-        <v>48.15294</v>
-      </c>
-      <c r="W100" t="n">
-        <v>-79.28442</v>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Bravo (Train No 3)</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Copper, Uranium, Silver, Gold, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I101" t="b">
-        <v>0</v>
-      </c>
-      <c r="J101" t="b">
-        <v>0</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="n">
-        <v>4</v>
-      </c>
-      <c r="T101" t="n">
-        <v>100</v>
-      </c>
-      <c r="U101" t="n">
-        <v>39</v>
-      </c>
-      <c r="V101" t="n">
-        <v>56.38071</v>
-      </c>
-      <c r="W101" t="n">
-        <v>-68.37362</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Struan Uranium</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Uranium, Nickel, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I102" t="b">
-        <v>0</v>
-      </c>
-      <c r="J102" t="b">
-        <v>0</v>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="n">
-        <v>5</v>
-      </c>
-      <c r="T102" t="n">
-        <v>125</v>
-      </c>
-      <c r="U102" t="n">
-        <v>39</v>
-      </c>
-      <c r="V102" t="n">
-        <v>45.72522</v>
-      </c>
-      <c r="W102" t="n">
-        <v>-76.71849</v>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Guimond</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I103" t="b">
-        <v>0</v>
-      </c>
-      <c r="J103" t="b">
-        <v>0</v>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="n">
-        <v>2</v>
-      </c>
-      <c r="T103" t="n">
-        <v>50</v>
-      </c>
-      <c r="U103" t="n">
-        <v>39</v>
-      </c>
-      <c r="V103" t="n">
-        <v>47.37388</v>
-      </c>
-      <c r="W103" t="n">
-        <v>-79.13840999999999</v>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Bismuth</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Bismuth, Gold, Silver, Molybdenum, Copper</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I104" t="b">
-        <v>0</v>
-      </c>
-      <c r="J104" t="b">
-        <v>0</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="n">
-        <v>8</v>
-      </c>
-      <c r="T104" t="n">
-        <v>200</v>
-      </c>
-      <c r="U104" t="n">
-        <v>39</v>
-      </c>
-      <c r="V104" t="n">
-        <v>47.43121</v>
-      </c>
-      <c r="W104" t="n">
-        <v>-79.32868999999999</v>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Fabre Nord</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I105" t="b">
-        <v>0</v>
-      </c>
-      <c r="J105" t="b">
-        <v>0</v>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Au 6.48 g/t</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="n">
-        <v>2</v>
-      </c>
-      <c r="T105" t="n">
-        <v>50</v>
-      </c>
-      <c r="U105" t="n">
-        <v>39</v>
-      </c>
-      <c r="V105" t="n">
-        <v>47.26406</v>
-      </c>
-      <c r="W105" t="n">
-        <v>-79.40157000000001</v>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>East Mac (Indice Nord)</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I106" t="b">
-        <v>0</v>
-      </c>
-      <c r="J106" t="b">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Au 108.96 g/t, Ag 1480.90 g/t</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="n">
-        <v>1</v>
-      </c>
-      <c r="T106" t="n">
-        <v>25</v>
-      </c>
-      <c r="U106" t="n">
-        <v>39</v>
-      </c>
-      <c r="V106" t="n">
-        <v>48.6126</v>
-      </c>
-      <c r="W106" t="n">
-        <v>-77.97836</v>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2804</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Pitchvein (RB Gold Zone)</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Zinc, Copper, Gold, Silver, Molybdenum, Lead, Antimony</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I107" t="b">
-        <v>0</v>
-      </c>
-      <c r="J107" t="b">
-        <v>0</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>Au 8.49 g/t, Cu 0.814%, Ag 21.10 g/t, Zn 0.93%</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="n">
-        <v>1</v>
-      </c>
-      <c r="T107" t="n">
-        <v>25</v>
-      </c>
-      <c r="U107" t="n">
-        <v>39</v>
-      </c>
-      <c r="V107" t="n">
-        <v>48.19746</v>
-      </c>
-      <c r="W107" t="n">
-        <v>-79.41042</v>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5111</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Kogaluc 1</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I108" t="b">
-        <v>0</v>
-      </c>
-      <c r="J108" t="b">
-        <v>0</v>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="n">
-        <v>2</v>
-      </c>
-      <c r="T108" t="n">
-        <v>50</v>
-      </c>
-      <c r="U108" t="n">
-        <v>39</v>
-      </c>
-      <c r="V108" t="n">
-        <v>58.81627</v>
-      </c>
-      <c r="W108" t="n">
-        <v>-74.70458000000001</v>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Kogaluc 4</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>1</v>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I109" t="b">
-        <v>0</v>
-      </c>
-      <c r="J109" t="b">
-        <v>0</v>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>Au 5.60 g/t</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="n">
-        <v>2</v>
-      </c>
-      <c r="T109" t="n">
-        <v>50</v>
-      </c>
-      <c r="U109" t="n">
-        <v>39</v>
-      </c>
-      <c r="V109" t="n">
-        <v>58.81552</v>
-      </c>
-      <c r="W109" t="n">
-        <v>-74.68685000000001</v>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Drouet</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>1</v>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I110" t="b">
-        <v>0</v>
-      </c>
-      <c r="J110" t="b">
-        <v>0</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>Au 6.00 g/t</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="n">
-        <v>1</v>
-      </c>
-      <c r="T110" t="n">
-        <v>25</v>
-      </c>
-      <c r="U110" t="n">
-        <v>39</v>
-      </c>
-      <c r="V110" t="n">
-        <v>49.49319</v>
-      </c>
-      <c r="W110" t="n">
-        <v>-75.12523</v>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Lepage No 2</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Antimony</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I111" t="b">
-        <v>0</v>
-      </c>
-      <c r="J111" t="b">
-        <v>0</v>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="n">
-        <v>2</v>
-      </c>
-      <c r="T111" t="n">
-        <v>50</v>
-      </c>
-      <c r="U111" t="n">
-        <v>39</v>
-      </c>
-      <c r="V111" t="n">
-        <v>48.33322</v>
-      </c>
-      <c r="W111" t="n">
-        <v>-66.99834</v>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>East Dalquier</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J112" t="b">
-        <v>0</v>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>W 1.86%, Au 5.49 g/t</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="n">
-        <v>1</v>
-      </c>
-      <c r="T112" t="n">
-        <v>25</v>
-      </c>
-      <c r="U112" t="n">
-        <v>39</v>
-      </c>
-      <c r="V112" t="n">
-        <v>48.65564</v>
-      </c>
-      <c r="W112" t="n">
-        <v>-78.02257</v>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Dalquier (rg 8 lot 14)</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>1</v>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Zinc, Lead, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I113" t="b">
-        <v>0</v>
-      </c>
-      <c r="J113" t="b">
-        <v>0</v>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="n">
-        <v>6</v>
-      </c>
-      <c r="T113" t="n">
-        <v>150</v>
-      </c>
-      <c r="U113" t="n">
-        <v>39</v>
-      </c>
-      <c r="V113" t="n">
-        <v>48.68159</v>
-      </c>
-      <c r="W113" t="n">
-        <v>-78.15861</v>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Perry (Lac Barbie-Nord)</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Molybdenum</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Molybdenum, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I114" t="b">
-        <v>0</v>
-      </c>
-      <c r="J114" t="b">
-        <v>0</v>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Au 10.94 g/t, Mo 0.531%, Cu 0.32%</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="n">
-        <v>1</v>
-      </c>
-      <c r="T114" t="n">
-        <v>25</v>
-      </c>
-      <c r="U114" t="n">
-        <v>39</v>
-      </c>
-      <c r="V114" t="n">
-        <v>49.5097</v>
-      </c>
-      <c r="W114" t="n">
-        <v>-76.02871</v>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3505</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Red Zone</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 31.13 g/t</t>
+          <t>Ni 5.75%, Cu 1.35%, Pd 2.97 g/t, Pt 0.46 g/t, EGP 0.000342%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>55.2524</v>
+        <v>61.35949</v>
       </c>
       <c r="W3" t="n">
-        <v>-67.95193</v>
+        <v>-76.01782</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23971</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rambull</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,23 +778,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>48.4824</v>
+        <v>60.16686</v>
       </c>
       <c r="W4" t="n">
-        <v>-78.10243</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Cobalt, Tungsten, Tellurium, Arsenic</t>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gauthier-Mcneely</t>
+          <t>Lac Lanctôt</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Nickel</t>
+          <t>Gold, Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
+          <t>Zn 11.7%, Au 1.30 g/t, Ag 34.00 g/t, Cu 0.48%, Pb 0.69%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>55.62931</v>
+        <v>47.2105</v>
       </c>
       <c r="W6" t="n">
-        <v>-66.83314</v>
+        <v>-72.46509</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3297</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Franelle</t>
+          <t>PAP Nord (Camp A-1)</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 60%, Ag 43.49 g/t</t>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>55.55824</v>
+        <v>60.2779</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.34804</v>
+        <v>-75.33311</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qarqasiaq - A1</t>
+          <t>Spirit-1</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
+          <t>Nickel, Cobalt, Platinum, Palladium, Egp, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
+          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>60.16686</v>
+        <v>61.39663</v>
       </c>
       <c r="W8" t="n">
-        <v>-70.29604999999999</v>
+        <v>-73.13239</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qarqasiaq - C</t>
+          <t>Lac Viking</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Palladium, Platinum, Copper, Cobalt, Gold</t>
+          <t>Gold, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
+          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>60.17776</v>
+        <v>47.20549</v>
       </c>
       <c r="W9" t="n">
-        <v>-70.30297</v>
+        <v>-72.45211999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Delta (Northeast)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Zinc, Cadmium, Mercury, Barium</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Zn 31.5%</t>
+          <t>Ni 3.49%, Pd 1.96 g/t, Pt 0.83 g/t, Cu 0.11%, EGP 0.000279%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1246,23 +1246,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U10" t="n">
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>46.11447</v>
+        <v>61.48916</v>
       </c>
       <c r="W10" t="n">
-        <v>-75.95323</v>
+        <v>-74.43673</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24306</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pio - Filons Est et Ouest</t>
+          <t>Gauthier-Mcneely</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Egp, Palladium, Silver, Cobalt, Gold</t>
+          <t>Zinc, Silver, Copper, Nickel</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>58.96701</v>
+        <v>55.62931</v>
       </c>
       <c r="W11" t="n">
-        <v>-69.59563</v>
+        <v>-66.83314</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sainte-Cécile (Maheu) - ancien</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum, Silver, Zinc, Lead, Bismuth, Gold, Copper</t>
+          <t>Tungsten, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
+          <t>W 0.188%, Cu 4.08%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>45.67446</v>
+        <v>60.39318</v>
       </c>
       <c r="W12" t="n">
-        <v>-70.96669</v>
+        <v>-75.53694</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mine Renzy</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,17 +1438,17 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Palladium, Platinum, Cobalt, Chromium, Gold, Egp, Silver</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>766 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ni 2.3%, Cu 1.75%, Co 0.11%, Pt 0.66 g/t, Pd 0.53 g/t</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>46.81194</v>
+        <v>58.96701</v>
       </c>
       <c r="W13" t="n">
-        <v>-76.70332999999999</v>
+        <v>-69.59563</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4560</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lac du Castor</t>
+          <t>Misery - Sond. ML14024</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Tungsten, Niobium, Zr, Etr, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>U 0.328%</t>
+          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>52.2149</v>
+        <v>55.35025</v>
       </c>
       <c r="W14" t="n">
-        <v>-70.93367000000001</v>
+        <v>-63.8991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>52.20175</v>
+        <v>52.17253</v>
       </c>
       <c r="W15" t="n">
-        <v>-70.89798</v>
+        <v>-76.55762</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lac Harris</t>
+          <t>Seahawk</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Platinum, Palladium, Egp, Nickel</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 5.07%</t>
+          <t>Ni 4.73%, Cu 1.93%, Pd 3.35 g/t, Pt 0.99 g/t, EGP 0.000434%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>47.68996</v>
+        <v>61.35511</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.66074999999999</v>
+        <v>-76.04816</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23960</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chalifour-1</t>
+          <t>Destorbelle</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
+          <t>Au 8.20 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1792,23 +1792,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>50.3781</v>
+        <v>48.4465</v>
       </c>
       <c r="W17" t="n">
-        <v>-73.70041000000001</v>
+        <v>-78.85312999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>St-Armand (Phillipsburg-Est)</t>
+          <t>Étoile d'or</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Uranium, Zinc</t>
+          <t>Lead, Copper, Zinc, Bismuth, Molybdenum, Silver, Cadmium, Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>U 0.578%, Zn 0.0798%</t>
+          <t>Bi 1.7%, Ag 505.00 g/t, Zn 7.84%, Mo 0.882%, Cu 1.6%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>45.02084</v>
+        <v>45.42701</v>
       </c>
       <c r="W18" t="n">
-        <v>-73.0196</v>
+        <v>-71.29181</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3321</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>45.03676</v>
+        <v>61.52449</v>
       </c>
       <c r="W19" t="n">
-        <v>-72.77243</v>
+        <v>-72.77941</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>50.31401</v>
+        <v>61.55073</v>
       </c>
       <c r="W20" t="n">
-        <v>-62.73908</v>
+        <v>-72.66555</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Northern Canada</t>
+          <t>Misery - Sond. ML11014</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gallium, Sc, Y, Niobium, Zr, Etr, Tantalum, Beryllium, Germanium, Thorium, Tin, Silver, Fluorite, Uranium, Lead, Hf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>U 0.373%</t>
+          <t>Ge 0.0097%, U 0.0387%, Ga 0.0216%, Sn 0.0913%, Ag 5.30 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>50.39968</v>
+        <v>55.34044</v>
       </c>
       <c r="W21" t="n">
-        <v>-62.92982</v>
+        <v>-63.93963</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5401</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25755</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ganiq</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Uranium, Lead, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>U 0.77%, Cu 0.52%, Pb 0.82%</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>53.7831</v>
+        <v>48.31932</v>
       </c>
       <c r="W22" t="n">
-        <v>-75.64593000000001</v>
+        <v>-64.9713</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4528</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cunning-Gault</t>
+          <t>Rambull</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Pb 32.7%, Zn 11.7%</t>
+          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2260,23 +2260,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.72575</v>
+        <v>48.4824</v>
       </c>
       <c r="W23" t="n">
-        <v>-64.47654</v>
+        <v>-78.10243</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5374</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mid-Patapédia</t>
+          <t>Qarqasiaq - C</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
+          <t>Copper, Platinum, Palladium, Egp, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>47.86378</v>
+        <v>60.17776</v>
       </c>
       <c r="W24" t="n">
-        <v>-67.38485</v>
+        <v>-70.30297</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>St-Benoit</t>
+          <t>Century</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Zinc, Lead</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
+          <t>Ni 15.5%, Cu 3.16%, Pd 1.22 g/t, Pt 0.36 g/t, EGP 0.00013%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>47.99637</v>
+        <v>61.35448</v>
       </c>
       <c r="W25" t="n">
-        <v>-67.11127</v>
+        <v>-76.06304</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23835</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Lac du Canoe</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Au 40.00 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>55.68696</v>
+        <v>55.23434</v>
       </c>
       <c r="W26" t="n">
-        <v>-71.02212</v>
+        <v>-67.62649</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Maro</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Copper, Palladium, Platinum</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>U 14.7%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>55.58892</v>
+        <v>53.54575</v>
       </c>
       <c r="W27" t="n">
-        <v>-71.1636</v>
+        <v>-76.93913999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5498</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Augustus Exploration</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Li 0.96%</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>48.42585</v>
+        <v>55.61902</v>
       </c>
       <c r="W28" t="n">
-        <v>-77.87544</v>
+        <v>-71.054</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5443</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.82919</v>
+        <v>55.5908</v>
       </c>
       <c r="W29" t="n">
-        <v>-70.58076</v>
+        <v>-71.13463</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Barre de fer</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>49.83681</v>
+        <v>51.6436</v>
       </c>
       <c r="W30" t="n">
-        <v>-70.57877999999999</v>
+        <v>-67.33749</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Golden Butterfly</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Gold, Silver, Iron</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T31" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U31" t="n">
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>49.84595</v>
+        <v>51.99697</v>
       </c>
       <c r="W31" t="n">
-        <v>-70.57626</v>
+        <v>-75.22655</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Cobalt, Palladium, Platinum</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>55.61902</v>
+        <v>49.84595</v>
       </c>
       <c r="W32" t="n">
-        <v>-71.054</v>
+        <v>-70.57626</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platinum, Nickel, Copper, Egp, Palladium, Cobalt</t>
+          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>55.5908</v>
+        <v>55.58892</v>
       </c>
       <c r="W33" t="n">
-        <v>-71.13463</v>
+        <v>-71.1636</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -3066,22 +3066,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Capri-2</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium</t>
+          <t>Thorium, Uranium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>U 1.7%, Th 6.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3118,23 +3118,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>46.265</v>
+        <v>46.63574</v>
       </c>
       <c r="W34" t="n">
-        <v>-71.21259999999999</v>
+        <v>-75.92203000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5528</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>St-Sylvestre-Noranda</t>
+          <t>Principal (Zone Olga)</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper, Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Zn 15.2%</t>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>46.32835</v>
+        <v>49.78784</v>
       </c>
       <c r="W35" t="n">
-        <v>-71.13679999999999</v>
+        <v>-77.08529</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1218</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>46.27176</v>
+        <v>55.68696</v>
       </c>
       <c r="W36" t="n">
-        <v>-71.28612</v>
+        <v>-71.02212</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill</t>
+          <t>Filion</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,17 +3310,17 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium, Molybdenum, Gold</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>453 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
+          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>46.26423</v>
+        <v>46.61092</v>
       </c>
       <c r="W37" t="n">
-        <v>-71.20608</v>
+        <v>-75.97769</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>OTS-15</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Nickel, Chromium, Zinc</t>
+          <t>Etr, Y, Thorium, Zinc, Uranium, Molybdenum, Lead, Silver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>U 1.91%, Ag 44.80 g/t, Mo 0.122%, Zn 0.873%, Pb 0.351%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>46.26109</v>
+        <v>51.78273</v>
       </c>
       <c r="W38" t="n">
-        <v>-71.22866</v>
+        <v>-71.96856</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=33065</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Martin-McNeely</t>
+          <t>Mine Harvey Hill</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,17 +3466,17 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lithium, Molybdenum</t>
+          <t>Uranium, Silver, Copper, Molybdenum, Gold</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I39" t="b">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>453 kt</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Li 1%</t>
+          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>48.43133</v>
+        <v>46.26423</v>
       </c>
       <c r="W39" t="n">
-        <v>-77.89922</v>
+        <v>-71.20608</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5442</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pari</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 730.77 g/t</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3586,23 +3586,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T40" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U40" t="n">
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>53.53306</v>
+        <v>48.32328</v>
       </c>
       <c r="W40" t="n">
-        <v>-76.55201</v>
+        <v>-79.44637</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brèche</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 8.56 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>53.53187</v>
+        <v>45.03676</v>
       </c>
       <c r="W41" t="n">
-        <v>-76.54353</v>
+        <v>-72.77243</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Castor</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Silver, Gold, Antimony, Arsenic, Barium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 251.66 g/t</t>
+          <t>Sb 47.6%, Au 30.00 g/t, Ag 110.00 g/t, As 1.8%, Ba 0.51%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>53.53343</v>
+        <v>48.08376</v>
       </c>
       <c r="W42" t="n">
-        <v>-76.53331</v>
+        <v>-66.92106</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3456</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Zinc, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>46.26265</v>
+        <v>48.09296</v>
       </c>
       <c r="W43" t="n">
-        <v>-71.21769</v>
+        <v>-66.78681</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Lac Noach-Sud</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Zn 9.8%, Cu 1.97%, Ag 44.00 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>46.26532</v>
+        <v>53.60084</v>
       </c>
       <c r="W44" t="n">
-        <v>-71.28788</v>
+        <v>-77.60271</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3442</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Maro</t>
+          <t>Big Dragon</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>U 14.7%</t>
+          <t>Au 6.57 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>53.54575</v>
+        <v>48.23154</v>
       </c>
       <c r="W45" t="n">
-        <v>-76.93913999999999</v>
+        <v>-66.80576000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5498</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Canadian Lithium</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lithium, Tantalum, Beryllium</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Li 0.814%, Be 0.0342%, Ta 0.019%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>48.43096</v>
+        <v>46.27176</v>
       </c>
       <c r="W46" t="n">
-        <v>-77.90853</v>
+        <v>-71.28612</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5441</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Valor Lithium</t>
+          <t>Bourdon</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lithium, Beryllium, Tantalum, Cs, Molybdenum, Niobium, Rb</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Li 1.46%, Be 3.23%, Cs 0.139%, Nb 0.0335%, Rb 0.312%</t>
+          <t>Au 21.80 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>48.38862</v>
+        <v>53.62313</v>
       </c>
       <c r="W47" t="n">
-        <v>-77.92084</v>
+        <v>-71.96111999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5440</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
         </is>
       </c>
     </row>
@@ -4158,22 +4158,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Projet 70-Landome</t>
+          <t>Dead Mouse extension</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
+          <t>Au 18.36 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4210,23 +4210,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T48" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U48" t="n">
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>48.46123</v>
+        <v>53.61747</v>
       </c>
       <c r="W48" t="n">
-        <v>-77.95265999999999</v>
+        <v>-71.97382</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>de l'Ours</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Au 27.00 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4288,23 +4288,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T49" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U49" t="n">
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>49.59836</v>
+        <v>53.61441</v>
       </c>
       <c r="W49" t="n">
-        <v>-76.92194000000001</v>
+        <v>-71.97407</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
         </is>
       </c>
     </row>
@@ -4314,11 +4314,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Iron</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,23 +4366,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U50" t="n">
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>49.63941</v>
+        <v>46.265</v>
       </c>
       <c r="W50" t="n">
-        <v>-76.90893</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -4392,22 +4392,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Monarch - Veine 1</t>
+          <t>St-Sylvestre-Noranda</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>Zn 15.2%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>48.23207</v>
+        <v>46.32835</v>
       </c>
       <c r="W51" t="n">
-        <v>-79.41287</v>
+        <v>-71.13679999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1218</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Grand-Prix Zone 1</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Copper, Gold, Lead, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Cu 10.1%, Au 1.41 g/t, Ag 39.30 g/t, Zn 1.56%, Pb 0.236%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>48.71945</v>
+        <v>45.52677</v>
       </c>
       <c r="W52" t="n">
-        <v>-78.33144</v>
+        <v>-71.75227</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5602</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Delta (Zone D-9)</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Egp, Nickel, Platinum, Gold, Copper, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Pd 28.00 g/t, Ni 7.2%, Cu 5.9%, Au 1.80 g/t, Pt 4.13 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4600,23 +4600,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U53" t="n">
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>49.79699</v>
+        <v>61.48634</v>
       </c>
       <c r="W53" t="n">
-        <v>-75.81529</v>
+        <v>-74.44287</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3401</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Papavoine</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Zinc, Copper, Nickel, Silver, Platinum, Palladium, Cobalt, Egp</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Ni 1.27%, Cu 1.12%, Co 0.11%, Zn 1.3%, Ag 10.70 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4678,23 +4678,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U54" t="n">
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>48.57696</v>
+        <v>57.09376</v>
       </c>
       <c r="W54" t="n">
-        <v>-78.14164</v>
+        <v>-66.48862</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9786</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Big Dragon</t>
+          <t>Grand-Prix</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 6.57 g/t</t>
+          <t>Zn 13.1%, Cu 2.32%, Au 1.43 g/t, Ag 52.60 g/t, Pb 5.5%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>48.23154</v>
+        <v>45.52282</v>
       </c>
       <c r="W55" t="n">
-        <v>-66.80576000000001</v>
+        <v>-71.76373</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5601</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Castor</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Antimony, Gold, Silver, Barium, Arsenic</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Sb 47.6%, Au 30.00 g/t, Ag 110.00 g/t, As 1.8%, Ba 0.51%</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>48.08376</v>
+        <v>49.59836</v>
       </c>
       <c r="W56" t="n">
-        <v>-66.92106</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3456</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4870,12 +4870,12 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Iron, Nickel, Copper</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4921,14 +4921,14 @@
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>48.09296</v>
+        <v>49.63941</v>
       </c>
       <c r="W57" t="n">
-        <v>-66.78681</v>
+        <v>-76.90893</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Josselin-Tonnancourt (Greenland)</t>
+          <t>Sond. S2-88-01</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,12 +4948,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Zinc, Gold, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Au 121.80 g/t, Cu 20%, Zn 13.1%, Ag 130.40 g/t</t>
+          <t>Au 4.86 g/t, Zn 1.95%, Ag 23.90 g/t, Cu 0.0222%, Pb 0.116%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>48.86335</v>
+        <v>45.56756</v>
       </c>
       <c r="W58" t="n">
-        <v>-76.99204</v>
+        <v>-71.66579</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3877</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5591</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Raglan (Lac Cross Est, zones C-1 et C-2)</t>
+          <t>Jackson (Minerais Lac)</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,12 +5026,12 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Gold, Palladium, Platinum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Ni 2.33%, Au 2.00 g/t, Cu 1.24%, Pd 2.26 g/t, Pt 0.86 g/t</t>
+          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>61.5996</v>
+        <v>45.52972</v>
       </c>
       <c r="W59" t="n">
-        <v>-74.24052</v>
+        <v>-71.65783999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3851</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Dudswell</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5104,33 +5104,33 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Copper, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Au 5.05 g/t, Cu 3.8%, Zn 0.52%, Ag 4.60 g/t, Pb 0.01%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5146,23 +5146,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T60" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U60" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>49.75792</v>
+        <v>45.58073</v>
       </c>
       <c r="W60" t="n">
-        <v>-74.3342</v>
+        <v>-71.63548</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5580</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,33 +5182,33 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T61" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U61" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>49.01028</v>
+        <v>49.82919</v>
       </c>
       <c r="W61" t="n">
-        <v>-66.00369999999999</v>
+        <v>-70.58076</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,21 +5260,21 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lead, Vanadium, Molybdenum, Uranium, Gold, Silver, Thorium</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5302,23 +5302,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>52.18408</v>
+        <v>49.83681</v>
       </c>
       <c r="W62" t="n">
-        <v>-70.99409</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sirmac</t>
+          <t>OTS-08</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,21 +5338,21 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lithium, Tantalum, Beryllium, Tin, Tungsten, Niobium</t>
+          <t>Uranium, Zinc, Silver</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
+          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T63" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="U63" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>50.62206</v>
+        <v>51.78509</v>
       </c>
       <c r="W63" t="n">
-        <v>-75.47598000000001</v>
+        <v>-71.96465999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,33 +5416,33 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5458,23 +5458,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T64" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U64" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>45.80476</v>
+        <v>52.03235</v>
       </c>
       <c r="W64" t="n">
-        <v>-71.28747</v>
+        <v>-69.13816</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5494,33 +5494,33 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5536,23 +5536,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U65" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>46.04018</v>
+        <v>48.70382</v>
       </c>
       <c r="W65" t="n">
-        <v>-71.28144</v>
+        <v>-78.25041</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fayolle (Renault)</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Copper, Gold, Molybdenum, Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="I66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Au 6.68 g/t, Cu 3.9%</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>48.20461</v>
+        <v>48.71945</v>
       </c>
       <c r="W66" t="n">
-        <v>-79.4071</v>
+        <v>-78.33144</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fabre Nord</t>
+          <t>Viau (ou Bordulac)</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Au 6.48 g/t</t>
+          <t>Au 31.00 g/t</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5692,23 +5692,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T67" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U67" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>47.26406</v>
+        <v>48.26547</v>
       </c>
       <c r="W67" t="n">
-        <v>-79.40157000000001</v>
+        <v>-79.41453</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
+          <t>Lac Fecteau Est</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,12 +5728,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Bismuth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="I68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+          <t>Au 8.80 g/t</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5770,23 +5770,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T68" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U68" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V68" t="n">
-        <v>47.43121</v>
+        <v>49.03096</v>
       </c>
       <c r="W68" t="n">
-        <v>-79.32868999999999</v>
+        <v>-75.24721</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Guimond</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>16 kt</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5854,17 +5854,17 @@
         <v>25</v>
       </c>
       <c r="U69" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="V69" t="n">
-        <v>47.37388</v>
+        <v>49.75792</v>
       </c>
       <c r="W69" t="n">
-        <v>-79.13840999999999</v>
+        <v>-74.3342</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5884,17 +5884,17 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5932,17 +5932,17 @@
         <v>125</v>
       </c>
       <c r="U70" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="V70" t="n">
-        <v>53.56991</v>
+        <v>49.01028</v>
       </c>
       <c r="W70" t="n">
-        <v>-77.31073000000001</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bravo (Train No 3)</t>
+          <t>Lavoie (Zone L)</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,17 +5962,17 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Uranium, Copper, Silver, Gold, Lead, Zinc</t>
+          <t>Gold, Uranium, Molybdenum, Vanadium, Lead, Thorium, Silver</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6004,23 +6004,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U71" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V71" t="n">
-        <v>56.38071</v>
+        <v>52.18408</v>
       </c>
       <c r="W71" t="n">
-        <v>-68.37362</v>
+        <v>-70.99409</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pio - Zone Du Synclinal</t>
+          <t>Solbec Copper</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,17 +6040,17 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Silver, Gold</t>
+          <t>Gold, Cadmium, Lead, Silver, Copper, Zinc, Cs</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>2.1 Mt</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T72" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="U72" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V72" t="n">
-        <v>58.99163</v>
+        <v>45.80476</v>
       </c>
       <c r="W72" t="n">
-        <v>-69.61172000000001</v>
+        <v>-71.28747</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kogaluc 1</t>
+          <t>Sirmac</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,17 +6118,17 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Tungsten, Tin, Beryllium, Tantalum, Lithium, Niobium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
+          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6160,23 +6160,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U73" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V73" t="n">
-        <v>58.81627</v>
+        <v>50.62206</v>
       </c>
       <c r="W73" t="n">
-        <v>-74.70458000000001</v>
+        <v>-75.47598000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kogaluc 4</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,17 +6196,17 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rh, Platinum, Nickel, Egp, Chromium, Palladium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I74" t="b">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 5.60 g/t</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6238,23 +6238,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T74" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="U74" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V74" t="n">
-        <v>58.81552</v>
+        <v>46.04018</v>
       </c>
       <c r="W74" t="n">
-        <v>-74.68685000000001</v>
+        <v>-71.28144</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Copperstream-Ouest</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 8.96 g/t</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6325,14 +6325,14 @@
         <v>39</v>
       </c>
       <c r="V75" t="n">
-        <v>48.48146</v>
+        <v>55.2524</v>
       </c>
       <c r="W75" t="n">
-        <v>-78.14755</v>
+        <v>-67.95193</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1541</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kerwin</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6352,12 +6352,12 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
+          <t>Au 20.57 g/t</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6394,23 +6394,23 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T76" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="U76" t="n">
         <v>39</v>
       </c>
       <c r="V76" t="n">
-        <v>48.39017</v>
+        <v>48.45213</v>
       </c>
       <c r="W76" t="n">
-        <v>-78.41151000000001</v>
+        <v>-78.82693</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5662</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Struan Uranium</t>
+          <t>Pio - Zone Du Synclinal</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6430,12 +6430,12 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nickel, Uranium, Copper, Zinc</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Silver</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>U 0.53%, Ni 1%, Cu 0.49%, Zn 0.3%</t>
+          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6481,14 +6481,14 @@
         <v>39</v>
       </c>
       <c r="V77" t="n">
-        <v>45.72522</v>
+        <v>58.99163</v>
       </c>
       <c r="W77" t="n">
-        <v>-76.71849</v>
+        <v>-69.61172000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4807</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lac Sheen</t>
+          <t>Copperstream-Ouest</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6508,12 +6508,12 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Egp, Platinum, Palladium, Rh, Copper, Nickel, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Cu 3.53%, Pt 4.24 g/t, Pd 3.00 g/t, Ni 0.6%, Ag 19.00 g/t</t>
+          <t>Au 8.96 g/t</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6559,14 +6559,14 @@
         <v>39</v>
       </c>
       <c r="V78" t="n">
-        <v>47.30605</v>
+        <v>48.48146</v>
       </c>
       <c r="W78" t="n">
-        <v>-78.57969</v>
+        <v>-78.14755</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1541</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vallée Lithium</t>
+          <t>Kerwin</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6586,12 +6586,12 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lithium, Tantalum, Beryllium, Gallium</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Li 1.38%, Ga 0.0077%, Be 0.0143%, Ta 0.0323%</t>
+          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6628,23 +6628,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U79" t="n">
         <v>39</v>
       </c>
       <c r="V79" t="n">
-        <v>48.40109</v>
+        <v>48.39017</v>
       </c>
       <c r="W79" t="n">
-        <v>-77.77728999999999</v>
+        <v>-78.41151000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5445</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
         </is>
       </c>
     </row>
@@ -6654,22 +6654,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lac Macleod-NE</t>
+          <t>Lac Tarsac : Veine II (Montbray)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Gold, Tungsten, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>W 0.111%, Mo 1.22%, Cu 2.65%, Au 2.00 g/t, Ag 24.00 g/t</t>
+          <t>Au 120.00 g/t</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,23 +6706,23 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U80" t="n">
         <v>39</v>
       </c>
       <c r="V80" t="n">
-        <v>52.23858</v>
+        <v>48.35326</v>
       </c>
       <c r="W80" t="n">
-        <v>-72.98878000000001</v>
+        <v>-79.42582</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5385</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5920</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>JR</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6742,12 +6742,12 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tantalum</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tantalum, Lithium, Rb, Gallium, Beryllium</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Au 7.29 g/t</t>
+          <t>Li 2.12%, Li2O 0.83%, Ga 0.0114%, Be 0.0237%, Rb 0.129%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6793,14 +6793,14 @@
         <v>39</v>
       </c>
       <c r="V81" t="n">
-        <v>49.3283</v>
+        <v>52.02638</v>
       </c>
       <c r="W81" t="n">
-        <v>-76.11469</v>
+        <v>-76.14072</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5343</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=31156</t>
         </is>
       </c>
     </row>
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Baillairgé-Ouest</t>
+          <t>Montbray (Poirier-Leith) : Zone 1</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lithium, Tantalum, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Li 0.9%, Ag 9.00 g/t, Ta 0.053%</t>
+          <t>Au 10.24 g/t, Ag 2.90 g/t</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6862,23 +6862,23 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T82" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U82" t="n">
         <v>39</v>
       </c>
       <c r="V82" t="n">
-        <v>48.32819</v>
+        <v>48.33071</v>
       </c>
       <c r="W82" t="n">
-        <v>-77.98884</v>
+        <v>-79.43351</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5929</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tri-Cor</t>
+          <t>Baillairgé-Ouest</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -6898,12 +6898,12 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Lithium, Tantalum, Silver</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Au 79.54 g/t, Cu 3.75%</t>
+          <t>Li 0.9%, Ag 9.00 g/t, Ta 0.053%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6940,23 +6940,23 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T83" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U83" t="n">
         <v>39</v>
       </c>
       <c r="V83" t="n">
-        <v>48.46064</v>
+        <v>48.32819</v>
       </c>
       <c r="W83" t="n">
-        <v>-77.62456</v>
+        <v>-77.98884</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5438</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5482</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Delta (Zone D-8)</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Au 54.80 g/t</t>
+          <t>Ni 7.8%, Pd 25.50 g/t, Cu 4%, Au 3.63 g/t, Pt 7.96 g/t</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7018,23 +7018,23 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T84" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U84" t="n">
         <v>39</v>
       </c>
       <c r="V84" t="n">
-        <v>48.46597</v>
+        <v>61.48642</v>
       </c>
       <c r="W84" t="n">
-        <v>-77.6782</v>
+        <v>-74.46145</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5437</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3396</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Albert (LH-90)</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -7054,12 +7054,12 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lithium, Molybdenum, Beryllium, Bismuth, Niobium, Rb, Tantalum</t>
+          <t>Zinc, Copper, Silver, Lead</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Mo 5.47%, Li 1.32%, Bi 0.0383%, Be 0.0688%, Rb 0.37%</t>
+          <t>Pb 50.6%, Zn 20.5%, Ag 173.70 g/t, Cu 0.53%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7096,23 +7096,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U85" t="n">
         <v>39</v>
       </c>
       <c r="V85" t="n">
-        <v>48.30767</v>
+        <v>48.74517</v>
       </c>
       <c r="W85" t="n">
-        <v>-77.95856000000001</v>
+        <v>-66.13224</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5459</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3389</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Western Buff II : Veine 2</t>
+          <t>Echo-1</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -7132,12 +7132,12 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Platinum, Cobalt, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Cu 6.03%, Ag 6.68 g/t</t>
+          <t>Ni 2.35%, Cu 2.6%, Co 0.56%, Pd 4.46 g/t, Pt 1.64 g/t</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7174,23 +7174,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U86" t="n">
         <v>39</v>
       </c>
       <c r="V86" t="n">
-        <v>48.15294</v>
+        <v>61.44723</v>
       </c>
       <c r="W86" t="n">
-        <v>-79.28442</v>
+        <v>-74.72001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3411</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PUI-87-43</t>
+          <t>Airport</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Au 3.73 g/t</t>
+          <t>Au 9.69 g/t</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7252,23 +7252,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U87" t="n">
         <v>39</v>
       </c>
       <c r="V87" t="n">
-        <v>49.68374</v>
+        <v>48.06063</v>
       </c>
       <c r="W87" t="n">
-        <v>-78.9585</v>
+        <v>-77.76470999999999</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29171</t>
         </is>
       </c>
     </row>
@@ -7278,22 +7278,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Norseman-2</t>
+          <t>Delta (Zone Nord)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Nickel, Palladium, Egp, Rh, Copper, Platinum, Ru, Cobalt</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
+          <t>Pd 17.30 g/t, Ni 3.32%, Pt 2.74 g/t, Cu 0.75%, Co 0.18%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7330,23 +7330,23 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T88" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U88" t="n">
         <v>39</v>
       </c>
       <c r="V88" t="n">
-        <v>48.05412</v>
+        <v>61.48852</v>
       </c>
       <c r="W88" t="n">
-        <v>-79.17482</v>
+        <v>-74.47212</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3408</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Black Bay</t>
+          <t>Dalquier (rg 8 lot 14)</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -7366,12 +7366,12 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc</t>
+          <t>Gold, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Cu 15.9%</t>
+          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7408,23 +7408,23 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T89" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="U89" t="n">
         <v>39</v>
       </c>
       <c r="V89" t="n">
-        <v>48.0662</v>
+        <v>48.68159</v>
       </c>
       <c r="W89" t="n">
-        <v>-79.18935</v>
+        <v>-78.15861</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>East Dalquier</t>
+          <t>Montserrat</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -7444,12 +7444,12 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>W 1.86%, Au 5.49 g/t</t>
+          <t>Au 13.93 g/t, Ag 2.30 g/t</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7486,23 +7486,23 @@
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T90" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U90" t="n">
         <v>39</v>
       </c>
       <c r="V90" t="n">
-        <v>48.65564</v>
+        <v>48.29238</v>
       </c>
       <c r="W90" t="n">
-        <v>-78.02257</v>
+        <v>-79.38334999999999</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5798</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chioak</t>
+          <t>Gand II: Rivière Opawica</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -7522,12 +7522,12 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Uranium, Thorium, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>U 0.425%, Cu 0.15%</t>
+          <t>Au 7.20 g/t</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7573,14 +7573,92 @@
         <v>39</v>
       </c>
       <c r="V91" t="n">
-        <v>58.12937</v>
+        <v>49.64493</v>
       </c>
       <c r="W91" t="n">
-        <v>-70.18866</v>
+        <v>-75.94013</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2988</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Anaconda Brass</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Au 5.10 g/t, Cu 1.29%</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>25</v>
+      </c>
+      <c r="U92" t="n">
+        <v>39</v>
+      </c>
+      <c r="V92" t="n">
+        <v>48.34022</v>
+      </c>
+      <c r="W92" t="n">
+        <v>-78.74214000000001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5739</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Lead, Silver, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Red Zone</t>
+          <t>Delhi Pacific</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ni 5.75%, Cu 1.35%, Pd 2.97 g/t, Pt 0.46 g/t, EGP 0.000342%</t>
+          <t>Cu 7.36%, Ag 24.90 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>61.35949</v>
+        <v>56.40258</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.01782</v>
+        <v>-67.9023</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23971</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qarqasiaq - A1</t>
+          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+          <t>Nickel, Copper, Cobalt, Egp, Palladium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
+          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>60.16686</v>
+        <v>58.23464</v>
       </c>
       <c r="W4" t="n">
-        <v>-70.29604999999999</v>
+        <v>-69.92364000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Chibtown</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>59.80634</v>
+        <v>56.39152</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.01831</v>
+        <v>-67.87103</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lac Lanctôt</t>
+          <t>Venditelli (Lac St-Pierre-Gold)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Silver, Copper</t>
+          <t>Gold, Egp, Palladium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Zn 11.7%, Au 1.30 g/t, Ag 34.00 g/t, Cu 0.48%, Pb 0.69%</t>
+          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>47.2105</v>
+        <v>58.15377</v>
       </c>
       <c r="W6" t="n">
-        <v>-72.46509</v>
+        <v>-69.53443</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3297</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PAP Nord (Camp A-1)</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
+          <t>Tungsten, Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>60.2779</v>
+        <v>53.39458</v>
       </c>
       <c r="W7" t="n">
-        <v>-75.33311</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spirit-1</t>
+          <t>Au-26</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nickel, Cobalt, Platinum, Palladium, Egp, Copper</t>
+          <t>Copper, Gold, Silver, Lead, Zinc, Arsenic</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
+          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>61.39663</v>
+        <v>53.39936</v>
       </c>
       <c r="W8" t="n">
-        <v>-73.13239</v>
+        <v>-77.29407</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lac Viking</t>
+          <t>Dessureault (Lac Rougemont)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
+          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>47.20549</v>
+        <v>58.02817</v>
       </c>
       <c r="W9" t="n">
-        <v>-72.45211999999999</v>
+        <v>-69.57268000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delta (Northeast)</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ni 3.49%, Pd 1.96 g/t, Pt 0.83 g/t, Cu 0.11%, EGP 0.000279%</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1246,23 +1246,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>61.48916</v>
+        <v>53.40387</v>
       </c>
       <c r="W10" t="n">
-        <v>-74.43673</v>
+        <v>-77.30118</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24306</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gauthier-Mcneely</t>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Nickel</t>
+          <t>Zinc, Silver, Nickel, Palladium, Gold, Copper, Lead, Cobalt, Egp</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>55.62931</v>
+        <v>53.39996</v>
       </c>
       <c r="W11" t="n">
-        <v>-66.83314</v>
+        <v>-77.33163999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tungsten, Copper</t>
+          <t>Copper, Gold, Egp, Palladium, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>W 0.188%, Cu 4.08%</t>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>60.39318</v>
+        <v>53.34013</v>
       </c>
       <c r="W12" t="n">
-        <v>-75.53694</v>
+        <v>-77.32316</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pio - Filons Est et Ouest</t>
+          <t>Lac Menarik</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
+          <t>Rh, Chromium, Egp, Nickel, Gold, Palladium, Platinum, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>58.96701</v>
+        <v>53.39786</v>
       </c>
       <c r="W13" t="n">
-        <v>-69.59563</v>
+        <v>-77.30625000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Misery - Sond. ML14024</t>
+          <t>Franelle</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tungsten, Niobium, Zr, Etr, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
+          <t>Cu 60%, Ag 43.49 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>55.35025</v>
+        <v>55.55824</v>
       </c>
       <c r="W14" t="n">
-        <v>-63.8991</v>
+        <v>-67.34804</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sandpit</t>
+          <t>Bonspot</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 18.05 g/t, As 0.158%</t>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>52.17253</v>
+        <v>53.41679</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.55762</v>
+        <v>-77.27167</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Seahawk</t>
+          <t>4930N-1</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Platinum, Palladium, Egp, Nickel</t>
+          <t>Chromium, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ni 4.73%, Cu 1.93%, Pd 3.35 g/t, Pt 0.99 g/t, EGP 0.000434%</t>
+          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>61.35511</v>
+        <v>53.38014</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.04816</v>
+        <v>-77.28712</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23960</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Destorbelle</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Tungsten, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 8.20 g/t</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>48.4465</v>
+        <v>53.39256</v>
       </c>
       <c r="W17" t="n">
-        <v>-78.85312999999999</v>
+        <v>-77.43714</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Étoile d'or</t>
+          <t>Lac Yasinski-NE</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lead, Copper, Zinc, Bismuth, Molybdenum, Silver, Cadmium, Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Bi 1.7%, Ag 505.00 g/t, Zn 7.84%, Mo 0.882%, Cu 1.6%</t>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>45.42701</v>
+        <v>53.35887</v>
       </c>
       <c r="W18" t="n">
-        <v>-71.29181</v>
+        <v>-77.31016</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3321</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>61.52449</v>
+        <v>49.84595</v>
       </c>
       <c r="W19" t="n">
-        <v>-72.77941</v>
+        <v>-70.57626</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Mistass</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel</t>
+          <t>Nickel, Copper, Iron, Cobalt</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>61.55073</v>
+        <v>49.24734</v>
       </c>
       <c r="W20" t="n">
-        <v>-72.66555</v>
+        <v>-71.98866</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Misery - Sond. ML11014</t>
+          <t>Fort Chimo (Lac Plissé)</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gallium, Sc, Y, Niobium, Zr, Etr, Tantalum, Beryllium, Germanium, Thorium, Tin, Silver, Fluorite, Uranium, Lead, Hf</t>
+          <t>Nickel, Copper, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ge 0.0097%, U 0.0387%, Ga 0.0216%, Sn 0.0913%, Ag 5.30 g/t</t>
+          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>55.34044</v>
+        <v>58.12861</v>
       </c>
       <c r="W21" t="n">
-        <v>-63.93963</v>
+        <v>-69.55745</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25755</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Qarqasiaq - C</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium, Platinum, Copper, Nickel, Egp, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>48.31932</v>
+        <v>60.17776</v>
       </c>
       <c r="W22" t="n">
-        <v>-64.9713</v>
+        <v>-70.30297</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rambull</t>
+          <t>Lac Rivon-Ouest</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum, Zinc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
+          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2260,23 +2260,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.4824</v>
+        <v>51.72313</v>
       </c>
       <c r="W23" t="n">
-        <v>-78.10243</v>
+        <v>-72.79697</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Qarqasiaq - C</t>
+          <t>Riv. Cheno-Ouest</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Platinum, Palladium, Egp, Nickel, Gold, Cobalt</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
+          <t>U 1.2%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>60.17776</v>
+        <v>51.53813</v>
       </c>
       <c r="W24" t="n">
-        <v>-70.30297</v>
+        <v>-72.67167999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4564</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Century</t>
+          <t>Mine Renzy</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,17 +2374,17 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
+          <t>Nickel, Copper, Palladium, Platinum, Cobalt, Chromium, Gold, Egp, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>766 kt</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ni 15.5%, Cu 3.16%, Pd 1.22 g/t, Pt 0.36 g/t, EGP 0.00013%</t>
+          <t>Ni 2.3%, Cu 1.75%, Co 0.11%, Pt 0.66 g/t, Pd 0.53 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>61.35448</v>
+        <v>46.81194</v>
       </c>
       <c r="W25" t="n">
-        <v>-76.06304</v>
+        <v>-76.70332999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23835</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4560</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lac du Canoe</t>
+          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 40.00 g/t</t>
+          <t>Au 21.70 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>55.23434</v>
+        <v>57.94973</v>
       </c>
       <c r="W26" t="n">
-        <v>-67.62649</v>
+        <v>-69.51281</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maro</t>
+          <t>Erickson Sud - Goose Pond</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Palladium, Gold, Platinum, Copper, Nickel, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>U 14.7%</t>
+          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>53.54575</v>
+        <v>57.99255</v>
       </c>
       <c r="W27" t="n">
-        <v>-76.93913999999999</v>
+        <v>-69.72347000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5498</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
         </is>
       </c>
     </row>
@@ -2598,22 +2598,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
+          <t>Copper, Silver, Uranium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2650,23 +2650,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U28" t="n">
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>55.61902</v>
+        <v>46.265</v>
       </c>
       <c r="W28" t="n">
-        <v>-71.054</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Rochelom</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>55.5908</v>
+        <v>49.77064</v>
       </c>
       <c r="W29" t="n">
-        <v>-71.13463</v>
+        <v>-76.01858</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Barre de fer</t>
+          <t>Goshawk</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Copper, Lead, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
+          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>51.6436</v>
+        <v>61.56992</v>
       </c>
       <c r="W30" t="n">
-        <v>-67.33749</v>
+        <v>-75.20258</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Golden Butterfly</t>
+          <t>Destorbelle</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold, Silver, Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
+          <t>Au 8.20 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T31" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U31" t="n">
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>51.99697</v>
+        <v>48.4465</v>
       </c>
       <c r="W31" t="n">
-        <v>-75.22655</v>
+        <v>-78.85312999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>49.84595</v>
+        <v>55.2524</v>
       </c>
       <c r="W32" t="n">
-        <v>-70.57626</v>
+        <v>-67.95193</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Gauthier-Mcneely</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
+          <t>Zinc, Copper, Silver, Nickel</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>55.58892</v>
+        <v>55.62931</v>
       </c>
       <c r="W33" t="n">
-        <v>-71.1636</v>
+        <v>-66.83314</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capri-2</t>
+          <t>Ganiq</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thorium, Uranium</t>
+          <t>Uranium, Lead, Copper</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>U 1.7%, Th 6.02%</t>
+          <t>U 0.77%, Cu 0.52%, Pb 0.82%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>46.63574</v>
+        <v>53.7831</v>
       </c>
       <c r="W34" t="n">
-        <v>-75.92203000000001</v>
+        <v>-75.64593000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5528</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4528</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Arsenic</t>
+          <t>Egp, Palladium, Platinum, Copper, Nickel, Silver, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>49.78784</v>
+        <v>58.96701</v>
       </c>
       <c r="W35" t="n">
-        <v>-77.08529</v>
+        <v>-69.59563</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Egp, Palladium, Platinum, Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>55.68696</v>
+        <v>60.16686</v>
       </c>
       <c r="W36" t="n">
-        <v>-71.02212</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Filion</t>
+          <t>Lac du Canoe</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
+          <t>Au 40.00 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>46.61092</v>
+        <v>55.23434</v>
       </c>
       <c r="W37" t="n">
-        <v>-75.97769</v>
+        <v>-67.62649</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OTS-15</t>
+          <t>PG-221094</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Etr, Y, Thorium, Zinc, Uranium, Molybdenum, Lead, Silver</t>
+          <t>Gold, Zinc, Lead, Silver, Arsenic, Copper</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>U 1.91%, Ag 44.80 g/t, Mo 0.122%, Zn 0.873%, Pb 0.351%</t>
+          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T38" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U38" t="n">
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>51.78273</v>
+        <v>53.40779</v>
       </c>
       <c r="W38" t="n">
-        <v>-71.96856</v>
+        <v>-77.28636</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=33065</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill</t>
+          <t>Lac Dunphy</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,17 +3466,17 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Uranium, Silver, Copper, Molybdenum, Gold</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I39" t="b">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>453 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
+          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>46.26423</v>
+        <v>56.05097</v>
       </c>
       <c r="W39" t="n">
-        <v>-71.20608</v>
+        <v>-67.71257</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>B-88-01</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Ag 203.00 g/t, Cu 1.56%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3586,23 +3586,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U40" t="n">
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>48.32328</v>
+        <v>45.52488</v>
       </c>
       <c r="W40" t="n">
-        <v>-79.44637</v>
+        <v>-72.07191</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Riv. Cascapedia</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Nickel, Arsenic, Chromium, Cobalt, Antimony</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Ni 12.8%, Co 0.13%, As 11.8%, Cr 0.14%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>45.03676</v>
+        <v>48.84847</v>
       </c>
       <c r="W41" t="n">
-        <v>-72.77243</v>
+        <v>-66.39704</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6070</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Castor</t>
+          <t>Josette</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Silver, Gold, Antimony, Arsenic, Barium</t>
+          <t>Etr, Iron, Tungsten, Uranium, Thorium, Copper, Y, Silver, Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sb 47.6%, Au 30.00 g/t, Ag 110.00 g/t, As 1.8%, Ba 0.51%</t>
+          <t>W 0.18%, Cu 2.81%, U 0.0654%, Ag 13.00 g/t, Au 0.15 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>48.08376</v>
+        <v>51.05069</v>
       </c>
       <c r="W42" t="n">
-        <v>-66.92106</v>
+        <v>-65.27048000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3456</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6032</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>Ruisseau 17e Mille</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Nickel, Egp, Platinum, Chromium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Ni 11.7%, Pt 1.70 g/t, Cr 0.25%, EGP 0.00017%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>48.09296</v>
+        <v>48.86434</v>
       </c>
       <c r="W43" t="n">
-        <v>-66.78681</v>
+        <v>-66.26813</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6072</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lac Noach-Sud</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Zn 9.8%, Cu 1.97%, Ag 44.00 g/t</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>53.60084</v>
+        <v>48.32328</v>
       </c>
       <c r="W44" t="n">
-        <v>-77.60271</v>
+        <v>-79.44637</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3442</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Big Dragon</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 6.57 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>48.23154</v>
+        <v>49.83681</v>
       </c>
       <c r="W45" t="n">
-        <v>-66.80576000000001</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>46.27176</v>
+        <v>49.82919</v>
       </c>
       <c r="W46" t="n">
-        <v>-71.28612</v>
+        <v>-70.58076</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bourdon</t>
+          <t>Cr-2</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium, Platinum, Rh, Gold, Iron, Chromium, Nickel, Copper, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 21.80 g/t</t>
+          <t>Pd 11.88 g/t, Ni 2.4%, Cu 2.36%, Pt 4.20 g/t, Au 1.30 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>53.62313</v>
+        <v>53.39341</v>
       </c>
       <c r="W47" t="n">
-        <v>-71.96111999999999</v>
+        <v>-77.30141</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6004</t>
         </is>
       </c>
     </row>
@@ -4158,22 +4158,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dead Mouse extension</t>
+          <t>Sainte-Cécile (Maheu) - ancien</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum, Silver, Zinc, Lead, Bismuth, Gold, Copper</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 18.36 g/t</t>
+          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4210,23 +4210,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T48" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U48" t="n">
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>53.61747</v>
+        <v>45.67446</v>
       </c>
       <c r="W48" t="n">
-        <v>-71.97382</v>
+        <v>-70.96669</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>de l'Ours</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Barium, Cadmium, Mercury</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 27.00 g/t</t>
+          <t>Zn 31.5%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4288,23 +4288,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T49" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U49" t="n">
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>53.61441</v>
+        <v>46.11447</v>
       </c>
       <c r="W49" t="n">
-        <v>-71.97407</v>
+        <v>-75.95323</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
         </is>
       </c>
     </row>
@@ -4314,22 +4314,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Palladium, Nickel, Egp, Copper, Platinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,23 +4366,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U50" t="n">
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>46.265</v>
+        <v>55.58892</v>
       </c>
       <c r="W50" t="n">
-        <v>-71.21259999999999</v>
+        <v>-71.1636</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>St-Sylvestre-Noranda</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Zn 15.2%</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>46.32835</v>
+        <v>55.5908</v>
       </c>
       <c r="W51" t="n">
-        <v>-71.13679999999999</v>
+        <v>-71.13463</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1218</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Grand-Prix Zone 1</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Lead, Silver</t>
+          <t>Nickel, Copper, Egp, Cobalt, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 1.41 g/t, Ag 39.30 g/t, Zn 1.56%, Pb 0.236%</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>45.52677</v>
+        <v>55.61902</v>
       </c>
       <c r="W52" t="n">
-        <v>-71.75227</v>
+        <v>-71.054</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5602</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Delta (Zone D-9)</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Egp, Nickel, Platinum, Gold, Copper, Palladium, Cobalt</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Pd 28.00 g/t, Ni 7.2%, Cu 5.9%, Au 1.80 g/t, Pt 4.13 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4600,23 +4600,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>61.48634</v>
+        <v>45.03676</v>
       </c>
       <c r="W53" t="n">
-        <v>-74.44287</v>
+        <v>-72.77243</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3401</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Papavoine</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Nickel, Silver, Platinum, Palladium, Cobalt, Egp</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Ni 1.27%, Cu 1.12%, Co 0.11%, Zn 1.3%, Ag 10.70 g/t</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>57.09376</v>
+        <v>55.68696</v>
       </c>
       <c r="W54" t="n">
-        <v>-66.48862</v>
+        <v>-71.02212</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9786</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Grand-Prix</t>
+          <t>Viau (ou Bordulac)</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Zn 13.1%, Cu 2.32%, Au 1.43 g/t, Ag 52.60 g/t, Pb 5.5%</t>
+          <t>Au 31.00 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>45.52282</v>
+        <v>48.26547</v>
       </c>
       <c r="W55" t="n">
-        <v>-71.76373</v>
+        <v>-79.41453</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5601</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Gold, Arsenic, Copper, Silver, Cobalt, Tungsten, Tellurium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>49.59836</v>
+        <v>59.80634</v>
       </c>
       <c r="W56" t="n">
-        <v>-76.92194000000001</v>
+        <v>-75.01831</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Lac Tarsac : Veine I et III</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4870,12 +4870,12 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Iron, Nickel, Copper</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Au 11.66 g/t</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4912,23 +4912,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T57" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U57" t="n">
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>49.63941</v>
+        <v>48.3561</v>
       </c>
       <c r="W57" t="n">
-        <v>-76.90893</v>
+        <v>-79.43788000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sond. S2-88-01</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,12 +4948,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Zinc, Gold, Copper, Lead, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Au 4.86 g/t, Zn 1.95%, Ag 23.90 g/t, Cu 0.0222%, Pb 0.116%</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>45.56756</v>
+        <v>49.59836</v>
       </c>
       <c r="W58" t="n">
-        <v>-71.66579</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jackson (Minerais Lac)</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,12 +5026,12 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Nickel, Iron</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>45.52972</v>
+        <v>49.63941</v>
       </c>
       <c r="W59" t="n">
-        <v>-71.65783999999999</v>
+        <v>-76.90893</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dudswell</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5104,12 +5104,12 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, Silver, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Au 5.05 g/t, Cu 3.8%, Zn 0.52%, Ag 4.60 g/t, Pb 0.01%</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>45.58073</v>
+        <v>48.71945</v>
       </c>
       <c r="W60" t="n">
-        <v>-71.63548</v>
+        <v>-78.33144</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5580</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,12 +5182,12 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Copper, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5233,14 +5233,14 @@
         <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>49.82919</v>
+        <v>46.26532</v>
       </c>
       <c r="W61" t="n">
-        <v>-70.58076</v>
+        <v>-71.28788</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5311,14 +5311,14 @@
         <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>49.83681</v>
+        <v>48.70382</v>
       </c>
       <c r="W62" t="n">
-        <v>-70.57877999999999</v>
+        <v>-78.25041</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OTS-08</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Uranium, Zinc, Silver</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U63" t="n">
         <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>51.78509</v>
+        <v>48.57696</v>
       </c>
       <c r="W63" t="n">
-        <v>-71.96465999999999</v>
+        <v>-78.14164</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Zone Nicholson (Puits Racicot)</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Zinc, Cadmium, Lead, Silver, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5467,14 +5467,14 @@
         <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>52.03235</v>
+        <v>45.29835</v>
       </c>
       <c r="W64" t="n">
-        <v>-69.13816</v>
+        <v>-72.31643</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
         </is>
       </c>
     </row>
@@ -5484,11 +5484,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Molybdenum, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5536,23 +5536,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T65" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U65" t="n">
         <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>48.70382</v>
+        <v>45.99171</v>
       </c>
       <c r="W65" t="n">
-        <v>-78.25041</v>
+        <v>-71.70617</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Glencoe</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Cu 4.28%, Ag 3.00 g/t</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5623,14 +5623,14 @@
         <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>48.71945</v>
+        <v>45.32873</v>
       </c>
       <c r="W66" t="n">
-        <v>-78.33144</v>
+        <v>-72.47421</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Viau (ou Bordulac)</t>
+          <t>Petit Lac Brompton</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper, Nickel, Gold, Silver</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Au 31.00 g/t</t>
+          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5692,23 +5692,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T67" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U67" t="n">
         <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>48.26547</v>
+        <v>45.44828</v>
       </c>
       <c r="W67" t="n">
-        <v>-79.41453</v>
+        <v>-72.1057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lac Fecteau Est</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,33 +5728,33 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>16 kt</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Au 8.80 g/t</t>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5770,23 +5770,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U68" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="V68" t="n">
-        <v>49.03096</v>
+        <v>49.75792</v>
       </c>
       <c r="W68" t="n">
-        <v>-75.24721</v>
+        <v>-74.3342</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver, Tungsten, Copper</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>29 kt</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5857,14 +5857,14 @@
         <v>46</v>
       </c>
       <c r="V69" t="n">
-        <v>49.75792</v>
+        <v>48.24607</v>
       </c>
       <c r="W69" t="n">
-        <v>-74.3342</v>
+        <v>-79.50617</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Solbec Copper</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,17 +5962,17 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gold, Uranium, Molybdenum, Vanadium, Lead, Thorium, Silver</t>
+          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>2.1 Mt</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6004,23 +6004,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T71" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U71" t="n">
         <v>43</v>
       </c>
       <c r="V71" t="n">
-        <v>52.18408</v>
+        <v>45.80476</v>
       </c>
       <c r="W71" t="n">
-        <v>-70.99409</v>
+        <v>-71.28747</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,17 +6040,17 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gold, Cadmium, Lead, Silver, Copper, Zinc, Cs</t>
+          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T72" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="U72" t="n">
         <v>43</v>
       </c>
       <c r="V72" t="n">
-        <v>45.80476</v>
+        <v>46.04018</v>
       </c>
       <c r="W72" t="n">
-        <v>-71.28747</v>
+        <v>-71.28144</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sirmac</t>
+          <t>Lavoie (Zone L)</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,12 +6118,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tungsten, Tin, Beryllium, Tantalum, Lithium, Niobium</t>
+          <t>Uranium, Gold, Lead, Vanadium, Molybdenum, Silver, Thorium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Li 1.56%, W 0.137%, Sn 0.594%, Be 0.1%, Ta 0.0862%</t>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>43</v>
       </c>
       <c r="V73" t="n">
-        <v>50.62206</v>
+        <v>52.18408</v>
       </c>
       <c r="W73" t="n">
-        <v>-75.47598000000001</v>
+        <v>-70.99409</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
         </is>
       </c>
     </row>
@@ -6186,22 +6186,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Galloway : Hendrick</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rh, Platinum, Nickel, Egp, Chromium, Palladium</t>
+          <t>Gold, Copper, Molybdenum, Silver, Zinc</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Au 1.12 g/t, Cu 0.98%, Mo 0.306%, Ag 36.20 g/t, Zn 0.566%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6238,23 +6238,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T74" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U74" t="n">
         <v>43</v>
       </c>
       <c r="V74" t="n">
-        <v>46.04018</v>
+        <v>48.18985</v>
       </c>
       <c r="W74" t="n">
-        <v>-71.28144</v>
+        <v>-79.42233</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67506</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Galloway : GP</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 31.13 g/t</t>
+          <t>Au 8.66 g/t, Cu 2%, Ag 4.53 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6322,17 +6322,17 @@
         <v>25</v>
       </c>
       <c r="U75" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V75" t="n">
-        <v>55.2524</v>
+        <v>48.19278</v>
       </c>
       <c r="W75" t="n">
-        <v>-67.95193</v>
+        <v>-79.4164</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5189</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Orco-Tranchée 35-2</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Zinc, Copper, Lead</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 20.57 g/t</t>
+          <t>Au 15.57 g/t, Ag 82.60 g/t, Zn 1%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6394,23 +6394,23 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U76" t="n">
         <v>39</v>
       </c>
       <c r="V76" t="n">
-        <v>48.45213</v>
+        <v>48.42459</v>
       </c>
       <c r="W76" t="n">
-        <v>-78.82693</v>
+        <v>-78.74975999999999</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5662</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5730</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pio - Zone Du Synclinal</t>
+          <t>Anaconda Brass</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6430,12 +6430,12 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
+          <t>Au 5.10 g/t, Cu 1.29%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6472,23 +6472,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U77" t="n">
         <v>39</v>
       </c>
       <c r="V77" t="n">
-        <v>58.99163</v>
+        <v>48.34022</v>
       </c>
       <c r="W77" t="n">
-        <v>-69.61172000000001</v>
+        <v>-78.74214000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5739</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kerwin</t>
+          <t>Golden Rock</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6586,12 +6586,12 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
+          <t>Au 27.23 g/t</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6637,14 +6637,14 @@
         <v>39</v>
       </c>
       <c r="V79" t="n">
-        <v>48.39017</v>
+        <v>48.81681</v>
       </c>
       <c r="W79" t="n">
-        <v>-78.41151000000001</v>
+        <v>-78.47028</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2694</t>
         </is>
       </c>
     </row>
@@ -6654,11 +6654,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lac Tarsac : Veine II (Montbray)</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 120.00 g/t</t>
+          <t>Au 20.57 g/t</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,23 +6706,23 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T80" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U80" t="n">
         <v>39</v>
       </c>
       <c r="V80" t="n">
-        <v>48.35326</v>
+        <v>48.45213</v>
       </c>
       <c r="W80" t="n">
-        <v>-79.42582</v>
+        <v>-78.82693</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5920</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5662</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JR</t>
+          <t>Pio - Zone Du Synclinal</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6742,12 +6742,12 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tantalum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tantalum, Lithium, Rb, Gallium, Beryllium</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Silver, Gold</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Li 2.12%, Li2O 0.83%, Ga 0.0114%, Be 0.0237%, Rb 0.129%</t>
+          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6784,23 +6784,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T81" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U81" t="n">
         <v>39</v>
       </c>
       <c r="V81" t="n">
-        <v>52.02638</v>
+        <v>58.99163</v>
       </c>
       <c r="W81" t="n">
-        <v>-76.14072</v>
+        <v>-69.61172000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=31156</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
         </is>
       </c>
     </row>
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Montbray (Poirier-Leith) : Zone 1</t>
+          <t>Ruisseau Castor</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Silver, Iron, Gold</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 10.24 g/t, Ag 2.90 g/t</t>
+          <t>Cu 2.94%, Ag 65.80 g/t, Au 0.16 g/t</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6862,23 +6862,23 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="U82" t="n">
         <v>39</v>
       </c>
       <c r="V82" t="n">
-        <v>48.33071</v>
+        <v>48.88387</v>
       </c>
       <c r="W82" t="n">
-        <v>-79.43351</v>
+        <v>-66.05629</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5929</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6068</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Baillairgé-Ouest</t>
+          <t>Lac Colnet - Ouest</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -6898,12 +6898,12 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lithium, Tantalum, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Li 0.9%, Ag 9.00 g/t, Ta 0.053%</t>
+          <t>Au 4.09 g/t, Ag 2.30 g/t</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6940,23 +6940,23 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T83" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U83" t="n">
         <v>39</v>
       </c>
       <c r="V83" t="n">
-        <v>48.32819</v>
+        <v>48.30437</v>
       </c>
       <c r="W83" t="n">
-        <v>-77.98884</v>
+        <v>-79.39239999999999</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5846</t>
         </is>
       </c>
     </row>
@@ -6966,11 +6966,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Delta (Zone D-8)</t>
+          <t>Montbray (Poirier-Leith) : Zone 1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gold, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ni 7.8%, Pd 25.50 g/t, Cu 4%, Au 3.63 g/t, Pt 7.96 g/t</t>
+          <t>Au 10.24 g/t, Ag 2.90 g/t</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7018,23 +7018,23 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T84" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="U84" t="n">
         <v>39</v>
       </c>
       <c r="V84" t="n">
-        <v>61.48642</v>
+        <v>48.33071</v>
       </c>
       <c r="W84" t="n">
-        <v>-74.46145</v>
+        <v>-79.43351</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3396</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5929</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Albert (LH-90)</t>
+          <t>Rambull</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -7054,12 +7054,12 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Lead</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Pb 50.6%, Zn 20.5%, Ag 173.70 g/t, Cu 0.53%</t>
+          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7096,23 +7096,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T85" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U85" t="n">
         <v>39</v>
       </c>
       <c r="V85" t="n">
-        <v>48.74517</v>
+        <v>48.4824</v>
       </c>
       <c r="W85" t="n">
-        <v>-66.13224</v>
+        <v>-78.10243</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3389</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Echo-1</t>
+          <t>Fabre Nord</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -7132,12 +7132,12 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Ni 2.35%, Cu 2.6%, Co 0.56%, Pd 4.46 g/t, Pt 1.64 g/t</t>
+          <t>Au 6.48 g/t</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7174,23 +7174,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U86" t="n">
         <v>39</v>
       </c>
       <c r="V86" t="n">
-        <v>61.44723</v>
+        <v>47.26406</v>
       </c>
       <c r="W86" t="n">
-        <v>-74.72001</v>
+        <v>-79.40157000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3411</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Airport</t>
+          <t>Montserrat</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Au 9.69 g/t</t>
+          <t>Au 13.93 g/t, Ag 2.30 g/t</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7252,23 +7252,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U87" t="n">
         <v>39</v>
       </c>
       <c r="V87" t="n">
-        <v>48.06063</v>
+        <v>48.29238</v>
       </c>
       <c r="W87" t="n">
-        <v>-77.76470999999999</v>
+        <v>-79.38334999999999</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29171</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5798</t>
         </is>
       </c>
     </row>
@@ -7278,22 +7278,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Delta (Zone Nord)</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nickel, Palladium, Egp, Rh, Copper, Platinum, Ru, Cobalt</t>
+          <t>Gold, Bismuth, Copper, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Pd 17.30 g/t, Ni 3.32%, Pt 2.74 g/t, Cu 0.75%, Co 0.18%</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7330,23 +7330,23 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T88" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U88" t="n">
         <v>39</v>
       </c>
       <c r="V88" t="n">
-        <v>61.48852</v>
+        <v>47.43121</v>
       </c>
       <c r="W88" t="n">
-        <v>-74.47212</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3408</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dalquier (rg 8 lot 14)</t>
+          <t>Guimond</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
+          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7408,23 +7408,23 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T89" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="U89" t="n">
         <v>39</v>
       </c>
       <c r="V89" t="n">
-        <v>48.68159</v>
+        <v>47.37388</v>
       </c>
       <c r="W89" t="n">
-        <v>-78.15861</v>
+        <v>-79.13840999999999</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Montserrat</t>
+          <t>Kerwin</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -7444,12 +7444,12 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 13.93 g/t, Ag 2.30 g/t</t>
+          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7495,14 +7495,14 @@
         <v>39</v>
       </c>
       <c r="V90" t="n">
-        <v>48.29238</v>
+        <v>48.39017</v>
       </c>
       <c r="W90" t="n">
-        <v>-79.38334999999999</v>
+        <v>-78.41151000000001</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5798</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gand II: Rivière Opawica</t>
+          <t>Weedon-Nord</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -7522,12 +7522,12 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Gold, Manganese</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Au 7.20 g/t</t>
+          <t>Cu 4%, Ag 63.60 g/t, Au 0.34 g/t, Zn 0.928%, Mn 0.365%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7573,14 +7573,14 @@
         <v>39</v>
       </c>
       <c r="V91" t="n">
-        <v>49.64493</v>
+        <v>45.81174</v>
       </c>
       <c r="W91" t="n">
-        <v>-75.94013</v>
+        <v>-71.52803</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2988</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2263</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Anaconda Brass</t>
+          <t>Western Buff II : Veine 2</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Au 5.10 g/t, Cu 1.29%</t>
+          <t>Cu 6.03%, Ag 6.68 g/t</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7651,14 +7651,560 @@
         <v>39</v>
       </c>
       <c r="V92" t="n">
-        <v>48.34022</v>
+        <v>48.15294</v>
       </c>
       <c r="W92" t="n">
-        <v>-78.74214000000001</v>
+        <v>-79.28442</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5739</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Dalquier (rg 8 lot 14)</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Zinc, Lead, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>6</v>
+      </c>
+      <c r="T93" t="n">
+        <v>150</v>
+      </c>
+      <c r="U93" t="n">
+        <v>39</v>
+      </c>
+      <c r="V93" t="n">
+        <v>48.68159</v>
+      </c>
+      <c r="W93" t="n">
+        <v>-78.15861</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>East Dalquier</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>W 1.86%, Au 5.49 g/t</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>25</v>
+      </c>
+      <c r="U94" t="n">
+        <v>39</v>
+      </c>
+      <c r="V94" t="n">
+        <v>48.65564</v>
+      </c>
+      <c r="W94" t="n">
+        <v>-78.02257</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Norseman-2</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>4</v>
+      </c>
+      <c r="T95" t="n">
+        <v>100</v>
+      </c>
+      <c r="U95" t="n">
+        <v>39</v>
+      </c>
+      <c r="V95" t="n">
+        <v>48.05412</v>
+      </c>
+      <c r="W95" t="n">
+        <v>-79.17482</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Kidd Creek - Zone Bréchique</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Au 13.20 g/t, Ag 2.40 g/t</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>25</v>
+      </c>
+      <c r="U96" t="n">
+        <v>39</v>
+      </c>
+      <c r="V96" t="n">
+        <v>48.23459</v>
+      </c>
+      <c r="W96" t="n">
+        <v>-79.1983</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5126</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Brompton Copper</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Zinc, Nickel</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I97" t="b">
+        <v>0</v>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>3</v>
+      </c>
+      <c r="T97" t="n">
+        <v>75</v>
+      </c>
+      <c r="U97" t="n">
+        <v>39</v>
+      </c>
+      <c r="V97" t="n">
+        <v>45.48343</v>
+      </c>
+      <c r="W97" t="n">
+        <v>-72.10835</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fayolle (Renault)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Lead, Molybdenum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I98" t="b">
+        <v>0</v>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Au 6.68 g/t, Cu 3.9%</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>25</v>
+      </c>
+      <c r="U98" t="n">
+        <v>39</v>
+      </c>
+      <c r="V98" t="n">
+        <v>48.20461</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-79.4071</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Pitchvein (RB Gold Zone)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Gold, Molybdenum, Silver, Lead, Antimony</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I99" t="b">
+        <v>0</v>
+      </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Au 11.45 g/t, Cu 0.814%, Ag 29.50 g/t, Zn 0.93%</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
+        <v>25</v>
+      </c>
+      <c r="U99" t="n">
+        <v>39</v>
+      </c>
+      <c r="V99" t="n">
+        <v>48.19746</v>
+      </c>
+      <c r="W99" t="n">
+        <v>-79.41042</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5111</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X99"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver, Gold</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Delhi Pacific</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>56.40258</v>
+        <v>58.96701</v>
       </c>
       <c r="W3" t="n">
-        <v>-67.9023</v>
+        <v>-69.59563</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
+          <t>K2-20-01 et K2-20-05</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Egp, Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
+          <t>Au 8.92 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>58.23464</v>
+        <v>52.27809</v>
       </c>
       <c r="W4" t="n">
-        <v>-69.92364000000001</v>
+        <v>-77.92237</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=61815</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chibtown</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>56.39152</v>
+        <v>59.80634</v>
       </c>
       <c r="W5" t="n">
-        <v>-67.87103</v>
+        <v>-75.01831</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Venditelli (Lac St-Pierre-Gold)</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Egp, Palladium</t>
+          <t>Silver, Copper, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>58.15377</v>
+        <v>52.21818</v>
       </c>
       <c r="W6" t="n">
-        <v>-69.53443</v>
+        <v>-77.45902</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Franelle</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tungsten, Gold, Silver, Copper, Lead</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Cu 60%, Ag 43.49 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>53.39458</v>
+        <v>55.55824</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.44683999999999</v>
+        <v>-67.34804</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Au-26</t>
+          <t>Rivière Pontois</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc, Arsenic</t>
+          <t>Copper, Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
+          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1090,23 +1090,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U8" t="n">
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>53.39936</v>
+        <v>53.51426</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.29407</v>
+        <v>-74.51608</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dessureault (Lac Rougemont)</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>58.02817</v>
+        <v>48.31932</v>
       </c>
       <c r="W9" t="n">
-        <v>-69.57268000000001</v>
+        <v>-64.9713</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>Lac Retty - Lac Pogo</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Gold, Platinum, Palladium, Egp, Nickel, Copper, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>53.40387</v>
+        <v>55.23261</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.30118</v>
+        <v>-66.16073</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>Golden Butterfly</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Nickel, Palladium, Gold, Copper, Lead, Cobalt, Egp</t>
+          <t>Gold, Silver, Iron</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1324,23 +1324,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>53.39996</v>
+        <v>51.99697</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.33163999999999</v>
+        <v>-75.22655</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>Relique</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Egp, Palladium, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Au 10.40 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>53.34013</v>
+        <v>49.61809</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.32316</v>
+        <v>-75.69525</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2962</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>Barre de fer</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rh, Chromium, Egp, Nickel, Gold, Palladium, Platinum, Copper</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>53.39786</v>
+        <v>51.6436</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.30625000000001</v>
+        <v>-67.33749</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Franelle</t>
+          <t>Gauthier-Mcneely</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Zinc, Silver, Copper, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 60%, Ag 43.49 g/t</t>
+          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>55.55824</v>
+        <v>55.62931</v>
       </c>
       <c r="W14" t="n">
-        <v>-67.34804</v>
+        <v>-66.83314</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>Qarqasiaq - C</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Copper, Platinum, Palladium, Egp, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>53.41679</v>
+        <v>60.17776</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.27167</v>
+        <v>-70.30297</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4930N-1</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chromium, Copper, Nickel, Silver</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>53.38014</v>
+        <v>60.16686</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.28712</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>Lac Retty - Lac Bleu</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten, Copper, Zinc, Lead</t>
+          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>53.39256</v>
+        <v>55.22879</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.43714</v>
+        <v>-66.12246</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>Lac Walsh-Ouest</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Cu 3.05%, Ni 0.67%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>53.35887</v>
+        <v>55.15269</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.31016</v>
+        <v>-66.35399</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Lac du Canoe</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 40.00 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>49.84595</v>
+        <v>55.23434</v>
       </c>
       <c r="W19" t="n">
-        <v>-70.57626</v>
+        <v>-67.62649</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Croix-3</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Iron, Cobalt</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.24734</v>
+        <v>49.05483</v>
       </c>
       <c r="W20" t="n">
-        <v>-71.98866</v>
+        <v>-75.39637999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fort Chimo (Lac Plissé)</t>
+          <t>Lac Fecteau Est</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Zinc, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
+          <t>Au 8.80 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>58.12861</v>
+        <v>49.03096</v>
       </c>
       <c r="W21" t="n">
-        <v>-69.55745</v>
+        <v>-75.24721</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qarqasiaq - C</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Palladium, Platinum, Copper, Nickel, Egp, Cobalt, Gold</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>60.17776</v>
+        <v>49.82919</v>
       </c>
       <c r="W22" t="n">
-        <v>-70.30297</v>
+        <v>-70.58076</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lac Rivon-Ouest</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum, Zinc</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>51.72313</v>
+        <v>49.84595</v>
       </c>
       <c r="W23" t="n">
-        <v>-72.79697</v>
+        <v>-70.57626</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Riv. Cheno-Ouest</t>
+          <t>Lac Phooey</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>U 1.2%</t>
+          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2338,23 +2338,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T24" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U24" t="n">
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>51.53813</v>
+        <v>49.32384</v>
       </c>
       <c r="W24" t="n">
-        <v>-72.67167999999999</v>
+        <v>-75.02628</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4564</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mine Renzy</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,17 +2374,17 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Palladium, Platinum, Cobalt, Chromium, Gold, Egp, Silver</t>
+          <t>Silver, Copper, Zinc, Manganese</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>766 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ni 2.3%, Cu 1.75%, Co 0.11%, Pt 0.66 g/t, Pd 0.53 g/t</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>46.81194</v>
+        <v>46.00535</v>
       </c>
       <c r="W25" t="n">
-        <v>-76.70332999999999</v>
+        <v>-71.70357</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4560</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
+          <t>Lac Rond</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium, Egp, Gold, Copper</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 21.70 g/t</t>
+          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>57.94973</v>
+        <v>55.28891</v>
       </c>
       <c r="W26" t="n">
-        <v>-69.51281</v>
+        <v>-65.74114</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Erickson Sud - Goose Pond</t>
+          <t>Mousquetaires</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Palladium, Gold, Platinum, Copper, Nickel, Egp, Cobalt</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
+          <t>Cu 13.7%, Ag 10.40 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>57.99255</v>
+        <v>60.29225</v>
       </c>
       <c r="W27" t="n">
-        <v>-69.72347000000001</v>
+        <v>-75.42643</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58434</t>
         </is>
       </c>
     </row>
@@ -2598,22 +2598,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Subtile</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium</t>
+          <t>Tungsten, Zinc, Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 141.00 g/t, Ag 915.00 g/t, W 0.476%, Zn 7.87%, Cu 0.57%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2650,23 +2650,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>46.265</v>
+        <v>60.35882</v>
       </c>
       <c r="W28" t="n">
-        <v>-71.21259999999999</v>
+        <v>-75.39583</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58443</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rochelom</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.77064</v>
+        <v>49.83681</v>
       </c>
       <c r="W29" t="n">
-        <v>-76.01858</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Goshawk</t>
+          <t>Sond. Umex 132</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Lead, Gold, Zinc, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
+          <t>Cu 4%, Zn 6%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>61.56992</v>
+        <v>49.79699</v>
       </c>
       <c r="W30" t="n">
-        <v>-75.20258</v>
+        <v>-75.81529</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Destorbelle</t>
+          <t>Marguerite</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 8.20 g/t</t>
+          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>48.4465</v>
+        <v>48.29078</v>
       </c>
       <c r="W31" t="n">
-        <v>-78.85312999999999</v>
+        <v>-69.96804</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 31.13 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>55.2524</v>
+        <v>45.03676</v>
       </c>
       <c r="W32" t="n">
-        <v>-67.95193</v>
+        <v>-72.77243</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gauthier-Mcneely</t>
+          <t>Lac Chicobi-2</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Nickel</t>
+          <t>Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
+          <t>Ag 932.70 g/t, Pb 19.2%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>55.62931</v>
+        <v>48.83881</v>
       </c>
       <c r="W33" t="n">
-        <v>-66.83314</v>
+        <v>-78.52331</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4194</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ganiq</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Uranium, Lead, Copper</t>
+          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>U 0.77%, Cu 0.52%, Pb 0.82%</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>53.7831</v>
+        <v>55.5908</v>
       </c>
       <c r="W34" t="n">
-        <v>-75.64593000000001</v>
+        <v>-71.13463</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4528</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pio - Filons Est et Ouest</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Egp, Palladium, Platinum, Copper, Nickel, Silver, Cobalt, Gold</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>58.96701</v>
+        <v>55.61902</v>
       </c>
       <c r="W35" t="n">
-        <v>-69.59563</v>
+        <v>-71.054</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qarqasiaq - A1</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Egp, Palladium, Platinum, Nickel, Copper, Cobalt</t>
+          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>60.16686</v>
+        <v>55.58892</v>
       </c>
       <c r="W36" t="n">
-        <v>-70.29604999999999</v>
+        <v>-71.1636</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lac du Canoe</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 40.00 g/t</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>55.23434</v>
+        <v>55.68696</v>
       </c>
       <c r="W37" t="n">
-        <v>-67.62649</v>
+        <v>-71.02212</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PG-221094</t>
+          <t>Ruisseau Lapointe</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Lead, Silver, Arsenic, Copper</t>
+          <t>Lead, Copper, Silver, Manganese, Zinc, Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
+          <t>Cu 2.9%, Ag 170.00 g/t, Au 0.39 g/t, Pb 1.77%, Zn 0.44%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>53.40779</v>
+        <v>47.91173</v>
       </c>
       <c r="W38" t="n">
-        <v>-77.28636</v>
+        <v>-74.4177</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=59593</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lac Dunphy</t>
+          <t>Delta (Zone D-9)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Egp, Nickel, Platinum, Gold, Copper, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
+          <t>Pd 28.00 g/t, Ni 7.2%, Cu 5.9%, Au 1.80 g/t, Pt 4.13 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>56.05097</v>
+        <v>61.48634</v>
       </c>
       <c r="W39" t="n">
-        <v>-67.71257</v>
+        <v>-74.44287</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3401</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B-88-01</t>
+          <t>Lac Lanctôt</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Gold, Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ag 203.00 g/t, Cu 1.56%</t>
+          <t>Zn 11.7%, Au 1.30 g/t, Ag 34.00 g/t, Cu 0.48%, Pb 0.69%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>45.52488</v>
+        <v>47.2105</v>
       </c>
       <c r="W40" t="n">
-        <v>-72.07191</v>
+        <v>-72.46509</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3297</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Riv. Cascapedia</t>
+          <t>Lac Viking</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nickel, Arsenic, Chromium, Cobalt, Antimony</t>
+          <t>Gold, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Ni 12.8%, Co 0.13%, As 11.8%, Cr 0.14%</t>
+          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>48.84847</v>
+        <v>47.20549</v>
       </c>
       <c r="W41" t="n">
-        <v>-66.39704</v>
+        <v>-72.45211999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6070</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Josette</t>
+          <t>Principal (Zone Olga)</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Etr, Iron, Tungsten, Uranium, Thorium, Copper, Y, Silver, Gold</t>
+          <t>Copper, Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>W 0.18%, Cu 2.81%, U 0.0654%, Ag 13.00 g/t, Au 0.15 g/t</t>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>51.05069</v>
+        <v>49.78784</v>
       </c>
       <c r="W42" t="n">
-        <v>-65.27048000000001</v>
+        <v>-77.08529</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6032</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ruisseau 17e Mille</t>
+          <t>Lac Noach-Sud</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Platinum, Chromium</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Ni 11.7%, Pt 1.70 g/t, Cr 0.25%, EGP 0.00017%</t>
+          <t>Zn 9.8%, Cu 1.97%, Ag 44.00 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>48.86434</v>
+        <v>53.60084</v>
       </c>
       <c r="W43" t="n">
-        <v>-66.26813</v>
+        <v>-77.60271</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6072</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3442</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Iron, Nickel, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>48.32328</v>
+        <v>49.63941</v>
       </c>
       <c r="W44" t="n">
-        <v>-79.44637</v>
+        <v>-76.90893</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>49.83681</v>
+        <v>49.59836</v>
       </c>
       <c r="W45" t="n">
-        <v>-70.57877999999999</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>49.82919</v>
+        <v>48.09296</v>
       </c>
       <c r="W46" t="n">
-        <v>-70.58076</v>
+        <v>-66.78681</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cr-2</t>
+          <t>Étoile d'or</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Palladium, Platinum, Rh, Gold, Iron, Chromium, Nickel, Copper, Egp, Cobalt</t>
+          <t>Lead, Copper, Zinc, Bismuth, Molybdenum, Silver, Cadmium, Gold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Pd 11.88 g/t, Ni 2.4%, Cu 2.36%, Pt 4.20 g/t, Au 1.30 g/t</t>
+          <t>Bi 1.7%, Ag 505.00 g/t, Zn 7.84%, Mo 0.882%, Cu 1.6%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>53.39341</v>
+        <v>45.42701</v>
       </c>
       <c r="W47" t="n">
-        <v>-77.30141</v>
+        <v>-71.29181</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6004</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3321</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sainte-Cécile (Maheu) - ancien</t>
+          <t>Robidoux-appalaches</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Molybdenum, Silver, Zinc, Lead, Bismuth, Gold, Copper</t>
+          <t>Lead, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
+          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>45.67446</v>
+        <v>48.35381</v>
       </c>
       <c r="W48" t="n">
-        <v>-70.96669</v>
+        <v>-65.56434</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Lepage No 2</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Zinc, Barium, Cadmium, Mercury</t>
+          <t>Gold, Arsenic, Antimony</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Zn 31.5%</t>
+          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4288,23 +4288,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U49" t="n">
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>46.11447</v>
+        <v>48.33322</v>
       </c>
       <c r="W49" t="n">
-        <v>-75.95323</v>
+        <v>-66.99834</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Harriman-1 (New Richmond-1)</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Palladium, Nickel, Egp, Copper, Platinum</t>
+          <t>Antimony, Gold, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>Sb 43.8%, Au 13.70 g/t, Ag 4.50 g/t</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>55.58892</v>
+        <v>48.24307</v>
       </c>
       <c r="W50" t="n">
-        <v>-71.1636</v>
+        <v>-65.79867</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3578</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Castor</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
+          <t>Silver, Gold, Antimony, Arsenic, Barium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>Sb 47.6%, Au 30.00 g/t, Ag 110.00 g/t, As 1.8%, Ba 0.51%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>55.5908</v>
+        <v>48.08376</v>
       </c>
       <c r="W51" t="n">
-        <v>-71.13463</v>
+        <v>-66.92106</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3456</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Big Dragon</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Cobalt, Palladium, Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>Au 6.57 g/t</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>55.61902</v>
+        <v>48.23154</v>
       </c>
       <c r="W52" t="n">
-        <v>-71.054</v>
+        <v>-66.80576000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,33 +4558,33 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Copper, Tungsten, Silver</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>29 kt</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4600,23 +4600,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U53" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="V53" t="n">
-        <v>45.03676</v>
+        <v>48.24607</v>
       </c>
       <c r="W53" t="n">
-        <v>-72.77243</v>
+        <v>-79.50617</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,33 +4636,33 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>16 kt</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4678,23 +4678,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U54" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="V54" t="n">
-        <v>55.68696</v>
+        <v>49.75792</v>
       </c>
       <c r="W54" t="n">
-        <v>-71.02212</v>
+        <v>-74.3342</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Viau (ou Bordulac)</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,33 +4714,33 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 31.00 g/t</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4756,23 +4756,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T55" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U55" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="V55" t="n">
-        <v>48.26547</v>
+        <v>49.01028</v>
       </c>
       <c r="W55" t="n">
-        <v>-79.41453</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Solbec Copper</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4797,28 +4797,28 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Copper, Silver, Cobalt, Tungsten, Tellurium</t>
+          <t>Gold, Cadmium, Lead, Silver, Copper, Zinc, Cs</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>2.1 Mt</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4834,23 +4834,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U56" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V56" t="n">
-        <v>59.80634</v>
+        <v>45.80476</v>
       </c>
       <c r="W56" t="n">
-        <v>-75.01831</v>
+        <v>-71.28747</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
         </is>
       </c>
     </row>
@@ -4860,11 +4860,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lac Tarsac : Veine I et III</t>
+          <t>Galloway : Hendrick</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4875,16 +4875,16 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Gold, Molybdenum, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Au 11.66 g/t</t>
+          <t>Au 1.12 g/t, Cu 0.98%, Mo 0.306%, Ag 36.20 g/t, Zn 0.566%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4912,23 +4912,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="U57" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V57" t="n">
-        <v>48.3561</v>
+        <v>48.18985</v>
       </c>
       <c r="W57" t="n">
-        <v>-79.43788000000001</v>
+        <v>-79.42233</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67506</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>Lavoie (Zone L)</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,21 +4948,21 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Uranium, Molybdenum, Vanadium, Lead, Thorium, Silver</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4990,23 +4990,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U58" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V58" t="n">
-        <v>49.59836</v>
+        <v>52.18408</v>
       </c>
       <c r="W58" t="n">
-        <v>-76.92194000000001</v>
+        <v>-70.99409</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,33 +5026,33 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Iron</t>
+          <t>Rh, Platinum, Nickel, Egp, Chromium, Palladium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5068,23 +5068,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T59" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U59" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V59" t="n">
-        <v>49.63941</v>
+        <v>46.04018</v>
       </c>
       <c r="W59" t="n">
-        <v>-76.90893</v>
+        <v>-71.28144</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Galloway : GP</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5109,16 +5109,16 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Au 8.66 g/t, Cu 2%, Ag 4.53 g/t</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5146,23 +5146,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U60" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="V60" t="n">
-        <v>48.71945</v>
+        <v>48.19278</v>
       </c>
       <c r="W60" t="n">
-        <v>-78.33144</v>
+        <v>-79.4164</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5189</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>PUI-87-43</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,12 +5182,12 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="I61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Au 3.73 g/t</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U61" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V61" t="n">
-        <v>46.26532</v>
+        <v>49.68374</v>
       </c>
       <c r="W61" t="n">
-        <v>-71.28788</v>
+        <v>-78.9585</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Kl Zone</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="I62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Au 5.17 g/t</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5302,23 +5302,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U62" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V62" t="n">
-        <v>48.70382</v>
+        <v>49.66889</v>
       </c>
       <c r="W62" t="n">
-        <v>-78.25041</v>
+        <v>-78.37572</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Pio - Zone Du Synclinal</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Silver</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="I63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T63" t="n">
-        <v>275</v>
+        <v>125</v>
       </c>
       <c r="U63" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V63" t="n">
-        <v>48.57696</v>
+        <v>58.99163</v>
       </c>
       <c r="W63" t="n">
-        <v>-78.14164</v>
+        <v>-69.61172000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
+          <t>Rambull</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Cadmium, Lead, Silver, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5458,23 +5458,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T64" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U64" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V64" t="n">
-        <v>45.29835</v>
+        <v>48.4824</v>
       </c>
       <c r="W64" t="n">
-        <v>-72.31643</v>
+        <v>-78.10243</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
         </is>
       </c>
     </row>
@@ -5484,22 +5484,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>Kerwin</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Lead, Silver, Zinc</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5536,23 +5536,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T65" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="U65" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V65" t="n">
-        <v>45.99171</v>
+        <v>48.39017</v>
       </c>
       <c r="W65" t="n">
-        <v>-71.70617</v>
+        <v>-78.41151000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Glencoe</t>
+          <t>East Mac (Indice Nord)</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5572,12 +5572,12 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="I66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
+          <t>Au 108.96 g/t, Ag 1480.90 g/t</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U66" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V66" t="n">
-        <v>45.32873</v>
+        <v>48.6126</v>
       </c>
       <c r="W66" t="n">
-        <v>-72.47421</v>
+        <v>-77.97836</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2804</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Petit Lac Brompton</t>
+          <t>Norzone</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Gold, Silver</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
+          <t>Au 8.25 g/t, Ag 134.22 g/t</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5692,23 +5692,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="U67" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="V67" t="n">
-        <v>45.44828</v>
+        <v>48.18843</v>
       </c>
       <c r="W67" t="n">
-        <v>-72.1057</v>
+        <v>-78.84910000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1700</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,17 +5728,17 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5776,17 +5776,17 @@
         <v>25</v>
       </c>
       <c r="U68" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="V68" t="n">
-        <v>49.75792</v>
+        <v>55.2524</v>
       </c>
       <c r="W68" t="n">
-        <v>-74.3342</v>
+        <v>-67.95193</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
+          <t>Lac Wachigabau</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>29 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
+          <t>Cu 4.46%, Au 3.14 g/t, Ag 16.60 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5854,17 +5854,17 @@
         <v>25</v>
       </c>
       <c r="U69" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="V69" t="n">
-        <v>48.24607</v>
+        <v>49.53002</v>
       </c>
       <c r="W69" t="n">
-        <v>-79.50617</v>
+        <v>-75.92335</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2974</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Gand II: Rivière Opawica</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5884,17 +5884,17 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Au 7.20 g/t</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5926,23 +5926,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="U70" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="V70" t="n">
-        <v>49.01028</v>
+        <v>49.64493</v>
       </c>
       <c r="W70" t="n">
-        <v>-66.00369999999999</v>
+        <v>-75.94013</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2988</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Bernierville-WNW</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,17 +5962,17 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold, Cs</t>
+          <t>Molybdenum, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Cu 4.96%, Mo 0.2%, Ag 14.50 g/t, Pb 0.31%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6004,23 +6004,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U71" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V71" t="n">
-        <v>45.80476</v>
+        <v>46.11365</v>
       </c>
       <c r="W71" t="n">
-        <v>-71.28747</v>
+        <v>-71.60383</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3611</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Drouet</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,17 +6040,17 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Au 6.00 g/t</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U72" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V72" t="n">
-        <v>46.04018</v>
+        <v>49.49319</v>
       </c>
       <c r="W72" t="n">
-        <v>-71.28144</v>
+        <v>-75.12523</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Chioak</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Uranium, Gold, Lead, Vanadium, Molybdenum, Silver, Thorium</t>
+          <t>Uranium, Copper, Thorium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>U 0.425%, Cu 0.15%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6160,23 +6160,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T73" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U73" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V73" t="n">
-        <v>52.18408</v>
+        <v>58.12937</v>
       </c>
       <c r="W73" t="n">
-        <v>-70.99409</v>
+        <v>-70.18866</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
         </is>
       </c>
     </row>
@@ -6186,11 +6186,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Galloway : Hendrick</t>
+          <t>Delta (Zone D-8)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gold, Copper, Molybdenum, Silver, Zinc</t>
+          <t>Gold, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I74" t="b">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 1.12 g/t, Cu 0.98%, Mo 0.306%, Ag 36.20 g/t, Zn 0.566%</t>
+          <t>Ni 7.8%, Pd 25.50 g/t, Cu 4%, Au 3.63 g/t, Pt 7.96 g/t</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6238,23 +6238,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T74" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U74" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V74" t="n">
-        <v>48.18985</v>
+        <v>61.48642</v>
       </c>
       <c r="W74" t="n">
-        <v>-79.42233</v>
+        <v>-74.46145</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67506</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3396</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Galloway : GP</t>
+          <t>Cedar Rapids-Zone 1</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6274,17 +6274,17 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Molybdenum</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 8.66 g/t, Cu 2%, Ag 4.53 g/t</t>
+          <t>Au 77.80 g/t, Cu 1.45%, Ag 68.60 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6316,23 +6316,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T75" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V75" t="n">
-        <v>48.19278</v>
+        <v>49.0051</v>
       </c>
       <c r="W75" t="n">
-        <v>-79.4164</v>
+        <v>-77.04089</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5189</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3521</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Orco-Tranchée 35-2</t>
+          <t>Albert (LH-90)</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6352,12 +6352,12 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Copper, Lead</t>
+          <t>Zinc, Copper, Silver, Lead</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 15.57 g/t, Ag 82.60 g/t, Zn 1%</t>
+          <t>Pb 50.6%, Zn 20.5%, Ag 173.70 g/t, Cu 0.53%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6403,14 +6403,14 @@
         <v>39</v>
       </c>
       <c r="V76" t="n">
-        <v>48.42459</v>
+        <v>48.74517</v>
       </c>
       <c r="W76" t="n">
-        <v>-78.74975999999999</v>
+        <v>-66.13224</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5730</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3389</t>
         </is>
       </c>
     </row>
@@ -6420,22 +6420,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Anaconda Brass</t>
+          <t>Delta (Zone Nord)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Nickel, Palladium, Egp, Rh, Copper, Platinum, Ru, Cobalt</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Au 5.10 g/t, Cu 1.29%</t>
+          <t>Pd 17.30 g/t, Ni 3.32%, Pt 2.74 g/t, Cu 0.75%, Co 0.18%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6481,14 +6481,14 @@
         <v>39</v>
       </c>
       <c r="V77" t="n">
-        <v>48.34022</v>
+        <v>61.48852</v>
       </c>
       <c r="W77" t="n">
-        <v>-78.74214000000001</v>
+        <v>-74.47212</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5739</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3408</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Copperstream-Ouest</t>
+          <t>Echo-1</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6508,12 +6508,12 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum, Cobalt, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 8.96 g/t</t>
+          <t>Ni 2.35%, Cu 2.6%, Co 0.56%, Pd 4.46 g/t, Pt 1.64 g/t</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6559,1652 +6559,14 @@
         <v>39</v>
       </c>
       <c r="V78" t="n">
-        <v>48.48146</v>
+        <v>61.44723</v>
       </c>
       <c r="W78" t="n">
-        <v>-78.14755</v>
+        <v>-74.72001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1541</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Golden Rock</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I79" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Au 27.23 g/t</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="n">
-        <v>1</v>
-      </c>
-      <c r="T79" t="n">
-        <v>25</v>
-      </c>
-      <c r="U79" t="n">
-        <v>39</v>
-      </c>
-      <c r="V79" t="n">
-        <v>48.81681</v>
-      </c>
-      <c r="W79" t="n">
-        <v>-78.47028</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2694</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I80" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Au 20.57 g/t</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="n">
-        <v>8</v>
-      </c>
-      <c r="T80" t="n">
-        <v>200</v>
-      </c>
-      <c r="U80" t="n">
-        <v>39</v>
-      </c>
-      <c r="V80" t="n">
-        <v>48.45213</v>
-      </c>
-      <c r="W80" t="n">
-        <v>-78.82693</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5662</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Pio - Zone Du Synclinal</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="n">
-        <v>5</v>
-      </c>
-      <c r="T81" t="n">
-        <v>125</v>
-      </c>
-      <c r="U81" t="n">
-        <v>39</v>
-      </c>
-      <c r="V81" t="n">
-        <v>58.99163</v>
-      </c>
-      <c r="W81" t="n">
-        <v>-69.61172000000001</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Ruisseau Castor</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Iron, Gold</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Cu 2.94%, Ag 65.80 g/t, Au 0.16 g/t</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="n">
-        <v>4</v>
-      </c>
-      <c r="T82" t="n">
-        <v>100</v>
-      </c>
-      <c r="U82" t="n">
-        <v>39</v>
-      </c>
-      <c r="V82" t="n">
-        <v>48.88387</v>
-      </c>
-      <c r="W82" t="n">
-        <v>-66.05629</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6068</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Lac Colnet - Ouest</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I83" t="b">
-        <v>0</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Au 4.09 g/t, Ag 2.30 g/t</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="n">
-        <v>2</v>
-      </c>
-      <c r="T83" t="n">
-        <v>50</v>
-      </c>
-      <c r="U83" t="n">
-        <v>39</v>
-      </c>
-      <c r="V83" t="n">
-        <v>48.30437</v>
-      </c>
-      <c r="W83" t="n">
-        <v>-79.39239999999999</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5846</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Montbray (Poirier-Leith) : Zone 1</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>4</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Au 10.24 g/t, Ag 2.90 g/t</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="n">
-        <v>5</v>
-      </c>
-      <c r="T84" t="n">
-        <v>125</v>
-      </c>
-      <c r="U84" t="n">
-        <v>39</v>
-      </c>
-      <c r="V84" t="n">
-        <v>48.33071</v>
-      </c>
-      <c r="W84" t="n">
-        <v>-79.43351</v>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5929</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Rambull</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I85" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="n">
-        <v>4</v>
-      </c>
-      <c r="T85" t="n">
-        <v>100</v>
-      </c>
-      <c r="U85" t="n">
-        <v>39</v>
-      </c>
-      <c r="V85" t="n">
-        <v>48.4824</v>
-      </c>
-      <c r="W85" t="n">
-        <v>-78.10243</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Fabre Nord</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I86" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Au 6.48 g/t</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="n">
-        <v>2</v>
-      </c>
-      <c r="T86" t="n">
-        <v>50</v>
-      </c>
-      <c r="U86" t="n">
-        <v>39</v>
-      </c>
-      <c r="V86" t="n">
-        <v>47.26406</v>
-      </c>
-      <c r="W86" t="n">
-        <v>-79.40157000000001</v>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Montserrat</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Au 13.93 g/t, Ag 2.30 g/t</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="n">
-        <v>2</v>
-      </c>
-      <c r="T87" t="n">
-        <v>50</v>
-      </c>
-      <c r="U87" t="n">
-        <v>39</v>
-      </c>
-      <c r="V87" t="n">
-        <v>48.29238</v>
-      </c>
-      <c r="W87" t="n">
-        <v>-79.38334999999999</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5798</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Gold, Bismuth, Copper, Molybdenum, Silver</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I88" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="n">
-        <v>8</v>
-      </c>
-      <c r="T88" t="n">
-        <v>200</v>
-      </c>
-      <c r="U88" t="n">
-        <v>39</v>
-      </c>
-      <c r="V88" t="n">
-        <v>47.43121</v>
-      </c>
-      <c r="W88" t="n">
-        <v>-79.32868999999999</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Guimond</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I89" t="b">
-        <v>0</v>
-      </c>
-      <c r="J89" t="b">
-        <v>0</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="n">
-        <v>2</v>
-      </c>
-      <c r="T89" t="n">
-        <v>50</v>
-      </c>
-      <c r="U89" t="n">
-        <v>39</v>
-      </c>
-      <c r="V89" t="n">
-        <v>47.37388</v>
-      </c>
-      <c r="W89" t="n">
-        <v>-79.13840999999999</v>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Kerwin</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I90" t="b">
-        <v>0</v>
-      </c>
-      <c r="J90" t="b">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="n">
-        <v>2</v>
-      </c>
-      <c r="T90" t="n">
-        <v>50</v>
-      </c>
-      <c r="U90" t="n">
-        <v>39</v>
-      </c>
-      <c r="V90" t="n">
-        <v>48.39017</v>
-      </c>
-      <c r="W90" t="n">
-        <v>-78.41151000000001</v>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Weedon-Nord</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Silver, Gold, Manganese</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" t="b">
-        <v>0</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Cu 4%, Ag 63.60 g/t, Au 0.34 g/t, Zn 0.928%, Mn 0.365%</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="n">
-        <v>2</v>
-      </c>
-      <c r="T91" t="n">
-        <v>50</v>
-      </c>
-      <c r="U91" t="n">
-        <v>39</v>
-      </c>
-      <c r="V91" t="n">
-        <v>45.81174</v>
-      </c>
-      <c r="W91" t="n">
-        <v>-71.52803</v>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2263</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Western Buff II : Veine 2</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I92" t="b">
-        <v>0</v>
-      </c>
-      <c r="J92" t="b">
-        <v>0</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Cu 6.03%, Ag 6.68 g/t</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="n">
-        <v>1</v>
-      </c>
-      <c r="T92" t="n">
-        <v>25</v>
-      </c>
-      <c r="U92" t="n">
-        <v>39</v>
-      </c>
-      <c r="V92" t="n">
-        <v>48.15294</v>
-      </c>
-      <c r="W92" t="n">
-        <v>-79.28442</v>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5158</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Dalquier (rg 8 lot 14)</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Zinc, Lead, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" t="b">
-        <v>0</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Zn 9.7%, Au 2.10 g/t, Pb 1.6%, Ag 12.30 g/t</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="n">
-        <v>6</v>
-      </c>
-      <c r="T93" t="n">
-        <v>150</v>
-      </c>
-      <c r="U93" t="n">
-        <v>39</v>
-      </c>
-      <c r="V93" t="n">
-        <v>48.68159</v>
-      </c>
-      <c r="W93" t="n">
-        <v>-78.15861</v>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2227</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>East Dalquier</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="b">
-        <v>0</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>W 1.86%, Au 5.49 g/t</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="n">
-        <v>1</v>
-      </c>
-      <c r="T94" t="n">
-        <v>25</v>
-      </c>
-      <c r="U94" t="n">
-        <v>39</v>
-      </c>
-      <c r="V94" t="n">
-        <v>48.65564</v>
-      </c>
-      <c r="W94" t="n">
-        <v>-78.02257</v>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2213</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Norseman-2</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I95" t="b">
-        <v>0</v>
-      </c>
-      <c r="J95" t="b">
-        <v>0</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="n">
-        <v>4</v>
-      </c>
-      <c r="T95" t="n">
-        <v>100</v>
-      </c>
-      <c r="U95" t="n">
-        <v>39</v>
-      </c>
-      <c r="V95" t="n">
-        <v>48.05412</v>
-      </c>
-      <c r="W95" t="n">
-        <v>-79.17482</v>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Kidd Creek - Zone Bréchique</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I96" t="b">
-        <v>0</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Au 13.20 g/t, Ag 2.40 g/t</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="n">
-        <v>1</v>
-      </c>
-      <c r="T96" t="n">
-        <v>25</v>
-      </c>
-      <c r="U96" t="n">
-        <v>39</v>
-      </c>
-      <c r="V96" t="n">
-        <v>48.23459</v>
-      </c>
-      <c r="W96" t="n">
-        <v>-79.1983</v>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5126</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Brompton Copper</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Zinc, Nickel</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I97" t="b">
-        <v>0</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="n">
-        <v>3</v>
-      </c>
-      <c r="T97" t="n">
-        <v>75</v>
-      </c>
-      <c r="U97" t="n">
-        <v>39</v>
-      </c>
-      <c r="V97" t="n">
-        <v>45.48343</v>
-      </c>
-      <c r="W97" t="n">
-        <v>-72.10835</v>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Fayolle (Renault)</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Lead, Molybdenum</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I98" t="b">
-        <v>0</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Au 6.68 g/t, Cu 3.9%</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="n">
-        <v>1</v>
-      </c>
-      <c r="T98" t="n">
-        <v>25</v>
-      </c>
-      <c r="U98" t="n">
-        <v>39</v>
-      </c>
-      <c r="V98" t="n">
-        <v>48.20461</v>
-      </c>
-      <c r="W98" t="n">
-        <v>-79.4071</v>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5113</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Pitchvein (RB Gold Zone)</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Gold, Molybdenum, Silver, Lead, Antimony</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I99" t="b">
-        <v>0</v>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Au 11.45 g/t, Cu 0.814%, Ag 29.50 g/t, Zn 0.93%</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="n">
-        <v>1</v>
-      </c>
-      <c r="T99" t="n">
-        <v>25</v>
-      </c>
-      <c r="U99" t="n">
-        <v>39</v>
-      </c>
-      <c r="V99" t="n">
-        <v>48.19746</v>
-      </c>
-      <c r="W99" t="n">
-        <v>-79.41042</v>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5111</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3411</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X78"/>
+  <dimension ref="A1:X75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pio - Filons Est et Ouest</t>
+          <t>Marguerite</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>58.96701</v>
+        <v>48.29078</v>
       </c>
       <c r="W3" t="n">
-        <v>-69.59563</v>
+        <v>-69.96804</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K2-20-01 et K2-20-05</t>
+          <t>PAP Nord (Camp A-1)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 8.92 g/t</t>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>52.27809</v>
+        <v>60.2779</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.92237</v>
+        <v>-75.33311</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=61815</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>59.80634</v>
+        <v>49.59836</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.01831</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lidge</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Arsenic</t>
+          <t>Iron, Nickel, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>52.21818</v>
+        <v>49.63941</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.45902</v>
+        <v>-76.90893</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Franelle</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 60%, Ag 43.49 g/t</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>55.55824</v>
+        <v>48.71945</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.34804</v>
+        <v>-78.33144</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rivière Pontois</t>
+          <t>Cunning-Gault</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Gold, Arsenic, Silver</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
+          <t>Pb 32.7%, Zn 11.7%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1090,23 +1090,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>53.51426</v>
+        <v>48.72575</v>
       </c>
       <c r="W8" t="n">
-        <v>-74.51608</v>
+        <v>-64.47654</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5374</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Projet 70-Landome</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>48.31932</v>
+        <v>48.46123</v>
       </c>
       <c r="W9" t="n">
-        <v>-64.9713</v>
+        <v>-77.95265999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Pogo</t>
+          <t>Northern Canada</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Platinum, Palladium, Egp, Nickel, Copper, Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
+          <t>U 0.373%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>55.23261</v>
+        <v>50.39968</v>
       </c>
       <c r="W10" t="n">
-        <v>-66.16073</v>
+        <v>-62.92982</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5401</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Golden Butterfly</t>
+          <t>BJB - Rustcliff (Boudrias)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Iron</t>
+          <t>Silver, Gold, Copper, Lead</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1324,23 +1324,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>51.99697</v>
+        <v>50.31401</v>
       </c>
       <c r="W11" t="n">
-        <v>-75.22655</v>
+        <v>-62.73908</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Relique</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 10.40 g/t</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>49.61809</v>
+        <v>58.96701</v>
       </c>
       <c r="W12" t="n">
-        <v>-75.69525</v>
+        <v>-69.59563</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2962</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Barre de fer</t>
+          <t>Misery - Sond. ML14024</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Tungsten, Niobium, Zr, Etr, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
+          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>51.6436</v>
+        <v>55.35025</v>
       </c>
       <c r="W13" t="n">
-        <v>-67.33749</v>
+        <v>-63.8991</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gauthier-Mcneely</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Nickel</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
+          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>55.62931</v>
+        <v>61.52449</v>
       </c>
       <c r="W14" t="n">
-        <v>-66.83314</v>
+        <v>-72.77941</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qarqasiaq - C</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Platinum, Palladium, Egp, Nickel, Gold, Cobalt</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
+          <t>Cu 6.33%, Pd 2.55 g/t, Ni 0.69%, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>60.17776</v>
+        <v>61.55073</v>
       </c>
       <c r="W15" t="n">
-        <v>-70.30297</v>
+        <v>-72.66555</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qarqasiaq - A1</t>
+          <t>Spirit-1</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+          <t>Nickel, Cobalt, Platinum, Palladium, Egp, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
+          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>60.16686</v>
+        <v>61.39663</v>
       </c>
       <c r="W16" t="n">
-        <v>-70.29604999999999</v>
+        <v>-73.13239</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Bleu</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>55.22879</v>
+        <v>59.80634</v>
       </c>
       <c r="W17" t="n">
-        <v>-66.12246</v>
+        <v>-75.01831</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lac Walsh-Ouest</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 3.05%, Ni 0.67%</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>55.15269</v>
+        <v>52.17253</v>
       </c>
       <c r="W18" t="n">
-        <v>-66.35399</v>
+        <v>-76.55762</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -1896,11 +1896,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lac du Canoe</t>
+          <t>Monarch - Veine 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 40.00 g/t</t>
+          <t>Au 83.00 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>55.23434</v>
+        <v>48.23207</v>
       </c>
       <c r="W19" t="n">
-        <v>-67.62649</v>
+        <v>-79.41287</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Croix-3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Tungsten, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
+          <t>W 0.188%, Cu 4.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.05483</v>
+        <v>60.39318</v>
       </c>
       <c r="W20" t="n">
-        <v>-75.39637999999999</v>
+        <v>-75.53694</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lac Fecteau Est</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 8.80 g/t</t>
+          <t>Au 29.25 g/t, W 0.122%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.03096</v>
+        <v>52.64108</v>
       </c>
       <c r="W21" t="n">
-        <v>-75.24721</v>
+        <v>-75.67010999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Dessureault (Lac Rougemont)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.82919</v>
+        <v>58.02817</v>
       </c>
       <c r="W22" t="n">
-        <v>-70.58076</v>
+        <v>-69.57268000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Venditelli (Lac St-Pierre-Gold)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold, Palladium, Egp</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>49.84595</v>
+        <v>58.15377</v>
       </c>
       <c r="W23" t="n">
-        <v>-70.57626</v>
+        <v>-69.53443</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lac Phooey</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2338,23 +2338,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>49.32384</v>
+        <v>49.82919</v>
       </c>
       <c r="W24" t="n">
-        <v>-75.02628</v>
+        <v>-70.58076</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Eli SE</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc, Manganese</t>
+          <t>Vanadium, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Au 25.00 g/t, Cu 1.02%, V 0.228%, Ag 16.70 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>46.00535</v>
+        <v>53.10465</v>
       </c>
       <c r="W25" t="n">
-        <v>-71.70357</v>
+        <v>-77.28514</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=32103</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lac Rond</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Gold, Copper</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>55.28891</v>
+        <v>55.68696</v>
       </c>
       <c r="W26" t="n">
-        <v>-65.74114</v>
+        <v>-71.02212</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mousquetaires</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 13.7%, Ag 10.40 g/t</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>60.29225</v>
+        <v>55.58892</v>
       </c>
       <c r="W27" t="n">
-        <v>-75.42643</v>
+        <v>-71.1636</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58434</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Subtile</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tungsten, Zinc, Silver, Gold, Copper</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 141.00 g/t, Ag 915.00 g/t, W 0.476%, Zn 7.87%, Cu 0.57%</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>60.35882</v>
+        <v>55.61902</v>
       </c>
       <c r="W28" t="n">
-        <v>-75.39583</v>
+        <v>-71.054</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=58443</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Mauve</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 9.13 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.83681</v>
+        <v>52.68441</v>
       </c>
       <c r="W29" t="n">
-        <v>-70.57877999999999</v>
+        <v>-76.29656</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>49.79699</v>
+        <v>55.5908</v>
       </c>
       <c r="W30" t="n">
-        <v>-75.81529</v>
+        <v>-71.13463</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marguerite</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T31" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U31" t="n">
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>48.29078</v>
+        <v>46.26265</v>
       </c>
       <c r="W31" t="n">
-        <v>-69.96804</v>
+        <v>-71.21769</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>45.03676</v>
+        <v>46.26532</v>
       </c>
       <c r="W32" t="n">
-        <v>-72.77243</v>
+        <v>-71.28788</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac Chicobi-2</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Silver, Lead, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ag 932.70 g/t, Pb 19.2%</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>48.83881</v>
+        <v>45.03676</v>
       </c>
       <c r="W33" t="n">
-        <v>-78.52331</v>
+        <v>-72.77243</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4194</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Sond. 82-LD-D-6</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>Au 5.33 g/t, Ag 7.80 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>55.5908</v>
+        <v>48.47521</v>
       </c>
       <c r="W34" t="n">
-        <v>-71.13463</v>
+        <v>-77.92301999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5471</t>
         </is>
       </c>
     </row>
@@ -3144,22 +3144,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>55.61902</v>
+        <v>46.265</v>
       </c>
       <c r="W35" t="n">
-        <v>-71.054</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lafrance (Willbob)</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>Au 6.56 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>55.58892</v>
+        <v>58.00928</v>
       </c>
       <c r="W36" t="n">
-        <v>-71.1636</v>
+        <v>-69.53870999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=34117</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Fort Chimo (Lac Plissé)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Nickel, Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>55.68696</v>
+        <v>58.12861</v>
       </c>
       <c r="W37" t="n">
-        <v>-71.02212</v>
+        <v>-69.55745</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ruisseau Lapointe</t>
+          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Manganese, Zinc, Gold</t>
+          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 2.9%, Ag 170.00 g/t, Au 0.39 g/t, Pb 1.77%, Zn 0.44%</t>
+          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>47.91173</v>
+        <v>58.23464</v>
       </c>
       <c r="W38" t="n">
-        <v>-74.4177</v>
+        <v>-69.92364000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=59593</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Delta (Zone D-9)</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Egp, Nickel, Platinum, Gold, Copper, Palladium, Cobalt</t>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Pd 28.00 g/t, Ni 7.2%, Cu 5.9%, Au 1.80 g/t, Pt 4.13 g/t</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>61.48634</v>
+        <v>46.26109</v>
       </c>
       <c r="W39" t="n">
-        <v>-74.44287</v>
+        <v>-71.22866</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3401</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lac Lanctôt</t>
+          <t>Mine Harvey Hill</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,17 +3544,17 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Silver, Copper</t>
+          <t>Uranium, Silver, Copper, Molybdenum, Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>453 kt</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Zn 11.7%, Au 1.30 g/t, Ag 34.00 g/t, Cu 0.48%, Pb 0.69%</t>
+          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3586,23 +3586,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U40" t="n">
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>47.2105</v>
+        <v>46.26423</v>
       </c>
       <c r="W40" t="n">
-        <v>-72.46509</v>
+        <v>-71.20608</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3297</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lac Viking</t>
+          <t>Erickson Sud - Goose Pond</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Silver</t>
+          <t>Platinum, Gold, Palladium, Egp, Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
+          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>47.20549</v>
+        <v>57.99255</v>
       </c>
       <c r="W41" t="n">
-        <v>-72.45211999999999</v>
+        <v>-69.72347000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>Au 21.70 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>49.78784</v>
+        <v>57.94973</v>
       </c>
       <c r="W42" t="n">
-        <v>-77.08529</v>
+        <v>-69.51281</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lac Noach-Sud</t>
+          <t>OTS-15</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Etr, Y, Thorium, Zinc, Uranium, Molybdenum, Lead, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Zn 9.8%, Cu 1.97%, Ag 44.00 g/t</t>
+          <t>U 1.91%, Ag 44.80 g/t, Mo 0.122%, Zn 0.873%, Pb 0.351%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T43" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U43" t="n">
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>53.60084</v>
+        <v>51.78273</v>
       </c>
       <c r="W43" t="n">
-        <v>-77.60271</v>
+        <v>-71.96856</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3442</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=33065</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Comtois NW</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Iron, Nickel, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>49.63941</v>
+        <v>49.18766</v>
       </c>
       <c r="W44" t="n">
-        <v>-76.90893</v>
+        <v>-77.31872</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>OTS-08</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Uranium, Zinc, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3976,23 +3976,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T45" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U45" t="n">
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>49.59836</v>
+        <v>51.78509</v>
       </c>
       <c r="W45" t="n">
-        <v>-76.92194000000001</v>
+        <v>-71.96465999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>48.09296</v>
+        <v>52.03235</v>
       </c>
       <c r="W46" t="n">
-        <v>-66.78681</v>
+        <v>-69.13816</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Étoile d'or</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lead, Copper, Zinc, Bismuth, Molybdenum, Silver, Cadmium, Gold</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Bi 1.7%, Ag 505.00 g/t, Zn 7.84%, Mo 0.882%, Cu 1.6%</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>45.42701</v>
+        <v>49.84595</v>
       </c>
       <c r="W47" t="n">
-        <v>-71.29181</v>
+        <v>-70.57626</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3321</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Robidoux-appalaches</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Zinc</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>48.35381</v>
+        <v>49.83681</v>
       </c>
       <c r="W48" t="n">
-        <v>-65.56434</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lepage No 2</t>
+          <t>Augustus Exploration</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Antimony</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
+          <t>Li 0.96%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>48.33322</v>
+        <v>48.42585</v>
       </c>
       <c r="W49" t="n">
-        <v>-66.99834</v>
+        <v>-77.87544</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5443</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Harriman-1 (New Richmond-1)</t>
+          <t>Martin-McNeely</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Antimony, Gold, Silver</t>
+          <t>Lithium, Molybdenum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Sb 43.8%, Au 13.70 g/t, Ag 4.50 g/t</t>
+          <t>Li 1%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>48.24307</v>
+        <v>48.43133</v>
       </c>
       <c r="W50" t="n">
-        <v>-65.79867</v>
+        <v>-77.89922</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3578</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5442</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Castor</t>
+          <t>Canadian Lithium</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tantalum</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Silver, Gold, Antimony, Arsenic, Barium</t>
+          <t>Tantalum, Lithium, Beryllium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sb 47.6%, Au 30.00 g/t, Ag 110.00 g/t, As 1.8%, Ba 0.51%</t>
+          <t>Li 0.814%, Be 0.0342%, Ta 0.019%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>48.08376</v>
+        <v>48.43096</v>
       </c>
       <c r="W51" t="n">
-        <v>-66.92106</v>
+        <v>-77.90853</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3456</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5441</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Big Dragon</t>
+          <t>Sond. Umex 132</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Au 6.57 g/t</t>
+          <t>Cu 4%, Zn 6%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>48.23154</v>
+        <v>49.79699</v>
       </c>
       <c r="W52" t="n">
-        <v>-66.80576000000001</v>
+        <v>-75.81529</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mine Dassen (Rocmec 1, Russian Kid)</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,33 +4558,33 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gold, Copper, Tungsten, Silver</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Au 32.92 g/t, W 0.0793%, Ag 13.71 g/t</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4600,23 +4600,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>48.24607</v>
+        <v>60.16686</v>
       </c>
       <c r="W53" t="n">
-        <v>-79.50617</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2375</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Amaruk</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4641,28 +4641,28 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4678,23 +4678,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U54" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>49.75792</v>
+        <v>59.60263</v>
       </c>
       <c r="W54" t="n">
-        <v>-74.3342</v>
+        <v>-74.86282</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Devlin (Riocanex)</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,17 +4714,17 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>16 kt</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 10.8%, Au 1.75 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4756,23 +4756,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U55" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V55" t="n">
-        <v>49.01028</v>
+        <v>49.75792</v>
       </c>
       <c r="W55" t="n">
-        <v>-66.00369999999999</v>
+        <v>-74.3342</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gold, Cadmium, Lead, Silver, Copper, Zinc, Cs</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4834,23 +4834,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U56" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V56" t="n">
-        <v>45.80476</v>
+        <v>49.01028</v>
       </c>
       <c r="W56" t="n">
-        <v>-71.28747</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -4860,22 +4860,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Galloway : Hendrick</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Copper, Zinc, Silver</t>
+          <t>Rh, Platinum, Nickel, Egp, Chromium, Palladium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Au 1.12 g/t, Cu 0.98%, Mo 0.306%, Ag 36.20 g/t, Zn 0.566%</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4912,23 +4912,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T57" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U57" t="n">
         <v>43</v>
       </c>
       <c r="V57" t="n">
-        <v>48.18985</v>
+        <v>46.04018</v>
       </c>
       <c r="W57" t="n">
-        <v>-79.42233</v>
+        <v>-71.28144</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67506</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Solbec Copper</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,17 +5026,17 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rh, Platinum, Nickel, Egp, Chromium, Palladium</t>
+          <t>Gold, Cadmium, Lead, Silver, Copper, Zinc, Cs</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I59" t="b">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>2.1 Mt</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5068,23 +5068,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="U59" t="n">
         <v>43</v>
       </c>
       <c r="V59" t="n">
-        <v>46.04018</v>
+        <v>45.80476</v>
       </c>
       <c r="W59" t="n">
-        <v>-71.28144</v>
+        <v>-71.28747</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Galloway : GP</t>
+          <t>Chioak</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5104,17 +5104,17 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Gold, Molybdenum, Silver</t>
+          <t>Uranium, Copper, Thorium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I60" t="b">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Au 8.66 g/t, Cu 2%, Ag 4.53 g/t</t>
+          <t>U 0.425%, Cu 0.15%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5146,23 +5146,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T60" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U60" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V60" t="n">
-        <v>48.19278</v>
+        <v>58.12937</v>
       </c>
       <c r="W60" t="n">
-        <v>-79.4164</v>
+        <v>-70.18866</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5189</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PUI-87-43</t>
+          <t>Baillairgé-Est</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,12 +5182,12 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Niobium, Tantalum, Molybdenum, Lithium, Beryllium</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Au 3.73 g/t</t>
+          <t>Mo 5.47%, Li 1.15%, Nb 0.132%, Ta 0.113%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U61" t="n">
         <v>39</v>
       </c>
       <c r="V61" t="n">
-        <v>49.68374</v>
+        <v>48.31589</v>
       </c>
       <c r="W61" t="n">
-        <v>-78.9585</v>
+        <v>-77.97241</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3199</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5454</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kl Zone</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Beryllium</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Beryllium, Molybdenum, Lithium, Tantalum, Rb, Niobium, Bismuth</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Au 5.17 g/t</t>
+          <t>Mo 5.47%, Li 1.32%, Bi 0.0383%, Be 0.0688%, Rb 0.37%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5302,23 +5302,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T62" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U62" t="n">
         <v>39</v>
       </c>
       <c r="V62" t="n">
-        <v>49.66889</v>
+        <v>48.30767</v>
       </c>
       <c r="W62" t="n">
-        <v>-78.37572</v>
+        <v>-77.95856000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3148</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5459</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pio - Zone Du Synclinal</t>
+          <t>Lac Macleod-NE</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Silver</t>
+          <t>Molybdenum, Copper, Tungsten, Gold, Silver</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
+          <t>W 0.111%, Mo 1.22%, Cu 2.65%, Au 2.00 g/t, Ag 24.00 g/t</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U63" t="n">
         <v>39</v>
       </c>
       <c r="V63" t="n">
-        <v>58.99163</v>
+        <v>52.23858</v>
       </c>
       <c r="W63" t="n">
-        <v>-69.61172000000001</v>
+        <v>-72.98878000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5385</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rambull</t>
+          <t>Pio - Zone Du Synclinal</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,12 +5416,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Silver</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
+          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5467,14 +5467,14 @@
         <v>39</v>
       </c>
       <c r="V64" t="n">
-        <v>48.4824</v>
+        <v>58.99163</v>
       </c>
       <c r="W64" t="n">
-        <v>-78.10243</v>
+        <v>-69.61172000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
         </is>
       </c>
     </row>
@@ -5536,10 +5536,10 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U65" t="n">
         <v>39</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>East Mac (Indice Nord)</t>
+          <t>Rambull</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5572,12 +5572,12 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Au 108.96 g/t, Ag 1480.90 g/t</t>
+          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T66" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U66" t="n">
         <v>39</v>
       </c>
       <c r="V66" t="n">
-        <v>48.6126</v>
+        <v>48.4824</v>
       </c>
       <c r="W66" t="n">
-        <v>-77.97836</v>
+        <v>-78.10243</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Norzone</t>
+          <t>Bouvier</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tantalum</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Tantalum, Lithium, Beryllium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Au 8.25 g/t, Ag 134.22 g/t</t>
+          <t>Li 1.78%, Be 0.025%, Ta 0.0553%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5692,23 +5692,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U67" t="n">
         <v>39</v>
       </c>
       <c r="V67" t="n">
-        <v>48.18843</v>
+        <v>48.4522</v>
       </c>
       <c r="W67" t="n">
-        <v>-78.84910000000001</v>
+        <v>-78.0981</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1700</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1508</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Inex</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Au 31.13 g/t</t>
+          <t>Au 54.10 g/t</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5770,23 +5770,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T68" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U68" t="n">
         <v>39</v>
       </c>
       <c r="V68" t="n">
-        <v>55.2524</v>
+        <v>52.74664</v>
       </c>
       <c r="W68" t="n">
-        <v>-67.95193</v>
+        <v>-75.92768</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lac Wachigabau</t>
+          <t>Norseman-2</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5806,12 +5806,12 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Cu 4.46%, Au 3.14 g/t, Ag 16.60 g/t</t>
+          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5848,23 +5848,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T69" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U69" t="n">
         <v>39</v>
       </c>
       <c r="V69" t="n">
-        <v>49.53002</v>
+        <v>48.05412</v>
       </c>
       <c r="W69" t="n">
-        <v>-75.92335</v>
+        <v>-79.17482</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gand II: Rivière Opawica</t>
+          <t>Black Bay</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5884,12 +5884,12 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Au 7.20 g/t</t>
+          <t>Cu 15.9%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5926,23 +5926,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U70" t="n">
         <v>39</v>
       </c>
       <c r="V70" t="n">
-        <v>49.64493</v>
+        <v>48.0662</v>
       </c>
       <c r="W70" t="n">
-        <v>-75.94013</v>
+        <v>-79.18935</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2988</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bernierville-WNW</t>
+          <t>JR</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,12 +5962,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Tantalum</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Lead, Silver</t>
+          <t>Tantalum, Lithium, Rb, Gallium, Beryllium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Cu 4.96%, Mo 0.2%, Ag 14.50 g/t, Pb 0.31%</t>
+          <t>Li 2.12%, Li2O 0.83%, Ga 0.0114%, Be 0.0237%, Rb 0.129%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>39</v>
       </c>
       <c r="V71" t="n">
-        <v>46.11365</v>
+        <v>52.02638</v>
       </c>
       <c r="W71" t="n">
-        <v>-71.60383</v>
+        <v>-76.14072</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3611</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=31156</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Drouet</t>
+          <t>Baillairgé-Ouest</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,12 +6040,12 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lithium, Tantalum, Silver</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t</t>
+          <t>Li 0.9%, Ag 9.00 g/t, Ta 0.053%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T72" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U72" t="n">
         <v>39</v>
       </c>
       <c r="V72" t="n">
-        <v>49.49319</v>
+        <v>48.32819</v>
       </c>
       <c r="W72" t="n">
-        <v>-75.12523</v>
+        <v>-77.98884</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5482</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chioak</t>
+          <t>Cedar Rapids-Zone 1</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,12 +6118,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Uranium, Copper, Thorium</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>U 0.425%, Cu 0.15%</t>
+          <t>Au 77.80 g/t, Cu 1.45%, Ag 68.60 g/t</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6160,23 +6160,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T73" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U73" t="n">
         <v>39</v>
       </c>
       <c r="V73" t="n">
-        <v>58.12937</v>
+        <v>49.0051</v>
       </c>
       <c r="W73" t="n">
-        <v>-70.18866</v>
+        <v>-77.04089</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3521</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Delta (Zone D-8)</t>
+          <t>Vallée Lithium</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,12 +6196,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tantalum</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gold, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+          <t>Tantalum, Lithium, Gallium, Beryllium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Ni 7.8%, Pd 25.50 g/t, Cu 4%, Au 3.63 g/t, Pt 7.96 g/t</t>
+          <t>Li 1.38%, Ga 0.0077%, Be 0.0143%, Ta 0.0323%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6238,23 +6238,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T74" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U74" t="n">
         <v>39</v>
       </c>
       <c r="V74" t="n">
-        <v>61.48642</v>
+        <v>48.40109</v>
       </c>
       <c r="W74" t="n">
-        <v>-74.46145</v>
+        <v>-77.77728999999999</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3396</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5445</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cedar Rapids-Zone 1</t>
+          <t>Lac Pascalis</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 77.80 g/t, Cu 1.45%, Ag 68.60 g/t</t>
+          <t>Au 6.86 g/t, Cu 1.63%, Ag 29.00 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6316,257 +6316,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U75" t="n">
         <v>39</v>
       </c>
       <c r="V75" t="n">
-        <v>49.0051</v>
+        <v>48.27224</v>
       </c>
       <c r="W75" t="n">
-        <v>-77.04089</v>
+        <v>-77.37222</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3521</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Albert (LH-90)</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Zinc, Copper, Silver, Lead</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Pb 50.6%, Zn 20.5%, Ag 173.70 g/t, Cu 0.53%</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>1</v>
-      </c>
-      <c r="T76" t="n">
-        <v>25</v>
-      </c>
-      <c r="U76" t="n">
-        <v>39</v>
-      </c>
-      <c r="V76" t="n">
-        <v>48.74517</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-66.13224</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3389</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Delta (Zone Nord)</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>2</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Nickel, Palladium, Egp, Rh, Copper, Platinum, Ru, Cobalt</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Pd 17.30 g/t, Ni 3.32%, Pt 2.74 g/t, Cu 0.75%, Co 0.18%</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" t="n">
-        <v>25</v>
-      </c>
-      <c r="U77" t="n">
-        <v>39</v>
-      </c>
-      <c r="V77" t="n">
-        <v>61.48852</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-74.47212</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3408</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Echo-1</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Platinum, Cobalt, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Ni 2.35%, Cu 2.6%, Co 0.56%, Pd 4.46 g/t, Pt 1.64 g/t</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>25</v>
-      </c>
-      <c r="U78" t="n">
-        <v>39</v>
-      </c>
-      <c r="V78" t="n">
-        <v>61.44723</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-74.72001</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3411</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2389</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X75"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marguerite</t>
+          <t>Qarqasiaq - C</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Copper, Platinum, Palladium, Egp, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Zn 14%, Ag 44.00 g/t, Pb 0.1%</t>
+          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>48.29078</v>
+        <v>60.17776</v>
       </c>
       <c r="W3" t="n">
-        <v>-69.96804</v>
+        <v>-70.30297</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PAP Nord (Camp A-1)</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>60.2779</v>
+        <v>60.16686</v>
       </c>
       <c r="W4" t="n">
-        <v>-75.33311</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Cu 6.33%, Pd 2.55 g/t, Ni 0.69%, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>49.59836</v>
+        <v>61.55073</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.92194000000001</v>
+        <v>-72.66555</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Spirit-1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iron, Nickel, Copper</t>
+          <t>Nickel, Cobalt, Platinum, Palladium, Egp, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.63941</v>
+        <v>61.39663</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.90893</v>
+        <v>-73.13239</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Mustang</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>48.71945</v>
+        <v>52.17024</v>
       </c>
       <c r="W7" t="n">
-        <v>-78.33144</v>
+        <v>-76.57532999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cunning-Gault</t>
+          <t>Lac Nitakwin</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Pb 32.7%, Zn 11.7%</t>
+          <t>Au 6.06 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>48.72575</v>
+        <v>52.1766</v>
       </c>
       <c r="W8" t="n">
-        <v>-64.47654</v>
+        <v>-76.71138999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5374</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Projet 70-Landome</t>
+          <t>Gauthier-Mcneely</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Copper, Gold</t>
+          <t>Zinc, Silver, Copper, Nickel</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
+          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>48.46123</v>
+        <v>55.62931</v>
       </c>
       <c r="W9" t="n">
-        <v>-77.95265999999999</v>
+        <v>-66.83314</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Northern Canada</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>U 0.373%</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>50.39968</v>
+        <v>55.2524</v>
       </c>
       <c r="W10" t="n">
-        <v>-62.92982</v>
+        <v>-67.95193</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5401</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Lead</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>50.31401</v>
+        <v>58.96701</v>
       </c>
       <c r="W11" t="n">
-        <v>-62.73908</v>
+        <v>-69.59563</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pio - Filons Est et Ouest</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>58.96701</v>
+        <v>61.52449</v>
       </c>
       <c r="W12" t="n">
-        <v>-69.59563</v>
+        <v>-72.77941</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Misery - Sond. ML14024</t>
+          <t>Century</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tungsten, Niobium, Zr, Etr, Silver</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
+          <t>Ni 15.5%, Cu 3.16%, Pd 1.22 g/t, Pt 0.36 g/t, EGP 0.00013%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>55.35025</v>
+        <v>61.35448</v>
       </c>
       <c r="W13" t="n">
-        <v>-63.8991</v>
+        <v>-76.06304</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23835</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Seahawk</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Copper, Platinum, Palladium, Egp, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
+          <t>Ni 4.73%, Cu 1.93%, Pd 3.35 g/t, Pt 0.99 g/t, EGP 0.000434%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>61.52449</v>
+        <v>61.35511</v>
       </c>
       <c r="W14" t="n">
-        <v>-72.77941</v>
+        <v>-76.04816</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23960</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Red Zone</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Pd 2.55 g/t, Ni 0.69%, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Ni 5.75%, Cu 1.35%, Pd 2.97 g/t, Pt 0.46 g/t, EGP 0.000342%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>61.55073</v>
+        <v>61.35949</v>
       </c>
       <c r="W15" t="n">
-        <v>-72.66555</v>
+        <v>-76.01782</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23971</t>
         </is>
       </c>
     </row>
@@ -1662,22 +1662,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spirit-1</t>
+          <t>Delta (Northeast)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nickel, Cobalt, Platinum, Palladium, Egp, Copper</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
+          <t>Ni 3.49%, Pd 1.96 g/t, Pt 0.83 g/t, Cu 0.11%, EGP 0.000279%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>61.39663</v>
+        <v>61.48916</v>
       </c>
       <c r="W16" t="n">
-        <v>-73.13239</v>
+        <v>-74.43673</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24306</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Franelle</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Cu 60%, Ag 43.49 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>59.80634</v>
+        <v>55.55824</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.01831</v>
+        <v>-67.34804</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandpit</t>
+          <t>Misery - Sond. ML14024</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Tungsten, Niobium, Zr, Etr, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 18.05 g/t, As 0.158%</t>
+          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>52.17253</v>
+        <v>55.35025</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.55762</v>
+        <v>-63.8991</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
         </is>
       </c>
     </row>
@@ -1896,22 +1896,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monarch - Veine 1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>W 0.188%, Cu 4.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>48.23207</v>
+        <v>60.39318</v>
       </c>
       <c r="W19" t="n">
-        <v>-79.41287</v>
+        <v>-75.53694</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Misery - Sond. ML11014</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tungsten, Copper</t>
+          <t>Gallium, Sc, Y, Niobium, Zr, Etr, Tantalum, Beryllium, Germanium, Thorium, Tin, Silver, Fluorite, Uranium, Lead, Hf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>W 0.188%, Cu 4.08%</t>
+          <t>Ge 0.0097%, U 0.0387%, Ga 0.0216%, Sn 0.0913%, Ag 5.30 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>60.39318</v>
+        <v>55.34044</v>
       </c>
       <c r="W20" t="n">
-        <v>-75.53694</v>
+        <v>-63.93963</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25755</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Lac Harris</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 29.25 g/t, W 0.122%</t>
+          <t>Cu 5.07%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>52.64108</v>
+        <v>47.68996</v>
       </c>
       <c r="W21" t="n">
-        <v>-75.67010999999999</v>
+        <v>-76.66074999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dessureault (Lac Rougemont)</t>
+          <t>Transfiguration (Labrador Expl.)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Copper, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
+          <t>Cu 3.08%, Pb 21.1%, Zn 8.52%, Ag 97.37 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>58.02817</v>
+        <v>47.93876</v>
       </c>
       <c r="W22" t="n">
-        <v>-69.57268000000001</v>
+        <v>-68.75702</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4162</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Venditelli (Lac St-Pierre-Gold)</t>
+          <t>Transfiguration: Zone E5</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Egp</t>
+          <t>Lead, Silver, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
+          <t>Ag 393.40 g/t, Cu 2.94%, Pb 1%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>58.15377</v>
+        <v>47.94973</v>
       </c>
       <c r="W23" t="n">
-        <v>-69.53443</v>
+        <v>-68.75534</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4165</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Transfiguration: Zone E3</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Lead, Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 6.57%, Pb 9.62%, Ag 32.10 g/t, Zn 0.541%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>49.82919</v>
+        <v>47.9394</v>
       </c>
       <c r="W24" t="n">
-        <v>-70.58076</v>
+        <v>-68.76391</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4166</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Eli SE</t>
+          <t>Sond. K2-22-10</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Vanadium, Copper, Gold, Silver</t>
+          <t>Gold, Zinc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 25.00 g/t, Cu 1.02%, V 0.228%, Ag 16.70 g/t</t>
+          <t>Au 3.64 g/t, Zn 0.55%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>53.10465</v>
+        <v>52.28963</v>
       </c>
       <c r="W25" t="n">
-        <v>-77.28514</v>
+        <v>-77.78149999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=32103</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Sond. PLP24-019</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Bismuth, Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Au 4.76 g/t, Bi 0.1%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>55.68696</v>
+        <v>52.59612</v>
       </c>
       <c r="W26" t="n">
-        <v>-71.02212</v>
+        <v>-77.37366</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>G-H-2-79 (Hudbay Mining)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>Cu 3.26%, Ni 1.12%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>55.58892</v>
+        <v>51.50451</v>
       </c>
       <c r="W27" t="n">
-        <v>-71.1636</v>
+        <v>-67.92737</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Kish</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
+          <t>Gold, Uranium, Thorium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>U 1%, Au 3.90 g/t, Th 0.0025%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>55.61902</v>
+        <v>56.42752</v>
       </c>
       <c r="W28" t="n">
-        <v>-71.054</v>
+        <v>-68.09778</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4904</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mauve</t>
+          <t>Lac Lyster</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 9.13 g/t</t>
+          <t>W 2.93%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>52.68441</v>
+        <v>45.03295</v>
       </c>
       <c r="W29" t="n">
-        <v>-76.29656</v>
+        <v>-71.89901999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4847</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Lac du Canoe</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>Au 40.00 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>55.5908</v>
+        <v>55.23434</v>
       </c>
       <c r="W30" t="n">
-        <v>-71.13463</v>
+        <v>-67.62649</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T31" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U31" t="n">
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>46.26265</v>
+        <v>58.23464</v>
       </c>
       <c r="W31" t="n">
-        <v>-71.21769</v>
+        <v>-69.92364000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Bismuth, Gold, Silver, Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>46.26532</v>
+        <v>47.43121</v>
       </c>
       <c r="W32" t="n">
-        <v>-71.28788</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Fabre Nord</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 6.48 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>45.03676</v>
+        <v>47.26406</v>
       </c>
       <c r="W33" t="n">
-        <v>-72.77243</v>
+        <v>-79.40157000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sond. 82-LD-D-6</t>
+          <t>H-1429-046</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 5.33 g/t, Ag 7.80 g/t</t>
+          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>48.47521</v>
+        <v>50.85296</v>
       </c>
       <c r="W34" t="n">
-        <v>-77.92301999999999</v>
+        <v>-76.47398</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5471</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
         </is>
       </c>
     </row>
@@ -3144,22 +3144,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Sheillan</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 90.30 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>46.265</v>
+        <v>49.10861</v>
       </c>
       <c r="W35" t="n">
-        <v>-71.21259999999999</v>
+        <v>-76.22864</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67165</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lafrance (Willbob)</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Silver, Copper, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 6.56 g/t</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>58.00928</v>
+        <v>52.21818</v>
       </c>
       <c r="W36" t="n">
-        <v>-69.53870999999999</v>
+        <v>-77.45902</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=34117</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fort Chimo (Lac Plissé)</t>
+          <t>Delhi Pacific</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nickel, Gold, Zinc, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
+          <t>Cu 7.36%, Ag 24.90 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>58.12861</v>
+        <v>56.40258</v>
       </c>
       <c r="W37" t="n">
-        <v>-69.55745</v>
+        <v>-67.9023</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
+          <t>Sainte-Cécile (Maheu) - ancien</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
+          <t>Bismuth, Lead, Zinc, Silver, Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
+          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>58.23464</v>
+        <v>45.67446</v>
       </c>
       <c r="W38" t="n">
-        <v>-69.92364000000001</v>
+        <v>-70.96669</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+          <t>Zinc, Barium, Mercury, Cadmium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Zn 31.5%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>46.26109</v>
+        <v>46.11447</v>
       </c>
       <c r="W39" t="n">
-        <v>-71.22866</v>
+        <v>-75.95323</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill</t>
+          <t>Lac Chicobi-2</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,17 +3544,17 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Uranium, Silver, Copper, Molybdenum, Gold</t>
+          <t>Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>453 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>U 2.26%, Cu 10.3%, Ag 140.00 g/t, Mo 0.47%, Au 0.62 g/t</t>
+          <t>Ag 932.70 g/t, Pb 19.2%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3586,23 +3586,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U40" t="n">
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>46.26423</v>
+        <v>48.83881</v>
       </c>
       <c r="W40" t="n">
-        <v>-71.20608</v>
+        <v>-78.52331</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1213</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4194</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Erickson Sud - Goose Pond</t>
+          <t>Propriété Authier</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platinum, Gold, Palladium, Egp, Nickel, Copper, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
+          <t>Au 173.90 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>57.99255</v>
+        <v>48.89617</v>
       </c>
       <c r="W41" t="n">
-        <v>-69.72347000000001</v>
+        <v>-78.78440000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4201</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
+          <t>AT-32-91</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 21.70 g/t</t>
+          <t>Au 5.09 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>57.94973</v>
+        <v>48.89509</v>
       </c>
       <c r="W42" t="n">
-        <v>-69.51281</v>
+        <v>-78.79843</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OTS-15</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Etr, Y, Thorium, Zinc, Uranium, Molybdenum, Lead, Silver</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>U 1.91%, Ag 44.80 g/t, Mo 0.122%, Zn 0.873%, Pb 0.351%</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>51.78273</v>
+        <v>53.56991</v>
       </c>
       <c r="W43" t="n">
-        <v>-71.96856</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=33065</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Comtois NW</t>
+          <t>Fort Chimo (Lac Plissé)</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Nickel, Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
+          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>49.18766</v>
+        <v>58.12861</v>
       </c>
       <c r="W44" t="n">
-        <v>-77.31872</v>
+        <v>-69.55745</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OTS-08</t>
+          <t>H-1451-032</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Uranium, Zinc, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
+          <t>Au 2.20 g/t, Cu 0.66%, Zn 1.59%, Ag 21.80 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3976,23 +3976,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T45" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U45" t="n">
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>51.78509</v>
+        <v>50.79734</v>
       </c>
       <c r="W45" t="n">
-        <v>-71.96465999999999</v>
+        <v>-76.70574000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4242</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Val-St-Gilles-SE</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Cu 7.88%, Ag 87.00 g/t, Au 1.06 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>52.03235</v>
+        <v>48.97212</v>
       </c>
       <c r="W46" t="n">
-        <v>-69.13816</v>
+        <v>-79.1088</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2703</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Kupfer : Mine Val-St-Gilles</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 7.96%, Ag 89.15 g/t, Zn 2.66%, Au 0.34 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>49.84595</v>
+        <v>48.97156</v>
       </c>
       <c r="W47" t="n">
-        <v>-70.57626</v>
+        <v>-79.08714999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2704</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Val-St-Gilles SO</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Gold, Lead, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 8.34 g/t, Zn 5.2%, Pb 9.9%, Ag 61.90 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>49.83681</v>
+        <v>48.96826</v>
       </c>
       <c r="W48" t="n">
-        <v>-70.57877999999999</v>
+        <v>-79.19454</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2702</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Augustus Exploration</t>
+          <t>Meilleur (Chess Uranium)</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Li 0.96%</t>
+          <t>Cu 3.27%, Pd 2.46 g/t, Ni 0.6%, Au 0.50 g/t, Pt 0.73 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>48.42585</v>
+        <v>45.6921</v>
       </c>
       <c r="W49" t="n">
-        <v>-77.87544</v>
+        <v>-76.64127999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5443</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4809</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Martin-McNeely</t>
+          <t>Venditelli (Lac St-Pierre-Gold)</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lithium, Molybdenum</t>
+          <t>Gold, Palladium, Egp</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Li 1%</t>
+          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>48.43133</v>
+        <v>58.15377</v>
       </c>
       <c r="W50" t="n">
-        <v>-77.89922</v>
+        <v>-69.53443</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5442</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Canadian Lithium</t>
+          <t>Dessureault (Lac Rougemont)</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tantalum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tantalum, Lithium, Beryllium</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Li 0.814%, Be 0.0342%, Ta 0.019%</t>
+          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>48.43096</v>
+        <v>58.02817</v>
       </c>
       <c r="W51" t="n">
-        <v>-77.90853</v>
+        <v>-69.57268000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5441</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Lac Retty - Lac Pogo</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold, Platinum, Palladium, Egp, Nickel, Copper, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>49.79699</v>
+        <v>55.23261</v>
       </c>
       <c r="W52" t="n">
-        <v>-75.81529</v>
+        <v>-66.16073</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Qarqasiaq - A1</t>
+          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
+          <t>Au 21.70 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>60.16686</v>
+        <v>57.94973</v>
       </c>
       <c r="W53" t="n">
-        <v>-70.29604999999999</v>
+        <v>-69.51281</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amaruk</t>
+          <t>Erickson Sud - Goose Pond</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Platinum, Gold, Palladium, Egp, Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
+          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>59.60263</v>
+        <v>57.99255</v>
       </c>
       <c r="W54" t="n">
-        <v>-74.86282</v>
+        <v>-69.72347000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Devlin (Riocanex)</t>
+          <t>Lac Retty - Lac Bleu</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,33 +4714,33 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>16 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Au 1.75 g/t</t>
+          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4756,23 +4756,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T55" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U55" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>49.75792</v>
+        <v>55.22879</v>
       </c>
       <c r="W55" t="n">
-        <v>-74.3342</v>
+        <v>-66.12246</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1982</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Lac Walsh-Ouest</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,33 +4792,33 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 3.05%, Ni 0.67%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4834,23 +4834,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T56" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U56" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>49.01028</v>
+        <v>55.15269</v>
       </c>
       <c r="W56" t="n">
-        <v>-66.00369999999999</v>
+        <v>-66.35399</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4870,33 +4870,33 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rh, Platinum, Nickel, Egp, Chromium, Palladium</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4912,23 +4912,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U57" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>46.04018</v>
+        <v>52.17253</v>
       </c>
       <c r="W57" t="n">
-        <v>-71.28144</v>
+        <v>-76.55762</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lavoie (Zone L)</t>
+          <t>Otel</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,21 +4948,21 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gold, Uranium, Molybdenum, Vanadium, Lead, Thorium, Silver</t>
+          <t>Copper, Uranium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>U 10.8%, Au 20.00 g/t, Mo 0.28%, Ag 40.70 g/t, V 0.167%</t>
+          <t>U 3.85%, Cu 6.88%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4990,23 +4990,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U58" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>52.18408</v>
+        <v>56.25666</v>
       </c>
       <c r="W58" t="n">
-        <v>-70.99409</v>
+        <v>-68.20592000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4966</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4906</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Solbec Copper</t>
+          <t>Train No 4 (Lac Crabe)</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,33 +5026,33 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gold, Cadmium, Lead, Silver, Copper, Zinc, Cs</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Cu 18.1%, Zn 23.8%, Au 4.08 g/t, Ag 218.60 g/t, Pb 5.22%</t>
+          <t>Cu 3.71%, U 0.07%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5068,23 +5068,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T59" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U59" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>45.80476</v>
+        <v>56.39584</v>
       </c>
       <c r="W59" t="n">
-        <v>-71.28747</v>
+        <v>-68.39176999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=444</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chioak</t>
+          <t>SGR-09</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Uranium, Copper, Thorium</t>
+          <t>Uranium, Gold</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>U 0.425%, Cu 0.15%</t>
+          <t>Au 3.31 g/t, U 0.11%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5146,23 +5146,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T60" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U60" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>58.12937</v>
+        <v>56.43951</v>
       </c>
       <c r="W60" t="n">
-        <v>-70.18866</v>
+        <v>-68.10245999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3879</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Baillairgé-Est</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,12 +5182,12 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Niobium, Tantalum, Molybdenum, Lithium, Beryllium</t>
+          <t>Uranium, Gold, Copper</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="I61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Mo 5.47%, Li 1.15%, Nb 0.132%, Ta 0.113%</t>
+          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T61" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U61" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>48.31589</v>
+        <v>56.43038</v>
       </c>
       <c r="W61" t="n">
-        <v>-77.97241</v>
+        <v>-68.09914000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Lac du Castor</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Beryllium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Beryllium, Molybdenum, Lithium, Tantalum, Rb, Niobium, Bismuth</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="I62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Mo 5.47%, Li 1.32%, Bi 0.0383%, Be 0.0688%, Rb 0.37%</t>
+          <t>U 0.328%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5302,23 +5302,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>48.30767</v>
+        <v>52.2149</v>
       </c>
       <c r="W62" t="n">
-        <v>-77.95856000000001</v>
+        <v>-70.93367000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5459</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lac Macleod-NE</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Tungsten, Gold, Silver</t>
+          <t>Gold, Lead, Silver</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="I63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>W 0.111%, Mo 1.22%, Cu 2.65%, Au 2.00 g/t, Ag 24.00 g/t</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T63" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U63" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>52.23858</v>
+        <v>52.20175</v>
       </c>
       <c r="W63" t="n">
-        <v>-72.98878000000001</v>
+        <v>-70.89798</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5385</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pio - Zone Du Synclinal</t>
+          <t>Kogaluc 1</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,12 +5416,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Cu 3.33%, Ni 1.3%, Pd 2.03 g/t, Au 0.44 g/t, Pt 0.60 g/t</t>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5458,23 +5458,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T64" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U64" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>58.99163</v>
+        <v>58.81627</v>
       </c>
       <c r="W64" t="n">
-        <v>-69.61172000000001</v>
+        <v>-74.70458000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1585</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kerwin</t>
+          <t>Kogaluc 4</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5494,12 +5494,12 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Pb 16.7%, Zn 4.62%, Cu 1.22%, Ag 75.20 g/t</t>
+          <t>Au 5.60 g/t</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5536,23 +5536,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U65" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>48.39017</v>
+        <v>58.81552</v>
       </c>
       <c r="W65" t="n">
-        <v>-78.41151000000001</v>
+        <v>-74.68685000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1513</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rambull</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5572,12 +5572,12 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="I66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Au 26.45 g/t, Ag 5.50 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>48.4824</v>
+        <v>49.84595</v>
       </c>
       <c r="W66" t="n">
-        <v>-78.10243</v>
+        <v>-70.57626</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1510</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bouvier</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tantalum</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tantalum, Lithium, Beryllium</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Li 1.78%, Be 0.025%, Ta 0.0553%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5692,23 +5692,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T67" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U67" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>48.4522</v>
+        <v>49.83681</v>
       </c>
       <c r="W67" t="n">
-        <v>-78.0981</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1508</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Inex</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,12 +5728,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="I68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Au 54.10 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5770,23 +5770,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T68" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U68" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V68" t="n">
-        <v>52.74664</v>
+        <v>49.82919</v>
       </c>
       <c r="W68" t="n">
-        <v>-75.92768</v>
+        <v>-70.58076</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Norseman-2</t>
+          <t>OTS-08</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5806,12 +5806,12 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Uranium, Zinc, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Cu 13.2%, Au 0.68 g/t, Ag 15.08 g/t</t>
+          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5848,23 +5848,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T69" t="n">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="U69" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V69" t="n">
-        <v>48.05412</v>
+        <v>51.78509</v>
       </c>
       <c r="W69" t="n">
-        <v>-79.17482</v>
+        <v>-71.96465999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5171</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Black Bay</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="I70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Cu 15.9%</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5926,23 +5926,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T70" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U70" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V70" t="n">
-        <v>48.0662</v>
+        <v>55.5908</v>
       </c>
       <c r="W70" t="n">
-        <v>-79.18935</v>
+        <v>-71.13463</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5164</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JR</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,12 +5962,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tantalum</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tantalum, Lithium, Rb, Gallium, Beryllium</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Li 2.12%, Li2O 0.83%, Ga 0.0114%, Be 0.0237%, Rb 0.129%</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6004,23 +6004,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V71" t="n">
-        <v>52.02638</v>
+        <v>55.61902</v>
       </c>
       <c r="W71" t="n">
-        <v>-76.14072</v>
+        <v>-71.054</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=31156</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Baillairgé-Ouest</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,12 +6040,12 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lithium, Tantalum, Silver</t>
+          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="I72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Li 0.9%, Ag 9.00 g/t, Ta 0.053%</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V72" t="n">
-        <v>48.32819</v>
+        <v>55.58892</v>
       </c>
       <c r="W72" t="n">
-        <v>-77.98884</v>
+        <v>-71.1636</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cedar Rapids-Zone 1</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,12 +6118,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Au 77.80 g/t, Cu 1.45%, Ag 68.60 g/t</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6160,23 +6160,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V73" t="n">
-        <v>49.0051</v>
+        <v>55.68696</v>
       </c>
       <c r="W73" t="n">
-        <v>-77.04089</v>
+        <v>-71.02212</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3521</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vallée Lithium</t>
+          <t>Bravo (Train No 3)</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,12 +6196,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tantalum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tantalum, Lithium, Gallium, Beryllium</t>
+          <t>Copper, Uranium, Zinc, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="I74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Li 1.38%, Ga 0.0077%, Be 0.0143%, Ta 0.0323%</t>
+          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6238,23 +6238,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T74" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U74" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V74" t="n">
-        <v>48.40109</v>
+        <v>56.38071</v>
       </c>
       <c r="W74" t="n">
-        <v>-77.77728999999999</v>
+        <v>-68.37362</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5445</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lac Pascalis</t>
+          <t>Lullwitz-Kaeppeli</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6274,12 +6274,12 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Ir, Gold, Zr, Gallium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 6.86 g/t, Cu 1.63%, Ag 29.00 g/t</t>
+          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6316,23 +6316,1193 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U75" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="V75" t="n">
-        <v>48.27224</v>
+        <v>47.76432</v>
       </c>
       <c r="W75" t="n">
-        <v>-77.37222</v>
+        <v>-70.46635000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2389</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Lac Couillard (Secteur A)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Zr, Y, Etr, Gd, Pr, Dy, La, Nd, Ce, Sm</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Nd 0.649%, Dy 0.0357%, Pr 0.11%, Ce 1.55%, La 0.2%</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>13</v>
+      </c>
+      <c r="T76" t="n">
+        <v>325</v>
+      </c>
+      <c r="U76" t="n">
+        <v>55</v>
+      </c>
+      <c r="V76" t="n">
+        <v>50.30421</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-60.82246</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4100</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bob West</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Gold, Antimony</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Sb 3.35%, Au 1.16 g/t</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>13</v>
+      </c>
+      <c r="T77" t="n">
+        <v>325</v>
+      </c>
+      <c r="U77" t="n">
+        <v>55</v>
+      </c>
+      <c r="V77" t="n">
+        <v>52.08812</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-75.41134</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67079</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Obamska</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Au 9.50 g/t</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>13</v>
+      </c>
+      <c r="T78" t="n">
+        <v>325</v>
+      </c>
+      <c r="U78" t="n">
+        <v>55</v>
+      </c>
+      <c r="V78" t="n">
+        <v>50.8353</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-78.66648000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>St-Armand (Phillipsburg-Est)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Uranium, Zinc</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>U 0.578%, Zn 0.0798%</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>325</v>
+      </c>
+      <c r="U79" t="n">
+        <v>55</v>
+      </c>
+      <c r="V79" t="n">
+        <v>45.02084</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-73.0196</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Chalifour-1</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Zinc, Lead, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>13</v>
+      </c>
+      <c r="T80" t="n">
+        <v>325</v>
+      </c>
+      <c r="U80" t="n">
+        <v>55</v>
+      </c>
+      <c r="V80" t="n">
+        <v>50.3781</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-73.70041000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Perch River</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Cu 9.06%, Ag 19.20 g/t</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>13</v>
+      </c>
+      <c r="T81" t="n">
+        <v>325</v>
+      </c>
+      <c r="U81" t="n">
+        <v>55</v>
+      </c>
+      <c r="V81" t="n">
+        <v>50.33998</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-73.71023</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Hunt (Port Daniel No. 2)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Cu 9.35%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>13</v>
+      </c>
+      <c r="T82" t="n">
+        <v>325</v>
+      </c>
+      <c r="U82" t="n">
+        <v>55</v>
+      </c>
+      <c r="V82" t="n">
+        <v>48.31932</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-64.9713</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PAP Nord (Camp A-1)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>13</v>
+      </c>
+      <c r="T83" t="n">
+        <v>325</v>
+      </c>
+      <c r="U83" t="n">
+        <v>55</v>
+      </c>
+      <c r="V83" t="n">
+        <v>60.2779</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-75.33311</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Harrison</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Iron, Nickel, Copper</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>13</v>
+      </c>
+      <c r="T84" t="n">
+        <v>325</v>
+      </c>
+      <c r="U84" t="n">
+        <v>55</v>
+      </c>
+      <c r="V84" t="n">
+        <v>49.63941</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-76.90893</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Qalluviartuuq-NW</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>13</v>
+      </c>
+      <c r="T85" t="n">
+        <v>325</v>
+      </c>
+      <c r="U85" t="n">
+        <v>55</v>
+      </c>
+      <c r="V85" t="n">
+        <v>59.80634</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-75.01831</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AC-2010-006</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Au 4.44 g/t</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>13</v>
+      </c>
+      <c r="T86" t="n">
+        <v>325</v>
+      </c>
+      <c r="U86" t="n">
+        <v>55</v>
+      </c>
+      <c r="V86" t="n">
+        <v>52.03235</v>
+      </c>
+      <c r="W86" t="n">
+        <v>-69.13816</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Twin</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>7</v>
+      </c>
+      <c r="T87" t="n">
+        <v>175</v>
+      </c>
+      <c r="U87" t="n">
+        <v>55</v>
+      </c>
+      <c r="V87" t="n">
+        <v>48.32328</v>
+      </c>
+      <c r="W87" t="n">
+        <v>-79.44637</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Barre de fer</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Copper, Nickel, Cobalt</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>13</v>
+      </c>
+      <c r="T88" t="n">
+        <v>325</v>
+      </c>
+      <c r="U88" t="n">
+        <v>55</v>
+      </c>
+      <c r="V88" t="n">
+        <v>51.6436</v>
+      </c>
+      <c r="W88" t="n">
+        <v>-67.33749</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mistass</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Iron, Copper, Nickel, Cobalt</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>13</v>
+      </c>
+      <c r="T89" t="n">
+        <v>325</v>
+      </c>
+      <c r="U89" t="n">
+        <v>55</v>
+      </c>
+      <c r="V89" t="n">
+        <v>49.24734</v>
+      </c>
+      <c r="W89" t="n">
+        <v>-71.98866</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Lac Beaupré-Est</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Nickel, Copper</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Cu 5.3%, Ni 0.88%</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>13</v>
+      </c>
+      <c r="T90" t="n">
+        <v>325</v>
+      </c>
+      <c r="U90" t="n">
+        <v>55</v>
+      </c>
+      <c r="V90" t="n">
+        <v>49.59836</v>
+      </c>
+      <c r="W90" t="n">
+        <v>-76.92194000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X90"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Lead, Silver, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qarqasiaq - C</t>
+          <t>Riv. Cascapedia</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Platinum, Palladium, Egp, Nickel, Gold, Cobalt</t>
+          <t>Nickel, Arsenic, Chromium, Cobalt, Antimony</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
+          <t>Ni 12.8%, Co 0.13%, As 11.8%, Cr 0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>60.17776</v>
+        <v>48.84847</v>
       </c>
       <c r="W3" t="n">
-        <v>-70.30297</v>
+        <v>-66.39704</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6070</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qarqasiaq - A1</t>
+          <t>Ruisseau 17e Mille</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+          <t>Nickel, Egp, Platinum, Chromium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
+          <t>Ni 11.7%, Pt 1.70 g/t, Cr 0.25%, EGP 0.00017%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>60.16686</v>
+        <v>48.86434</v>
       </c>
       <c r="W4" t="n">
-        <v>-70.29604999999999</v>
+        <v>-66.26813</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6072</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Pd 2.55 g/t, Ni 0.69%, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>61.55073</v>
+        <v>55.5908</v>
       </c>
       <c r="W5" t="n">
-        <v>-72.66555</v>
+        <v>-71.13463</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spirit-1</t>
+          <t>Pistolaté</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nickel, Cobalt, Platinum, Palladium, Egp, Copper</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>61.39663</v>
+        <v>55.68696</v>
       </c>
       <c r="W6" t="n">
-        <v>-73.13239</v>
+        <v>-71.02212</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mustang</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Palladium, Nickel, Egp, Copper, Platinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>52.17024</v>
+        <v>55.58892</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.57532999999999</v>
+        <v>-71.1636</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lac Nitakwin</t>
+          <t>Ganiq</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 6.06 g/t</t>
+          <t>U 0.77%, Cu 0.52%, Pb 0.82%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>52.1766</v>
+        <v>53.7831</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.71138999999999</v>
+        <v>-75.64593000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4528</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gauthier-Mcneely</t>
+          <t>B-88-01</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Nickel</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
+          <t>Ag 203.00 g/t, Cu 1.56%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>55.62931</v>
+        <v>45.52488</v>
       </c>
       <c r="W9" t="n">
-        <v>-66.83314</v>
+        <v>-72.07191</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Qarqasiaq - C</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium, Platinum, Copper, Nickel, Egp, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 31.13 g/t</t>
+          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>55.2524</v>
+        <v>60.17776</v>
       </c>
       <c r="W10" t="n">
-        <v>-67.95193</v>
+        <v>-70.30297</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pio - Filons Est et Ouest</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
+          <t>Egp, Palladium, Platinum, Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>58.96701</v>
+        <v>60.16686</v>
       </c>
       <c r="W11" t="n">
-        <v>-69.59563</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Egp, Palladium, Platinum, Copper, Nickel, Silver, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>61.52449</v>
+        <v>58.96701</v>
       </c>
       <c r="W12" t="n">
-        <v>-72.77941</v>
+        <v>-69.59563</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Century</t>
+          <t>Franelle</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ni 15.5%, Cu 3.16%, Pd 1.22 g/t, Pt 0.36 g/t, EGP 0.00013%</t>
+          <t>Cu 60%, Ag 43.49 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>61.35448</v>
+        <v>55.55824</v>
       </c>
       <c r="W13" t="n">
-        <v>-76.06304</v>
+        <v>-67.34804</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23835</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Seahawk</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Platinum, Palladium, Egp, Nickel</t>
+          <t>Gold, Silver, Tungsten, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ni 4.73%, Cu 1.93%, Pd 3.35 g/t, Pt 0.99 g/t, EGP 0.000434%</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>61.35511</v>
+        <v>53.39256</v>
       </c>
       <c r="W14" t="n">
-        <v>-76.04816</v>
+        <v>-77.43714</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23960</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Red Zone</t>
+          <t>Josette</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
+          <t>Etr, Iron, Tungsten, Uranium, Thorium, Copper, Y, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ni 5.75%, Cu 1.35%, Pd 2.97 g/t, Pt 0.46 g/t, EGP 0.000342%</t>
+          <t>W 0.18%, Cu 2.81%, U 0.0654%, Ag 13.00 g/t, Au 0.15 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>61.35949</v>
+        <v>51.05069</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.01782</v>
+        <v>-65.27048000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23971</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6032</t>
         </is>
       </c>
     </row>
@@ -1662,22 +1662,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Delta (Northeast)</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ni 3.49%, Pd 1.96 g/t, Pt 0.83 g/t, Cu 0.11%, EGP 0.000279%</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>61.48916</v>
+        <v>45.03676</v>
       </c>
       <c r="W16" t="n">
-        <v>-74.43673</v>
+        <v>-72.77243</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24306</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Franelle</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Nickel, Copper, Egp, Cobalt, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 60%, Ag 43.49 g/t</t>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>55.55824</v>
+        <v>55.61902</v>
       </c>
       <c r="W17" t="n">
-        <v>-67.34804</v>
+        <v>-71.054</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Misery - Sond. ML14024</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tungsten, Niobium, Zr, Etr, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>55.35025</v>
+        <v>55.2524</v>
       </c>
       <c r="W18" t="n">
-        <v>-63.8991</v>
+        <v>-67.95193</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Lac du Canoe</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tungsten, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>W 0.188%, Cu 4.08%</t>
+          <t>Au 40.00 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>60.39318</v>
+        <v>55.23434</v>
       </c>
       <c r="W19" t="n">
-        <v>-75.53694</v>
+        <v>-67.62649</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Misery - Sond. ML11014</t>
+          <t>Au-26</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gallium, Sc, Y, Niobium, Zr, Etr, Tantalum, Beryllium, Germanium, Thorium, Tin, Silver, Fluorite, Uranium, Lead, Hf</t>
+          <t>Copper, Gold, Silver, Lead, Zinc, Arsenic</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ge 0.0097%, U 0.0387%, Ga 0.0216%, Sn 0.0913%, Ag 5.30 g/t</t>
+          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>55.34044</v>
+        <v>53.39936</v>
       </c>
       <c r="W20" t="n">
-        <v>-63.93963</v>
+        <v>-77.29407</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25755</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lac Harris</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten, Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 5.07%</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>47.68996</v>
+        <v>53.39458</v>
       </c>
       <c r="W21" t="n">
-        <v>-76.66074999999999</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Transfiguration (Labrador Expl.)</t>
+          <t>Bonspot</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Lead</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 3.08%, Pb 21.1%, Zn 8.52%, Ag 97.37 g/t</t>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>47.93876</v>
+        <v>53.41679</v>
       </c>
       <c r="W22" t="n">
-        <v>-68.75702</v>
+        <v>-77.27167</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4162</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Transfiguration: Zone E5</t>
+          <t>4930N-1</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lead, Silver, Copper</t>
+          <t>Chromium, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 393.40 g/t, Cu 2.94%, Pb 1%</t>
+          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>47.94973</v>
+        <v>53.38014</v>
       </c>
       <c r="W23" t="n">
-        <v>-68.75534</v>
+        <v>-77.28712</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4165</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Transfiguration: Zone E3</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lead, Copper, Gold, Zinc, Silver</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 6.57%, Pb 9.62%, Ag 32.10 g/t, Zn 0.541%</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>47.9394</v>
+        <v>53.40387</v>
       </c>
       <c r="W24" t="n">
-        <v>-68.76391</v>
+        <v>-77.30118</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4166</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sond. K2-22-10</t>
+          <t>Gauthier-Mcneely</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Zinc</t>
+          <t>Zinc, Copper, Silver, Nickel</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 3.64 g/t, Zn 0.55%</t>
+          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>52.28963</v>
+        <v>55.62931</v>
       </c>
       <c r="W25" t="n">
-        <v>-77.78149999999999</v>
+        <v>-66.83314</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sond. PLP24-019</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bismuth, Gold</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 4.76 g/t, Bi 0.1%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>52.59612</v>
+        <v>49.82919</v>
       </c>
       <c r="W26" t="n">
-        <v>-77.37366</v>
+        <v>-70.58076</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>G-H-2-79 (Hudbay Mining)</t>
+          <t>Lac Tarsac : Veine I et III</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 3.26%, Ni 1.12%</t>
+          <t>Au 11.66 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U27" t="n">
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>51.50451</v>
+        <v>48.3561</v>
       </c>
       <c r="W27" t="n">
-        <v>-67.92737</v>
+        <v>-79.43788000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kish</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold, Uranium, Thorium</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>U 1%, Au 3.90 g/t, Th 0.0025%</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2650,23 +2650,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U28" t="n">
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>56.42752</v>
+        <v>48.32328</v>
       </c>
       <c r="W28" t="n">
-        <v>-68.09778</v>
+        <v>-79.44637</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4904</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lac Lyster</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Zinc, Barium, Cadmium, Mercury</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>W 2.93%</t>
+          <t>Zn 31.5%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U29" t="n">
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>45.03295</v>
+        <v>46.11447</v>
       </c>
       <c r="W29" t="n">
-        <v>-71.89901999999999</v>
+        <v>-75.95323</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4847</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lac du Canoe</t>
+          <t>Viau (ou Bordulac)</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 40.00 g/t</t>
+          <t>Au 31.00 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>55.23434</v>
+        <v>48.26547</v>
       </c>
       <c r="W30" t="n">
-        <v>-67.62649</v>
+        <v>-79.41453</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
+          <t>Sainte-Cécile (Maheu) - ancien</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
+          <t>Molybdenum, Silver, Zinc, Lead, Bismuth, Gold, Copper</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
+          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>58.23464</v>
+        <v>45.67446</v>
       </c>
       <c r="W31" t="n">
-        <v>-69.92364000000001</v>
+        <v>-70.96669</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bismuth, Gold, Silver, Molybdenum, Copper</t>
+          <t>Copper, Gold, Egp, Palladium, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>47.43121</v>
+        <v>53.34013</v>
       </c>
       <c r="W32" t="n">
-        <v>-79.32868999999999</v>
+        <v>-77.32316</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fabre Nord</t>
+          <t>Mistass</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Iron, Cobalt</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 6.48 g/t</t>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>47.26406</v>
+        <v>49.24734</v>
       </c>
       <c r="W33" t="n">
-        <v>-79.40157000000001</v>
+        <v>-71.98866</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H-1429-046</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>50.85296</v>
+        <v>49.83681</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.47398</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sheillan</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 90.30 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>49.10861</v>
+        <v>49.84595</v>
       </c>
       <c r="W35" t="n">
-        <v>-76.22864</v>
+        <v>-70.57626</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67165</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lidge</t>
+          <t>PG-221094</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Arsenic</t>
+          <t>Gold, Zinc, Lead, Silver, Arsenic, Copper</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
+          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>52.21818</v>
+        <v>53.40779</v>
       </c>
       <c r="W36" t="n">
-        <v>-77.45902</v>
+        <v>-77.28636</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Delhi Pacific</t>
+          <t>Cr-2</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Palladium, Platinum, Rh, Gold, Iron, Chromium, Nickel, Copper, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
+          <t>Pd 11.88 g/t, Ni 2.4%, Cu 2.36%, Pt 4.20 g/t, Au 1.30 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>56.40258</v>
+        <v>53.39341</v>
       </c>
       <c r="W37" t="n">
-        <v>-67.9023</v>
+        <v>-77.30141</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6004</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sainte-Cécile (Maheu) - ancien</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bismuth, Lead, Zinc, Silver, Molybdenum, Copper, Gold</t>
+          <t>Gold, Arsenic, Copper, Silver, Cobalt, Tungsten, Tellurium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>45.67446</v>
+        <v>59.80634</v>
       </c>
       <c r="W38" t="n">
-        <v>-70.96669</v>
+        <v>-75.01831</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Lac Menarik</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Zinc, Barium, Mercury, Cadmium</t>
+          <t>Rh, Chromium, Egp, Nickel, Gold, Palladium, Platinum, Copper</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Zn 31.5%</t>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>46.11447</v>
+        <v>53.39786</v>
       </c>
       <c r="W39" t="n">
-        <v>-75.95323</v>
+        <v>-77.30625000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lac Chicobi-2</t>
+          <t>Lac Yasinski-NE</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Silver, Lead, Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ag 932.70 g/t, Pb 19.2%</t>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>48.83881</v>
+        <v>53.35887</v>
       </c>
       <c r="W40" t="n">
-        <v>-78.52331</v>
+        <v>-77.31016</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4194</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Propriété Authier</t>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Silver, Nickel, Palladium, Gold, Copper, Lead, Cobalt, Egp</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 173.90 g/t</t>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>48.89617</v>
+        <v>53.39996</v>
       </c>
       <c r="W41" t="n">
-        <v>-78.78440000000001</v>
+        <v>-77.33163999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4201</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AT-32-91</t>
+          <t>Delandore</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 5.09 g/t</t>
+          <t>Au 26.74 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>48.89509</v>
+        <v>48.63582</v>
       </c>
       <c r="W42" t="n">
-        <v>-78.79843</v>
+        <v>-77.03851</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2065</t>
         </is>
       </c>
     </row>
@@ -3768,22 +3768,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Ducros : Pyroxénite</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper, Palladium, Platinum, Nickel, Gold, Egp</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Cu 2.64%, Ni 1.44%, Au 1.32 g/t, Pt 1.42 g/t, Pd 1.61 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>53.56991</v>
+        <v>48.69916</v>
       </c>
       <c r="W43" t="n">
-        <v>-77.31073000000001</v>
+        <v>-77.0911</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2081</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fort Chimo (Lac Plissé)</t>
+          <t>Cunning-Gault</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nickel, Gold, Zinc, Copper, Silver</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
+          <t>Pb 32.7%, Zn 11.7%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>58.12861</v>
+        <v>48.72575</v>
       </c>
       <c r="W44" t="n">
-        <v>-69.55745</v>
+        <v>-64.47654</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5374</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H-1451-032</t>
+          <t>Northern Canada</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 2.20 g/t, Cu 0.66%, Zn 1.59%, Ag 21.80 g/t</t>
+          <t>U 0.373%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>50.79734</v>
+        <v>50.39968</v>
       </c>
       <c r="W45" t="n">
-        <v>-76.70574000000001</v>
+        <v>-62.92982</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4242</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5401</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Val-St-Gilles-SE</t>
+          <t>Mid-Patapédia</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 7.88%, Ag 87.00 g/t, Au 1.06 g/t</t>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>48.97212</v>
+        <v>47.86378</v>
       </c>
       <c r="W46" t="n">
-        <v>-79.1088</v>
+        <v>-67.38485</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2703</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kupfer : Mine Val-St-Gilles</t>
+          <t>St-Benoit</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Copper, Gold</t>
+          <t>Copper, Gold, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Cu 7.96%, Ag 89.15 g/t, Zn 2.66%, Au 0.34 g/t</t>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>48.97156</v>
+        <v>47.99637</v>
       </c>
       <c r="W47" t="n">
-        <v>-79.08714999999999</v>
+        <v>-67.11127</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
         </is>
       </c>
     </row>
@@ -4158,22 +4158,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Val-St-Gilles SO</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold, Lead, Silver, Zinc, Copper</t>
+          <t>Copper, Molybdenum, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 8.34 g/t, Zn 5.2%, Pb 9.9%, Ag 61.90 g/t</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4210,23 +4210,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T48" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U48" t="n">
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>48.96826</v>
+        <v>45.99171</v>
       </c>
       <c r="W48" t="n">
-        <v>-79.19454</v>
+        <v>-71.70617</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2702</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Meilleur (Chess Uranium)</t>
+          <t>Glencoe</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Cu 3.27%, Pd 2.46 g/t, Ni 0.6%, Au 0.50 g/t, Pt 0.73 g/t</t>
+          <t>Cu 4.28%, Ag 3.00 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,3212 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>45.6921</v>
+        <v>45.32873</v>
       </c>
       <c r="W49" t="n">
-        <v>-76.64127999999999</v>
+        <v>-72.47421</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4809</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Venditelli (Lac St-Pierre-Gold)</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Gold, Palladium, Egp</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="n">
-        <v>13</v>
-      </c>
-      <c r="T50" t="n">
-        <v>325</v>
-      </c>
-      <c r="U50" t="n">
-        <v>55</v>
-      </c>
-      <c r="V50" t="n">
-        <v>58.15377</v>
-      </c>
-      <c r="W50" t="n">
-        <v>-69.53443</v>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Dessureault (Lac Rougemont)</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>13</v>
-      </c>
-      <c r="T51" t="n">
-        <v>325</v>
-      </c>
-      <c r="U51" t="n">
-        <v>55</v>
-      </c>
-      <c r="V51" t="n">
-        <v>58.02817</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-69.57268000000001</v>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Lac Retty - Lac Pogo</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Gold, Platinum, Palladium, Egp, Nickel, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="n">
-        <v>13</v>
-      </c>
-      <c r="T52" t="n">
-        <v>325</v>
-      </c>
-      <c r="U52" t="n">
-        <v>55</v>
-      </c>
-      <c r="V52" t="n">
-        <v>55.23261</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-66.16073</v>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Au 21.70 g/t</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="n">
-        <v>13</v>
-      </c>
-      <c r="T53" t="n">
-        <v>325</v>
-      </c>
-      <c r="U53" t="n">
-        <v>55</v>
-      </c>
-      <c r="V53" t="n">
-        <v>57.94973</v>
-      </c>
-      <c r="W53" t="n">
-        <v>-69.51281</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Erickson Sud - Goose Pond</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Platinum, Gold, Palladium, Egp, Nickel, Copper, Cobalt</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>13</v>
-      </c>
-      <c r="T54" t="n">
-        <v>325</v>
-      </c>
-      <c r="U54" t="n">
-        <v>55</v>
-      </c>
-      <c r="V54" t="n">
-        <v>57.99255</v>
-      </c>
-      <c r="W54" t="n">
-        <v>-69.72347000000001</v>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Lac Retty - Lac Bleu</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Niobium</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="n">
-        <v>13</v>
-      </c>
-      <c r="T55" t="n">
-        <v>325</v>
-      </c>
-      <c r="U55" t="n">
-        <v>55</v>
-      </c>
-      <c r="V55" t="n">
-        <v>55.22879</v>
-      </c>
-      <c r="W55" t="n">
-        <v>-66.12246</v>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Lac Walsh-Ouest</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Nickel, Copper</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Cu 3.05%, Ni 0.67%</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="n">
-        <v>13</v>
-      </c>
-      <c r="T56" t="n">
-        <v>325</v>
-      </c>
-      <c r="U56" t="n">
-        <v>55</v>
-      </c>
-      <c r="V56" t="n">
-        <v>55.15269</v>
-      </c>
-      <c r="W56" t="n">
-        <v>-66.35399</v>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Sandpit</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Au 18.05 g/t, As 0.158%</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="n">
-        <v>13</v>
-      </c>
-      <c r="T57" t="n">
-        <v>325</v>
-      </c>
-      <c r="U57" t="n">
-        <v>55</v>
-      </c>
-      <c r="V57" t="n">
-        <v>52.17253</v>
-      </c>
-      <c r="W57" t="n">
-        <v>-76.55762</v>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Otel</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Copper, Uranium</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>U 3.85%, Cu 6.88%</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="n">
-        <v>13</v>
-      </c>
-      <c r="T58" t="n">
-        <v>325</v>
-      </c>
-      <c r="U58" t="n">
-        <v>55</v>
-      </c>
-      <c r="V58" t="n">
-        <v>56.25666</v>
-      </c>
-      <c r="W58" t="n">
-        <v>-68.20592000000001</v>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4906</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Train No 4 (Lac Crabe)</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Uranium, Copper</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Cu 3.71%, U 0.07%</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>13</v>
-      </c>
-      <c r="T59" t="n">
-        <v>325</v>
-      </c>
-      <c r="U59" t="n">
-        <v>55</v>
-      </c>
-      <c r="V59" t="n">
-        <v>56.39584</v>
-      </c>
-      <c r="W59" t="n">
-        <v>-68.39176999999999</v>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>SGR-09</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Uranium, Gold</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Au 3.31 g/t, U 0.11%</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>13</v>
-      </c>
-      <c r="T60" t="n">
-        <v>325</v>
-      </c>
-      <c r="U60" t="n">
-        <v>55</v>
-      </c>
-      <c r="V60" t="n">
-        <v>56.43951</v>
-      </c>
-      <c r="W60" t="n">
-        <v>-68.10245999999999</v>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Viking</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Uranium, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
-        <v>13</v>
-      </c>
-      <c r="T61" t="n">
-        <v>325</v>
-      </c>
-      <c r="U61" t="n">
-        <v>55</v>
-      </c>
-      <c r="V61" t="n">
-        <v>56.43038</v>
-      </c>
-      <c r="W61" t="n">
-        <v>-68.09914000000001</v>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Lac du Castor</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>U 0.328%</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
-        <v>13</v>
-      </c>
-      <c r="T62" t="n">
-        <v>325</v>
-      </c>
-      <c r="U62" t="n">
-        <v>55</v>
-      </c>
-      <c r="V62" t="n">
-        <v>52.2149</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-70.93367000000001</v>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Lac du Crapet</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Gold, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>13</v>
-      </c>
-      <c r="T63" t="n">
-        <v>325</v>
-      </c>
-      <c r="U63" t="n">
-        <v>55</v>
-      </c>
-      <c r="V63" t="n">
-        <v>52.20175</v>
-      </c>
-      <c r="W63" t="n">
-        <v>-70.89798</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Kogaluc 1</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="n">
-        <v>13</v>
-      </c>
-      <c r="T64" t="n">
-        <v>325</v>
-      </c>
-      <c r="U64" t="n">
-        <v>55</v>
-      </c>
-      <c r="V64" t="n">
-        <v>58.81627</v>
-      </c>
-      <c r="W64" t="n">
-        <v>-74.70458000000001</v>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Kogaluc 4</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Au 5.60 g/t</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>13</v>
-      </c>
-      <c r="T65" t="n">
-        <v>325</v>
-      </c>
-      <c r="U65" t="n">
-        <v>55</v>
-      </c>
-      <c r="V65" t="n">
-        <v>58.81552</v>
-      </c>
-      <c r="W65" t="n">
-        <v>-74.68685000000001</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>MHY B (97-C340)</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Copper, Nickel, Cobalt</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>13</v>
-      </c>
-      <c r="T66" t="n">
-        <v>325</v>
-      </c>
-      <c r="U66" t="n">
-        <v>55</v>
-      </c>
-      <c r="V66" t="n">
-        <v>49.84595</v>
-      </c>
-      <c r="W66" t="n">
-        <v>-70.57626</v>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MHY Nord</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="n">
-        <v>13</v>
-      </c>
-      <c r="T67" t="n">
-        <v>325</v>
-      </c>
-      <c r="U67" t="n">
-        <v>55</v>
-      </c>
-      <c r="V67" t="n">
-        <v>49.83681</v>
-      </c>
-      <c r="W67" t="n">
-        <v>-70.57877999999999</v>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MHY Ap (Gravi)</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="n">
-        <v>13</v>
-      </c>
-      <c r="T68" t="n">
-        <v>325</v>
-      </c>
-      <c r="U68" t="n">
-        <v>55</v>
-      </c>
-      <c r="V68" t="n">
-        <v>49.82919</v>
-      </c>
-      <c r="W68" t="n">
-        <v>-70.58076</v>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTS-08</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Uranium, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="n">
-        <v>9</v>
-      </c>
-      <c r="T69" t="n">
-        <v>225</v>
-      </c>
-      <c r="U69" t="n">
-        <v>55</v>
-      </c>
-      <c r="V69" t="n">
-        <v>51.78509</v>
-      </c>
-      <c r="W69" t="n">
-        <v>-71.96465999999999</v>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Gagnon</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="n">
-        <v>13</v>
-      </c>
-      <c r="T70" t="n">
-        <v>325</v>
-      </c>
-      <c r="U70" t="n">
-        <v>55</v>
-      </c>
-      <c r="V70" t="n">
-        <v>55.5908</v>
-      </c>
-      <c r="W70" t="n">
-        <v>-71.13463</v>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="n">
-        <v>13</v>
-      </c>
-      <c r="T71" t="n">
-        <v>325</v>
-      </c>
-      <c r="U71" t="n">
-        <v>55</v>
-      </c>
-      <c r="V71" t="n">
-        <v>55.61902</v>
-      </c>
-      <c r="W71" t="n">
-        <v>-71.054</v>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Palladium</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="n">
-        <v>13</v>
-      </c>
-      <c r="T72" t="n">
-        <v>325</v>
-      </c>
-      <c r="U72" t="n">
-        <v>55</v>
-      </c>
-      <c r="V72" t="n">
-        <v>55.58892</v>
-      </c>
-      <c r="W72" t="n">
-        <v>-71.1636</v>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Pistolaté</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="n">
-        <v>13</v>
-      </c>
-      <c r="T73" t="n">
-        <v>325</v>
-      </c>
-      <c r="U73" t="n">
-        <v>55</v>
-      </c>
-      <c r="V73" t="n">
-        <v>55.68696</v>
-      </c>
-      <c r="W73" t="n">
-        <v>-71.02212</v>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Bravo (Train No 3)</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Copper, Uranium, Zinc, Lead, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="n">
-        <v>13</v>
-      </c>
-      <c r="T74" t="n">
-        <v>325</v>
-      </c>
-      <c r="U74" t="n">
-        <v>55</v>
-      </c>
-      <c r="V74" t="n">
-        <v>56.38071</v>
-      </c>
-      <c r="W74" t="n">
-        <v>-68.37362</v>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Lullwitz-Kaeppeli</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Ir, Gold, Zr, Gallium</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="n">
-        <v>13</v>
-      </c>
-      <c r="T75" t="n">
-        <v>325</v>
-      </c>
-      <c r="U75" t="n">
-        <v>55</v>
-      </c>
-      <c r="V75" t="n">
-        <v>47.76432</v>
-      </c>
-      <c r="W75" t="n">
-        <v>-70.46635000000001</v>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Lac Couillard (Secteur A)</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Zr, Y, Etr, Gd, Pr, Dy, La, Nd, Ce, Sm</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Nd 0.649%, Dy 0.0357%, Pr 0.11%, Ce 1.55%, La 0.2%</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>13</v>
-      </c>
-      <c r="T76" t="n">
-        <v>325</v>
-      </c>
-      <c r="U76" t="n">
-        <v>55</v>
-      </c>
-      <c r="V76" t="n">
-        <v>50.30421</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-60.82246</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4100</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Bob West</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Gold, Antimony</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Sb 3.35%, Au 1.16 g/t</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>13</v>
-      </c>
-      <c r="T77" t="n">
-        <v>325</v>
-      </c>
-      <c r="U77" t="n">
-        <v>55</v>
-      </c>
-      <c r="V77" t="n">
-        <v>52.08812</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-75.41134</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67079</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Obamska</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Au 9.50 g/t</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>13</v>
-      </c>
-      <c r="T78" t="n">
-        <v>325</v>
-      </c>
-      <c r="U78" t="n">
-        <v>55</v>
-      </c>
-      <c r="V78" t="n">
-        <v>50.8353</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-78.66648000000001</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>St-Armand (Phillipsburg-Est)</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Uranium, Zinc</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>U 0.578%, Zn 0.0798%</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="n">
-        <v>13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>325</v>
-      </c>
-      <c r="U79" t="n">
-        <v>55</v>
-      </c>
-      <c r="V79" t="n">
-        <v>45.02084</v>
-      </c>
-      <c r="W79" t="n">
-        <v>-73.0196</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Chalifour-1</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Zinc, Lead, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="n">
-        <v>13</v>
-      </c>
-      <c r="T80" t="n">
-        <v>325</v>
-      </c>
-      <c r="U80" t="n">
-        <v>55</v>
-      </c>
-      <c r="V80" t="n">
-        <v>50.3781</v>
-      </c>
-      <c r="W80" t="n">
-        <v>-73.70041000000001</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Perch River</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Cu 9.06%, Ag 19.20 g/t</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="n">
-        <v>13</v>
-      </c>
-      <c r="T81" t="n">
-        <v>325</v>
-      </c>
-      <c r="U81" t="n">
-        <v>55</v>
-      </c>
-      <c r="V81" t="n">
-        <v>50.33998</v>
-      </c>
-      <c r="W81" t="n">
-        <v>-73.71023</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Hunt (Port Daniel No. 2)</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I82" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Cu 9.35%</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="n">
-        <v>13</v>
-      </c>
-      <c r="T82" t="n">
-        <v>325</v>
-      </c>
-      <c r="U82" t="n">
-        <v>55</v>
-      </c>
-      <c r="V82" t="n">
-        <v>48.31932</v>
-      </c>
-      <c r="W82" t="n">
-        <v>-64.9713</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>PAP Nord (Camp A-1)</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I83" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="n">
-        <v>13</v>
-      </c>
-      <c r="T83" t="n">
-        <v>325</v>
-      </c>
-      <c r="U83" t="n">
-        <v>55</v>
-      </c>
-      <c r="V83" t="n">
-        <v>60.2779</v>
-      </c>
-      <c r="W83" t="n">
-        <v>-75.33311</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Harrison</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Iron, Nickel, Copper</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I84" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="n">
-        <v>13</v>
-      </c>
-      <c r="T84" t="n">
-        <v>325</v>
-      </c>
-      <c r="U84" t="n">
-        <v>55</v>
-      </c>
-      <c r="V84" t="n">
-        <v>49.63941</v>
-      </c>
-      <c r="W84" t="n">
-        <v>-76.90893</v>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Qalluviartuuq-NW</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="n">
-        <v>13</v>
-      </c>
-      <c r="T85" t="n">
-        <v>325</v>
-      </c>
-      <c r="U85" t="n">
-        <v>55</v>
-      </c>
-      <c r="V85" t="n">
-        <v>59.80634</v>
-      </c>
-      <c r="W85" t="n">
-        <v>-75.01831</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>AC-2010-006</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I86" t="b">
-        <v>1</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Au 4.44 g/t</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="n">
-        <v>13</v>
-      </c>
-      <c r="T86" t="n">
-        <v>325</v>
-      </c>
-      <c r="U86" t="n">
-        <v>55</v>
-      </c>
-      <c r="V86" t="n">
-        <v>52.03235</v>
-      </c>
-      <c r="W86" t="n">
-        <v>-69.13816</v>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Twin</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I87" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="n">
-        <v>7</v>
-      </c>
-      <c r="T87" t="n">
-        <v>175</v>
-      </c>
-      <c r="U87" t="n">
-        <v>55</v>
-      </c>
-      <c r="V87" t="n">
-        <v>48.32328</v>
-      </c>
-      <c r="W87" t="n">
-        <v>-79.44637</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Barre de fer</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Copper, Nickel, Cobalt</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I88" t="b">
-        <v>1</v>
-      </c>
-      <c r="J88" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="n">
-        <v>13</v>
-      </c>
-      <c r="T88" t="n">
-        <v>325</v>
-      </c>
-      <c r="U88" t="n">
-        <v>55</v>
-      </c>
-      <c r="V88" t="n">
-        <v>51.6436</v>
-      </c>
-      <c r="W88" t="n">
-        <v>-67.33749</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Mistass</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I89" t="b">
-        <v>1</v>
-      </c>
-      <c r="J89" t="b">
-        <v>0</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="n">
-        <v>13</v>
-      </c>
-      <c r="T89" t="n">
-        <v>325</v>
-      </c>
-      <c r="U89" t="n">
-        <v>55</v>
-      </c>
-      <c r="V89" t="n">
-        <v>49.24734</v>
-      </c>
-      <c r="W89" t="n">
-        <v>-71.98866</v>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Lac Beaupré-Est</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Nickel, Copper</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I90" t="b">
-        <v>1</v>
-      </c>
-      <c r="J90" t="b">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="n">
-        <v>13</v>
-      </c>
-      <c r="T90" t="n">
-        <v>325</v>
-      </c>
-      <c r="U90" t="n">
-        <v>55</v>
-      </c>
-      <c r="V90" t="n">
-        <v>49.59836</v>
-      </c>
-      <c r="W90" t="n">
-        <v>-76.92194000000001</v>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver, Gold</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Riv. Cascapedia</t>
+          <t>Qarqasiaq - C</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nickel, Arsenic, Chromium, Cobalt, Antimony</t>
+          <t>Copper, Platinum, Palladium, Egp, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ni 12.8%, Co 0.13%, As 11.8%, Cr 0.14%</t>
+          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>48.84847</v>
+        <v>60.17776</v>
       </c>
       <c r="W3" t="n">
-        <v>-66.39704</v>
+        <v>-70.30297</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6070</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ruisseau 17e Mille</t>
+          <t>Qarqasiaq - A1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nickel, Egp, Platinum, Chromium</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ni 11.7%, Pt 1.70 g/t, Cr 0.25%, EGP 0.00017%</t>
+          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>48.86434</v>
+        <v>60.16686</v>
       </c>
       <c r="W4" t="n">
-        <v>-66.26813</v>
+        <v>-70.29604999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6072</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Cobalt</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+          <t>Cu 6.33%, Pd 2.55 g/t, Ni 0.69%, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>55.5908</v>
+        <v>61.55073</v>
       </c>
       <c r="W5" t="n">
-        <v>-71.13463</v>
+        <v>-72.66555</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pistolaté</t>
+          <t>Spirit-1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum</t>
+          <t>Nickel, Cobalt, Platinum, Palladium, Egp, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+          <t>Pd 827.00 g/t, Pt 237.00 g/t, Cu 11.1%, Ni 1.02%, Co 0.131%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>55.68696</v>
+        <v>61.39663</v>
       </c>
       <c r="W6" t="n">
-        <v>-71.02212</v>
+        <v>-73.13239</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24594</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Mustang</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Palladium, Nickel, Egp, Copper, Platinum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>55.58892</v>
+        <v>52.17024</v>
       </c>
       <c r="W7" t="n">
-        <v>-71.1636</v>
+        <v>-76.57532999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ganiq</t>
+          <t>Lac Nitakwin</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Uranium, Lead, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>U 0.77%, Cu 0.52%, Pb 0.82%</t>
+          <t>Au 6.06 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>53.7831</v>
+        <v>52.1766</v>
       </c>
       <c r="W8" t="n">
-        <v>-75.64593000000001</v>
+        <v>-76.71138999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4528</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B-88-01</t>
+          <t>Gauthier-Mcneely</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Zinc, Silver, Copper, Nickel</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 203.00 g/t, Cu 1.56%</t>
+          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>45.52488</v>
+        <v>55.62931</v>
       </c>
       <c r="W9" t="n">
-        <v>-72.07191</v>
+        <v>-66.83314</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4625</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qarqasiaq - C</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Palladium, Platinum, Copper, Nickel, Egp, Cobalt, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ni 6.5%, Cu 7.1%, Co 0.34%, Pt 1.45 g/t, Pd 0.88 g/t</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>60.17776</v>
+        <v>55.2524</v>
       </c>
       <c r="W10" t="n">
-        <v>-70.30297</v>
+        <v>-67.95193</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qarqasiaq - A1</t>
+          <t>Pio - Filons Est et Ouest</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Egp, Palladium, Platinum, Nickel, Copper, Cobalt</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ni 3.6%, Cu 1.17%, Pd 2.35 g/t, Co 0.18%, Pt 0.68 g/t</t>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>60.16686</v>
+        <v>58.96701</v>
       </c>
       <c r="W11" t="n">
-        <v>-70.29604999999999</v>
+        <v>-69.59563</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1617</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pio - Filons Est et Ouest</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Egp, Palladium, Platinum, Copper, Nickel, Silver, Cobalt, Gold</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+          <t>Ni 2.85%, Cu 1.18%, Pd 3.18 g/t, Pt 1.02 g/t, EGP 0.00042%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>58.96701</v>
+        <v>61.52449</v>
       </c>
       <c r="W12" t="n">
-        <v>-69.59563</v>
+        <v>-72.77941</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25608</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Franelle</t>
+          <t>Century</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 60%, Ag 43.49 g/t</t>
+          <t>Ni 15.5%, Cu 3.16%, Pd 1.22 g/t, Pt 0.36 g/t, EGP 0.00013%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>55.55824</v>
+        <v>61.35448</v>
       </c>
       <c r="W13" t="n">
-        <v>-67.34804</v>
+        <v>-76.06304</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23835</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>Seahawk</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten, Copper, Zinc, Lead</t>
+          <t>Copper, Platinum, Palladium, Egp, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Ni 4.73%, Cu 1.93%, Pd 3.35 g/t, Pt 0.99 g/t, EGP 0.000434%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>53.39256</v>
+        <v>61.35511</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.43714</v>
+        <v>-76.04816</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23960</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Josette</t>
+          <t>Red Zone</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Etr, Iron, Tungsten, Uranium, Thorium, Copper, Y, Silver, Gold</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>W 0.18%, Cu 2.81%, U 0.0654%, Ag 13.00 g/t, Au 0.15 g/t</t>
+          <t>Ni 5.75%, Cu 1.35%, Pd 2.97 g/t, Pt 0.46 g/t, EGP 0.000342%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>51.05069</v>
+        <v>61.35949</v>
       </c>
       <c r="W15" t="n">
-        <v>-65.27048000000001</v>
+        <v>-76.01782</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6032</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23971</t>
         </is>
       </c>
     </row>
@@ -1662,22 +1662,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Delta (Northeast)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Ni 3.49%, Pd 1.96 g/t, Pt 0.83 g/t, Cu 0.11%, EGP 0.000279%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>45.03676</v>
+        <v>61.48916</v>
       </c>
       <c r="W16" t="n">
-        <v>-72.77243</v>
+        <v>-74.43673</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24306</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Franelle</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Cobalt, Palladium, Platinum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+          <t>Cu 60%, Ag 43.49 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>55.61902</v>
+        <v>55.55824</v>
       </c>
       <c r="W17" t="n">
-        <v>-71.054</v>
+        <v>-67.34804</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Misery - Sond. ML14024</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten, Niobium, Zr, Etr, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 31.13 g/t</t>
+          <t>W 0.185%, Ag 9.50 g/t, ETR 0.336%, Nb 0.111%, Zr 0.558%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>55.2524</v>
+        <v>55.35025</v>
       </c>
       <c r="W18" t="n">
-        <v>-67.95193</v>
+        <v>-63.8991</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25818</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lac du Canoe</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 40.00 g/t</t>
+          <t>W 0.188%, Cu 4.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>55.23434</v>
+        <v>60.39318</v>
       </c>
       <c r="W19" t="n">
-        <v>-67.62649</v>
+        <v>-75.53694</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26603</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Au-26</t>
+          <t>Misery - Sond. ML11014</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc, Arsenic</t>
+          <t>Gallium, Sc, Y, Niobium, Zr, Etr, Tantalum, Beryllium, Germanium, Thorium, Tin, Silver, Fluorite, Uranium, Lead, Hf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
+          <t>Ge 0.0097%, U 0.0387%, Ga 0.0216%, Sn 0.0913%, Ag 5.30 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>53.39936</v>
+        <v>55.34044</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.29407</v>
+        <v>-63.93963</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25755</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Lac Harris</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tungsten, Gold, Silver, Copper, Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Cu 5.07%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>53.39458</v>
+        <v>47.68996</v>
       </c>
       <c r="W21" t="n">
-        <v>-77.44683999999999</v>
+        <v>-76.66074999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>Transfiguration (Labrador Expl.)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Copper, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Cu 3.08%, Pb 21.1%, Zn 8.52%, Ag 97.37 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>53.41679</v>
+        <v>47.93876</v>
       </c>
       <c r="W22" t="n">
-        <v>-77.27167</v>
+        <v>-68.75702</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4162</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4930N-1</t>
+          <t>Transfiguration: Zone E5</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chromium, Copper, Nickel, Silver</t>
+          <t>Lead, Silver, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+          <t>Ag 393.40 g/t, Cu 2.94%, Pb 1%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>53.38014</v>
+        <v>47.94973</v>
       </c>
       <c r="W23" t="n">
-        <v>-77.28712</v>
+        <v>-68.75534</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4165</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>Transfiguration: Zone E3</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Lead, Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Cu 6.57%, Pb 9.62%, Ag 32.10 g/t, Zn 0.541%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>53.40387</v>
+        <v>47.9394</v>
       </c>
       <c r="W24" t="n">
-        <v>-77.30118</v>
+        <v>-68.76391</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4166</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gauthier-Mcneely</t>
+          <t>Sond. K2-22-10</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Nickel</t>
+          <t>Gold, Zinc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Zn 6.72%, Ag 52.11 g/t, Cu 0.72%, Ni 0.07%</t>
+          <t>Au 3.64 g/t, Zn 0.55%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>55.62931</v>
+        <v>52.28963</v>
       </c>
       <c r="W25" t="n">
-        <v>-66.83314</v>
+        <v>-77.78149999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Sond. PLP24-019</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Bismuth, Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 4.76 g/t, Bi 0.1%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>49.82919</v>
+        <v>52.59612</v>
       </c>
       <c r="W26" t="n">
-        <v>-70.58076</v>
+        <v>-77.37366</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lac Tarsac : Veine I et III</t>
+          <t>G-H-2-79 (Hudbay Mining)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 11.66 g/t</t>
+          <t>Cu 3.26%, Ni 1.12%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>48.3561</v>
+        <v>51.50451</v>
       </c>
       <c r="W27" t="n">
-        <v>-79.43788000000001</v>
+        <v>-67.92737</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Kish</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Uranium, Thorium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>U 1%, Au 3.90 g/t, Th 0.0025%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2650,23 +2650,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>48.32328</v>
+        <v>56.42752</v>
       </c>
       <c r="W28" t="n">
-        <v>-79.44637</v>
+        <v>-68.09778</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4904</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Lac Lyster</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Zinc, Barium, Cadmium, Mercury</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Zn 31.5%</t>
+          <t>W 2.93%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T29" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U29" t="n">
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>46.11447</v>
+        <v>45.03295</v>
       </c>
       <c r="W29" t="n">
-        <v>-75.95323</v>
+        <v>-71.89901999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4847</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Viau (ou Bordulac)</t>
+          <t>Lac du Canoe</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 31.00 g/t</t>
+          <t>Au 40.00 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>48.26547</v>
+        <v>55.23434</v>
       </c>
       <c r="W30" t="n">
-        <v>-79.41453</v>
+        <v>-67.62649</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1651</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sainte-Cécile (Maheu) - ancien</t>
+          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Molybdenum, Silver, Zinc, Lead, Bismuth, Gold, Copper</t>
+          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
+          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>45.67446</v>
+        <v>58.23464</v>
       </c>
       <c r="W31" t="n">
-        <v>-70.96669</v>
+        <v>-69.92364000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Gold, Egp, Palladium, Silver</t>
+          <t>Bismuth, Gold, Silver, Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>53.34013</v>
+        <v>47.43121</v>
       </c>
       <c r="W32" t="n">
-        <v>-77.32316</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Fabre Nord</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Iron, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Au 6.48 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>49.24734</v>
+        <v>47.26406</v>
       </c>
       <c r="W33" t="n">
-        <v>-71.98866</v>
+        <v>-79.40157000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>H-1429-046</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
+          <t>Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>49.83681</v>
+        <v>50.85296</v>
       </c>
       <c r="W34" t="n">
-        <v>-70.57877999999999</v>
+        <v>-76.47398</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Sheillan</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 90.30 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>49.84595</v>
+        <v>49.10861</v>
       </c>
       <c r="W35" t="n">
-        <v>-70.57626</v>
+        <v>-76.22864</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67165</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PG-221094</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Lead, Silver, Arsenic, Copper</t>
+          <t>Silver, Copper, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>53.40779</v>
+        <v>52.21818</v>
       </c>
       <c r="W36" t="n">
-        <v>-77.28636</v>
+        <v>-77.45902</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cr-2</t>
+          <t>Delhi Pacific</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Palladium, Platinum, Rh, Gold, Iron, Chromium, Nickel, Copper, Egp, Cobalt</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Pd 11.88 g/t, Ni 2.4%, Cu 2.36%, Pt 4.20 g/t, Au 1.30 g/t</t>
+          <t>Cu 7.36%, Ag 24.90 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>53.39341</v>
+        <v>56.40258</v>
       </c>
       <c r="W37" t="n">
-        <v>-77.30141</v>
+        <v>-67.9023</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6004</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Sainte-Cécile (Maheu) - ancien</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Copper, Silver, Cobalt, Tungsten, Tellurium</t>
+          <t>Bismuth, Lead, Zinc, Silver, Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Ag 579.50 g/t, Mo 1.26%, Bi 0.19%, Zn 3.2%, Pb 5.75%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>59.80634</v>
+        <v>45.67446</v>
       </c>
       <c r="W38" t="n">
-        <v>-75.01831</v>
+        <v>-70.96669</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4708</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rh, Chromium, Egp, Nickel, Gold, Palladium, Platinum, Copper</t>
+          <t>Zinc, Barium, Mercury, Cadmium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Zn 31.5%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>53.39786</v>
+        <v>46.11447</v>
       </c>
       <c r="W39" t="n">
-        <v>-77.30625000000001</v>
+        <v>-75.95323</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4732</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>Lac Chicobi-2</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Ag 932.70 g/t, Pb 19.2%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>53.35887</v>
+        <v>48.83881</v>
       </c>
       <c r="W40" t="n">
-        <v>-77.31016</v>
+        <v>-78.52331</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4194</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>Propriété Authier</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Nickel, Palladium, Gold, Copper, Lead, Cobalt, Egp</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Au 173.90 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>53.39996</v>
+        <v>48.89617</v>
       </c>
       <c r="W41" t="n">
-        <v>-77.33163999999999</v>
+        <v>-78.78440000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4201</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Delandore</t>
+          <t>AT-32-91</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 26.74 g/t</t>
+          <t>Au 5.09 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>48.63582</v>
+        <v>48.89509</v>
       </c>
       <c r="W42" t="n">
-        <v>-77.03851</v>
+        <v>-78.79843</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2065</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
         </is>
       </c>
     </row>
@@ -3768,22 +3768,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ducros : Pyroxénite</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Copper, Palladium, Platinum, Nickel, Gold, Egp</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 2.64%, Ni 1.44%, Au 1.32 g/t, Pt 1.42 g/t, Pd 1.61 g/t</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>48.69916</v>
+        <v>53.56991</v>
       </c>
       <c r="W43" t="n">
-        <v>-77.0911</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2081</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cunning-Gault</t>
+          <t>Fort Chimo (Lac Plissé)</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Nickel, Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Pb 32.7%, Zn 11.7%</t>
+          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>48.72575</v>
+        <v>58.12861</v>
       </c>
       <c r="W44" t="n">
-        <v>-64.47654</v>
+        <v>-69.55745</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5374</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Northern Canada</t>
+          <t>H-1451-032</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>U 0.373%</t>
+          <t>Au 2.20 g/t, Cu 0.66%, Zn 1.59%, Ag 21.80 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>50.39968</v>
+        <v>50.79734</v>
       </c>
       <c r="W45" t="n">
-        <v>-62.92982</v>
+        <v>-76.70574000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5401</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4242</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mid-Patapédia</t>
+          <t>Val-St-Gilles-SE</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lead, Copper, Gold, Zinc, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+          <t>Cu 7.88%, Ag 87.00 g/t, Au 1.06 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>47.86378</v>
+        <v>48.97212</v>
       </c>
       <c r="W46" t="n">
-        <v>-67.38485</v>
+        <v>-79.1088</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2703</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St-Benoit</t>
+          <t>Kupfer : Mine Val-St-Gilles</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Lead, Silver</t>
+          <t>Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
+          <t>Cu 7.96%, Ag 89.15 g/t, Zn 2.66%, Au 0.34 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>47.99637</v>
+        <v>48.97156</v>
       </c>
       <c r="W47" t="n">
-        <v>-67.11127</v>
+        <v>-79.08714999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2704</t>
         </is>
       </c>
     </row>
@@ -4158,22 +4158,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>Val-St-Gilles SO</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Lead, Silver, Zinc</t>
+          <t>Gold, Lead, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Au 8.34 g/t, Zn 5.2%, Pb 9.9%, Ag 61.90 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4210,23 +4210,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T48" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U48" t="n">
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>45.99171</v>
+        <v>48.96826</v>
       </c>
       <c r="W48" t="n">
-        <v>-71.70617</v>
+        <v>-79.19454</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2702</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Glencoe</t>
+          <t>Meilleur (Chess Uranium)</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
+          <t>Cu 3.27%, Pd 2.46 g/t, Ni 0.6%, Au 0.50 g/t, Pt 0.73 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,3212 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>45.32873</v>
+        <v>45.6921</v>
       </c>
       <c r="W49" t="n">
-        <v>-72.47421</v>
+        <v>-76.64127999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4809</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Venditelli (Lac St-Pierre-Gold)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Gold, Palladium, Egp</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Au 27.98 g/t, Pd 0.22 g/t, EGP 2.23e-05%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>13</v>
+      </c>
+      <c r="T50" t="n">
+        <v>325</v>
+      </c>
+      <c r="U50" t="n">
+        <v>55</v>
+      </c>
+      <c r="V50" t="n">
+        <v>58.15377</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-69.53443</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2648</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dessureault (Lac Rougemont)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>13</v>
+      </c>
+      <c r="T51" t="n">
+        <v>325</v>
+      </c>
+      <c r="U51" t="n">
+        <v>55</v>
+      </c>
+      <c r="V51" t="n">
+        <v>58.02817</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-69.57268000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Lac Retty - Lac Pogo</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Gold, Platinum, Palladium, Egp, Nickel, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>13</v>
+      </c>
+      <c r="T52" t="n">
+        <v>325</v>
+      </c>
+      <c r="U52" t="n">
+        <v>55</v>
+      </c>
+      <c r="V52" t="n">
+        <v>55.23261</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-66.16073</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Au 21.70 g/t</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>13</v>
+      </c>
+      <c r="T53" t="n">
+        <v>325</v>
+      </c>
+      <c r="U53" t="n">
+        <v>55</v>
+      </c>
+      <c r="V53" t="n">
+        <v>57.94973</v>
+      </c>
+      <c r="W53" t="n">
+        <v>-69.51281</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Erickson Sud - Goose Pond</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Platinum, Gold, Palladium, Egp, Nickel, Copper, Cobalt</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Cu 2.69%, Au 1.27 g/t, Pd 2.61 g/t, Ni 0.41%, Pt 0.73 g/t</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>13</v>
+      </c>
+      <c r="T54" t="n">
+        <v>325</v>
+      </c>
+      <c r="U54" t="n">
+        <v>55</v>
+      </c>
+      <c r="V54" t="n">
+        <v>57.99255</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-69.72347000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2667</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Lac Retty - Lac Bleu</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Niobium</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>13</v>
+      </c>
+      <c r="T55" t="n">
+        <v>325</v>
+      </c>
+      <c r="U55" t="n">
+        <v>55</v>
+      </c>
+      <c r="V55" t="n">
+        <v>55.22879</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-66.12246</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Lac Walsh-Ouest</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nickel, Copper</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Cu 3.05%, Ni 0.67%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>13</v>
+      </c>
+      <c r="T56" t="n">
+        <v>325</v>
+      </c>
+      <c r="U56" t="n">
+        <v>55</v>
+      </c>
+      <c r="V56" t="n">
+        <v>55.15269</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-66.35399</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sandpit</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Au 18.05 g/t, As 0.158%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>13</v>
+      </c>
+      <c r="T57" t="n">
+        <v>325</v>
+      </c>
+      <c r="U57" t="n">
+        <v>55</v>
+      </c>
+      <c r="V57" t="n">
+        <v>52.17253</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-76.55762</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Otel</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Copper, Uranium</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>U 3.85%, Cu 6.88%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>13</v>
+      </c>
+      <c r="T58" t="n">
+        <v>325</v>
+      </c>
+      <c r="U58" t="n">
+        <v>55</v>
+      </c>
+      <c r="V58" t="n">
+        <v>56.25666</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-68.20592000000001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4906</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Train No 4 (Lac Crabe)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Uranium, Copper</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Cu 3.71%, U 0.07%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>13</v>
+      </c>
+      <c r="T59" t="n">
+        <v>325</v>
+      </c>
+      <c r="U59" t="n">
+        <v>55</v>
+      </c>
+      <c r="V59" t="n">
+        <v>56.39584</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-68.39176999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SGR-09</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Uranium, Gold</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Au 3.31 g/t, U 0.11%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>13</v>
+      </c>
+      <c r="T60" t="n">
+        <v>325</v>
+      </c>
+      <c r="U60" t="n">
+        <v>55</v>
+      </c>
+      <c r="V60" t="n">
+        <v>56.43951</v>
+      </c>
+      <c r="W60" t="n">
+        <v>-68.10245999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Uranium, Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>13</v>
+      </c>
+      <c r="T61" t="n">
+        <v>325</v>
+      </c>
+      <c r="U61" t="n">
+        <v>55</v>
+      </c>
+      <c r="V61" t="n">
+        <v>56.43038</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-68.09914000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Lac du Castor</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>U 0.328%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>13</v>
+      </c>
+      <c r="T62" t="n">
+        <v>325</v>
+      </c>
+      <c r="U62" t="n">
+        <v>55</v>
+      </c>
+      <c r="V62" t="n">
+        <v>52.2149</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-70.93367000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4967</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Lac du Crapet</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gold, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>13</v>
+      </c>
+      <c r="T63" t="n">
+        <v>325</v>
+      </c>
+      <c r="U63" t="n">
+        <v>55</v>
+      </c>
+      <c r="V63" t="n">
+        <v>52.20175</v>
+      </c>
+      <c r="W63" t="n">
+        <v>-70.89798</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kogaluc 1</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>13</v>
+      </c>
+      <c r="T64" t="n">
+        <v>325</v>
+      </c>
+      <c r="U64" t="n">
+        <v>55</v>
+      </c>
+      <c r="V64" t="n">
+        <v>58.81627</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-74.70458000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kogaluc 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Au 5.60 g/t</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>13</v>
+      </c>
+      <c r="T65" t="n">
+        <v>325</v>
+      </c>
+      <c r="U65" t="n">
+        <v>55</v>
+      </c>
+      <c r="V65" t="n">
+        <v>58.81552</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-74.68685000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MHY B (97-C340)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Copper, Nickel, Cobalt</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="n">
+        <v>325</v>
+      </c>
+      <c r="U66" t="n">
+        <v>55</v>
+      </c>
+      <c r="V66" t="n">
+        <v>49.84595</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-70.57626</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MHY Nord</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>13</v>
+      </c>
+      <c r="T67" t="n">
+        <v>325</v>
+      </c>
+      <c r="U67" t="n">
+        <v>55</v>
+      </c>
+      <c r="V67" t="n">
+        <v>49.83681</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-70.57877999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MHY Ap (Gravi)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>13</v>
+      </c>
+      <c r="T68" t="n">
+        <v>325</v>
+      </c>
+      <c r="U68" t="n">
+        <v>55</v>
+      </c>
+      <c r="V68" t="n">
+        <v>49.82919</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-70.58076</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OTS-08</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Uranium, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>U 1.65%, Zn 1.85%, Ag 9.50 g/t</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>9</v>
+      </c>
+      <c r="T69" t="n">
+        <v>225</v>
+      </c>
+      <c r="U69" t="n">
+        <v>55</v>
+      </c>
+      <c r="V69" t="n">
+        <v>51.78509</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-71.96465999999999</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=29338</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Gagnon</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Copper, Nickel, Platinum, Palladium, Egp, Cobalt</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Ni 9.26%, Pd 17.11 g/t, Cu 1.99%, Co 0.39%, Pt 1.49 g/t</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>13</v>
+      </c>
+      <c r="T70" t="n">
+        <v>325</v>
+      </c>
+      <c r="U70" t="n">
+        <v>55</v>
+      </c>
+      <c r="V70" t="n">
+        <v>55.5908</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-71.13463</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Egp, Copper, Nickel, Platinum, Palladium, Cobalt</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Ni 6.24%, Cu 1.93%, EGP 0.00073%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>13</v>
+      </c>
+      <c r="T71" t="n">
+        <v>325</v>
+      </c>
+      <c r="U71" t="n">
+        <v>55</v>
+      </c>
+      <c r="V71" t="n">
+        <v>55.61902</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-71.054</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1284</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Palladium</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Palladium, Copper, Egp, Nickel, Platinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Ni 3.1%, Cu 0.85%, Pd 1.39 g/t, Pt 0.36 g/t, EGP 0.000175%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>13</v>
+      </c>
+      <c r="T72" t="n">
+        <v>325</v>
+      </c>
+      <c r="U72" t="n">
+        <v>55</v>
+      </c>
+      <c r="V72" t="n">
+        <v>55.58892</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-71.1636</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1285</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pistolaté</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Ni 2.88%, Cu 1.5%, EGP 0.000108%</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>13</v>
+      </c>
+      <c r="T73" t="n">
+        <v>325</v>
+      </c>
+      <c r="U73" t="n">
+        <v>55</v>
+      </c>
+      <c r="V73" t="n">
+        <v>55.68696</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-71.02212</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1290</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Bravo (Train No 3)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Copper, Uranium, Zinc, Lead, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>U 18.9%, Cu 0.576%, Ag 34.00 g/t, Zn 0.388%, Au 0.27 g/t</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>13</v>
+      </c>
+      <c r="T74" t="n">
+        <v>325</v>
+      </c>
+      <c r="U74" t="n">
+        <v>55</v>
+      </c>
+      <c r="V74" t="n">
+        <v>56.38071</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-68.37362</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4905</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Lullwitz-Kaeppeli</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ir, Gold, Zr, Gallium</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>13</v>
+      </c>
+      <c r="T75" t="n">
+        <v>325</v>
+      </c>
+      <c r="U75" t="n">
+        <v>55</v>
+      </c>
+      <c r="V75" t="n">
+        <v>47.76432</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-70.46635000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Lac Couillard (Secteur A)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Zr, Y, Etr, Gd, Pr, Dy, La, Nd, Ce, Sm</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Nd 0.649%, Dy 0.0357%, Pr 0.11%, Ce 1.55%, La 0.2%</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>13</v>
+      </c>
+      <c r="T76" t="n">
+        <v>325</v>
+      </c>
+      <c r="U76" t="n">
+        <v>55</v>
+      </c>
+      <c r="V76" t="n">
+        <v>50.30421</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-60.82246</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4100</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bob West</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Gold, Antimony</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Sb 3.35%, Au 1.16 g/t</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>13</v>
+      </c>
+      <c r="T77" t="n">
+        <v>325</v>
+      </c>
+      <c r="U77" t="n">
+        <v>55</v>
+      </c>
+      <c r="V77" t="n">
+        <v>52.08812</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-75.41134</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67079</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Obamska</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Au 9.50 g/t</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>13</v>
+      </c>
+      <c r="T78" t="n">
+        <v>325</v>
+      </c>
+      <c r="U78" t="n">
+        <v>55</v>
+      </c>
+      <c r="V78" t="n">
+        <v>50.8353</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-78.66648000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>St-Armand (Phillipsburg-Est)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Uranium, Zinc</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>U 0.578%, Zn 0.0798%</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>325</v>
+      </c>
+      <c r="U79" t="n">
+        <v>55</v>
+      </c>
+      <c r="V79" t="n">
+        <v>45.02084</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-73.0196</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5027</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Chalifour-1</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Zinc, Lead, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Zn 9.22%, Pb 13.3%, Ag 33.00 g/t</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>13</v>
+      </c>
+      <c r="T80" t="n">
+        <v>325</v>
+      </c>
+      <c r="U80" t="n">
+        <v>55</v>
+      </c>
+      <c r="V80" t="n">
+        <v>50.3781</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-73.70041000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5046</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Perch River</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Cu 9.06%, Ag 19.20 g/t</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>13</v>
+      </c>
+      <c r="T81" t="n">
+        <v>325</v>
+      </c>
+      <c r="U81" t="n">
+        <v>55</v>
+      </c>
+      <c r="V81" t="n">
+        <v>50.33998</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-73.71023</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Hunt (Port Daniel No. 2)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Cu 9.35%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>13</v>
+      </c>
+      <c r="T82" t="n">
+        <v>325</v>
+      </c>
+      <c r="U82" t="n">
+        <v>55</v>
+      </c>
+      <c r="V82" t="n">
+        <v>48.31932</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-64.9713</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PAP Nord (Camp A-1)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>13</v>
+      </c>
+      <c r="T83" t="n">
+        <v>325</v>
+      </c>
+      <c r="U83" t="n">
+        <v>55</v>
+      </c>
+      <c r="V83" t="n">
+        <v>60.2779</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-75.33311</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Harrison</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Iron, Nickel, Copper</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>13</v>
+      </c>
+      <c r="T84" t="n">
+        <v>325</v>
+      </c>
+      <c r="U84" t="n">
+        <v>55</v>
+      </c>
+      <c r="V84" t="n">
+        <v>49.63941</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-76.90893</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Qalluviartuuq-NW</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>13</v>
+      </c>
+      <c r="T85" t="n">
+        <v>325</v>
+      </c>
+      <c r="U85" t="n">
+        <v>55</v>
+      </c>
+      <c r="V85" t="n">
+        <v>59.80634</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-75.01831</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+        </i